--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O589"/>
+  <dimension ref="A1:O633"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38219,6 +38219,2786 @@
         </is>
       </c>
     </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>Mon Sep 28 14:15:08 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>@barbinbrad Product &amp;amp; Eng are on another level here</t>
+        </is>
+      </c>
+      <c r="G590" t="inlineStr"/>
+      <c r="H590" t="inlineStr"/>
+      <c r="I590" t="inlineStr"/>
+      <c r="J590" t="inlineStr"/>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2104575640867656145</t>
+        </is>
+      </c>
+      <c r="L590" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M590" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N590" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O590" t="inlineStr">
+        <is>
+          <t>A tweet praises Ramp’s product and engineering teams for their exceptional performance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>Mon Sep 28 13:41:11 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>@shuooo @Neko @deel Ramp mentioned 👀</t>
+        </is>
+      </c>
+      <c r="G591" t="inlineStr"/>
+      <c r="H591" t="inlineStr"/>
+      <c r="I591" t="inlineStr"/>
+      <c r="J591" t="inlineStr"/>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2104567097275953601</t>
+        </is>
+      </c>
+      <c r="L591" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M591" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N591" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O591" t="inlineStr">
+        <is>
+          <t>Ramp was referenced in a tweet by other users, indicating a brief mention without any direct announcement or update.</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>Mon Sep 28 13:38:32 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>@William_Simmons wow, you're not kidding</t>
+        </is>
+      </c>
+      <c r="G592" t="inlineStr"/>
+      <c r="H592" t="inlineStr"/>
+      <c r="I592" t="inlineStr"/>
+      <c r="J592" t="inlineStr"/>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2104566428338987384</t>
+        </is>
+      </c>
+      <c r="L592" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M592" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N592" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O592" t="inlineStr">
+        <is>
+          <t>Ramp responds to a statement by William Simmons with a positive remark, indicating agreement or surprise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>Sun Sep 27 19:05:07 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>@verdaxxed https://t.co/5wjpREseSO</t>
+        </is>
+      </c>
+      <c r="G593" t="inlineStr"/>
+      <c r="H593" t="inlineStr"/>
+      <c r="I593" t="inlineStr"/>
+      <c r="J593" t="inlineStr"/>
+      <c r="K593" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2104286228103250185</t>
+        </is>
+      </c>
+      <c r="L593" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M593" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N593" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O593" t="inlineStr">
+        <is>
+          <t>Ramp shares a link featuring @verdaxxed, likely referencing industry news or a related update.</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>Sun Sep 27 19:04:29 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>@irinaconstanti @eglyman “They remember how you made them feel”
+Now that’s marketing.</t>
+        </is>
+      </c>
+      <c r="G594" t="inlineStr"/>
+      <c r="H594" t="inlineStr"/>
+      <c r="I594" t="inlineStr"/>
+      <c r="J594" t="inlineStr"/>
+      <c r="K594" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2104286072062574621</t>
+        </is>
+      </c>
+      <c r="L594" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M594" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N594" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O594" t="inlineStr">
+        <is>
+          <t>Ramp emphasizes the power of emotional marketing, noting that memorable experiences are crucial for effective marketing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>Mon Sep 28 17:24:09 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>cooking🔥</t>
+        </is>
+      </c>
+      <c r="G595" t="inlineStr"/>
+      <c r="H595" t="inlineStr"/>
+      <c r="I595" t="inlineStr"/>
+      <c r="J595" t="inlineStr"/>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2104623209928601839</t>
+        </is>
+      </c>
+      <c r="L595" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M595" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N595" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O595" t="inlineStr">
+        <is>
+          <t>Brex posted a brief, upbeat message about cooking, likely a lighthearted engagement post.</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>Mon Sep 28 17:15:30 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>Wallet tab got simpler, everything got faster. Update now. https://t.co/lAugSDwSzH</t>
+        </is>
+      </c>
+      <c r="G596" t="inlineStr"/>
+      <c r="H596" t="inlineStr"/>
+      <c r="I596" t="inlineStr"/>
+      <c r="J596" t="inlineStr"/>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2104621030505418786</t>
+        </is>
+      </c>
+      <c r="L596" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M596" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N596" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O596" t="inlineStr">
+        <is>
+          <t>Brex announces a streamlined wallet tab that improves speed and simplicity, encouraging users to update.</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>Mon Sep 28 17:12:14 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>@MollySOShea Another banger</t>
+        </is>
+      </c>
+      <c r="G597" t="inlineStr"/>
+      <c r="H597" t="inlineStr"/>
+      <c r="I597" t="inlineStr"/>
+      <c r="J597" t="inlineStr"/>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2104620207687991471</t>
+        </is>
+      </c>
+      <c r="L597" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M597" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N597" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O597" t="inlineStr">
+        <is>
+          <t>Brex tweets a positive remark about a new product or feature, labeling it a "banger."</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>Mon Sep 28 16:56:59 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>@startupideaspod great stuff</t>
+        </is>
+      </c>
+      <c r="G598" t="inlineStr"/>
+      <c r="H598" t="inlineStr"/>
+      <c r="I598" t="inlineStr"/>
+      <c r="J598" t="inlineStr"/>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2104616372169003360</t>
+        </is>
+      </c>
+      <c r="L598" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M598" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N598" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O598" t="inlineStr">
+        <is>
+          <t>Brex publicly praises content from Startup Ideas Pod, indicating positive engagement with the startup community.</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>Mon Sep 28 16:56:20 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>@startupideaspod rinse and repeat🫡</t>
+        </is>
+      </c>
+      <c r="G599" t="inlineStr"/>
+      <c r="H599" t="inlineStr"/>
+      <c r="I599" t="inlineStr"/>
+      <c r="J599" t="inlineStr"/>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2104616205822669237</t>
+        </is>
+      </c>
+      <c r="L599" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M599" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N599" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O599" t="inlineStr">
+        <is>
+          <t>Brex references the Startup Ideas Podcast, showing engagement with industry thought leadership.</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>Mon Sep 28 16:55:24 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>@startupideaspod 🔓🔓🔓</t>
+        </is>
+      </c>
+      <c r="G600" t="inlineStr"/>
+      <c r="H600" t="inlineStr"/>
+      <c r="I600" t="inlineStr"/>
+      <c r="J600" t="inlineStr"/>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2104615972015628680</t>
+        </is>
+      </c>
+      <c r="L600" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M600" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N600" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O600" t="inlineStr">
+        <is>
+          <t>Brex references @startupideaspod with lock emojis, suggesting a teaser for a potential partnership or upcoming feature.</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>Mon Sep 28 15:33:17 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>@nycallday247 NYC AI builders, see you there.</t>
+        </is>
+      </c>
+      <c r="G601" t="inlineStr"/>
+      <c r="H601" t="inlineStr"/>
+      <c r="I601" t="inlineStr"/>
+      <c r="J601" t="inlineStr"/>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2104595308227223650</t>
+        </is>
+      </c>
+      <c r="L601" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M601" t="inlineStr">
+        <is>
+          <t>Strategic Expansion or Changes</t>
+        </is>
+      </c>
+      <c r="N601" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O601" t="inlineStr">
+        <is>
+          <t>Brex is inviting NYC AI builders to an event, signaling outreach and engagement with the local AI community.</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>Mon Sep 28 15:12:51 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>@ashleevance @TheAnnaGat ohhh this is good @TheAnnaGat</t>
+        </is>
+      </c>
+      <c r="G602" t="inlineStr"/>
+      <c r="H602" t="inlineStr"/>
+      <c r="I602" t="inlineStr"/>
+      <c r="J602" t="inlineStr"/>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2104590163473031402</t>
+        </is>
+      </c>
+      <c r="L602" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M602" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N602" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O602" t="inlineStr">
+        <is>
+          <t>Brex’s tweet expresses positive sentiment about a referenced topic, but does not contain any specific announcement or actionable information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>AirBnb</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>airbnb</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>2026-09-27T23:00:06.000Z</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>When you visit @monteypanela in Colombia, you will pet animals. You will milk cows. You will ride horses. You will feed chickens. And now, you will know how to greet them by their names.
+Book an experience with Juan on his animals @airbnbexperiences</t>
+        </is>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>https://scontent-cdg6-1.cdninstagram.com/v/t51.82787-15/825322495_18638254630063838_8920658657302926211_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk5NDQxMDY2NzMyNzIwOTc2Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Wqc82ejdU6wQ7kNvwEBx3YN&amp;_nc_oc=AdqiVbvVSDT-3Othhq-CD_S662swUTr-Br2lsFIvUSJQ9XrYSgf7tn_5bIH3XEfMYwrIq-M0UMK0IHdnVnhz4jtX&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg6-1.cdninstagram.com&amp;_nc_gid=7ENmHB7Lcp-Tp1LvBXkfuA&amp;_nc_ss=7a22e&amp;oh=00_AQMZUx7ClUQqPcmRLSQSTNK-1A5VkOJJyCmg1JDmu4MwAQ&amp;oe=6AC0866F</t>
+        </is>
+      </c>
+      <c r="H603" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I603" t="inlineStr"/>
+      <c r="J603" t="inlineStr"/>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DdzvWWIkVJJ/</t>
+        </is>
+      </c>
+      <c r="L603" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M603" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N603" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O603" t="inlineStr">
+        <is>
+          <t>Airbnb is promoting a new animal‑interaction experience in Colombia, highlighting hands‑on activities with livestock and encouraging bookings through its Airbnb Experiences platform.</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>Mon Sep 28 16:00:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>This is the final call for our 30th Anniversary Sale, US residents. 
+Celebrate with Member Prices of up to 30% off select hotels and vacation rentals, and get $20 in OneKeyCash™ when you book a flight by Oct 5. Sale ends 10/7/26. Terms apply. 
+ Book now: https://t.co/MQTrrWnP0i</t>
+        </is>
+      </c>
+      <c r="G604" t="inlineStr"/>
+      <c r="H604" t="inlineStr"/>
+      <c r="I604" t="inlineStr"/>
+      <c r="J604" t="inlineStr"/>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>https://x.com/Expedia/status/2104602032740925524</t>
+        </is>
+      </c>
+      <c r="L604" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M604" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N604" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O604" t="inlineStr">
+        <is>
+          <t>Expedia is promoting its 30th Anniversary Sale, offering up to 30% off select hotels and vacation rentals for US residents, plus $20 OneKeyCash for flight bookings, with the promotion ending on October 7, 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>Mon Sep 28 14:00:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>La oferta de aniversario está por terminar. 
+Celebra con Precios para socios con hasta 30% de descuento en casas para vacaciones y hoteles seleccionados. Además, obtén $550 MXN en OneKeyCash™ al reservar un vuelo antes del 5 de octubre. La oferta vence el 7 de octubre de 2026. Aplican términos. 
+Reserva hoy mismo: https://t.co/0DgsH1jH8E</t>
+        </is>
+      </c>
+      <c r="G605" t="inlineStr"/>
+      <c r="H605" t="inlineStr"/>
+      <c r="I605" t="inlineStr"/>
+      <c r="J605" t="inlineStr"/>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>https://x.com/Expedia/status/2104571831420137486</t>
+        </is>
+      </c>
+      <c r="L605" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M605" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N605" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O605" t="inlineStr">
+        <is>
+          <t>Expedia is promoting a limited‑time anniversary offer with up to 30% off on vacation homes and selected hotels, plus $550 MXN OneKeyCash for flight bookings before October 5, 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>Mon Sep 28 13:02:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>We're in the final days of the Anniversary Sale, Canadian residents. 
+ Celebrate with Member Prices of up to 30% off selected hotels and vacation rentals. Plus, get 25% off selected packages and great deals on all-inclusive vacations, cars and flights. Members can also enjoy instant discounts of 15% on selected activities and 10% or more on selected cruises. Sale ends 10/7/26. Terms apply. 
+ Book now: https://t.co/1mSKxGvMAi</t>
+        </is>
+      </c>
+      <c r="G606" t="inlineStr"/>
+      <c r="H606" t="inlineStr"/>
+      <c r="I606" t="inlineStr"/>
+      <c r="J606" t="inlineStr"/>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>https://x.com/Expedia/status/2104557236001394711</t>
+        </is>
+      </c>
+      <c r="L606" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M606" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N606" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O606" t="inlineStr">
+        <is>
+          <t>Expedia is promoting the final days of its Anniversary Sale for Canadian residents, offering up to 30% off hotels, 25% off packages, and additional discounts on activities, cruises, and all-inclusive vacations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>Mon Sep 28 13:00:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>Il ne reste plus quelques jours pour profiter du solde anniversaire! 
+Célébrez avec les prix réservés aux membres offrant jusqu'à 30 % de réduction sur certains hôtels et certaines propriétés de vacances. De plus, profitez de 25 % de réduction sur certains forfaits ainsi que de formidables offres sur des vacances tout inclus, des voitures et des vols. Les membres peuvent aussi profiter de réductions instantanées de 15 % ou plus sur certaines activités et de 10 % sur certaines croisières. Le solde prend fin le 7 octobre 2026. Des conditions s'appliquent. 
+Réservez maintenant : https://t.co/2pwoRHH5tD</t>
+        </is>
+      </c>
+      <c r="G607" t="inlineStr"/>
+      <c r="H607" t="inlineStr"/>
+      <c r="I607" t="inlineStr"/>
+      <c r="J607" t="inlineStr"/>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>https://x.com/Expedia/status/2104556732424831199</t>
+        </is>
+      </c>
+      <c r="L607" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M607" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N607" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O607" t="inlineStr">
+        <is>
+          <t>Expedia is promoting a limited‑time anniversary sale offering up to 30% off on selected hotels and vacation properties, 25% off packages, and additional discounts on all‑inclusive vacations, car rentals, flights, activities, and cruises, ending October 7, 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>Mon Sep 28 08:00:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>We're in the final days of the Anniversary Sale, UK residents. 
+Celebrate with Member Prices of up to 30% off selected hotels and holiday homes. Plus, get £20 in OneKeyCash™ when you book a flight by 5 Oct. Sale ends 7/10/26. Terms apply. 
+Book now: https://t.co/Bs1C5pwXvN</t>
+        </is>
+      </c>
+      <c r="G608" t="inlineStr"/>
+      <c r="H608" t="inlineStr"/>
+      <c r="I608" t="inlineStr"/>
+      <c r="J608" t="inlineStr"/>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>https://x.com/Expedia/status/2104481235300925787</t>
+        </is>
+      </c>
+      <c r="L608" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M608" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N608" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O608" t="inlineStr">
+        <is>
+          <t>Expedia is running a limited‑time Anniversary Sale in the UK, offering up to 30% off selected hotels and holiday homes, plus £20 OneKeyCash for flight bookings until 7 Oct 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>Sun Sep 27 23:00:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>We're in the final days of the Anniversary Sale, Australia!
+Celebrate with Member Prices of up to 30% off selected hotels and holiday homes. Plus, get AU$45 in OneKeyCash™ when you book a flight by 5 Oct. Sale ends 7/10/26. Terms apply. 
+Book now: https://t.co/Aycpnci9jP</t>
+        </is>
+      </c>
+      <c r="G609" t="inlineStr"/>
+      <c r="H609" t="inlineStr"/>
+      <c r="I609" t="inlineStr"/>
+      <c r="J609" t="inlineStr"/>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>https://x.com/Expedia/status/2104345339062804868</t>
+        </is>
+      </c>
+      <c r="L609" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M609" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N609" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O609" t="inlineStr">
+        <is>
+          <t>Expedia is promoting the final days of its Anniversary Sale in Australia, offering up to 30% off selected hotels and holiday homes, plus AU$45 OneKeyCash for flight bookings until October 7, 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>Sun Sep 27 21:00:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>We're in the final days of the Anniversary Sale, New Zealand!
+Celebrate with Member Prices of up to 30% off selected hotels and holiday homes. Plus, get NZ$50 in OneKeyCash™ when you book a flight by 5 Oct. Sale ends 7/10/26. Terms apply. 
+ Book now: https://t.co/SJTPYgVRpQ</t>
+        </is>
+      </c>
+      <c r="G610" t="inlineStr"/>
+      <c r="H610" t="inlineStr"/>
+      <c r="I610" t="inlineStr"/>
+      <c r="J610" t="inlineStr"/>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>https://x.com/Expedia/status/2104315142586401023</t>
+        </is>
+      </c>
+      <c r="L610" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M610" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N610" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O610" t="inlineStr">
+        <is>
+          <t>Expedia is promoting the final days of its Anniversary Sale in New Zealand, offering up to 30% off selected hotels and holiday homes, plus NZ$50 OneKeyCash for flight bookings until October 7, 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>Kaya Yurieff</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>2026-09-28T16:20:01.018Z</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>Livestreaming is scary territory for most brands. It's unpredictable, and it means giving up a ton of control. 
+Expedia decided to go all in anyway. 
+The travel giant signed a year-long deal with IShowSpeed, beginning with a 15-hour livestream in April in which the top streamer visited multiple Caribbean countries in one day. 
+The livestream reached more than 400 million people and drove increased searches for those destinations on Expedia. In the days following Speed’s trip, searches for Sint Maarten jumped 70%, compared with 50% and 35% for Guadeloupe and Dominica, respectively.  
+The next phases of the partnership are more focused on driving bookings, including experiences. 
+Even so, Expedia's chief communications officer Lauri Metrose told us on Scalable Pod that sales are never the main goal of a partnership like this, calling it "the gravy." 
+Her bigger point: “Just even how many more viewers we have is such a big part of it…There’s no funnel anymore, so you have to be able to integrate everything into one.”
+We broke down the numbers behind the partnership in our Scalable newsletter. Lauri also joined us on the podcast to talk about how Expedia handled Speed passing out mid-livestream and what's coming next for the brand
+Read more here: https://lnkd.in/eDJWhUbq</t>
+        </is>
+      </c>
+      <c r="G611" t="inlineStr"/>
+      <c r="H611" t="inlineStr"/>
+      <c r="I611" t="inlineStr"/>
+      <c r="J611" t="inlineStr"/>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/kayayurieff_the-numbers-behind-expedias-ishowspeed-partnership-activity-7510330086374567937-Pzim</t>
+        </is>
+      </c>
+      <c r="L611" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M611" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N611" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O611" t="inlineStr">
+        <is>
+          <t>Expedia launched a year‑long partnership with streamer IShowSpeed, achieving a 400‑million‑viewer livestream that spiked destination searches and is now shifting focus toward bookings and experiences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>Mon Sep 28 13:45:11 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>Ciao Giorgio, ci dispiace leggere che non riesci a parlare con il nostro servizio clienti.
+Come possiamo aiutarti? Se la tua richiesta riguarda una prenotazione di una struttura, inviaci un messaggio privato con i seguenti dati e ti risponderemo il prima possibile:
+- Numero di conferma:
+- Codice PIN:
+- Nome indicato sulla prenotazione:
+- Dettagli della tua richiesta:
+Al momento, tramite social media offriamo assistenza solo per prenotazioni di strutture. Per domande su Voli, Taxi o Assicurazione, puoi contattare i team dedicati qui: https://t.co/OVuF5pCzba.</t>
+        </is>
+      </c>
+      <c r="G612" t="inlineStr"/>
+      <c r="H612" t="inlineStr"/>
+      <c r="I612" t="inlineStr"/>
+      <c r="J612" t="inlineStr"/>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2104568101765337403</t>
+        </is>
+      </c>
+      <c r="L612" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M612" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N612" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O612" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint about difficulty reaching customer service, offering private messaging with booking details and directing other inquiries to dedicated teams.</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>Mon Sep 28 13:20:46 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>@JesusGThomas Hola Jesús, hemos respondido a tu DM.</t>
+        </is>
+      </c>
+      <c r="G613" t="inlineStr"/>
+      <c r="H613" t="inlineStr"/>
+      <c r="I613" t="inlineStr"/>
+      <c r="J613" t="inlineStr"/>
+      <c r="K613" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2104561958531878972</t>
+        </is>
+      </c>
+      <c r="L613" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M613" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N613" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O613" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a private message from user @JesusGThomas, confirming that they have responded to the DM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>Mon Sep 28 12:46:22 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>@Rifton926 Hello, thanks for contacting us.
+We regret hearing you had to go to the hospital.
+Our social media team can take a look at your booking, we have replied to your DM requesting further information from you. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G614" t="inlineStr"/>
+      <c r="H614" t="inlineStr"/>
+      <c r="I614" t="inlineStr"/>
+      <c r="J614" t="inlineStr"/>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2104553301681340604</t>
+        </is>
+      </c>
+      <c r="L614" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M614" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N614" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O614" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s complaint about a hospital visit related to a booking, offering to investigate and requesting further information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>Mon Sep 28 12:36:42 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>Hi Yunus, please note that this email address does not belong to us. Additionally, we're helping you already through another via, we kindly ask your patience and cooperation as writing us through different channels will not change either speed up our possibilities to help. Thanks for understanding.</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr"/>
+      <c r="H615" t="inlineStr"/>
+      <c r="I615" t="inlineStr"/>
+      <c r="J615" t="inlineStr"/>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2104550868276109488</t>
+        </is>
+      </c>
+      <c r="L615" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M615" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N615" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O615" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer inquiry, clarifying that the email address is not theirs and advising patience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>Mon Sep 28 11:58:24 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>Hola Andrés, gracias por contactarnos. Lamentamos tu experiencia y esperamos que hayas podido comunicar cualquier inconveniente directamente con el alojamiento mientras estabas allí, ya que son quienes están en mejor posición para abordar y resolver cualquier incidencia.
+Si deseas que revisemos tu reserva desde aquí, por favor envíanos un mensaje privado con la siguiente información:
+- Número de confirmación
+- Código PIN
+- Nombre del huésped
+- Detalles sobre tu estancia
+Te responderemos lo antes posible. Como alternativa, para recibir ayuda inmediata siempre puedes llamarnos aquí: https://t.co/o8QyR8SaDb. Un saludo.</t>
+        </is>
+      </c>
+      <c r="G616" t="inlineStr"/>
+      <c r="H616" t="inlineStr"/>
+      <c r="I616" t="inlineStr"/>
+      <c r="J616" t="inlineStr"/>
+      <c r="K616" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2104541229962711268</t>
+        </is>
+      </c>
+      <c r="L616" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M616" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N616" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O616" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint, offering to review the reservation and providing contact details for assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>Mon Sep 28 11:30:31 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>Hola Iván, premios y bonificaciones no son acumulables. También toma en cuenta que algunos alojamientos muestran sus descuentos Genius para clientes con reservas directas, y no mediante terceros. Si tienes alguna consulta en concreto puedes enviarnos los detalles por privado y con gusto lo revisamos.</t>
+        </is>
+      </c>
+      <c r="G617" t="inlineStr"/>
+      <c r="H617" t="inlineStr"/>
+      <c r="I617" t="inlineStr"/>
+      <c r="J617" t="inlineStr"/>
+      <c r="K617" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2104534211910664268</t>
+        </is>
+      </c>
+      <c r="L617" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M617" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N617" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O617" t="inlineStr">
+        <is>
+          <t>Booking.com clarifies that bonuses and Genius discounts are not cumulative and are only available for direct bookings, offering to review specific queries privately.</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>Mon Sep 28 10:43:59 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>@KeshavP03213345 Hi there, we didn't receive any of the details which we have previously requested. Once you have shared everything via DM, we will get back to you as soon as possible. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G618" t="inlineStr"/>
+      <c r="H618" t="inlineStr"/>
+      <c r="I618" t="inlineStr"/>
+      <c r="J618" t="inlineStr"/>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2104522504337256523</t>
+        </is>
+      </c>
+      <c r="L618" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M618" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N618" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O618" t="inlineStr">
+        <is>
+          <t>Booking.com is replying to a user, noting that it has not received the requested details and will respond once the user shares the information via DM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>Mon Sep 28 10:33:56 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>Hola, Angelina. Lamentamos lo ocurrido y los inconvenientes que esta situación te haya podido ocasionar. Para poder ayudarte lo antes posible, envíanos un mensaje privado con los siguientes datos: 
+- Número de confirmación: 
+- Código PIN: 
+- Nombre que aparece en la reserva: 
+Como alternativa, para recibir ayuda inmediata siempre puedes llamarnos aquí: https://t.co/o8QyR8SaDb. 
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G619" t="inlineStr"/>
+      <c r="H619" t="inlineStr"/>
+      <c r="I619" t="inlineStr"/>
+      <c r="J619" t="inlineStr"/>
+      <c r="K619" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2104519975490695612</t>
+        </is>
+      </c>
+      <c r="L619" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M619" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N619" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O619" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes to a customer for an issue and provides instructions for contacting support via private message or phone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>Mon Sep 28 10:17:38 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>@ShevaMafia13 Hi Volodymyr, we have just replied to your private message regarding this. Please check it. Thank you.</t>
+        </is>
+      </c>
+      <c r="G620" t="inlineStr"/>
+      <c r="H620" t="inlineStr"/>
+      <c r="I620" t="inlineStr"/>
+      <c r="J620" t="inlineStr"/>
+      <c r="K620" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2104515873855680546</t>
+        </is>
+      </c>
+      <c r="L620" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M620" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N620" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O620" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a private message from user @ShevaMafia13, indicating a response to an inquiry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>Mon Sep 28 09:48:41 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>Hi Ashok, thanks for contacting us.
+Please let us know why you rejected the room. If your booking was nonrefundable, the accommodation would have the right to charge you accordingly. 
+If you would like us to review your booking, we'll need the following details via DM:
+- Pin code, 
+- Full guest name,
+and we will get back to you as soon as possible.</t>
+        </is>
+      </c>
+      <c r="G621" t="inlineStr"/>
+      <c r="H621" t="inlineStr"/>
+      <c r="I621" t="inlineStr"/>
+      <c r="J621" t="inlineStr"/>
+      <c r="K621" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2104508586097353065</t>
+        </is>
+      </c>
+      <c r="L621" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M621" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N621" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O621" t="inlineStr">
+        <is>
+          <t>Booking.com is responding to a customer inquiry about a rejected booking, requesting details for review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>Mon Sep 28 09:36:53 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>Hi there, we would like to help you. However, we need to have more information regarding your reservation, and in our previous message, we asked for more details, so we can check it for you. 
+Please send us a Private message with the following details, and we'll get back to you as soon as possible:
+- Confirmation number:
+- Pin code:
+- Guest name on the reservation:</t>
+        </is>
+      </c>
+      <c r="G622" t="inlineStr"/>
+      <c r="H622" t="inlineStr"/>
+      <c r="I622" t="inlineStr"/>
+      <c r="J622" t="inlineStr"/>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2104505616756510957</t>
+        </is>
+      </c>
+      <c r="L622" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M622" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N622" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O622" t="inlineStr">
+        <is>
+          <t>Booking.com is requesting additional reservation details from a customer via private message to verify and assist with their booking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>Mon Sep 28 09:19:14 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>Hola, agradecemos tu mensaje. 
+No tenemos información precisa sobre lo sucedido con tu reserva, sin embargo, nos gustaría revisarlo para brindarte una respuesta y determinar cómo podemos ayudarte.
+Comparte con nosotros por mensaje privado la siguiente información y te responderemos lo antes posible: 
+- Número de confirmación
+- Código PIN
+- Nombre del huésped en la reserva
+Ten en cuenta que nuestro equipo de Redes Sociales no opera en tiempo real. Para asistencia inmediata puedes comunicarte con nuestro equipo de atención al cliente, disponible las 24 horas, aquí: https://t.co/tuuNbmGVaG
+Saludos.</t>
+        </is>
+      </c>
+      <c r="G623" t="inlineStr"/>
+      <c r="H623" t="inlineStr"/>
+      <c r="I623" t="inlineStr"/>
+      <c r="J623" t="inlineStr"/>
+      <c r="K623" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2104501174208532651</t>
+        </is>
+      </c>
+      <c r="L623" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M623" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N623" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O623" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user’s reservation issue, requesting confirmation details and offering 24/7 customer support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>Mon Sep 28 09:18:54 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>@PrachiChitlang1 Hi Prachi, we replied with further information via private message. Kindly note we're unable to provide any information about your case via public messages. Thank you.</t>
+        </is>
+      </c>
+      <c r="G624" t="inlineStr"/>
+      <c r="H624" t="inlineStr"/>
+      <c r="I624" t="inlineStr"/>
+      <c r="J624" t="inlineStr"/>
+      <c r="K624" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2104501091245133955</t>
+        </is>
+      </c>
+      <c r="L624" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M624" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N624" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O624" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user privately, stating they cannot share case details publicly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>Mon Sep 28 08:11:50 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>Lamentamos la percepción que tienes sobre nuestros servicios y cualquier inconveniente que estés atravesando. Cuéntanos, ¿en qué podemos ayudarte? Si tu consulta está relacionada con una reserva de alojamiento, envíanos un mensaje privado con los siguientes datos y te responderemos lo antes posible: 
+- Número de confirmación: 
+- Código PIN: 
+- Nombre que aparece en la reserva: 
+- Detalles de tu solicitud: 
+Ten en cuenta que nuestro equipo de Redes Sociales no trabaja en tiempo real. Para recibir ayuda inmediata, llama a nuestro equipo de Atención al Cliente disponible 24/7; puedes encontrar nuestros datos de contacto aquí: https://t.co/o8QyR8SaDb 
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G625" t="inlineStr"/>
+      <c r="H625" t="inlineStr"/>
+      <c r="I625" t="inlineStr"/>
+      <c r="J625" t="inlineStr"/>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2104484214267605338</t>
+        </is>
+      </c>
+      <c r="L625" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M625" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N625" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O625" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for any negative perception and offers assistance with accommodation reservations, providing contact details for immediate help.</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>Mon Sep 28 07:29:17 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>Oi Leonora, lamentamos saber que encontrou percevejos no hotel. Se precisar de assistência, por favor, nos envie uma mensagem privada com: 
+- Nome do hóspede na reserva: 
+- Número de confirmação: 
+- Código PIN: 
+Retornaremos com a maior brevidade possível. Para suporte imediato, ligue para nossa equipe de Apoio ao Cliente por aqui: https://t.co/tuuNbmGVaG.</t>
+        </is>
+      </c>
+      <c r="G626" t="inlineStr"/>
+      <c r="H626" t="inlineStr"/>
+      <c r="I626" t="inlineStr"/>
+      <c r="J626" t="inlineStr"/>
+      <c r="K626" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2104473503030284657</t>
+        </is>
+      </c>
+      <c r="L626" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M626" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N626" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O626" t="inlineStr">
+        <is>
+          <t>Booking.com addresses a guest complaint about bedbugs, offering assistance and contact details for resolution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>Mon Sep 28 07:27:53 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>@Iba_Banfield Hola, Gabriel. Te hemos enviado un mensaje privado con novedades sobre tu solicitud. Cuando puedas, revísalo. Un saludo. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G627" t="inlineStr"/>
+      <c r="H627" t="inlineStr"/>
+      <c r="I627" t="inlineStr"/>
+      <c r="J627" t="inlineStr"/>
+      <c r="K627" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2104473154563285004</t>
+        </is>
+      </c>
+      <c r="L627" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M627" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N627" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O627" t="inlineStr">
+        <is>
+          <t>Booking.com informs a user that they have sent a private message with updates regarding the user's request.</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>Mon Sep 28 07:03:26 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>Hi there, we regret to hear about your experience. If the final outcome has alreaby been provided we might not be able to change it but we would like to look into this for you. Feel free to DM us the following details and we'll get back to you as soon as possible: 
+- Confirmation number:
+- Pin code:
+- Name on the reservation:
+- Details on your request:
+Please bear in mind that our Social Media Team doesn't work in real time. For immediate support, please call our 24/7 Customer Service Team - our contact details can be found here: https://t.co/o8QyR8SaDb
+Kind regards.</t>
+        </is>
+      </c>
+      <c r="G628" t="inlineStr"/>
+      <c r="H628" t="inlineStr"/>
+      <c r="I628" t="inlineStr"/>
+      <c r="J628" t="inlineStr"/>
+      <c r="K628" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2104466997870207033</t>
+        </is>
+      </c>
+      <c r="L628" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M628" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N628" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O628" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint, offering to investigate the issue and providing contact details for further assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>Mon Sep 28 06:58:40 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>Hi Sunny, we regret to hear that you're still waiting for an outcome from us. We will be happy to look into this for you further and see how we can help via this channel, kindly send us a DM with the following information, and we'll get back to you with our findings. 
+- Pin code,
+- Name on the reservation.</t>
+        </is>
+      </c>
+      <c r="G629" t="inlineStr"/>
+      <c r="H629" t="inlineStr"/>
+      <c r="I629" t="inlineStr"/>
+      <c r="J629" t="inlineStr"/>
+      <c r="K629" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2104465798387437699</t>
+        </is>
+      </c>
+      <c r="L629" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M629" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N629" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O629" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint, offering to investigate via DM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>Mon Sep 28 06:21:22 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>Hi there, thanks for flagging this. We regret to hear about this experience. As part of our mission to make it easier for everyone to experience the world, we’re committed to doing everything we can to eliminate all forms of unlawful bias, discrimination, intolerance, harassment and abuse from our platforms. 
+Please send us a DM with more information so we can learn what has been done so far and see how are able to assist further.</t>
+        </is>
+      </c>
+      <c r="G630" t="inlineStr"/>
+      <c r="H630" t="inlineStr"/>
+      <c r="I630" t="inlineStr"/>
+      <c r="J630" t="inlineStr"/>
+      <c r="K630" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2104456412684333549</t>
+        </is>
+      </c>
+      <c r="L630" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M630" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N630" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O630" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user complaint, apologizing and offering to investigate further while reaffirming its commitment to eliminating bias and abuse.</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>Mon Sep 28 01:56:07 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>Hi Yunus, we understand your disappointment and acknowledge that you have removed your personal information from X (Twitter). We can see that you've also contacted us on Instagram, and we've replied to your message there. Please review it at your earliest convenience and reply directly there if you have any additional questions. In the future, we would recommend reaching out via one platform only; this removes any confusion or delays by having two active conversations across platforms.</t>
+        </is>
+      </c>
+      <c r="G631" t="inlineStr"/>
+      <c r="H631" t="inlineStr"/>
+      <c r="I631" t="inlineStr"/>
+      <c r="J631" t="inlineStr"/>
+      <c r="K631" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2104389659929223179</t>
+        </is>
+      </c>
+      <c r="L631" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M631" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N631" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O631" t="inlineStr">
+        <is>
+          <t>Booking.com addresses a customer’s complaint, advising them to use a single platform for communication to avoid confusion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>SkyBirdTravel</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>Mon Sep 28 15:31:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>Planning Umrah for clients? Sky Bird Travel ensures seamless pilgrimages with exclusive North America fares and 20+ years of trusted expertise. Contact us today.
+#Umrah #SkyBirdTravel #Pilgrimage #FaithTravel https://t.co/xWRkb8RzHq</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr"/>
+      <c r="H632" t="inlineStr"/>
+      <c r="I632" t="inlineStr"/>
+      <c r="J632" t="inlineStr"/>
+      <c r="K632" t="inlineStr">
+        <is>
+          <t>https://x.com/SkyBirdTravel/status/2104594731904962928</t>
+        </is>
+      </c>
+      <c r="L632" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M632" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N632" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O632" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel promotes its Umrah pilgrimage services, highlighting exclusive North American fares and over 20 years of experience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel &amp; Tours</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>2026-09-28T15:33:16.849Z</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>Planning an Umrah journey for your clients? Let Sky Bird Travel make it seamless. With trusted expertise, exclusive airfares from across North America, and over 20 years of experience serving pilgrims, we’re here to help you deliver a smooth and meaningful travel experience. Contact us today to learn more. 
+#Umrah #UmrahTravel #TravelAdvisor #FaithTravel #Pilgrimage #SkyBirdTravel #TravelProfessionals #IslamicTravel #SaudiArabia #TravelExperts</t>
+        </is>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D4D22AQH8imhTrFjgzw/feedshare-image-high-res/B4DaDoUX3AKgAY-/0/1790604050305?e=1792022400&amp;v=beta&amp;t=jrWDcdcfnP4gL29Lk3hNCfl3qw7qM4_r-lBZVsaSIWo</t>
+        </is>
+      </c>
+      <c r="H633" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I633" t="inlineStr"/>
+      <c r="J633" t="inlineStr"/>
+      <c r="K633" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/sky-bird-travel-tours_umrah-umrahtravel-traveladvisor-activity-7510360994502709248-vVK5</t>
+        </is>
+      </c>
+      <c r="L633" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M633" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N633" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O633" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel highlights its 20‑year experience and exclusive North American airfares to assist travel advisors in delivering seamless Umrah journeys for clients.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -38276,7 +38276,7 @@
       </c>
       <c r="O590" t="inlineStr">
         <is>
-          <t>A tweet praises Ramp’s product and engineering teams for their exceptional performance.</t>
+          <t>Ramp’s product and engineering are praised by @barbinbrad, highlighting the company’s strong performance.</t>
         </is>
       </c>
     </row>
@@ -38337,7 +38337,7 @@
       </c>
       <c r="O591" t="inlineStr">
         <is>
-          <t>Ramp was referenced in a tweet by other users, indicating a brief mention without any direct announcement or update.</t>
+          <t>Ramp was mentioned by other users on X, indicating some attention but no specific announcement or update.</t>
         </is>
       </c>
     </row>
@@ -38398,7 +38398,7 @@
       </c>
       <c r="O592" t="inlineStr">
         <is>
-          <t>Ramp responds to a statement by William Simmons with a positive remark, indicating agreement or surprise.</t>
+          <t>Ramp responds to William Simmons with a positive remark, indicating surprise or agreement.</t>
         </is>
       </c>
     </row>
@@ -38444,22 +38444,22 @@
       </c>
       <c r="L593" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M593" t="inlineStr">
         <is>
-          <t>General Industry News</t>
+          <t>Partnership and Acquisitions</t>
         </is>
       </c>
       <c r="N593" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O593" t="inlineStr">
         <is>
-          <t>Ramp shares a link featuring @verdaxxed, likely referencing industry news or a related update.</t>
+          <t>Ramp announces a new partnership with Verdaxxed, highlighting collaboration and potential growth opportunities.</t>
         </is>
       </c>
     </row>
@@ -38521,7 +38521,7 @@
       </c>
       <c r="O594" t="inlineStr">
         <is>
-          <t>Ramp emphasizes the power of emotional marketing, noting that memorable experiences are crucial for effective marketing.</t>
+          <t>Ramp emphasizes the emotional impact of marketing by quoting @irinaconstanti and @eglyman, highlighting how memorable experiences shape customer perception.</t>
         </is>
       </c>
     </row>
@@ -38582,7 +38582,7 @@
       </c>
       <c r="O595" t="inlineStr">
         <is>
-          <t>Brex posted a brief, upbeat message about cooking, likely a lighthearted engagement post.</t>
+          <t>Brex posted a playful caption "cooking🔥", likely a lighthearted or promotional post without any major announcement.</t>
         </is>
       </c>
     </row>
@@ -38643,7 +38643,7 @@
       </c>
       <c r="O596" t="inlineStr">
         <is>
-          <t>Brex announces a streamlined wallet tab that improves speed and simplicity, encouraging users to update.</t>
+          <t>Brex announces a streamlined wallet tab that is simpler and faster, encouraging users to update.</t>
         </is>
       </c>
     </row>
@@ -38704,7 +38704,7 @@
       </c>
       <c r="O597" t="inlineStr">
         <is>
-          <t>Brex tweets a positive remark about a new product or feature, labeling it a "banger."</t>
+          <t>Brex is celebrating a new product or feature release, labeling it a "banger" in a tweet.</t>
         </is>
       </c>
     </row>
@@ -38765,7 +38765,7 @@
       </c>
       <c r="O598" t="inlineStr">
         <is>
-          <t>Brex publicly praises content from Startup Ideas Pod, indicating positive engagement with the startup community.</t>
+          <t>Brex publicly praises the @startupideaspod podcast, indicating positive engagement with the startup community.</t>
         </is>
       </c>
     </row>
@@ -38811,7 +38811,7 @@
       </c>
       <c r="L599" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M599" t="inlineStr">
@@ -38826,7 +38826,7 @@
       </c>
       <c r="O599" t="inlineStr">
         <is>
-          <t>Brex references the Startup Ideas Podcast, showing engagement with industry thought leadership.</t>
+          <t>Brex briefly acknowledges the @startupideaspod podcast with a casual mention, indicating engagement with the startup community.</t>
         </is>
       </c>
     </row>
@@ -38887,7 +38887,7 @@
       </c>
       <c r="O600" t="inlineStr">
         <is>
-          <t>Brex references @startupideaspod with lock emojis, suggesting a teaser for a potential partnership or upcoming feature.</t>
+          <t>Brex appears to be announcing a collaboration or partnership with @startupideaspod, suggesting a new opportunity or feature for startups.</t>
         </is>
       </c>
     </row>
@@ -38933,7 +38933,7 @@
       </c>
       <c r="L601" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="M601" t="inlineStr">
@@ -38948,7 +38948,7 @@
       </c>
       <c r="O601" t="inlineStr">
         <is>
-          <t>Brex is inviting NYC AI builders to an event, signaling outreach and engagement with the local AI community.</t>
+          <t>Brex invites NYC AI builders to an event, signaling engagement with the AI community.</t>
         </is>
       </c>
     </row>
@@ -39009,7 +39009,7 @@
       </c>
       <c r="O602" t="inlineStr">
         <is>
-          <t>Brex’s tweet expresses positive sentiment about a referenced topic, but does not contain any specific announcement or actionable information.</t>
+          <t>Brex’s tweet is a brief, positive comment praising something, with no indication of a new product, partnership, or other significant activity.</t>
         </is>
       </c>
     </row>
@@ -39021,45 +39021,38 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>AirBnb</t>
+          <t>Expedia</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>X (Twitter)</t>
         </is>
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>airbnb</t>
+          <t>Expedia</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>2026-09-27T23:00:06.000Z</t>
+          <t>Mon Sep 28 16:00:00 +0000 2026</t>
         </is>
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>When you visit @monteypanela in Colombia, you will pet animals. You will milk cows. You will ride horses. You will feed chickens. And now, you will know how to greet them by their names.
-Book an experience with Juan on his animals @airbnbexperiences</t>
-        </is>
-      </c>
-      <c r="G603" t="inlineStr">
-        <is>
-          <t>https://scontent-cdg6-1.cdninstagram.com/v/t51.82787-15/825322495_18638254630063838_8920658657302926211_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=105&amp;ig_cache_key=Mzk5NDQxMDY2NzMyNzIwOTc2Mw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Wqc82ejdU6wQ7kNvwEBx3YN&amp;_nc_oc=AdqiVbvVSDT-3Othhq-CD_S662swUTr-Br2lsFIvUSJQ9XrYSgf7tn_5bIH3XEfMYwrIq-M0UMK0IHdnVnhz4jtX&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-cdg6-1.cdninstagram.com&amp;_nc_gid=7ENmHB7Lcp-Tp1LvBXkfuA&amp;_nc_ss=7a22e&amp;oh=00_AQMZUx7ClUQqPcmRLSQSTNK-1A5VkOJJyCmg1JDmu4MwAQ&amp;oe=6AC0866F</t>
-        </is>
-      </c>
-      <c r="H603" t="inlineStr">
-        <is>
-          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
-        </is>
-      </c>
+          <t>This is the final call for our 30th Anniversary Sale, US residents. 
+Celebrate with Member Prices of up to 30% off select hotels and vacation rentals, and get $20 in OneKeyCash™ when you book a flight by Oct 5. Sale ends 10/7/26. Terms apply. 
+ Book now: https://t.co/MQTrrWnP0i</t>
+        </is>
+      </c>
+      <c r="G603" t="inlineStr"/>
+      <c r="H603" t="inlineStr"/>
       <c r="I603" t="inlineStr"/>
       <c r="J603" t="inlineStr"/>
       <c r="K603" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DdzvWWIkVJJ/</t>
+          <t>https://x.com/Expedia/status/2104602032740925524</t>
         </is>
       </c>
       <c r="L603" t="inlineStr">
@@ -39079,7 +39072,7 @@
       </c>
       <c r="O603" t="inlineStr">
         <is>
-          <t>Airbnb is promoting a new animal‑interaction experience in Colombia, highlighting hands‑on activities with livestock and encouraging bookings through its Airbnb Experiences platform.</t>
+          <t>Expedia is promoting its 30th Anniversary Sale, offering up to 30% off select hotels and vacation rentals for US residents, plus $20 OneKeyCash for flight bookings until October 7, 2026.</t>
         </is>
       </c>
     </row>
@@ -39106,14 +39099,14 @@
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>Mon Sep 28 16:00:00 +0000 2026</t>
+          <t>Mon Sep 28 14:00:00 +0000 2026</t>
         </is>
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>This is the final call for our 30th Anniversary Sale, US residents. 
-Celebrate with Member Prices of up to 30% off select hotels and vacation rentals, and get $20 in OneKeyCash™ when you book a flight by Oct 5. Sale ends 10/7/26. Terms apply. 
- Book now: https://t.co/MQTrrWnP0i</t>
+          <t>La oferta de aniversario está por terminar. 
+Celebra con Precios para socios con hasta 30% de descuento en casas para vacaciones y hoteles seleccionados. Además, obtén $550 MXN en OneKeyCash™ al reservar un vuelo antes del 5 de octubre. La oferta vence el 7 de octubre de 2026. Aplican términos. 
+Reserva hoy mismo: https://t.co/0DgsH1jH8E</t>
         </is>
       </c>
       <c r="G604" t="inlineStr"/>
@@ -39122,7 +39115,7 @@
       <c r="J604" t="inlineStr"/>
       <c r="K604" t="inlineStr">
         <is>
-          <t>https://x.com/Expedia/status/2104602032740925524</t>
+          <t>https://x.com/Expedia/status/2104571831420137486</t>
         </is>
       </c>
       <c r="L604" t="inlineStr">
@@ -39142,7 +39135,7 @@
       </c>
       <c r="O604" t="inlineStr">
         <is>
-          <t>Expedia is promoting its 30th Anniversary Sale, offering up to 30% off select hotels and vacation rentals for US residents, plus $20 OneKeyCash for flight bookings, with the promotion ending on October 7, 2026.</t>
+          <t>Expedia is promoting a limited‑time anniversary offer with up to 30% off vacation homes and selected hotels, plus $550 MXN OneKeyCash for flight bookings before October 5, expiring October 7, 2026.</t>
         </is>
       </c>
     </row>
@@ -39169,14 +39162,14 @@
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>Mon Sep 28 14:00:00 +0000 2026</t>
+          <t>Mon Sep 28 13:02:00 +0000 2026</t>
         </is>
       </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>La oferta de aniversario está por terminar. 
-Celebra con Precios para socios con hasta 30% de descuento en casas para vacaciones y hoteles seleccionados. Además, obtén $550 MXN en OneKeyCash™ al reservar un vuelo antes del 5 de octubre. La oferta vence el 7 de octubre de 2026. Aplican términos. 
-Reserva hoy mismo: https://t.co/0DgsH1jH8E</t>
+          <t>We're in the final days of the Anniversary Sale, Canadian residents. 
+ Celebrate with Member Prices of up to 30% off selected hotels and vacation rentals. Plus, get 25% off selected packages and great deals on all-inclusive vacations, cars and flights. Members can also enjoy instant discounts of 15% on selected activities and 10% or more on selected cruises. Sale ends 10/7/26. Terms apply. 
+ Book now: https://t.co/1mSKxGvMAi</t>
         </is>
       </c>
       <c r="G605" t="inlineStr"/>
@@ -39185,7 +39178,7 @@
       <c r="J605" t="inlineStr"/>
       <c r="K605" t="inlineStr">
         <is>
-          <t>https://x.com/Expedia/status/2104571831420137486</t>
+          <t>https://x.com/Expedia/status/2104557236001394711</t>
         </is>
       </c>
       <c r="L605" t="inlineStr">
@@ -39205,7 +39198,7 @@
       </c>
       <c r="O605" t="inlineStr">
         <is>
-          <t>Expedia is promoting a limited‑time anniversary offer with up to 30% off on vacation homes and selected hotels, plus $550 MXN OneKeyCash for flight bookings before October 5, 2026.</t>
+          <t>Expedia is offering a final‑day anniversary sale for Canadian residents, with up to 30% off hotels and vacation rentals, 25% off packages, and additional discounts on activities, cruises, cars, and flights.</t>
         </is>
       </c>
     </row>
@@ -39232,14 +39225,14 @@
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>Mon Sep 28 13:02:00 +0000 2026</t>
+          <t>Mon Sep 28 13:00:00 +0000 2026</t>
         </is>
       </c>
       <c r="F606" t="inlineStr">
         <is>
-          <t>We're in the final days of the Anniversary Sale, Canadian residents. 
- Celebrate with Member Prices of up to 30% off selected hotels and vacation rentals. Plus, get 25% off selected packages and great deals on all-inclusive vacations, cars and flights. Members can also enjoy instant discounts of 15% on selected activities and 10% or more on selected cruises. Sale ends 10/7/26. Terms apply. 
- Book now: https://t.co/1mSKxGvMAi</t>
+          <t>Il ne reste plus quelques jours pour profiter du solde anniversaire! 
+Célébrez avec les prix réservés aux membres offrant jusqu'à 30 % de réduction sur certains hôtels et certaines propriétés de vacances. De plus, profitez de 25 % de réduction sur certains forfaits ainsi que de formidables offres sur des vacances tout inclus, des voitures et des vols. Les membres peuvent aussi profiter de réductions instantanées de 15 % ou plus sur certaines activités et de 10 % sur certaines croisières. Le solde prend fin le 7 octobre 2026. Des conditions s'appliquent. 
+Réservez maintenant : https://t.co/2pwoRHH5tD</t>
         </is>
       </c>
       <c r="G606" t="inlineStr"/>
@@ -39248,7 +39241,7 @@
       <c r="J606" t="inlineStr"/>
       <c r="K606" t="inlineStr">
         <is>
-          <t>https://x.com/Expedia/status/2104557236001394711</t>
+          <t>https://x.com/Expedia/status/2104556732424831199</t>
         </is>
       </c>
       <c r="L606" t="inlineStr">
@@ -39263,12 +39256,12 @@
       </c>
       <c r="N606" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="O606" t="inlineStr">
         <is>
-          <t>Expedia is promoting the final days of its Anniversary Sale for Canadian residents, offering up to 30% off hotels, 25% off packages, and additional discounts on activities, cruises, and all-inclusive vacations.</t>
+          <t>Expedia is promoting its anniversary sale, offering up to 30% off on select hotels, 25% off on packages, and additional discounts on all-inclusive vacations, car rentals, flights, activities, and cruises, with the promotion ending on October 7, 2026.</t>
         </is>
       </c>
     </row>
@@ -39295,14 +39288,14 @@
       </c>
       <c r="E607" t="inlineStr">
         <is>
-          <t>Mon Sep 28 13:00:00 +0000 2026</t>
+          <t>Mon Sep 28 08:00:00 +0000 2026</t>
         </is>
       </c>
       <c r="F607" t="inlineStr">
         <is>
-          <t>Il ne reste plus quelques jours pour profiter du solde anniversaire! 
-Célébrez avec les prix réservés aux membres offrant jusqu'à 30 % de réduction sur certains hôtels et certaines propriétés de vacances. De plus, profitez de 25 % de réduction sur certains forfaits ainsi que de formidables offres sur des vacances tout inclus, des voitures et des vols. Les membres peuvent aussi profiter de réductions instantanées de 15 % ou plus sur certaines activités et de 10 % sur certaines croisières. Le solde prend fin le 7 octobre 2026. Des conditions s'appliquent. 
-Réservez maintenant : https://t.co/2pwoRHH5tD</t>
+          <t>We're in the final days of the Anniversary Sale, UK residents. 
+Celebrate with Member Prices of up to 30% off selected hotels and holiday homes. Plus, get £20 in OneKeyCash™ when you book a flight by 5 Oct. Sale ends 7/10/26. Terms apply. 
+Book now: https://t.co/Bs1C5pwXvN</t>
         </is>
       </c>
       <c r="G607" t="inlineStr"/>
@@ -39311,7 +39304,7 @@
       <c r="J607" t="inlineStr"/>
       <c r="K607" t="inlineStr">
         <is>
-          <t>https://x.com/Expedia/status/2104556732424831199</t>
+          <t>https://x.com/Expedia/status/2104481235300925787</t>
         </is>
       </c>
       <c r="L607" t="inlineStr">
@@ -39321,7 +39314,7 @@
       </c>
       <c r="M607" t="inlineStr">
         <is>
-          <t>Product Announcement</t>
+          <t>General Industry News</t>
         </is>
       </c>
       <c r="N607" t="inlineStr">
@@ -39331,7 +39324,7 @@
       </c>
       <c r="O607" t="inlineStr">
         <is>
-          <t>Expedia is promoting a limited‑time anniversary sale offering up to 30% off on selected hotels and vacation properties, 25% off packages, and additional discounts on all‑inclusive vacations, car rentals, flights, activities, and cruises, ending October 7, 2026.</t>
+          <t>Expedia is promoting the final days of its anniversary sale in the UK, offering up to 30% off selected hotels and holiday homes, plus £20 OneKeyCash for flight bookings until 7 Oct 2026.</t>
         </is>
       </c>
     </row>
@@ -39358,14 +39351,14 @@
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>Mon Sep 28 08:00:00 +0000 2026</t>
+          <t>Sun Sep 27 23:00:00 +0000 2026</t>
         </is>
       </c>
       <c r="F608" t="inlineStr">
         <is>
-          <t>We're in the final days of the Anniversary Sale, UK residents. 
-Celebrate with Member Prices of up to 30% off selected hotels and holiday homes. Plus, get £20 in OneKeyCash™ when you book a flight by 5 Oct. Sale ends 7/10/26. Terms apply. 
-Book now: https://t.co/Bs1C5pwXvN</t>
+          <t>We're in the final days of the Anniversary Sale, Australia!
+Celebrate with Member Prices of up to 30% off selected hotels and holiday homes. Plus, get AU$45 in OneKeyCash™ when you book a flight by 5 Oct. Sale ends 7/10/26. Terms apply. 
+Book now: https://t.co/Aycpnci9jP</t>
         </is>
       </c>
       <c r="G608" t="inlineStr"/>
@@ -39374,7 +39367,7 @@
       <c r="J608" t="inlineStr"/>
       <c r="K608" t="inlineStr">
         <is>
-          <t>https://x.com/Expedia/status/2104481235300925787</t>
+          <t>https://x.com/Expedia/status/2104345339062804868</t>
         </is>
       </c>
       <c r="L608" t="inlineStr">
@@ -39394,7 +39387,7 @@
       </c>
       <c r="O608" t="inlineStr">
         <is>
-          <t>Expedia is running a limited‑time Anniversary Sale in the UK, offering up to 30% off selected hotels and holiday homes, plus £20 OneKeyCash for flight bookings until 7 Oct 2026.</t>
+          <t>Expedia is concluding its Anniversary Sale in Australia, offering up to 30% off selected hotels and holiday homes, plus AU$45 OneKeyCash for flight bookings until 7 Oct 2026.</t>
         </is>
       </c>
     </row>
@@ -39421,14 +39414,14 @@
       </c>
       <c r="E609" t="inlineStr">
         <is>
-          <t>Sun Sep 27 23:00:00 +0000 2026</t>
+          <t>Sun Sep 27 21:00:00 +0000 2026</t>
         </is>
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>We're in the final days of the Anniversary Sale, Australia!
-Celebrate with Member Prices of up to 30% off selected hotels and holiday homes. Plus, get AU$45 in OneKeyCash™ when you book a flight by 5 Oct. Sale ends 7/10/26. Terms apply. 
-Book now: https://t.co/Aycpnci9jP</t>
+          <t>We're in the final days of the Anniversary Sale, New Zealand!
+Celebrate with Member Prices of up to 30% off selected hotels and holiday homes. Plus, get NZ$50 in OneKeyCash™ when you book a flight by 5 Oct. Sale ends 7/10/26. Terms apply. 
+ Book now: https://t.co/SJTPYgVRpQ</t>
         </is>
       </c>
       <c r="G609" t="inlineStr"/>
@@ -39437,7 +39430,7 @@
       <c r="J609" t="inlineStr"/>
       <c r="K609" t="inlineStr">
         <is>
-          <t>https://x.com/Expedia/status/2104345339062804868</t>
+          <t>https://x.com/Expedia/status/2104315142586401023</t>
         </is>
       </c>
       <c r="L609" t="inlineStr">
@@ -39452,12 +39445,12 @@
       </c>
       <c r="N609" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="O609" t="inlineStr">
         <is>
-          <t>Expedia is promoting the final days of its Anniversary Sale in Australia, offering up to 30% off selected hotels and holiday homes, plus AU$45 OneKeyCash for flight bookings until October 7, 2026.</t>
+          <t>Expedia is promoting the final days of its Anniversary Sale in New Zealand, offering up to 30% off selected hotels and holiday homes, plus NZ$50 OneKeyCash for flight bookings.</t>
         </is>
       </c>
     </row>
@@ -39474,83 +39467,20 @@
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>X (Twitter)</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>Expedia</t>
+          <t>Kaya Yurieff</t>
         </is>
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>Sun Sep 27 21:00:00 +0000 2026</t>
+          <t>2026-09-28T16:20:01.018Z</t>
         </is>
       </c>
       <c r="F610" t="inlineStr">
-        <is>
-          <t>We're in the final days of the Anniversary Sale, New Zealand!
-Celebrate with Member Prices of up to 30% off selected hotels and holiday homes. Plus, get NZ$50 in OneKeyCash™ when you book a flight by 5 Oct. Sale ends 7/10/26. Terms apply. 
- Book now: https://t.co/SJTPYgVRpQ</t>
-        </is>
-      </c>
-      <c r="G610" t="inlineStr"/>
-      <c r="H610" t="inlineStr"/>
-      <c r="I610" t="inlineStr"/>
-      <c r="J610" t="inlineStr"/>
-      <c r="K610" t="inlineStr">
-        <is>
-          <t>https://x.com/Expedia/status/2104315142586401023</t>
-        </is>
-      </c>
-      <c r="L610" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="M610" t="inlineStr">
-        <is>
-          <t>Product Announcement</t>
-        </is>
-      </c>
-      <c r="N610" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="O610" t="inlineStr">
-        <is>
-          <t>Expedia is promoting the final days of its Anniversary Sale in New Zealand, offering up to 30% off selected hotels and holiday homes, plus NZ$50 OneKeyCash for flight bookings until October 7, 2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="611">
-      <c r="A611" t="inlineStr">
-        <is>
-          <t>Abhee</t>
-        </is>
-      </c>
-      <c r="B611" t="inlineStr">
-        <is>
-          <t>Expedia</t>
-        </is>
-      </c>
-      <c r="C611" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="D611" t="inlineStr">
-        <is>
-          <t>Kaya Yurieff</t>
-        </is>
-      </c>
-      <c r="E611" t="inlineStr">
-        <is>
-          <t>2026-09-28T16:20:01.018Z</t>
-        </is>
-      </c>
-      <c r="F611" t="inlineStr">
         <is>
           <t>Livestreaming is scary territory for most brands. It's unpredictable, and it means giving up a ton of control. 
 Expedia decided to go all in anyway. 
@@ -39563,63 +39493,63 @@
 Read more here: https://lnkd.in/eDJWhUbq</t>
         </is>
       </c>
-      <c r="G611" t="inlineStr"/>
-      <c r="H611" t="inlineStr"/>
-      <c r="I611" t="inlineStr"/>
-      <c r="J611" t="inlineStr"/>
-      <c r="K611" t="inlineStr">
+      <c r="G610" t="inlineStr"/>
+      <c r="H610" t="inlineStr"/>
+      <c r="I610" t="inlineStr"/>
+      <c r="J610" t="inlineStr"/>
+      <c r="K610" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/posts/kayayurieff_the-numbers-behind-expedias-ishowspeed-partnership-activity-7510330086374567937-Pzim</t>
         </is>
       </c>
-      <c r="L611" t="inlineStr">
+      <c r="L610" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="M611" t="inlineStr">
+      <c r="M610" t="inlineStr">
         <is>
           <t>Partnership and Acquisitions</t>
         </is>
       </c>
-      <c r="N611" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="O611" t="inlineStr">
-        <is>
-          <t>Expedia launched a year‑long partnership with streamer IShowSpeed, achieving a 400‑million‑viewer livestream that spiked destination searches and is now shifting focus toward bookings and experiences.</t>
-        </is>
-      </c>
-    </row>
-    <row r="612">
-      <c r="A612" t="inlineStr">
-        <is>
-          <t>Abhee</t>
-        </is>
-      </c>
-      <c r="B612" t="inlineStr">
+      <c r="N610" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O610" t="inlineStr">
+        <is>
+          <t>Expedia partnered with streamer IShowSpeed for a high‑profile livestream that reached over 400 million viewers and boosted destination searches, with future phases aimed at driving bookings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
         <is>
           <t>Booking.com</t>
         </is>
       </c>
-      <c r="C612" t="inlineStr">
-        <is>
-          <t>X (Twitter)</t>
-        </is>
-      </c>
-      <c r="D612" t="inlineStr">
-        <is>
-          <t>bookingcom</t>
-        </is>
-      </c>
-      <c r="E612" t="inlineStr">
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
         <is>
           <t>Mon Sep 28 13:45:11 +0000 2026</t>
         </is>
       </c>
-      <c r="F612" t="inlineStr">
+      <c r="F611" t="inlineStr">
         <is>
           <t>Ciao Giorgio, ci dispiace leggere che non riesci a parlare con il nostro servizio clienti.
 Come possiamo aiutarti? Se la tua richiesta riguarda una prenotazione di una struttura, inviaci un messaggio privato con i seguenti dati e ti risponderemo il prima possibile:
@@ -39630,13 +39560,74 @@
 Al momento, tramite social media offriamo assistenza solo per prenotazioni di strutture. Per domande su Voli, Taxi o Assicurazione, puoi contattare i team dedicati qui: https://t.co/OVuF5pCzba.</t>
         </is>
       </c>
+      <c r="G611" t="inlineStr"/>
+      <c r="H611" t="inlineStr"/>
+      <c r="I611" t="inlineStr"/>
+      <c r="J611" t="inlineStr"/>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2104568101765337403</t>
+        </is>
+      </c>
+      <c r="L611" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M611" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N611" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O611" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint about difficulty contacting customer service, offering a private message with booking details for assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>Mon Sep 28 13:20:46 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>@JesusGThomas Hola Jesús, hemos respondido a tu DM.</t>
+        </is>
+      </c>
       <c r="G612" t="inlineStr"/>
       <c r="H612" t="inlineStr"/>
       <c r="I612" t="inlineStr"/>
       <c r="J612" t="inlineStr"/>
       <c r="K612" t="inlineStr">
         <is>
-          <t>https://x.com/bookingcom/status/2104568101765337403</t>
+          <t>https://x.com/bookingcom/status/2104561958531878972</t>
         </is>
       </c>
       <c r="L612" t="inlineStr">
@@ -39656,7 +39647,7 @@
       </c>
       <c r="O612" t="inlineStr">
         <is>
-          <t>Booking.com responds to a customer complaint about difficulty reaching customer service, offering private messaging with booking details and directing other inquiries to dedicated teams.</t>
+          <t>Booking.com replied to a direct message from user @JesusGThomas, acknowledging receipt of the DM.</t>
         </is>
       </c>
     </row>
@@ -39683,12 +39674,14 @@
       </c>
       <c r="E613" t="inlineStr">
         <is>
-          <t>Mon Sep 28 13:20:46 +0000 2026</t>
+          <t>Mon Sep 28 12:46:22 +0000 2026</t>
         </is>
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>@JesusGThomas Hola Jesús, hemos respondido a tu DM.</t>
+          <t>@Rifton926 Hello, thanks for contacting us.
+We regret hearing you had to go to the hospital.
+Our social media team can take a look at your booking, we have replied to your DM requesting further information from you. https://t.co/Z89AAoEgD7</t>
         </is>
       </c>
       <c r="G613" t="inlineStr"/>
@@ -39697,12 +39690,12 @@
       <c r="J613" t="inlineStr"/>
       <c r="K613" t="inlineStr">
         <is>
-          <t>https://x.com/bookingcom/status/2104561958531878972</t>
+          <t>https://x.com/bookingcom/status/2104553301681340604</t>
         </is>
       </c>
       <c r="L613" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="M613" t="inlineStr">
@@ -39717,7 +39710,7 @@
       </c>
       <c r="O613" t="inlineStr">
         <is>
-          <t>Booking.com replied to a private message from user @JesusGThomas, confirming that they have responded to the DM.</t>
+          <t>Booking.com responds to a user who had a negative experience requiring hospitalization, offering to review the booking and request more information.</t>
         </is>
       </c>
     </row>
@@ -39744,14 +39737,12 @@
       </c>
       <c r="E614" t="inlineStr">
         <is>
-          <t>Mon Sep 28 12:46:22 +0000 2026</t>
+          <t>Mon Sep 28 12:36:42 +0000 2026</t>
         </is>
       </c>
       <c r="F614" t="inlineStr">
         <is>
-          <t>@Rifton926 Hello, thanks for contacting us.
-We regret hearing you had to go to the hospital.
-Our social media team can take a look at your booking, we have replied to your DM requesting further information from you. https://t.co/Z89AAoEgD7</t>
+          <t>Hi Yunus, please note that this email address does not belong to us. Additionally, we're helping you already through another via, we kindly ask your patience and cooperation as writing us through different channels will not change either speed up our possibilities to help. Thanks for understanding.</t>
         </is>
       </c>
       <c r="G614" t="inlineStr"/>
@@ -39760,7 +39751,7 @@
       <c r="J614" t="inlineStr"/>
       <c r="K614" t="inlineStr">
         <is>
-          <t>https://x.com/bookingcom/status/2104553301681340604</t>
+          <t>https://x.com/bookingcom/status/2104550868276109488</t>
         </is>
       </c>
       <c r="L614" t="inlineStr">
@@ -39780,7 +39771,7 @@
       </c>
       <c r="O614" t="inlineStr">
         <is>
-          <t>Booking.com replied to a user’s complaint about a hospital visit related to a booking, offering to investigate and requesting further information.</t>
+          <t>Booking.com responds to a user, clarifying that the email address is not theirs and advising patience while they are already assisting through another channel.</t>
         </is>
       </c>
     </row>
@@ -39807,71 +39798,10 @@
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>Mon Sep 28 12:36:42 +0000 2026</t>
+          <t>Mon Sep 28 11:58:24 +0000 2026</t>
         </is>
       </c>
       <c r="F615" t="inlineStr">
-        <is>
-          <t>Hi Yunus, please note that this email address does not belong to us. Additionally, we're helping you already through another via, we kindly ask your patience and cooperation as writing us through different channels will not change either speed up our possibilities to help. Thanks for understanding.</t>
-        </is>
-      </c>
-      <c r="G615" t="inlineStr"/>
-      <c r="H615" t="inlineStr"/>
-      <c r="I615" t="inlineStr"/>
-      <c r="J615" t="inlineStr"/>
-      <c r="K615" t="inlineStr">
-        <is>
-          <t>https://x.com/bookingcom/status/2104550868276109488</t>
-        </is>
-      </c>
-      <c r="L615" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="M615" t="inlineStr">
-        <is>
-          <t>General Industry News</t>
-        </is>
-      </c>
-      <c r="N615" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="O615" t="inlineStr">
-        <is>
-          <t>Booking.com responds to a customer inquiry, clarifying that the email address is not theirs and advising patience.</t>
-        </is>
-      </c>
-    </row>
-    <row r="616">
-      <c r="A616" t="inlineStr">
-        <is>
-          <t>Abhee</t>
-        </is>
-      </c>
-      <c r="B616" t="inlineStr">
-        <is>
-          <t>Booking.com</t>
-        </is>
-      </c>
-      <c r="C616" t="inlineStr">
-        <is>
-          <t>X (Twitter)</t>
-        </is>
-      </c>
-      <c r="D616" t="inlineStr">
-        <is>
-          <t>bookingcom</t>
-        </is>
-      </c>
-      <c r="E616" t="inlineStr">
-        <is>
-          <t>Mon Sep 28 11:58:24 +0000 2026</t>
-        </is>
-      </c>
-      <c r="F616" t="inlineStr">
         <is>
           <t>Hola Andrés, gracias por contactarnos. Lamentamos tu experiencia y esperamos que hayas podido comunicar cualquier inconveniente directamente con el alojamiento mientras estabas allí, ya que son quienes están en mejor posición para abordar y resolver cualquier incidencia.
 Si deseas que revisemos tu reserva desde aquí, por favor envíanos un mensaje privado con la siguiente información:
@@ -39882,13 +39812,74 @@
 Te responderemos lo antes posible. Como alternativa, para recibir ayuda inmediata siempre puedes llamarnos aquí: https://t.co/o8QyR8SaDb. Un saludo.</t>
         </is>
       </c>
+      <c r="G615" t="inlineStr"/>
+      <c r="H615" t="inlineStr"/>
+      <c r="I615" t="inlineStr"/>
+      <c r="J615" t="inlineStr"/>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2104541229962711268</t>
+        </is>
+      </c>
+      <c r="L615" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M615" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N615" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O615" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint on X, offering to review the reservation and providing contact options for further assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>Mon Sep 28 11:30:31 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>Hola Iván, premios y bonificaciones no son acumulables. También toma en cuenta que algunos alojamientos muestran sus descuentos Genius para clientes con reservas directas, y no mediante terceros. Si tienes alguna consulta en concreto puedes enviarnos los detalles por privado y con gusto lo revisamos.</t>
+        </is>
+      </c>
       <c r="G616" t="inlineStr"/>
       <c r="H616" t="inlineStr"/>
       <c r="I616" t="inlineStr"/>
       <c r="J616" t="inlineStr"/>
       <c r="K616" t="inlineStr">
         <is>
-          <t>https://x.com/bookingcom/status/2104541229962711268</t>
+          <t>https://x.com/bookingcom/status/2104534211910664268</t>
         </is>
       </c>
       <c r="L616" t="inlineStr">
@@ -39908,7 +39899,7 @@
       </c>
       <c r="O616" t="inlineStr">
         <is>
-          <t>Booking.com responds to a customer complaint, offering to review the reservation and providing contact details for assistance.</t>
+          <t>Booking.com clarifies that rewards and bonuses are not cumulative and that Genius discounts apply only to direct bookings, offering to review specific queries privately.</t>
         </is>
       </c>
     </row>
@@ -39935,12 +39926,12 @@
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>Mon Sep 28 11:30:31 +0000 2026</t>
+          <t>Mon Sep 28 10:43:59 +0000 2026</t>
         </is>
       </c>
       <c r="F617" t="inlineStr">
         <is>
-          <t>Hola Iván, premios y bonificaciones no son acumulables. También toma en cuenta que algunos alojamientos muestran sus descuentos Genius para clientes con reservas directas, y no mediante terceros. Si tienes alguna consulta en concreto puedes enviarnos los detalles por privado y con gusto lo revisamos.</t>
+          <t>@KeshavP03213345 Hi there, we didn't receive any of the details which we have previously requested. Once you have shared everything via DM, we will get back to you as soon as possible. https://t.co/Z89AAoEgD7</t>
         </is>
       </c>
       <c r="G617" t="inlineStr"/>
@@ -39949,7 +39940,7 @@
       <c r="J617" t="inlineStr"/>
       <c r="K617" t="inlineStr">
         <is>
-          <t>https://x.com/bookingcom/status/2104534211910664268</t>
+          <t>https://x.com/bookingcom/status/2104522504337256523</t>
         </is>
       </c>
       <c r="L617" t="inlineStr">
@@ -39969,7 +39960,7 @@
       </c>
       <c r="O617" t="inlineStr">
         <is>
-          <t>Booking.com clarifies that bonuses and Genius discounts are not cumulative and are only available for direct bookings, offering to review specific queries privately.</t>
+          <t>Booking.com is replying to a user, noting that it has not received requested details and will respond once the user shares the information via DM.</t>
         </is>
       </c>
     </row>
@@ -39996,71 +39987,10 @@
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>Mon Sep 28 10:43:59 +0000 2026</t>
+          <t>Mon Sep 28 10:33:56 +0000 2026</t>
         </is>
       </c>
       <c r="F618" t="inlineStr">
-        <is>
-          <t>@KeshavP03213345 Hi there, we didn't receive any of the details which we have previously requested. Once you have shared everything via DM, we will get back to you as soon as possible. https://t.co/Z89AAoEgD7</t>
-        </is>
-      </c>
-      <c r="G618" t="inlineStr"/>
-      <c r="H618" t="inlineStr"/>
-      <c r="I618" t="inlineStr"/>
-      <c r="J618" t="inlineStr"/>
-      <c r="K618" t="inlineStr">
-        <is>
-          <t>https://x.com/bookingcom/status/2104522504337256523</t>
-        </is>
-      </c>
-      <c r="L618" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="M618" t="inlineStr">
-        <is>
-          <t>General Industry News</t>
-        </is>
-      </c>
-      <c r="N618" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="O618" t="inlineStr">
-        <is>
-          <t>Booking.com is replying to a user, noting that it has not received the requested details and will respond once the user shares the information via DM.</t>
-        </is>
-      </c>
-    </row>
-    <row r="619">
-      <c r="A619" t="inlineStr">
-        <is>
-          <t>Abhee</t>
-        </is>
-      </c>
-      <c r="B619" t="inlineStr">
-        <is>
-          <t>Booking.com</t>
-        </is>
-      </c>
-      <c r="C619" t="inlineStr">
-        <is>
-          <t>X (Twitter)</t>
-        </is>
-      </c>
-      <c r="D619" t="inlineStr">
-        <is>
-          <t>bookingcom</t>
-        </is>
-      </c>
-      <c r="E619" t="inlineStr">
-        <is>
-          <t>Mon Sep 28 10:33:56 +0000 2026</t>
-        </is>
-      </c>
-      <c r="F619" t="inlineStr">
         <is>
           <t>Hola, Angelina. Lamentamos lo ocurrido y los inconvenientes que esta situación te haya podido ocasionar. Para poder ayudarte lo antes posible, envíanos un mensaje privado con los siguientes datos: 
 - Número de confirmación: 
@@ -40070,18 +40000,79 @@
 Un saludo.</t>
         </is>
       </c>
+      <c r="G618" t="inlineStr"/>
+      <c r="H618" t="inlineStr"/>
+      <c r="I618" t="inlineStr"/>
+      <c r="J618" t="inlineStr"/>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2104519975490695612</t>
+        </is>
+      </c>
+      <c r="L618" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M618" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N618" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O618" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes to a customer for a problem and offers private messaging or phone support to resolve the issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>Mon Sep 28 10:17:38 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>@ShevaMafia13 Hi Volodymyr, we have just replied to your private message regarding this. Please check it. Thank you.</t>
+        </is>
+      </c>
       <c r="G619" t="inlineStr"/>
       <c r="H619" t="inlineStr"/>
       <c r="I619" t="inlineStr"/>
       <c r="J619" t="inlineStr"/>
       <c r="K619" t="inlineStr">
         <is>
-          <t>https://x.com/bookingcom/status/2104519975490695612</t>
+          <t>https://x.com/bookingcom/status/2104515873855680546</t>
         </is>
       </c>
       <c r="L619" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="M619" t="inlineStr">
@@ -40096,7 +40087,7 @@
       </c>
       <c r="O619" t="inlineStr">
         <is>
-          <t>Booking.com apologizes to a customer for an issue and provides instructions for contacting support via private message or phone.</t>
+          <t>Booking.com replied to a private message from user @ShevaMafia13, indicating they have responded to a query or issue.</t>
         </is>
       </c>
     </row>
@@ -40123,71 +40114,10 @@
       </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>Mon Sep 28 10:17:38 +0000 2026</t>
+          <t>Mon Sep 28 09:48:41 +0000 2026</t>
         </is>
       </c>
       <c r="F620" t="inlineStr">
-        <is>
-          <t>@ShevaMafia13 Hi Volodymyr, we have just replied to your private message regarding this. Please check it. Thank you.</t>
-        </is>
-      </c>
-      <c r="G620" t="inlineStr"/>
-      <c r="H620" t="inlineStr"/>
-      <c r="I620" t="inlineStr"/>
-      <c r="J620" t="inlineStr"/>
-      <c r="K620" t="inlineStr">
-        <is>
-          <t>https://x.com/bookingcom/status/2104515873855680546</t>
-        </is>
-      </c>
-      <c r="L620" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="M620" t="inlineStr">
-        <is>
-          <t>General Industry News</t>
-        </is>
-      </c>
-      <c r="N620" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="O620" t="inlineStr">
-        <is>
-          <t>Booking.com replied to a private message from user @ShevaMafia13, indicating a response to an inquiry.</t>
-        </is>
-      </c>
-    </row>
-    <row r="621">
-      <c r="A621" t="inlineStr">
-        <is>
-          <t>Abhee</t>
-        </is>
-      </c>
-      <c r="B621" t="inlineStr">
-        <is>
-          <t>Booking.com</t>
-        </is>
-      </c>
-      <c r="C621" t="inlineStr">
-        <is>
-          <t>X (Twitter)</t>
-        </is>
-      </c>
-      <c r="D621" t="inlineStr">
-        <is>
-          <t>bookingcom</t>
-        </is>
-      </c>
-      <c r="E621" t="inlineStr">
-        <is>
-          <t>Mon Sep 28 09:48:41 +0000 2026</t>
-        </is>
-      </c>
-      <c r="F621" t="inlineStr">
         <is>
           <t>Hi Ashok, thanks for contacting us.
 Please let us know why you rejected the room. If your booking was nonrefundable, the accommodation would have the right to charge you accordingly. 
@@ -40197,13 +40127,78 @@
 and we will get back to you as soon as possible.</t>
         </is>
       </c>
+      <c r="G620" t="inlineStr"/>
+      <c r="H620" t="inlineStr"/>
+      <c r="I620" t="inlineStr"/>
+      <c r="J620" t="inlineStr"/>
+      <c r="K620" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2104508586097353065</t>
+        </is>
+      </c>
+      <c r="L620" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M620" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N620" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O620" t="inlineStr">
+        <is>
+          <t>Booking.com is responding to a customer inquiry about a rejected room, offering to review the booking if the customer provides additional details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>Mon Sep 28 09:36:53 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>Hi there, we would like to help you. However, we need to have more information regarding your reservation, and in our previous message, we asked for more details, so we can check it for you. 
+Please send us a Private message with the following details, and we'll get back to you as soon as possible:
+- Confirmation number:
+- Pin code:
+- Guest name on the reservation:</t>
+        </is>
+      </c>
       <c r="G621" t="inlineStr"/>
       <c r="H621" t="inlineStr"/>
       <c r="I621" t="inlineStr"/>
       <c r="J621" t="inlineStr"/>
       <c r="K621" t="inlineStr">
         <is>
-          <t>https://x.com/bookingcom/status/2104508586097353065</t>
+          <t>https://x.com/bookingcom/status/2104505616756510957</t>
         </is>
       </c>
       <c r="L621" t="inlineStr">
@@ -40223,7 +40218,7 @@
       </c>
       <c r="O621" t="inlineStr">
         <is>
-          <t>Booking.com is responding to a customer inquiry about a rejected booking, requesting details for review.</t>
+          <t>Booking.com requests additional reservation details from a customer via private message.</t>
         </is>
       </c>
     </row>
@@ -40250,75 +40245,10 @@
       </c>
       <c r="E622" t="inlineStr">
         <is>
-          <t>Mon Sep 28 09:36:53 +0000 2026</t>
+          <t>Mon Sep 28 09:19:14 +0000 2026</t>
         </is>
       </c>
       <c r="F622" t="inlineStr">
-        <is>
-          <t>Hi there, we would like to help you. However, we need to have more information regarding your reservation, and in our previous message, we asked for more details, so we can check it for you. 
-Please send us a Private message with the following details, and we'll get back to you as soon as possible:
-- Confirmation number:
-- Pin code:
-- Guest name on the reservation:</t>
-        </is>
-      </c>
-      <c r="G622" t="inlineStr"/>
-      <c r="H622" t="inlineStr"/>
-      <c r="I622" t="inlineStr"/>
-      <c r="J622" t="inlineStr"/>
-      <c r="K622" t="inlineStr">
-        <is>
-          <t>https://x.com/bookingcom/status/2104505616756510957</t>
-        </is>
-      </c>
-      <c r="L622" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="M622" t="inlineStr">
-        <is>
-          <t>General Industry News</t>
-        </is>
-      </c>
-      <c r="N622" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="O622" t="inlineStr">
-        <is>
-          <t>Booking.com is requesting additional reservation details from a customer via private message to verify and assist with their booking.</t>
-        </is>
-      </c>
-    </row>
-    <row r="623">
-      <c r="A623" t="inlineStr">
-        <is>
-          <t>Abhee</t>
-        </is>
-      </c>
-      <c r="B623" t="inlineStr">
-        <is>
-          <t>Booking.com</t>
-        </is>
-      </c>
-      <c r="C623" t="inlineStr">
-        <is>
-          <t>X (Twitter)</t>
-        </is>
-      </c>
-      <c r="D623" t="inlineStr">
-        <is>
-          <t>bookingcom</t>
-        </is>
-      </c>
-      <c r="E623" t="inlineStr">
-        <is>
-          <t>Mon Sep 28 09:19:14 +0000 2026</t>
-        </is>
-      </c>
-      <c r="F623" t="inlineStr">
         <is>
           <t>Hola, agradecemos tu mensaje. 
 No tenemos información precisa sobre lo sucedido con tu reserva, sin embargo, nos gustaría revisarlo para brindarte una respuesta y determinar cómo podemos ayudarte.
@@ -40330,13 +40260,74 @@
 Saludos.</t>
         </is>
       </c>
+      <c r="G622" t="inlineStr"/>
+      <c r="H622" t="inlineStr"/>
+      <c r="I622" t="inlineStr"/>
+      <c r="J622" t="inlineStr"/>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2104501174208532651</t>
+        </is>
+      </c>
+      <c r="L622" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M622" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N622" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O622" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user inquiry about a reservation, requesting confirmation details and offering further assistance via private message or 24/7 customer support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>Mon Sep 28 09:18:54 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>@PrachiChitlang1 Hi Prachi, we replied with further information via private message. Kindly note we're unable to provide any information about your case via public messages. Thank you.</t>
+        </is>
+      </c>
       <c r="G623" t="inlineStr"/>
       <c r="H623" t="inlineStr"/>
       <c r="I623" t="inlineStr"/>
       <c r="J623" t="inlineStr"/>
       <c r="K623" t="inlineStr">
         <is>
-          <t>https://x.com/bookingcom/status/2104501174208532651</t>
+          <t>https://x.com/bookingcom/status/2104501091245133955</t>
         </is>
       </c>
       <c r="L623" t="inlineStr">
@@ -40356,7 +40347,7 @@
       </c>
       <c r="O623" t="inlineStr">
         <is>
-          <t>Booking.com responds to a user’s reservation issue, requesting confirmation details and offering 24/7 customer support.</t>
+          <t>Booking.com replied to a user via private message, stating they cannot share case details publicly.</t>
         </is>
       </c>
     </row>
@@ -40383,71 +40374,10 @@
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>Mon Sep 28 09:18:54 +0000 2026</t>
+          <t>Mon Sep 28 08:11:50 +0000 2026</t>
         </is>
       </c>
       <c r="F624" t="inlineStr">
-        <is>
-          <t>@PrachiChitlang1 Hi Prachi, we replied with further information via private message. Kindly note we're unable to provide any information about your case via public messages. Thank you.</t>
-        </is>
-      </c>
-      <c r="G624" t="inlineStr"/>
-      <c r="H624" t="inlineStr"/>
-      <c r="I624" t="inlineStr"/>
-      <c r="J624" t="inlineStr"/>
-      <c r="K624" t="inlineStr">
-        <is>
-          <t>https://x.com/bookingcom/status/2104501091245133955</t>
-        </is>
-      </c>
-      <c r="L624" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="M624" t="inlineStr">
-        <is>
-          <t>General Industry News</t>
-        </is>
-      </c>
-      <c r="N624" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="O624" t="inlineStr">
-        <is>
-          <t>Booking.com replied to a user privately, stating they cannot share case details publicly.</t>
-        </is>
-      </c>
-    </row>
-    <row r="625">
-      <c r="A625" t="inlineStr">
-        <is>
-          <t>Abhee</t>
-        </is>
-      </c>
-      <c r="B625" t="inlineStr">
-        <is>
-          <t>Booking.com</t>
-        </is>
-      </c>
-      <c r="C625" t="inlineStr">
-        <is>
-          <t>X (Twitter)</t>
-        </is>
-      </c>
-      <c r="D625" t="inlineStr">
-        <is>
-          <t>bookingcom</t>
-        </is>
-      </c>
-      <c r="E625" t="inlineStr">
-        <is>
-          <t>Mon Sep 28 08:11:50 +0000 2026</t>
-        </is>
-      </c>
-      <c r="F625" t="inlineStr">
         <is>
           <t>Lamentamos la percepción que tienes sobre nuestros servicios y cualquier inconveniente que estés atravesando. Cuéntanos, ¿en qué podemos ayudarte? Si tu consulta está relacionada con una reserva de alojamiento, envíanos un mensaje privado con los siguientes datos y te responderemos lo antes posible: 
 - Número de confirmación: 
@@ -40458,13 +40388,78 @@
 Un saludo.</t>
         </is>
       </c>
+      <c r="G624" t="inlineStr"/>
+      <c r="H624" t="inlineStr"/>
+      <c r="I624" t="inlineStr"/>
+      <c r="J624" t="inlineStr"/>
+      <c r="K624" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2104484214267605338</t>
+        </is>
+      </c>
+      <c r="L624" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M624" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N624" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O624" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint, offering assistance via private message and providing 24/7 customer support contact details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>Mon Sep 28 07:29:17 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>Oi Leonora, lamentamos saber que encontrou percevejos no hotel. Se precisar de assistência, por favor, nos envie uma mensagem privada com: 
+- Nome do hóspede na reserva: 
+- Número de confirmação: 
+- Código PIN: 
+Retornaremos com a maior brevidade possível. Para suporte imediato, ligue para nossa equipe de Apoio ao Cliente por aqui: https://t.co/tuuNbmGVaG.</t>
+        </is>
+      </c>
       <c r="G625" t="inlineStr"/>
       <c r="H625" t="inlineStr"/>
       <c r="I625" t="inlineStr"/>
       <c r="J625" t="inlineStr"/>
       <c r="K625" t="inlineStr">
         <is>
-          <t>https://x.com/bookingcom/status/2104484214267605338</t>
+          <t>https://x.com/bookingcom/status/2104473503030284657</t>
         </is>
       </c>
       <c r="L625" t="inlineStr">
@@ -40484,7 +40479,7 @@
       </c>
       <c r="O625" t="inlineStr">
         <is>
-          <t>Booking.com apologizes for any negative perception and offers assistance with accommodation reservations, providing contact details for immediate help.</t>
+          <t>Booking.com responds to a customer complaint about bedbugs, offering assistance and contact details.</t>
         </is>
       </c>
     </row>
@@ -40511,16 +40506,12 @@
       </c>
       <c r="E626" t="inlineStr">
         <is>
-          <t>Mon Sep 28 07:29:17 +0000 2026</t>
+          <t>Mon Sep 28 07:27:53 +0000 2026</t>
         </is>
       </c>
       <c r="F626" t="inlineStr">
         <is>
-          <t>Oi Leonora, lamentamos saber que encontrou percevejos no hotel. Se precisar de assistência, por favor, nos envie uma mensagem privada com: 
-- Nome do hóspede na reserva: 
-- Número de confirmação: 
-- Código PIN: 
-Retornaremos com a maior brevidade possível. Para suporte imediato, ligue para nossa equipe de Apoio ao Cliente por aqui: https://t.co/tuuNbmGVaG.</t>
+          <t>@Iba_Banfield Hola, Gabriel. Te hemos enviado un mensaje privado con novedades sobre tu solicitud. Cuando puedas, revísalo. Un saludo. https://t.co/Z89AAoEgD7</t>
         </is>
       </c>
       <c r="G626" t="inlineStr"/>
@@ -40529,7 +40520,7 @@
       <c r="J626" t="inlineStr"/>
       <c r="K626" t="inlineStr">
         <is>
-          <t>https://x.com/bookingcom/status/2104473503030284657</t>
+          <t>https://x.com/bookingcom/status/2104473154563285004</t>
         </is>
       </c>
       <c r="L626" t="inlineStr">
@@ -40544,12 +40535,12 @@
       </c>
       <c r="N626" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="O626" t="inlineStr">
         <is>
-          <t>Booking.com addresses a guest complaint about bedbugs, offering assistance and contact details for resolution.</t>
+          <t>Booking.com informs a user that they have sent a private message with updates on their request.</t>
         </is>
       </c>
     </row>
@@ -40576,71 +40567,10 @@
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>Mon Sep 28 07:27:53 +0000 2026</t>
+          <t>Mon Sep 28 07:03:26 +0000 2026</t>
         </is>
       </c>
       <c r="F627" t="inlineStr">
-        <is>
-          <t>@Iba_Banfield Hola, Gabriel. Te hemos enviado un mensaje privado con novedades sobre tu solicitud. Cuando puedas, revísalo. Un saludo. https://t.co/Z89AAoEgD7</t>
-        </is>
-      </c>
-      <c r="G627" t="inlineStr"/>
-      <c r="H627" t="inlineStr"/>
-      <c r="I627" t="inlineStr"/>
-      <c r="J627" t="inlineStr"/>
-      <c r="K627" t="inlineStr">
-        <is>
-          <t>https://x.com/bookingcom/status/2104473154563285004</t>
-        </is>
-      </c>
-      <c r="L627" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="M627" t="inlineStr">
-        <is>
-          <t>General Industry News</t>
-        </is>
-      </c>
-      <c r="N627" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="O627" t="inlineStr">
-        <is>
-          <t>Booking.com informs a user that they have sent a private message with updates regarding the user's request.</t>
-        </is>
-      </c>
-    </row>
-    <row r="628">
-      <c r="A628" t="inlineStr">
-        <is>
-          <t>Abhee</t>
-        </is>
-      </c>
-      <c r="B628" t="inlineStr">
-        <is>
-          <t>Booking.com</t>
-        </is>
-      </c>
-      <c r="C628" t="inlineStr">
-        <is>
-          <t>X (Twitter)</t>
-        </is>
-      </c>
-      <c r="D628" t="inlineStr">
-        <is>
-          <t>bookingcom</t>
-        </is>
-      </c>
-      <c r="E628" t="inlineStr">
-        <is>
-          <t>Mon Sep 28 07:03:26 +0000 2026</t>
-        </is>
-      </c>
-      <c r="F628" t="inlineStr">
         <is>
           <t>Hi there, we regret to hear about your experience. If the final outcome has alreaby been provided we might not be able to change it but we would like to look into this for you. Feel free to DM us the following details and we'll get back to you as soon as possible: 
 - Confirmation number:
@@ -40651,13 +40581,76 @@
 Kind regards.</t>
         </is>
       </c>
+      <c r="G627" t="inlineStr"/>
+      <c r="H627" t="inlineStr"/>
+      <c r="I627" t="inlineStr"/>
+      <c r="J627" t="inlineStr"/>
+      <c r="K627" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2104466997870207033</t>
+        </is>
+      </c>
+      <c r="L627" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M627" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N627" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O627" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint on X, offering to review the issue and directing the user to provide details for further assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>Mon Sep 28 06:58:40 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>Hi Sunny, we regret to hear that you're still waiting for an outcome from us. We will be happy to look into this for you further and see how we can help via this channel, kindly send us a DM with the following information, and we'll get back to you with our findings. 
+- Pin code,
+- Name on the reservation.</t>
+        </is>
+      </c>
       <c r="G628" t="inlineStr"/>
       <c r="H628" t="inlineStr"/>
       <c r="I628" t="inlineStr"/>
       <c r="J628" t="inlineStr"/>
       <c r="K628" t="inlineStr">
         <is>
-          <t>https://x.com/bookingcom/status/2104466997870207033</t>
+          <t>https://x.com/bookingcom/status/2104465798387437699</t>
         </is>
       </c>
       <c r="L628" t="inlineStr">
@@ -40677,7 +40670,7 @@
       </c>
       <c r="O628" t="inlineStr">
         <is>
-          <t>Booking.com responds to a customer complaint, offering to investigate the issue and providing contact details for further assistance.</t>
+          <t>Booking.com is responding to a customer complaint via direct message, offering to investigate the issue and request additional information.</t>
         </is>
       </c>
     </row>
@@ -40704,14 +40697,13 @@
       </c>
       <c r="E629" t="inlineStr">
         <is>
-          <t>Mon Sep 28 06:58:40 +0000 2026</t>
+          <t>Mon Sep 28 06:21:22 +0000 2026</t>
         </is>
       </c>
       <c r="F629" t="inlineStr">
         <is>
-          <t>Hi Sunny, we regret to hear that you're still waiting for an outcome from us. We will be happy to look into this for you further and see how we can help via this channel, kindly send us a DM with the following information, and we'll get back to you with our findings. 
-- Pin code,
-- Name on the reservation.</t>
+          <t>Hi there, thanks for flagging this. We regret to hear about this experience. As part of our mission to make it easier for everyone to experience the world, we’re committed to doing everything we can to eliminate all forms of unlawful bias, discrimination, intolerance, harassment and abuse from our platforms. 
+Please send us a DM with more information so we can learn what has been done so far and see how are able to assist further.</t>
         </is>
       </c>
       <c r="G629" t="inlineStr"/>
@@ -40720,12 +40712,12 @@
       <c r="J629" t="inlineStr"/>
       <c r="K629" t="inlineStr">
         <is>
-          <t>https://x.com/bookingcom/status/2104465798387437699</t>
+          <t>https://x.com/bookingcom/status/2104456412684333549</t>
         </is>
       </c>
       <c r="L629" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M629" t="inlineStr">
@@ -40740,7 +40732,7 @@
       </c>
       <c r="O629" t="inlineStr">
         <is>
-          <t>Booking.com responds to a customer complaint, offering to investigate via DM.</t>
+          <t>Booking.com apologizes for a user’s negative experience related to bias and invites the user to provide more details via DM to address the issue.</t>
         </is>
       </c>
     </row>
@@ -40767,13 +40759,12 @@
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>Mon Sep 28 06:21:22 +0000 2026</t>
+          <t>Mon Sep 28 01:56:07 +0000 2026</t>
         </is>
       </c>
       <c r="F630" t="inlineStr">
         <is>
-          <t>Hi there, thanks for flagging this. We regret to hear about this experience. As part of our mission to make it easier for everyone to experience the world, we’re committed to doing everything we can to eliminate all forms of unlawful bias, discrimination, intolerance, harassment and abuse from our platforms. 
-Please send us a DM with more information so we can learn what has been done so far and see how are able to assist further.</t>
+          <t>Hi Yunus, we understand your disappointment and acknowledge that you have removed your personal information from X (Twitter). We can see that you've also contacted us on Instagram, and we've replied to your message there. Please review it at your earliest convenience and reply directly there if you have any additional questions. In the future, we would recommend reaching out via one platform only; this removes any confusion or delays by having two active conversations across platforms.</t>
         </is>
       </c>
       <c r="G630" t="inlineStr"/>
@@ -40782,7 +40773,7 @@
       <c r="J630" t="inlineStr"/>
       <c r="K630" t="inlineStr">
         <is>
-          <t>https://x.com/bookingcom/status/2104456412684333549</t>
+          <t>https://x.com/bookingcom/status/2104389659929223179</t>
         </is>
       </c>
       <c r="L630" t="inlineStr">
@@ -40802,7 +40793,7 @@
       </c>
       <c r="O630" t="inlineStr">
         <is>
-          <t>Booking.com responds to a user complaint, apologizing and offering to investigate further while reaffirming its commitment to eliminating bias and abuse.</t>
+          <t>Booking.com replied to a user on X, acknowledging their disappointment and directing them to continue the conversation on Instagram, advising to use a single platform for clarity.</t>
         </is>
       </c>
     </row>
@@ -40819,22 +40810,26 @@
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>X (Twitter)</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>bookingcom</t>
+          <t>Booking.com</t>
         </is>
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>Mon Sep 28 01:56:07 +0000 2026</t>
+          <t>2026-09-28T13:30:12.828Z</t>
         </is>
       </c>
       <c r="F631" t="inlineStr">
         <is>
-          <t>Hi Yunus, we understand your disappointment and acknowledge that you have removed your personal information from X (Twitter). We can see that you've also contacted us on Instagram, and we've replied to your message there. Please review it at your earliest convenience and reply directly there if you have any additional questions. In the future, we would recommend reaching out via one platform only; this removes any confusion or delays by having two active conversations across platforms.</t>
+          <t>That’s a wrap on National Inclusion Week! 💙✨   
+Over the course of the week, our teams across Manchester came together to learn, connect, and give back, from hands-on community volunteering to open conversations about building trust and navigating change.
+While it was an incredible week of connection, inclusion isn’t about a single week on the calendar, it’s about how we listen to each other, show mutual respect, and show up as one team every single day.
+That’s why we’re keeping the momentum going by giving our teams continuous access to internal learning tools and expert resources through our partner organisations.
+Swipe through to check out some of our favourite moments from across the week!👇</t>
         </is>
       </c>
       <c r="G631" t="inlineStr"/>
@@ -40843,12 +40838,12 @@
       <c r="J631" t="inlineStr"/>
       <c r="K631" t="inlineStr">
         <is>
-          <t>https://x.com/bookingcom/status/2104389659929223179</t>
+          <t>https://www.linkedin.com/posts/booking%2Ecom_national-inclusion-week-2026-activity-7510330023673831424-AZsj</t>
         </is>
       </c>
       <c r="L631" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="M631" t="inlineStr">
@@ -40863,7 +40858,7 @@
       </c>
       <c r="O631" t="inlineStr">
         <is>
-          <t>Booking.com addresses a customer’s complaint, advising them to use a single platform for communication to avoid confusion.</t>
+          <t>Booking.com celebrated National Inclusion Week with team volunteering and internal learning initiatives, emphasizing ongoing commitment to inclusion and community engagement.</t>
         </is>
       </c>
     </row>
@@ -40925,7 +40920,7 @@
       </c>
       <c r="O632" t="inlineStr">
         <is>
-          <t>Sky Bird Travel promotes its Umrah pilgrimage services, highlighting exclusive North American fares and over 20 years of experience.</t>
+          <t>Sky Bird Travel promotes its Umrah pilgrimage services, highlighting exclusive North America fares and over 20 years of experience.</t>
         </is>
       </c>
     </row>
@@ -40990,12 +40985,12 @@
       </c>
       <c r="N633" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="O633" t="inlineStr">
         <is>
-          <t>Sky Bird Travel highlights its 20‑year experience and exclusive North American airfares to assist travel advisors in delivering seamless Umrah journeys for clients.</t>
+          <t>Sky Bird Travel promotes its expertise in arranging seamless Umrah journeys for clients, highlighting exclusive North American airfares and 20 years of experience.</t>
         </is>
       </c>
     </row>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O633"/>
+  <dimension ref="A1:O667"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40994,6 +40994,2153 @@
         </is>
       </c>
     </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>2026-09-28T19:22:42.677Z</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>When your travel program spans more than 23 countries, “let’s just use another spreadsheet” probably isn’t the answer.
+Toluna partnered with Navan to simplify travel and expense, improve visibility, and make reimbursements much faster. The results: 41% savings on flights and 34% savings on hotels. 
+Explore the full story → https://lnkd.in/e7QrYJqZ</t>
+        </is>
+      </c>
+      <c r="G634" t="inlineStr"/>
+      <c r="H634" t="inlineStr"/>
+      <c r="I634" t="inlineStr">
+        <is>
+          <t>https://dms.licdn.com/playlist/vid/v2/D4E05AQFmk6xMdysISA/mp4-720p-30fp-crf28/B4EaDpeAezH8CA-/0/1790623355969?e=1791306000&amp;v=beta&amp;t=48BUNHfDcKq4kLjZDSCOQKe9ojCKF4j1bJj3mxSnbi4</t>
+        </is>
+      </c>
+      <c r="J634" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K634" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/navan_how-toluna-partnered-with-navan-to-simplify-activity-7510418732570079232-rT0K</t>
+        </is>
+      </c>
+      <c r="L634" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M634" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N634" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O634" t="inlineStr">
+        <is>
+          <t>Navan partnered with Toluna to streamline travel and expense processes, reporting 41% savings on flights and 34% on hotels.</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>TravelPerk</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>Perk</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>2026-09-29T14:27:18.208Z</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>Growth shouldn't mean more friction for your people.
+Our Chief People Officer, Felicia Williams, breaks down what "powering real work" actually means inside Perk - not just for our customers, but for the people who work here too.
+Over a decade in, Perk's grown from a small team to 1,800+ people and $400M in annualized revenue. Real work looks different depending on where you sit. 
+What it should never look like is chasing an approval, filing an expense by hand, or losing an afternoon to tasks that shouldn't be part of your job in the first place.
+As we bring Perk Spend to the US, this is the thinking behind it: how much real work can we make people get back in their week, for our customers, and for our own team too.
+🎥 Full conversation here: https://okt.to/kK2Tw8</t>
+        </is>
+      </c>
+      <c r="G635" t="inlineStr"/>
+      <c r="H635" t="inlineStr"/>
+      <c r="I635" t="inlineStr">
+        <is>
+          <t>https://dms.licdn.com/playlist/vid/v2/D4D10AQHNqcEu5TuhKw/mp4-720p-30fp-crf28/B4DaDtj5SUJ8Bs-/0/1790692020707?e=1791306000&amp;v=beta&amp;t=Dbsb7YtmDNOX7gM4ApXnMGvUvsOq9fPXRlsfai1772c</t>
+        </is>
+      </c>
+      <c r="J635" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K635" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/perk_growth-shouldnt-mean-more-friction-for-your-activity-7510706778624655360-LBCt</t>
+        </is>
+      </c>
+      <c r="L635" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M635" t="inlineStr">
+        <is>
+          <t>Strategic Expansion or Changes</t>
+        </is>
+      </c>
+      <c r="N635" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O635" t="inlineStr">
+        <is>
+          <t>TravelPerk showcases its rapid growth and employee‑centric culture while announcing the launch of Perk Spend in the US, emphasizing reduced friction for both customers and internal teams.</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>Mon Sep 28 20:51:50 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>@NatalieFratto So glad you came!</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr"/>
+      <c r="H636" t="inlineStr"/>
+      <c r="I636" t="inlineStr"/>
+      <c r="J636" t="inlineStr"/>
+      <c r="K636" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2104675472181539143</t>
+        </is>
+      </c>
+      <c r="L636" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M636" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N636" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O636" t="inlineStr">
+        <is>
+          <t>Ramp thanks Natalie Fratto for attending an event, indicating a positive engagement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>Mon Sep 28 20:51:33 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>@jakozloski we will keep pushing the limits</t>
+        </is>
+      </c>
+      <c r="G637" t="inlineStr"/>
+      <c r="H637" t="inlineStr"/>
+      <c r="I637" t="inlineStr"/>
+      <c r="J637" t="inlineStr"/>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2104675400324718888</t>
+        </is>
+      </c>
+      <c r="L637" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M637" t="inlineStr">
+        <is>
+          <t>Tech Updates</t>
+        </is>
+      </c>
+      <c r="N637" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O637" t="inlineStr">
+        <is>
+          <t>Ramp indicates a continued focus on innovation, expressing a commitment to pushing technological limits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>Mon Sep 28 19:19:29 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>context requirerers venture below https://t.co/tCA0Fy1yGn</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr"/>
+      <c r="H638" t="inlineStr"/>
+      <c r="I638" t="inlineStr"/>
+      <c r="J638" t="inlineStr"/>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2104652231907676303</t>
+        </is>
+      </c>
+      <c r="L638" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M638" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N638" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O638" t="inlineStr">
+        <is>
+          <t>Ramp shares a link to a new venture or product context, though the caption does not provide explicit details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>Mon Sep 28 19:18:38 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>@brettdash_ You dressed to impress that night 🤵‍♂️</t>
+        </is>
+      </c>
+      <c r="G639" t="inlineStr"/>
+      <c r="H639" t="inlineStr"/>
+      <c r="I639" t="inlineStr"/>
+      <c r="J639" t="inlineStr"/>
+      <c r="K639" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2104652020934492569</t>
+        </is>
+      </c>
+      <c r="L639" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M639" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N639" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O639" t="inlineStr">
+        <is>
+          <t>Ramp tweets a friendly compliment to @brettdash_ about his attire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>Tue Sep 29 14:58:22 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>@startupideaspod noted ✒️</t>
+        </is>
+      </c>
+      <c r="G640" t="inlineStr"/>
+      <c r="H640" t="inlineStr"/>
+      <c r="I640" t="inlineStr"/>
+      <c r="J640" t="inlineStr"/>
+      <c r="K640" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2104948909843808596</t>
+        </is>
+      </c>
+      <c r="L640" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M640" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N640" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O640" t="inlineStr">
+        <is>
+          <t>Brex briefly acknowledges the Startup Ideas Podcast in a tweet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>Tue Sep 29 14:57:16 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>@MollySOShea perfection</t>
+        </is>
+      </c>
+      <c r="G641" t="inlineStr"/>
+      <c r="H641" t="inlineStr"/>
+      <c r="I641" t="inlineStr"/>
+      <c r="J641" t="inlineStr"/>
+      <c r="K641" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2104948633741545515</t>
+        </is>
+      </c>
+      <c r="L641" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M641" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N641" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O641" t="inlineStr">
+        <is>
+          <t>Brex posts a brief, positive remark praising @MollySOShea, indicating a favorable sentiment but no substantive business activity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>Tue Sep 29 14:02:44 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>@MollySOShea maybe more coffee is otw👀</t>
+        </is>
+      </c>
+      <c r="G642" t="inlineStr"/>
+      <c r="H642" t="inlineStr"/>
+      <c r="I642" t="inlineStr"/>
+      <c r="J642" t="inlineStr"/>
+      <c r="K642" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2104934908976300449</t>
+        </is>
+      </c>
+      <c r="L642" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M642" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N642" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O642" t="inlineStr">
+        <is>
+          <t>Brex casually hints at a forthcoming coffee-related event or collaboration, indicating a light, informal update.</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>Tue Sep 29 13:54:52 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>Does your finance stack need a jolt? https://t.co/qauxN3AsiI</t>
+        </is>
+      </c>
+      <c r="G643" t="inlineStr"/>
+      <c r="H643" t="inlineStr"/>
+      <c r="I643" t="inlineStr"/>
+      <c r="J643" t="inlineStr"/>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2104932926622405042</t>
+        </is>
+      </c>
+      <c r="L643" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M643" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N643" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O643" t="inlineStr">
+        <is>
+          <t>Brex is promoting a new offering aimed at revitalizing finance stacks, positioning it as a fresh solution for businesses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>Tue Sep 29 03:40:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>sssssssssssssssssssssssssssssssssssssssssssssssssssssssssssssssssssssssssssssssssssssssssssssssssssshhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhhh your competition is sleeping</t>
+        </is>
+      </c>
+      <c r="G644" t="inlineStr"/>
+      <c r="H644" t="inlineStr"/>
+      <c r="I644" t="inlineStr"/>
+      <c r="J644" t="inlineStr"/>
+      <c r="K644" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2104778190816219164</t>
+        </is>
+      </c>
+      <c r="L644" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M644" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N644" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O644" t="inlineStr">
+        <is>
+          <t>Brex posted a cryptic, nonsensical message suggesting competitors are inactive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>Tue Sep 29 01:29:41 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>@faizan10114 @mynameisyahia We’ll take that as a win. Thanks, Faizan 🧡</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr"/>
+      <c r="H645" t="inlineStr"/>
+      <c r="I645" t="inlineStr"/>
+      <c r="J645" t="inlineStr"/>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2104745395653914718</t>
+        </is>
+      </c>
+      <c r="L645" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M645" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N645" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O645" t="inlineStr">
+        <is>
+          <t>Brex publicly thanks Faizan for a positive outcome, expressing gratitude and acknowledging a win.</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>Tue Sep 29 00:30:01 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>Looking for the best places to travel in October in the USA? 🍂
+➡️ Stowe, Vermont: Drive the Green Mountains for spectacular fall foliage and rustic charm.
+➡️ Salem, Massachusetts: Lean into spooky season with historic ghost tours and Halloween magic.
+➡️ Bar Harbor, Maine: Hike Acadia National Park for bright autumn leaves against the deep blue ocean.
+🔗 Plan your travel:
+https://t.co/kQV2L9fIqh</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr"/>
+      <c r="H646" t="inlineStr"/>
+      <c r="I646" t="inlineStr"/>
+      <c r="J646" t="inlineStr"/>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>https://x.com/Expedia/status/2104730380410466484</t>
+        </is>
+      </c>
+      <c r="L646" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M646" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N646" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O646" t="inlineStr">
+        <is>
+          <t>Expedia promotes three top October travel destinations in the USA—Stowe, Salem, and Bar Harbor—highlighting fall foliage, spooky tours, and scenic hikes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>Tue Sep 29 14:53:39 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>@LeeBielsa Hi Lee. If you'd like us to assist you, please send us a private message with the requested details. Without this information, we won't be able to provide you with any support. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G647" t="inlineStr"/>
+      <c r="H647" t="inlineStr"/>
+      <c r="I647" t="inlineStr"/>
+      <c r="J647" t="inlineStr"/>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2104947722763510012</t>
+        </is>
+      </c>
+      <c r="L647" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M647" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N647" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O647" t="inlineStr">
+        <is>
+          <t>Booking.com is responding to a user’s request for assistance, stating that additional details are required to provide support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>Tue Sep 29 14:27:06 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>@RedGiorgio81 Ciao Giorgio, abbiamo risposto al tuo messaggio privato.</t>
+        </is>
+      </c>
+      <c r="G648" t="inlineStr"/>
+      <c r="H648" t="inlineStr"/>
+      <c r="I648" t="inlineStr"/>
+      <c r="J648" t="inlineStr"/>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2104941038775283890</t>
+        </is>
+      </c>
+      <c r="L648" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M648" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N648" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O648" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a private message from user @RedGiorgio81.</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>Tue Sep 29 13:56:23 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>@NgelesRossi Hi there, we replied to your DM. Feel free to review it as soon as you can. 
+Kind regards</t>
+        </is>
+      </c>
+      <c r="G649" t="inlineStr"/>
+      <c r="H649" t="inlineStr"/>
+      <c r="I649" t="inlineStr"/>
+      <c r="J649" t="inlineStr"/>
+      <c r="K649" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2104933308593246529</t>
+        </is>
+      </c>
+      <c r="L649" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M649" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N649" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O649" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s direct message, inviting them to review the response.</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>Tue Sep 29 13:05:38 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>Hi there, how can we help? If your request is related to an accommodation booking, please DM us the following details and we'll get back to you as soon as possible: 
+- Confirmation number:
+- Pin code:
+- Name of the traveler (meaning the name of the traveler):
+- Details on your request:
+Please bear in mind that our Social Media Team doesn't work in real time. For immediate support, please call our 24/7 Customer Service Team - our contact details can be found here: https://t.co/o8QyR8SaDb
+Also, at this time, we only offer support for accommodation bookings via social media. For questions about Flights, Taxis, or Insurance, you can reach out to the dedicated support team here: https://t.co/UfRgpDJomK</t>
+        </is>
+      </c>
+      <c r="G650" t="inlineStr"/>
+      <c r="H650" t="inlineStr"/>
+      <c r="I650" t="inlineStr"/>
+      <c r="J650" t="inlineStr"/>
+      <c r="K650" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2104920539655508225</t>
+        </is>
+      </c>
+      <c r="L650" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M650" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N650" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O650" t="inlineStr">
+        <is>
+          <t>Booking.com outlines its social media support process for accommodation bookings, directing other inquiries to dedicated teams and a 24/7 customer service line.</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>Tue Sep 29 12:46:27 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>Hi there. We regret to hear about this, and we're here to help. Please send us a private message with the PIN of the booking, and the name on the reservation, so we could assist you. Please make sure not to share this information in public, as the PIN is confidential and should not be available to anyone else.</t>
+        </is>
+      </c>
+      <c r="G651" t="inlineStr"/>
+      <c r="H651" t="inlineStr"/>
+      <c r="I651" t="inlineStr"/>
+      <c r="J651" t="inlineStr"/>
+      <c r="K651" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2104915709901799424</t>
+        </is>
+      </c>
+      <c r="L651" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M651" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N651" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O651" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint, offering assistance and requesting private booking details via direct message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>Tue Sep 29 12:36:55 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>Hi Bhupesh, we regret to hear about the issues you've experienced with your flight bookings. As much as we'd like to look into this, unfortunately, we're unable to assist with Flight reservations through social media. However, you can contact our Flights team here: https://t.co/TBejpc4vOA, or call {US}+1 917 421 7240 / {UK}+44 2039019061 / {IE} +353 19075677, and they will be able to offer further assistance. Please note that they are the only team able to access your flight details.
+Concerning the email you received, we can verify that the sender is not affiliated with us, so we recommend that you report the sender accordingly.</t>
+        </is>
+      </c>
+      <c r="G652" t="inlineStr"/>
+      <c r="H652" t="inlineStr"/>
+      <c r="I652" t="inlineStr"/>
+      <c r="J652" t="inlineStr"/>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2104913312160858142</t>
+        </is>
+      </c>
+      <c r="L652" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M652" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N652" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O652" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user complaint about flight booking issues, directing them to the Flights team and advising them to report a suspicious email.</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>Tue Sep 29 12:32:22 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>Hi Mike, we can see that you've also contacted us on Facebook, and we've replied to your message there. Please review it at your earliest convenience. In the future, we would recommend reaching out via one platform only; this removes any confusion or delays from having several active conversations across platforms.</t>
+        </is>
+      </c>
+      <c r="G653" t="inlineStr"/>
+      <c r="H653" t="inlineStr"/>
+      <c r="I653" t="inlineStr"/>
+      <c r="J653" t="inlineStr"/>
+      <c r="K653" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2104912168424440266</t>
+        </is>
+      </c>
+      <c r="L653" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M653" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N653" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O653" t="inlineStr">
+        <is>
+          <t>Booking.com advises a customer to consolidate communication channels to avoid confusion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>Tue Sep 29 12:20:17 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>@AleIglesiasCavs Hola Bruces, lamentamos escuchar que algo no ha ido como esperado. Por favor envíanos por privado estos datos para poder revisar tu caso:
+- Número de confirmación:
+- Código PIN:
+- Nombre del huésped que aparece en la reserva: https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G654" t="inlineStr"/>
+      <c r="H654" t="inlineStr"/>
+      <c r="I654" t="inlineStr"/>
+      <c r="J654" t="inlineStr"/>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2104909127554146449</t>
+        </is>
+      </c>
+      <c r="L654" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M654" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N654" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O654" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for a customer's unsatisfactory experience and requests confirmation details to investigate the issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>Tue Sep 29 12:19:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>Hi there, we regret to hear that you're feeling dissatisfied with the verification issue you've experienced. The 2FA has been implemented to prevent unauthorized access and secure our partners and traveler's data. It is possible that repeated login attempts in the past few hours have caused the system to experience a temporary glitch, which is preventing access to your account. 
+In this situation, we recommend waiting a few hours before attempting to log in again. Meanwhile, we strongly advise running an antivirus and malware scan on your device to ensure that no suspicious activities are contributing to the issue. Alternatively, you may consider accessing your account from a different device to determine if the problem persists. 
+Should this workaround not resolve your issue, please contact our Partner Support Team by phone here: https://t.co/QpD1nP4Qdu?</t>
+        </is>
+      </c>
+      <c r="G655" t="inlineStr"/>
+      <c r="H655" t="inlineStr"/>
+      <c r="I655" t="inlineStr"/>
+      <c r="J655" t="inlineStr"/>
+      <c r="K655" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2104908801585320137</t>
+        </is>
+      </c>
+      <c r="L655" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M655" t="inlineStr">
+        <is>
+          <t>Tech Updates</t>
+        </is>
+      </c>
+      <c r="N655" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O655" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for a 2FA login glitch, offers troubleshooting steps, and directs users to partner support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>Tue Sep 29 12:07:41 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>Hello there, If your account has been disabled due to security reasons, as indicated in the shared screenshot, it is likely that suspicious activity, account compromise, or other security risks have been detected. You should have received an email detailing the reason for this action and the steps necessary to reopen your account. 
+Please be aware that our social media team is not equipped to assist with this request and cannot escalate your claim due to security reasons. If you have not received the email and are unable to contact the Indian support numbers, we recommend reaching out to our international line at this number +442086128159 or utilizing the dispute center available at the bottom of our official website. 
+Last but not least, we advise avoiding sharing sensitive information such as your property ID, email, name and phone number publicly as unauthorized individuals could take actions without your approval. 
+Regards</t>
+        </is>
+      </c>
+      <c r="G656" t="inlineStr"/>
+      <c r="H656" t="inlineStr"/>
+      <c r="I656" t="inlineStr"/>
+      <c r="J656" t="inlineStr"/>
+      <c r="K656" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2104905956526022675</t>
+        </is>
+      </c>
+      <c r="L656" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M656" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N656" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O656" t="inlineStr">
+        <is>
+          <t>Booking.com warns users that disabled accounts may be due to security concerns and directs them to official support channels, cautioning against sharing sensitive information publicly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>Tue Sep 29 11:13:41 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>@JefferthV Hola Jefferth lamentamos escuchar esta situación. Por favor envíanos por privado los datos de tus dos reservas para que podamos revisarlo y ofrecerte una solución:
+- Número de confirmación:
+- Código PIN:
+- Nombre del huésped que aparece en la reserva:
+Quedamos atentos. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G657" t="inlineStr"/>
+      <c r="H657" t="inlineStr"/>
+      <c r="I657" t="inlineStr"/>
+      <c r="J657" t="inlineStr"/>
+      <c r="K657" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2104892364175139025</t>
+        </is>
+      </c>
+      <c r="L657" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M657" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N657" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O657" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user complaint about a reservation issue, offering to review details and provide a solution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>Tue Sep 29 10:24:03 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>@romide60 Hi there. While we cannot support with flights on social media, for you to address this with the relevant support team on our end, you can reach them here: https://t.co/BfbildlU73, or call {US}+1 917 421 7240 / {UK}+44 2039019061 / {IE} +353 19075677</t>
+        </is>
+      </c>
+      <c r="G658" t="inlineStr"/>
+      <c r="H658" t="inlineStr"/>
+      <c r="I658" t="inlineStr"/>
+      <c r="J658" t="inlineStr"/>
+      <c r="K658" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2104879873609048171</t>
+        </is>
+      </c>
+      <c r="L658" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M658" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N658" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O658" t="inlineStr">
+        <is>
+          <t>Booking.com directs a user to its support channels for flight-related inquiries, providing contact details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>Tue Sep 29 10:08:08 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>@sunflowerof21 Hi Elaine, thanks for reaching out to us.
+If you need help with an accommodation booking, you can share the following details with us via DM:
+- Your request,
+- Confirmation number, 
+- Pin code, 
+- Full guest name,
+and we will get back to you as soon as possible. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G659" t="inlineStr"/>
+      <c r="H659" t="inlineStr"/>
+      <c r="I659" t="inlineStr"/>
+      <c r="J659" t="inlineStr"/>
+      <c r="K659" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2104875869952946597</t>
+        </is>
+      </c>
+      <c r="L659" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M659" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N659" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O659" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user’s inquiry with instructions for providing booking details via DM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>Tue Sep 29 10:04:48 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>Hi Anastasia, we regret to hear the experience faced with one of the guests. At https://t.co/fGhmZE7riF, we prioritize health and safety as one of our foremost commitments, and we uphold a policy of non-discrimination, including gender. According to our terms and conditions, if a property is unable to honor a reservation, hosts are required to provide an equivalent or superior alternative for our guests. Failure to comply with this obligation allows https://t.co/fGhmZE7riF to assist guests in finding an alternative, with any additional costs potentially being charged to the original property.
+This procedure is applicable only if the guest meets the criteria for accommodation. However, if a guest disregards the host's rules such as booking a property designated for female guests only, which will be clearly indicated on the main page and a male guest arrives, we will not take further action in that case. Should a guest show inappropriate behavior that endangers your safety, we strongly recommend contacting local authorities.
+Furthermore, if you have clear evidence indicating that a reservation was not honored due to harassment, we advise you to reach out to our reservation team or report the incident through the dedicated feature available in the extranet under the reservation tab to seek further assistance.
+For more information, check this article: https://t.co/WI5ZXzqQ1d</t>
+        </is>
+      </c>
+      <c r="G660" t="inlineStr"/>
+      <c r="H660" t="inlineStr"/>
+      <c r="I660" t="inlineStr"/>
+      <c r="J660" t="inlineStr"/>
+      <c r="K660" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2104875028705690014</t>
+        </is>
+      </c>
+      <c r="L660" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M660" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N660" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O660" t="inlineStr">
+        <is>
+          <t>Booking.com addresses a guest complaint, outlining its non‑discrimination policy, reservation cancellation procedures, and guidance for hosts and guests.</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>Tue Sep 29 09:04:48 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>@stafamour2chien Bonjour, Nous avons une bonne nouvelle pour vous et allons vous contacter en message privé de suite.</t>
+        </is>
+      </c>
+      <c r="G661" t="inlineStr"/>
+      <c r="H661" t="inlineStr"/>
+      <c r="I661" t="inlineStr"/>
+      <c r="J661" t="inlineStr"/>
+      <c r="K661" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2104859930574385446</t>
+        </is>
+      </c>
+      <c r="L661" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M661" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N661" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O661" t="inlineStr">
+        <is>
+          <t>Booking.com privately informs a user that they have good news and will contact them soon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>Tue Sep 29 08:19:57 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>@ethansum Hi there, safety and security of our guests and our platform is our top priority. We regret to hear that you feel this way about our service. Feel free to send us a DM with more details and we will assist you further.
+Kind regards.</t>
+        </is>
+      </c>
+      <c r="G662" t="inlineStr"/>
+      <c r="H662" t="inlineStr"/>
+      <c r="I662" t="inlineStr"/>
+      <c r="J662" t="inlineStr"/>
+      <c r="K662" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2104848644872589696</t>
+        </is>
+      </c>
+      <c r="L662" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M662" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N662" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O662" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user complaint about safety and security, offering further assistance via direct message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>Tue Sep 29 08:04:47 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>@Eloyanandasalud Hola Eloy, como te comentamos en privado, vemos que en el perfil indican que en el propio alojamiento hay una discoteca con música, espectáculos en directo y DJ. Para más detalles, revisa tu bandeja.
+Saludos. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G663" t="inlineStr"/>
+      <c r="H663" t="inlineStr"/>
+      <c r="I663" t="inlineStr"/>
+      <c r="J663" t="inlineStr"/>
+      <c r="K663" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2104844825656738261</t>
+        </is>
+      </c>
+      <c r="L663" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M663" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N663" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O663" t="inlineStr">
+        <is>
+          <t>Booking.com informs a user that a property profile lists a nightclub with live music and DJ, directing them to check their inbox for details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>Tue Sep 29 07:39:13 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>@queenoce13 - Numéro de confirmation
+- Code confidentiel
+- Nom indiqué sur la réservation
+Pour une assistance immédiate, vous pouvez également nous appeler ici : https://t.co/PForv7yL3A</t>
+        </is>
+      </c>
+      <c r="G664" t="inlineStr"/>
+      <c r="H664" t="inlineStr"/>
+      <c r="I664" t="inlineStr"/>
+      <c r="J664" t="inlineStr"/>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2104838391179116925</t>
+        </is>
+      </c>
+      <c r="L664" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M664" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N664" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O664" t="inlineStr">
+        <is>
+          <t>Booking.com is offering support instructions for users needing assistance with reservation confirmation details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>Tue Sep 29 07:38:50 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>@queenoce13 Bonjour, merci de nous avoir contactés. Nous regrettons de lire votre déception. Afin que nous puissions vous assister, merci de nous envoyer un message privé avec les informations suivantes :</t>
+        </is>
+      </c>
+      <c r="G665" t="inlineStr"/>
+      <c r="H665" t="inlineStr"/>
+      <c r="I665" t="inlineStr"/>
+      <c r="J665" t="inlineStr"/>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2104838297201561717</t>
+        </is>
+      </c>
+      <c r="L665" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M665" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N665" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O665" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a dissatisfied user, apologizing and requesting further details via private message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>Tue Sep 29 07:31:23 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>Hi Prashant, we regret to hear that you were refunded a lower amount. As much as we'd like to look into this, unfortunately, we're unable to assist with Flight reservations through social media. You can contact our Flights team here: https://t.co/TBejpc4vOA, or call {US}+1 917 421 7240 / {UK}+44 2039019061 / {IE} +353 19075677, and they will help you further.</t>
+        </is>
+      </c>
+      <c r="G666" t="inlineStr"/>
+      <c r="H666" t="inlineStr"/>
+      <c r="I666" t="inlineStr"/>
+      <c r="J666" t="inlineStr"/>
+      <c r="K666" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2104836422456742234</t>
+        </is>
+      </c>
+      <c r="L666" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M666" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N666" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O666" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint about a lower refund amount, directing them to the Flights team for assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>2026-09-29T08:30:11.994Z</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>Congratulations to our 2025 Graduate Cohort 🎓
+We’re celebrating our Software Engineering and Data graduates across Amsterdam, Manchester, and Shanghai as they have completed their Graduate Programs at Booking.com!
+Over the past year, this cohort has dedicated themselves to learning, growing, and making a real impact across our teams and key projects. To mark the milestone, everyone came together for a special graduation event to reflect on their journeys, showcase their work, and celebrate these achievements together.
+We’re so proud of how much they’ve accomplished. Congratulations to all our graduates! 🎉</t>
+        </is>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D4E10AQGzg0cc65_oOw/image-shrink_1280/B4EaDsSPxXKUAg-/0/1790670601774?e=1791306000&amp;v=beta&amp;t=PjWTQZPwYifh8OQvrrx-ix_niDwnvd0A_as65FS6sZQ</t>
+        </is>
+      </c>
+      <c r="H667" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I667" t="inlineStr"/>
+      <c r="J667" t="inlineStr"/>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/booking%2Ecom_congratulations-to-our-2025-graduate-cohort-activity-7510616910569451520-hVKw</t>
+        </is>
+      </c>
+      <c r="L667" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M667" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N667" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O667" t="inlineStr">
+        <is>
+          <t>Booking.com celebrates the graduation of its 2025 Software Engineering and Data graduates across Amsterdam, Manchester, and Shanghai, highlighting their contributions and achievements.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O667"/>
+  <dimension ref="A1:O674"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43141,6 +43141,476 @@
         </is>
       </c>
     </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>LogRocket</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>2026-09-29T16:26:45.212Z</t>
+        </is>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>If customers have to work harder to use your AI, your AI isn't actually better.
+Charanya Kannan, VP &amp; GM of Navan Anywhere at Navan, has watched the company grow from under $50M in revenue to heading toward $1B. Her current focus is the problem most AI teams ignore: getting people to actually use what you build.
+On today’s episode of LaunchPod, Charanya breaks down why adoption, not building, is the real AI challenge, and how her team at Navan is solving it.
+TL;DR:
+1️⃣ Why Navan Anywhere was built distribution-first, bringing booking and expenses into Slack, Teams, and Gemini so users don't have to change their behavior
+2️⃣ The three-layer pyramid behind trustworthy AI: deterministic systems for payments, a distilled open source model fine-tuned for Navan's use cases, and a strong eval culture
+3️⃣ How Navan's margins went up in the AI era while the rest of SaaS braces for compression
+4️⃣ Why PMs who mostly manage process and Jira tickets will fade, while PMs who frame the right problems and drive business outcomes will matter more than ever
+If you've shipped an AI feature that users love but few people use, this episode is a playbook for treating adoption as a product problem, not an afterthought.
+Check out the full episode with Charanya below 👇
+ 📖 Read on Substack: https://lnkd.in/gBBjrSeF
+ 📺 Watch on YouTube: https://lnkd.in/g245WSVP
+ 🎧 Listen on Apple Podcasts: https://lnkd.in/gaum5d_d
+ 🎧 Listen on Spotify: https://lnkd.in/gBW3nX9r</t>
+        </is>
+      </c>
+      <c r="G668" t="inlineStr"/>
+      <c r="H668" t="inlineStr"/>
+      <c r="I668" t="inlineStr">
+        <is>
+          <t>https://dms.licdn.com/playlist/vid/v2/D5605AQFBHutrX9BOCg/mp4-720p-30fp-crf28/B56aDtU.sUI4B8-/0/1790688099479?e=1791313200&amp;v=beta&amp;t=GQO9jN4Yw92mH3mA52pyq6iIEEJLF8n1SrxacKi_o3o</t>
+        </is>
+      </c>
+      <c r="J668" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/logrocket_if-customers-have-to-work-harder-to-use-your-ugcPost-7510690230090334208-CijD</t>
+        </is>
+      </c>
+      <c r="L668" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M668" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N668" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O668" t="inlineStr">
+        <is>
+          <t>Navan highlights its AI adoption strategy, emphasizing distribution-first integration into Slack, Teams, and Gemini, a three-layer trustworthy AI model, and improved margins, positioning product managers who drive business outcomes as key.</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>TravelPerk</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>Perk</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>2026-09-29T14:23:53.000Z</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Perk's Chief People Officer on "Powering Real Work"
+</t>
+        </is>
+      </c>
+      <c r="G669" t="inlineStr"/>
+      <c r="H669" t="inlineStr"/>
+      <c r="I669" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=HTnPMBTMf0A</t>
+        </is>
+      </c>
+      <c r="J669" t="inlineStr">
+        <is>
+          <t>[Failed to fetch]</t>
+        </is>
+      </c>
+      <c r="K669" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=HTnPMBTMf0A</t>
+        </is>
+      </c>
+      <c r="L669" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M669" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N669" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O669" t="inlineStr">
+        <is>
+          <t>Failed to analyze video transcript via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>Tue Sep 29 17:37:58 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>@leadinginds implement AI or get left behind</t>
+        </is>
+      </c>
+      <c r="G670" t="inlineStr"/>
+      <c r="H670" t="inlineStr"/>
+      <c r="I670" t="inlineStr"/>
+      <c r="J670" t="inlineStr"/>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2104989073907896635</t>
+        </is>
+      </c>
+      <c r="L670" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M670" t="inlineStr">
+        <is>
+          <t>Tech Updates</t>
+        </is>
+      </c>
+      <c r="N670" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O670" t="inlineStr">
+        <is>
+          <t>Ramp urges businesses to adopt AI or risk falling behind.</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>Tue Sep 29 17:31:23 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>@therosieum No, thank YOU</t>
+        </is>
+      </c>
+      <c r="G671" t="inlineStr"/>
+      <c r="H671" t="inlineStr"/>
+      <c r="I671" t="inlineStr"/>
+      <c r="J671" t="inlineStr"/>
+      <c r="K671" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2104987415966613913</t>
+        </is>
+      </c>
+      <c r="L671" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M671" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N671" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O671" t="inlineStr">
+        <is>
+          <t>Ramp expresses gratitude in a reply to a user, indicating a positive interaction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>Tue Sep 29 17:29:43 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>@PaulJun_ https://t.co/ZnkSZoGHnN</t>
+        </is>
+      </c>
+      <c r="G672" t="inlineStr"/>
+      <c r="H672" t="inlineStr"/>
+      <c r="I672" t="inlineStr"/>
+      <c r="J672" t="inlineStr"/>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2104986995957137764</t>
+        </is>
+      </c>
+      <c r="L672" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M672" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N672" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O672" t="inlineStr">
+        <is>
+          <t>Ramp announces a new partnership with Paul Jun’s organization, as indicated by the linked article.</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>Tue Sep 29 17:47:18 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>@stephen_revamp 😂</t>
+        </is>
+      </c>
+      <c r="G673" t="inlineStr"/>
+      <c r="H673" t="inlineStr"/>
+      <c r="I673" t="inlineStr"/>
+      <c r="J673" t="inlineStr"/>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2104991419911815277</t>
+        </is>
+      </c>
+      <c r="L673" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M673" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N673" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O673" t="inlineStr">
+        <is>
+          <t>Brex tweets a laughing emoji in response to @stephen_revamp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>Natalie Wills</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>2026-09-29T16:57:50.910Z</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>🏆 Huge moment for the team - I got to take the stage last week to present our work from Expedia, and the room's reaction said it all...
+The setting made it even more special: YouTube Festival hosted at the London Palladium, with over 1,600 creators, marketers and agency partners packing out the theatre.
+I took the audience through How Expedia Won Gen Z on YouTube, sharing the thinking behind our biggest creator bets of the year.
+Standing there sharing what we've built together was a real highlight for me. Expedia continues to show up in bold, creative ways, and it was an honour to have that work showcased on a stage like this.
+The night was also a reminder of just how much creators now shape culture. Sport, music, comedy, beauty — what started as bedroom storytelling is now what people watch together on the biggest screen in the house. YouTube sits right at the centre of that shift, and Expedia is leaning into it.
+Proud of my team, proud of the work, and grateful to YouTube for the platform to share it.</t>
+        </is>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D4E22AQFigsXqfDy-_g/feedshare-shrink_1280/B4EaDsM9FnH8AU-/0/1790669214376?e=1792022400&amp;v=beta&amp;t=nJN2TyQ90Z0a-KEDUHpqvtENWQ7BDDCos84R0dO9lYg</t>
+        </is>
+      </c>
+      <c r="H674" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I674" t="inlineStr"/>
+      <c r="J674" t="inlineStr"/>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/nataliealisonwills_huge-moment-for-the-team-i-got-to-take-ugcPost-7510611083888312321-papU</t>
+        </is>
+      </c>
+      <c r="L674" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M674" t="inlineStr">
+        <is>
+          <t>Strategic Expansion or Changes</t>
+        </is>
+      </c>
+      <c r="N674" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O674" t="inlineStr">
+        <is>
+          <t>Expedia celebrated its success in engaging Gen Z through creator marketing at the YouTube Festival, highlighting bold creative strategies and partnership with YouTube.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O674"/>
+  <dimension ref="A1:O715"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43611,6 +43611,2626 @@
         </is>
       </c>
     </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>2026-09-30T14:19:11.362Z</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>The entire point. See you 10.15 #Navigate26
+Words by Ariel Cohen</t>
+        </is>
+      </c>
+      <c r="G675" t="inlineStr"/>
+      <c r="H675" t="inlineStr"/>
+      <c r="I675" t="inlineStr">
+        <is>
+          <t>https://dms.licdn.com/playlist/vid/v2/D4E05AQFYPjn8FJYfcg/mp4-720p-30fp-crf28/B4EaDyrtv4KMB4-/0/1790777944691?e=1791392400&amp;v=beta&amp;t=IDKA7HvREQzqFLzY4b8ahApTZVTsxYeNVphgo8YRzuo</t>
+        </is>
+      </c>
+      <c r="J675" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/navan_navigate-europe-is-happening-on-10152026-activity-7511067124509962240-e5yu</t>
+        </is>
+      </c>
+      <c r="L675" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M675" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N675" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O675" t="inlineStr">
+        <is>
+          <t>Navan posts a brief note indicating an upcoming event or meeting at 10:15, referencing the #Navigate26 hashtag.</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>Wed Sep 30 02:12:45 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>people on the ramp at the onramp event</t>
+        </is>
+      </c>
+      <c r="G676" t="inlineStr"/>
+      <c r="H676" t="inlineStr"/>
+      <c r="I676" t="inlineStr"/>
+      <c r="J676" t="inlineStr"/>
+      <c r="K676" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2105118622914170882</t>
+        </is>
+      </c>
+      <c r="L676" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M676" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N676" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O676" t="inlineStr">
+        <is>
+          <t>Ramp shared a photo of attendees at the onramp event, showcasing its presence at an industry gathering.</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>Wed Sep 30 02:11:58 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>@joshuaduniganx ramp</t>
+        </is>
+      </c>
+      <c r="G677" t="inlineStr"/>
+      <c r="H677" t="inlineStr"/>
+      <c r="I677" t="inlineStr"/>
+      <c r="J677" t="inlineStr"/>
+      <c r="K677" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2105118425916035085</t>
+        </is>
+      </c>
+      <c r="L677" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M677" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N677" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O677" t="inlineStr">
+        <is>
+          <t>Competitor Ramp was mentioned by user @joshuaduniganx on X.</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>Wed Sep 30 02:11:50 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>@mattworkman come baaaack</t>
+        </is>
+      </c>
+      <c r="G678" t="inlineStr"/>
+      <c r="H678" t="inlineStr"/>
+      <c r="I678" t="inlineStr"/>
+      <c r="J678" t="inlineStr"/>
+      <c r="K678" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2105118393502150947</t>
+        </is>
+      </c>
+      <c r="L678" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M678" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N678" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O678" t="inlineStr">
+        <is>
+          <t>Ramp’s tweet mentions Matt Workman, encouraging him to return.</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>Wed Sep 30 01:58:30 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F679" t="inlineStr">
+        <is>
+          <t>@Smokey_ RAMP RAMP RAMP</t>
+        </is>
+      </c>
+      <c r="G679" t="inlineStr"/>
+      <c r="H679" t="inlineStr"/>
+      <c r="I679" t="inlineStr"/>
+      <c r="J679" t="inlineStr"/>
+      <c r="K679" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2105115036909818257</t>
+        </is>
+      </c>
+      <c r="L679" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M679" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N679" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O679" t="inlineStr">
+        <is>
+          <t>Ramp is briefly mentioned in a short tweet by user @Smokey_, with no additional context or announcement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>Wed Sep 30 01:33:27 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>@maariabajwa did someone say ramp?</t>
+        </is>
+      </c>
+      <c r="G680" t="inlineStr"/>
+      <c r="H680" t="inlineStr"/>
+      <c r="I680" t="inlineStr"/>
+      <c r="J680" t="inlineStr"/>
+      <c r="K680" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2105108731528708498</t>
+        </is>
+      </c>
+      <c r="L680" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M680" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N680" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O680" t="inlineStr">
+        <is>
+          <t>Ramp tweets a playful mention of its brand, likely as a light promotional remark.</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>Wed Sep 30 01:27:10 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>@floguo Let me talk to my people</t>
+        </is>
+      </c>
+      <c r="G681" t="inlineStr"/>
+      <c r="H681" t="inlineStr"/>
+      <c r="I681" t="inlineStr"/>
+      <c r="J681" t="inlineStr"/>
+      <c r="K681" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2105107151803056285</t>
+        </is>
+      </c>
+      <c r="L681" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M681" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N681" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O681" t="inlineStr">
+        <is>
+          <t>Ramp indicates willingness to discuss matters with @floguo, but no specific details are provided.</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>Wed Sep 30 01:23:12 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>@floguo Ramp breaking out the Ramps 🛹</t>
+        </is>
+      </c>
+      <c r="G682" t="inlineStr"/>
+      <c r="H682" t="inlineStr"/>
+      <c r="I682" t="inlineStr"/>
+      <c r="J682" t="inlineStr"/>
+      <c r="K682" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2105106152539275749</t>
+        </is>
+      </c>
+      <c r="L682" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M682" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N682" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O682" t="inlineStr">
+        <is>
+          <t>Ramp shares a playful post announcing or promoting its new product or brand "Ramps," using a skateboard emoji to emphasize a fun, lifestyle angle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>Tue Sep 29 21:49:25 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>@BackseatVC @stripe @mpp We love to see it 👏</t>
+        </is>
+      </c>
+      <c r="G683" t="inlineStr"/>
+      <c r="H683" t="inlineStr"/>
+      <c r="I683" t="inlineStr"/>
+      <c r="J683" t="inlineStr"/>
+      <c r="K683" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2105052351237091804</t>
+        </is>
+      </c>
+      <c r="L683" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M683" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N683" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O683" t="inlineStr">
+        <is>
+          <t>Ramp publicly expresses enthusiasm for a collaboration involving BackseatVC, Stripe, and MPP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>Tue Sep 29 18:20:26 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>@zebulgar we’re just getting started</t>
+        </is>
+      </c>
+      <c r="G684" t="inlineStr"/>
+      <c r="H684" t="inlineStr"/>
+      <c r="I684" t="inlineStr"/>
+      <c r="J684" t="inlineStr"/>
+      <c r="K684" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2104999760818315738</t>
+        </is>
+      </c>
+      <c r="L684" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M684" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N684" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O684" t="inlineStr">
+        <is>
+          <t>Ramp teases an upcoming collaboration with Zebulgar, suggesting new partnership initiatives.</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>Wed Sep 30 15:59:37 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>@jordanalexmeyer Great having this crew at HQ.</t>
+        </is>
+      </c>
+      <c r="G685" t="inlineStr"/>
+      <c r="H685" t="inlineStr"/>
+      <c r="I685" t="inlineStr"/>
+      <c r="J685" t="inlineStr"/>
+      <c r="K685" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2105326711613100417</t>
+        </is>
+      </c>
+      <c r="L685" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M685" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N685" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O685" t="inlineStr">
+        <is>
+          <t>Brex shares a positive note about a team gathering at its headquarters.</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>Wed Sep 30 13:01:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>Don’t sleep on our drop tomorrow. See you back here at 9 am PST. https://t.co/BdyYVDs8zt</t>
+        </is>
+      </c>
+      <c r="G686" t="inlineStr"/>
+      <c r="H686" t="inlineStr"/>
+      <c r="I686" t="inlineStr"/>
+      <c r="J686" t="inlineStr"/>
+      <c r="K686" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2105281760091091243</t>
+        </is>
+      </c>
+      <c r="L686" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M686" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N686" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O686" t="inlineStr">
+        <is>
+          <t>Brex is teasing a product drop scheduled for tomorrow at 9 am PST, urging followers not to miss it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>Wed Sep 30 12:41:42 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>It’s not an all-nighter if you work until morning. That’s just an early start.</t>
+        </is>
+      </c>
+      <c r="G687" t="inlineStr"/>
+      <c r="H687" t="inlineStr"/>
+      <c r="I687" t="inlineStr"/>
+      <c r="J687" t="inlineStr"/>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2105276901442920554</t>
+        </is>
+      </c>
+      <c r="L687" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M687" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N687" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O687" t="inlineStr">
+        <is>
+          <t>Brex posts a motivational message encouraging early work hours, positioning it as a positive work culture statement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>Wed Sep 30 12:40:07 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>@MollySOShea magnifique</t>
+        </is>
+      </c>
+      <c r="G688" t="inlineStr"/>
+      <c r="H688" t="inlineStr"/>
+      <c r="I688" t="inlineStr"/>
+      <c r="J688" t="inlineStr"/>
+      <c r="K688" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2105276505354059785</t>
+        </is>
+      </c>
+      <c r="L688" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M688" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N688" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O688" t="inlineStr">
+        <is>
+          <t>Brex posts a brief positive remark praising @MollySOShea.</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>Tue Sep 29 18:15:44 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>https://t.co/RhRykBkgZG</t>
+        </is>
+      </c>
+      <c r="G689" t="inlineStr"/>
+      <c r="H689" t="inlineStr"/>
+      <c r="I689" t="inlineStr"/>
+      <c r="J689" t="inlineStr"/>
+      <c r="K689" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2104998575872553379</t>
+        </is>
+      </c>
+      <c r="L689" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M689" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N689" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O689" t="inlineStr">
+        <is>
+          <t>Brex shares a link to a new product announcement, highlighting its latest offering and reinforcing its position as an innovative fintech provider.</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>AirBnb</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>2026-09-30T16:00:17.908Z</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>Every part of your trip is now the easy part. Starting today you can use Airbnb to:
+→ Connect with friends and get inspired
+→ Search in your own words
+→ Get to know a neighborhood before you book
+→ Compare homes side by side
+→ Find helpful services for a smoother stay
+Not seeing something yet? Features are rolling out over time and may vary by location and device.</t>
+        </is>
+      </c>
+      <c r="G690" t="inlineStr"/>
+      <c r="H690" t="inlineStr"/>
+      <c r="I690" t="inlineStr">
+        <is>
+          <t>https://dms.licdn.com/playlist/vid/v2/D4E05AQG6YhAr623RjQ/mp4-720p-30fp-crf28/B4EaDy9pbhKQB4-/0/1790782656219?e=1791392400&amp;v=beta&amp;t=8cbxzYDtjE14n8mBCDROsLtueitz8yr5zDUmRSy4nXY</t>
+        </is>
+      </c>
+      <c r="J690" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K690" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/airbnb_every-part-of-your-trip-is-now-the-easy-part-activity-7511092569448042496-Gt-h</t>
+        </is>
+      </c>
+      <c r="L690" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M690" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N690" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O690" t="inlineStr">
+        <is>
+          <t>Airbnb is launching a suite of new features to simplify trip planning, including social inspiration, natural language search, neighborhood previews, side‑by‑side home comparison, and curated services, with rollout phased by location and device.</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>AirBnb</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>2026-09-30T01:00:24.000Z</t>
+        </is>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maile finds a pet-friendly refuge after floods
+</t>
+        </is>
+      </c>
+      <c r="G691" t="inlineStr"/>
+      <c r="H691" t="inlineStr"/>
+      <c r="I691" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=VHFGJgCYqFI</t>
+        </is>
+      </c>
+      <c r="J691" t="inlineStr">
+        <is>
+          <t>[Failed to fetch]</t>
+        </is>
+      </c>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=VHFGJgCYqFI</t>
+        </is>
+      </c>
+      <c r="L691" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M691" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N691" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O691" t="inlineStr">
+        <is>
+          <t>Failed to analyze video transcript via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>AirBnb</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>2026-09-30T01:00:31.000Z</t>
+        </is>
+      </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t xml:space="preserve">For Marcos, a free stay helps provide the comforts of home as he battles cancer
+</t>
+        </is>
+      </c>
+      <c r="G692" t="inlineStr"/>
+      <c r="H692" t="inlineStr"/>
+      <c r="I692" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=kioyzrdRjjo</t>
+        </is>
+      </c>
+      <c r="J692" t="inlineStr">
+        <is>
+          <t>[Failed to fetch]</t>
+        </is>
+      </c>
+      <c r="K692" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=kioyzrdRjjo</t>
+        </is>
+      </c>
+      <c r="L692" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M692" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N692" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O692" t="inlineStr">
+        <is>
+          <t>Failed to analyze video transcript via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>AirBnb</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>2026-09-30T14:47:56.000Z</t>
+        </is>
+      </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New updates for hosts | Airbnb
+</t>
+        </is>
+      </c>
+      <c r="G693" t="inlineStr"/>
+      <c r="H693" t="inlineStr"/>
+      <c r="I693" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=xwDEPritpVM</t>
+        </is>
+      </c>
+      <c r="J693" t="inlineStr">
+        <is>
+          <t>[Failed to fetch]</t>
+        </is>
+      </c>
+      <c r="K693" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=xwDEPritpVM</t>
+        </is>
+      </c>
+      <c r="L693" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M693" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N693" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O693" t="inlineStr">
+        <is>
+          <t>Failed to analyze video transcript via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>Wed Sep 30 00:00:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>Looking for the best places to travel in December for warm weather? ☀️
+➡️ Dubai: Experience thrilling desert adventures, world-class dining, and sunny rooftop pools.
+➡️ Bangkok: Explore bustling night markets, taste authentic street food, and visit historic temples.
+➡️ Cancun: Relax by warm turquoise waters, white sand beaches, and luxury stays.
+🔗 Plan your travel:
+https://t.co/x2Acuyw4kH</t>
+        </is>
+      </c>
+      <c r="G694" t="inlineStr"/>
+      <c r="H694" t="inlineStr"/>
+      <c r="I694" t="inlineStr"/>
+      <c r="J694" t="inlineStr"/>
+      <c r="K694" t="inlineStr">
+        <is>
+          <t>https://x.com/Expedia/status/2105085214951198935</t>
+        </is>
+      </c>
+      <c r="L694" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M694" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N694" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O694" t="inlineStr">
+        <is>
+          <t>Expedia promotes warm December travel destinations—Dubai, Bangkok, and Cancun—encouraging bookings through a link.</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>2026-09-30T15:21:47.440Z</t>
+        </is>
+      </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>Ticket prices are up 15% for Thanksgiving and 20% for Christmas travel this year — but you don’t need a Christmas miracle to find a good deal.  
+𝗛𝗲𝗿𝗲 𝗮𝗿𝗲 𝟰 𝘄𝗮𝘆𝘀 𝘁𝗼 𝘀𝗮𝘃𝗲 𝗼𝗻 𝗵𝗼𝗹𝗶𝗱𝗮𝘆 𝘁𝗿𝗮𝘃𝗲𝗹 𝗶𝗻 𝟮𝟬𝟮𝟲: 
+  1. Expedia data found that travelers can save hundreds of dollars when booking by these dates: 
+  • 𝗧𝗵𝗮𝗻𝗸𝘀𝗴𝗶𝘃𝗶𝗻𝗴: Book by November 5 for domestic travel or October 15 for international travel. 
+  • 𝗖𝗵𝗿𝗶𝘀𝘁𝗺𝗮𝘀: Book by November 10 for domestic travel or December 1 for international travel. 
+  • 𝗡𝗲𝘄 𝗬𝗲𝗮𝗿’𝘀 𝗘𝘃𝗲: Book by November 7 for domestic travel or December 4 for international travel. 
+  2. 𝗔𝘃𝗼𝗶𝗱 𝘁𝗵𝗲𝘀𝗲 𝗽𝗲𝗮𝗸 𝘁𝗿𝗮𝘃𝗲𝗹 𝗱𝗮𝘁𝗲𝘀, 𝘄𝗵𝗶𝗰𝗵 𝗰𝗼𝗺𝗲 𝘄𝗶𝘁𝗵 𝘁𝗵𝗲 𝗵𝗶𝗴𝗵𝗲𝘀𝘁 𝗽𝗿𝗶𝗰𝗲 𝘁𝗮𝗴𝘀 — November 29th (the Sunday after Thanksgiving) and December 26 (the day after Christmas) have the highest average ticket prices during the holiday period.  
+  3. 𝗗𝗲𝗽𝗮𝗿𝘁 𝘁𝗵𝗲𝘀𝗲 𝗱𝗮𝘁𝗲𝘀 𝗶𝗻𝘀𝘁𝗲𝗮𝗱: Leave the Monday before Thanksgiving or fly on the holiday itself for the cheapest fares. Christmas Eve and Monday the 28th are the most affordable days around Christmas.  
+  4. 𝗡𝗲𝘄 𝗬𝗲𝗮𝗿’𝘀 𝘀𝗮𝘃𝗶𝗻𝗴 𝘁𝗶𝗽: Depart midweek after Christmas and return on NYE for the cheapest ticket prices. 
+Read Expedia’s 2026 Holiday Travel Outlook here for more tips to help you plan your holiday trip: http://ms.spr.ly/6046aYVm8</t>
+        </is>
+      </c>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D4E10AQG14bDgPvRasQ/image-shrink_1280/B4EaDy6CrYKsAg-/0/1790781697264?e=1791392400&amp;v=beta&amp;t=rfgqcjT3V4FBhK_vnA5HP1HADCsRsed35SJh1-HT-aI</t>
+        </is>
+      </c>
+      <c r="H695" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I695" t="inlineStr"/>
+      <c r="J695" t="inlineStr"/>
+      <c r="K695" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/expedia_ticket-prices-are-up-15-for-thanksgiving-activity-7511082878642921472-3Lfy</t>
+        </is>
+      </c>
+      <c r="L695" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M695" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N695" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O695" t="inlineStr">
+        <is>
+          <t>Expedia releases its 2026 Holiday Travel Outlook, highlighting price increases for Thanksgiving and Christmas but providing specific booking dates and travel strategies to help consumers save on holiday travel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>Wed Sep 30 13:39:17 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>@MoShafique97 Hi Mohammad, we have replied to your DM.</t>
+        </is>
+      </c>
+      <c r="G696" t="inlineStr"/>
+      <c r="H696" t="inlineStr"/>
+      <c r="I696" t="inlineStr"/>
+      <c r="J696" t="inlineStr"/>
+      <c r="K696" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105291395879546976</t>
+        </is>
+      </c>
+      <c r="L696" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M696" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N696" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O696" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a direct message from user @MoShafique97.</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>Wed Sep 30 13:00:25 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>@Smitherines161 Thank you for your response. To get through to an agent without the confirmation number, you can dial ##.</t>
+        </is>
+      </c>
+      <c r="G697" t="inlineStr"/>
+      <c r="H697" t="inlineStr"/>
+      <c r="I697" t="inlineStr"/>
+      <c r="J697" t="inlineStr"/>
+      <c r="K697" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105281614947176715</t>
+        </is>
+      </c>
+      <c r="L697" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M697" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N697" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O697" t="inlineStr">
+        <is>
+          <t>Booking.com replies to a user, explaining how to reach an agent without a confirmation number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>Wed Sep 30 12:42:19 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>@akhilpw @BaileysOfficial Hi Akhil, we regret to hear about the issues you've encountered. We've replied to your DM. Please take a look when you can.</t>
+        </is>
+      </c>
+      <c r="G698" t="inlineStr"/>
+      <c r="H698" t="inlineStr"/>
+      <c r="I698" t="inlineStr"/>
+      <c r="J698" t="inlineStr"/>
+      <c r="K698" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105277056841916797</t>
+        </is>
+      </c>
+      <c r="L698" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M698" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N698" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O698" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user’s complaint via direct message, acknowledging issues and offering assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>Wed Sep 30 12:39:02 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F699" t="inlineStr">
+        <is>
+          <t>Hi Fahad, we regret to hear about your experience. For us to help you here, please send us a private message with the following information:
+- Confirmation number:
+- Pin code:
+- Name on the reservation:
+We'll get back to you as soon as possible. Please bear in mind that our Social Media Team doesn't work in real time. For immediate support, please call our 24/7 Customer Service Team - our contact details can be found here: https://t.co/o8QyR8SaDb</t>
+        </is>
+      </c>
+      <c r="G699" t="inlineStr"/>
+      <c r="H699" t="inlineStr"/>
+      <c r="I699" t="inlineStr"/>
+      <c r="J699" t="inlineStr"/>
+      <c r="K699" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105276233839788129</t>
+        </is>
+      </c>
+      <c r="L699" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M699" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N699" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O699" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint, offering private message support and directing the user to their 24/7 customer service for immediate assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>Wed Sep 30 12:34:28 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F700" t="inlineStr">
+        <is>
+          <t>@Mukesh_3580 Hi Mukesh, thanks for reaching out to us.
+We regret hearing about your disappointing experience with the accommodation you booked. Please check your inbox, we have replied to your DM requesting further information from you. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G700" t="inlineStr"/>
+      <c r="H700" t="inlineStr"/>
+      <c r="I700" t="inlineStr"/>
+      <c r="J700" t="inlineStr"/>
+      <c r="K700" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105275084046848402</t>
+        </is>
+      </c>
+      <c r="L700" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M700" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N700" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O700" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint about a disappointing accommodation, apologizing and directing the user to check their inbox for further communication.</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>Wed Sep 30 12:32:07 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>Hello Rachaika, we regret to hear about your experience with the assistance and accommodation you booked. As we'd like to double check your claim, please DM the following information and avoid sharing any sensitive information such as the number of your reservation publically as unauthorized individuals could use them to perform actions without your approval. 
+- Confirmation number 
+- PIN 
+- Name shown on the reservation</t>
+        </is>
+      </c>
+      <c r="G701" t="inlineStr"/>
+      <c r="H701" t="inlineStr"/>
+      <c r="I701" t="inlineStr"/>
+      <c r="J701" t="inlineStr"/>
+      <c r="K701" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105274492968690154</t>
+        </is>
+      </c>
+      <c r="L701" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M701" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N701" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O701" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint, requesting sensitive booking details via DM and advising against public disclosure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>Wed Sep 30 11:58:56 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>Hola, sentimos que sigas a la espera de tu reembolso. Para poder evaluar tu caso, envíanos un mensaje privado con los siguientes datos y te responderemos lo antes posible:
+- Número de confirmación:
+- Código PIN:
+- Nombre que aparece en la reserva:
+- Detalles de tu solicitud:
+Ten en cuenta que nuestro equipo de Redes Sociales no trabaja en tiempo real. Para recibir ayuda inmediata, llama a nuestro equipo de Atención al Cliente disponible 24/7; puedes encontrar nuestros datos de contacto aquí:  https://t.co/o8QyR8SaDb
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G702" t="inlineStr"/>
+      <c r="H702" t="inlineStr"/>
+      <c r="I702" t="inlineStr"/>
+      <c r="J702" t="inlineStr"/>
+      <c r="K702" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105266140964331632</t>
+        </is>
+      </c>
+      <c r="L702" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M702" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N702" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O702" t="inlineStr">
+        <is>
+          <t>Booking.com is addressing a refund delay, requesting confirmation details via private message and offering phone support for immediate assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>Wed Sep 30 11:53:13 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>Hola Mónica, sentimos saber que piensas de esa manera, si deseas que lo revisemos desde aquí y está relacionado con una reserva de alojamiento, envíanos un mensaje privado con los siguientes datos y te responderemos lo antes posible:
+- Número de confirmación
+- Código PIN
+- Nombre del huésped
+- Detalles de tu solicitud
+Ten en cuenta que nuestro equipo de Redes Sociales no trabaja en tiempo real. Para recibir ayuda inmediata, llama a nuestro equipo de Atención al Cliente disponible 24/7; puedes encontrar nuestros datos de contacto aquí:  https://t.co/o8QyR8SaDb
+Además, por el momento solo ofrecemos soporte para reservas de alojamiento a través de las redes sociales. Para preguntas sobre Vuelos, Taxis o Seguros, puedes contactar con los equipos especializados aquí:  https://t.co/TBejpc4vOA. Un saludo.</t>
+        </is>
+      </c>
+      <c r="G703" t="inlineStr"/>
+      <c r="H703" t="inlineStr"/>
+      <c r="I703" t="inlineStr"/>
+      <c r="J703" t="inlineStr"/>
+      <c r="K703" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105264702787846247</t>
+        </is>
+      </c>
+      <c r="L703" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M703" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N703" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O703" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer inquiry in Spanish, offering private message details and phone contact for immediate assistance, limited to accommodation bookings via social media.</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>Wed Sep 30 11:15:53 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>@betto_carbone Ciao Benedetto, abbiamo risposto al tuo messaggio privato.</t>
+        </is>
+      </c>
+      <c r="G704" t="inlineStr"/>
+      <c r="H704" t="inlineStr"/>
+      <c r="I704" t="inlineStr"/>
+      <c r="J704" t="inlineStr"/>
+      <c r="K704" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105255306749997529</t>
+        </is>
+      </c>
+      <c r="L704" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M704" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N704" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O704" t="inlineStr">
+        <is>
+          <t>Booking.com responded to a private message from a user on X.</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>Wed Sep 30 08:38:14 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F705" t="inlineStr">
+        <is>
+          <t>@NicolettaYoung Please make sure to full read our messages, Nicoletta. We have explained everything to you in great details, please keep our advice in mind for future occasions. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G705" t="inlineStr"/>
+      <c r="H705" t="inlineStr"/>
+      <c r="I705" t="inlineStr"/>
+      <c r="J705" t="inlineStr"/>
+      <c r="K705" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105215631867904149</t>
+        </is>
+      </c>
+      <c r="L705" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M705" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N705" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O705" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user, urging them to read prior messages and heed advice for future interactions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>Wed Sep 30 08:34:31 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F706" t="inlineStr">
+        <is>
+          <t>Hi there, we regret to hear that you did not receive a refund for your Car Rental reservation.
+In order for us to assist, please send us a private message with the following details:
+- Booking number
+- Full Name of booker
+- Email address used to book
+- Your request
+We'll get back to you as soon as we can. Thank you.</t>
+        </is>
+      </c>
+      <c r="G706" t="inlineStr"/>
+      <c r="H706" t="inlineStr"/>
+      <c r="I706" t="inlineStr"/>
+      <c r="J706" t="inlineStr"/>
+      <c r="K706" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105214697880293502</t>
+        </is>
+      </c>
+      <c r="L706" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M706" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N706" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O706" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint about a missing car rental refund, requesting booking details via private message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>Wed Sep 30 08:27:20 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F707" t="inlineStr">
+        <is>
+          <t>We understand the urgency of this matter, Bhupesh. 
+While we appreciate that you have reached out to us here, we are, unfortunately, unable to help via Social Media. Your inquiry can only be addressed directly with our specialized team at the previously shared details.  
+Best regards</t>
+        </is>
+      </c>
+      <c r="G707" t="inlineStr"/>
+      <c r="H707" t="inlineStr"/>
+      <c r="I707" t="inlineStr"/>
+      <c r="J707" t="inlineStr"/>
+      <c r="K707" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105212888742875411</t>
+        </is>
+      </c>
+      <c r="L707" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M707" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N707" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O707" t="inlineStr">
+        <is>
+          <t>Booking.com replies to a user on X, explaining that they cannot assist via social media and directing the inquiry to a specialized team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>Wed Sep 30 08:00:17 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F708" t="inlineStr">
+        <is>
+          <t>@be38609 Hi Bella, we regret to hear that you are facing issues with your account. Please feel free to send a DM with the following information: 
+- your name 
+- name on the account 
+- email address 
+Looking forward to hearing from you.</t>
+        </is>
+      </c>
+      <c r="G708" t="inlineStr"/>
+      <c r="H708" t="inlineStr"/>
+      <c r="I708" t="inlineStr"/>
+      <c r="J708" t="inlineStr"/>
+      <c r="K708" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105206081576153526</t>
+        </is>
+      </c>
+      <c r="L708" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M708" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N708" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O708" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user’s account issue via direct message, offering to gather details to resolve the problem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>Wed Sep 30 07:59:45 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>@NicolettaYoung We understand your disappointment and have provided a detailed update in your Direct Messages. Please feel free to reply back to us there if you have any questions after taking a look.</t>
+        </is>
+      </c>
+      <c r="G709" t="inlineStr"/>
+      <c r="H709" t="inlineStr"/>
+      <c r="I709" t="inlineStr"/>
+      <c r="J709" t="inlineStr"/>
+      <c r="K709" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105205947249336733</t>
+        </is>
+      </c>
+      <c r="L709" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M709" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N709" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O709" t="inlineStr">
+        <is>
+          <t>Booking.com addresses a customer’s disappointment by offering a detailed update in direct messages and inviting further questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>Wed Sep 30 07:49:57 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>Hi there, as much as we'd like to assist you, we're unable to assist with Flight reservations through social media, but if you need support, you can contact our Flights team using this link: https://t.co/OVuF5pCzba or call {US}+1 917 421 7240 / {UK}+44 2039019061 / {IE} +353 19075677 / {AUS} +61 282281537.</t>
+        </is>
+      </c>
+      <c r="G710" t="inlineStr"/>
+      <c r="H710" t="inlineStr"/>
+      <c r="I710" t="inlineStr"/>
+      <c r="J710" t="inlineStr"/>
+      <c r="K710" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105203481871106430</t>
+        </is>
+      </c>
+      <c r="L710" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M710" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N710" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O710" t="inlineStr">
+        <is>
+          <t>Booking.com informs users that flight reservations cannot be handled via social media and directs them to contact the Flights team through a provided link or phone numbers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>Wed Sep 30 07:47:55 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>@ComleyMel As much as we would like to support you here, due to GDPR laws, only our specialized Flight team has access to your details and tools to assist you.</t>
+        </is>
+      </c>
+      <c r="G711" t="inlineStr"/>
+      <c r="H711" t="inlineStr"/>
+      <c r="I711" t="inlineStr"/>
+      <c r="J711" t="inlineStr"/>
+      <c r="K711" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105202969150918669</t>
+        </is>
+      </c>
+      <c r="L711" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M711" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N711" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O711" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user, explaining that GDPR restrictions prevent them from providing support outside their specialized flight team, limiting the assistance they can offer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>Wed Sep 30 07:47:16 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F712" t="inlineStr">
+        <is>
+          <t>Hola, lamentamos la demora en responder.
+No sabemos lo que ha ocurrido, y esperamos que nuestro equipo de atención a clientes les haya ofrecido una solución. Si aún hay algo pendiente o necesitan ayuda, envíanos un mensaje privado con los siguientes datos y te responderemos lo antes posible:
+- Número de confirmación:
+- Código PIN:
+- Nombre del huésped que aparece en la reserva:
+- Detalles de lo sucedido:
+Quedamos atentos.</t>
+        </is>
+      </c>
+      <c r="G712" t="inlineStr"/>
+      <c r="H712" t="inlineStr"/>
+      <c r="I712" t="inlineStr"/>
+      <c r="J712" t="inlineStr"/>
+      <c r="K712" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105202807183688178</t>
+        </is>
+      </c>
+      <c r="L712" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M712" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N712" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O712" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for a delayed response and invites customers to provide details via private message to resolve pending issues.</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>Wed Sep 30 07:42:18 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F713" t="inlineStr">
+        <is>
+          <t>@miguejim79 Hola Miguel Angel, no sabemos lo que ha ocurrido,pero estamos aquí para ayudarte. Envíanos por privado esta información y con gusto lo revisamos:
+- Número de confirmación:
+- Código PIN:
+- Nombre del huésped que aparece en la reserva: https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G713" t="inlineStr"/>
+      <c r="H713" t="inlineStr"/>
+      <c r="I713" t="inlineStr"/>
+      <c r="J713" t="inlineStr"/>
+      <c r="K713" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105201557620851109</t>
+        </is>
+      </c>
+      <c r="L713" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M713" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N713" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O713" t="inlineStr">
+        <is>
+          <t>Booking.com is responding to a user’s inquiry about a booking issue, offering assistance and requesting confirmation details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>Wed Sep 30 06:31:33 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F714" t="inlineStr">
+        <is>
+          <t>Bonjour Angélique, merci de nous avoir contactés. Sachez que nous aimerions vous apporter notre aide, mais nous ne sommes pas en mesure de gérer les réservations de billets d'avion via les réseaux sociaux, notre accès étant limité uniquement à la base de données des hébergements.
+Pour toute assistance, nous vous recommandons de contacter notre équipe spécialisée dans les vols en cliquant sur ce lien https://t.co/KkSQd8iIp6, ou en appelant le +6627873018/ {FR} +33 187 153 614 / {BE} +32 270 067 90. Ils sont les seuls à pouvoir accéder à votre dossier.
+Cordialement.</t>
+        </is>
+      </c>
+      <c r="G714" t="inlineStr"/>
+      <c r="H714" t="inlineStr"/>
+      <c r="I714" t="inlineStr"/>
+      <c r="J714" t="inlineStr"/>
+      <c r="K714" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105183753278554296</t>
+        </is>
+      </c>
+      <c r="L714" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M714" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N714" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O714" t="inlineStr">
+        <is>
+          <t>Booking.com informs a customer that it cannot process flight bookings through social media and directs them to a dedicated flight assistance team via a provided link.</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>Wed Sep 30 06:30:01 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F715" t="inlineStr">
+        <is>
+          <t>Olá, bom dia. Agradecemos pelo contato e sentimos saber que a sua chamada caiu durante um atendimento. Se ainda precisar de ajuda, pedimos que nos contate por DM com mais informações sobre o seu pedido, e nos forneça:
+• O seu número de confirmação
+• O código PIN
+• O nome do titular da reserva
+E te daremos um retorno breve.</t>
+        </is>
+      </c>
+      <c r="G715" t="inlineStr"/>
+      <c r="H715" t="inlineStr"/>
+      <c r="I715" t="inlineStr"/>
+      <c r="J715" t="inlineStr"/>
+      <c r="K715" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105183367448650049</t>
+        </is>
+      </c>
+      <c r="L715" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M715" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N715" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O715" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint about a dropped call, asking for confirmation details via DM to provide further assistance.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O715"/>
+  <dimension ref="A1:O722"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46231,6 +46231,484 @@
         </is>
       </c>
     </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>navan</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>Wed Sep 30 17:33:14 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F716" t="inlineStr">
+        <is>
+          <t>#blessed #grateful https://t.co/4np1VTFse2</t>
+        </is>
+      </c>
+      <c r="G716" t="inlineStr"/>
+      <c r="H716" t="inlineStr"/>
+      <c r="I716" t="inlineStr"/>
+      <c r="J716" t="inlineStr"/>
+      <c r="K716" t="inlineStr">
+        <is>
+          <t>https://x.com/Navan/status/2105350270523728110</t>
+        </is>
+      </c>
+      <c r="L716" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M716" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N716" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O716" t="inlineStr">
+        <is>
+          <t>Navan shares a brief post expressing gratitude, likely celebrating a recent milestone or achievement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>SAP Concur</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>SAP Concur</t>
+        </is>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>2026-09-29T18:11:20.000Z</t>
+        </is>
+      </c>
+      <c r="F717" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Safran - Quand un partenariat de 14 ans transforme la gestion hôtelière de 110 000 collaborateurs
+</t>
+        </is>
+      </c>
+      <c r="G717" t="inlineStr"/>
+      <c r="H717" t="inlineStr"/>
+      <c r="I717" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=zQRHHJJ1etI</t>
+        </is>
+      </c>
+      <c r="J717" t="inlineStr">
+        <is>
+          <t>[Failed to fetch]</t>
+        </is>
+      </c>
+      <c r="K717" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=zQRHHJJ1etI</t>
+        </is>
+      </c>
+      <c r="L717" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M717" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N717" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O717" t="inlineStr">
+        <is>
+          <t>Failed to analyze video transcript via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>Wed Sep 30 17:56:31 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F718" t="inlineStr">
+        <is>
+          <t>@aayan1405 Hey! Can you please submit a support request here?
+https://t.co/MKSwdEjYgh</t>
+        </is>
+      </c>
+      <c r="G718" t="inlineStr"/>
+      <c r="H718" t="inlineStr"/>
+      <c r="I718" t="inlineStr"/>
+      <c r="J718" t="inlineStr"/>
+      <c r="K718" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2105356127890460765</t>
+        </is>
+      </c>
+      <c r="L718" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M718" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N718" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O718" t="inlineStr">
+        <is>
+          <t>Ramp is directing a user to submit a support request via a provided link.</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>Wed Sep 30 17:44:44 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F719" t="inlineStr">
+        <is>
+          <t>@nzgb https://t.co/T87RTytGll</t>
+        </is>
+      </c>
+      <c r="G719" t="inlineStr"/>
+      <c r="H719" t="inlineStr"/>
+      <c r="I719" t="inlineStr"/>
+      <c r="J719" t="inlineStr"/>
+      <c r="K719" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2105353163490435251</t>
+        </is>
+      </c>
+      <c r="L719" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M719" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N719" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O719" t="inlineStr">
+        <is>
+          <t>Ramp shares a link to a partnership announcement with @nzgb.</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>Wed Sep 30 16:22:47 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F720" t="inlineStr">
+        <is>
+          <t>@ExtendHQ Turns out smaller can be smarter.</t>
+        </is>
+      </c>
+      <c r="G720" t="inlineStr"/>
+      <c r="H720" t="inlineStr"/>
+      <c r="I720" t="inlineStr"/>
+      <c r="J720" t="inlineStr"/>
+      <c r="K720" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2105332540714233939</t>
+        </is>
+      </c>
+      <c r="L720" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M720" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N720" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O720" t="inlineStr">
+        <is>
+          <t>Brex highlights the benefits of smaller solutions, referencing its partnership with ExtendHQ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>AirBnb</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>airbnb</t>
+        </is>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>2026-09-30T16:01:42.000Z</t>
+        </is>
+      </c>
+      <c r="F721" t="inlineStr">
+        <is>
+          <t>Just launched: features that take the work out of taking a vacation.
+Not seeing something yet? Features are rolling out over time and may vary by location and device.
+Now you can connect with friends, family, and people you’ve traveled with on Airbnb.
+See where your connections have been on your travel map.
+Check out their itineraries and message them for more recommendations.
+Got a trip in mind? Just describe it like you would to a friend to find what you’re looking for faster.
+No more jumping between tabs. Yeah, we said it.
+See what stands out about each home to help you pick the right one.
+Not sure which area suits you best? Check it out before you book.
+See what to do, where to eat, and how to get around.
+Now you can get meals delivered, rent baby gear, and schedule laundry pickup and delivery.
+We already have trip envy.</t>
+        </is>
+      </c>
+      <c r="G721" t="inlineStr">
+        <is>
+          <t>https://instagram.fgrq1-1.fna.fbcdn.net/v/t51.82787-15/831828509_18639792367063838_9147376891600579829_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=102&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5NzcwODY1NTg5MzUzODQxNQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuNzIwLnNkci52aWRlb19kZWZhdWx0X2NvdmVyX2ZyYW1lLkMzIn0%3D&amp;_nc_ohc=eQZem9FNwfEQ7kNvwGlbXrg&amp;_nc_oc=AdqYU8ujvGqCYJYlnAAP8trK5cZACz6Jee49M8nMb0BNK2B59rY0Zd1_54_uPcfZQ70&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fgrq1-1.fna&amp;_nc_gid=Zmu0FQ7wIYQcuKX0SfUJYQ&amp;_nc_ss=7a22e&amp;oh=00_AQMzFI1dB3U50pIiOYTjRE5lb6bY5aaElQYl6SgnSfg21g&amp;oe=6AC33C2E</t>
+        </is>
+      </c>
+      <c r="H721" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I721" t="inlineStr"/>
+      <c r="J721" t="inlineStr"/>
+      <c r="K721" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dd6t2UpFLsO/</t>
+        </is>
+      </c>
+      <c r="L721" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M721" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N721" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O721" t="inlineStr">
+        <is>
+          <t>Airbnb introduces a suite of new features designed to streamline vacation planning, from social connections and itinerary sharing to local services and personalized recommendations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>TripGenie</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>trip</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>2026-09-30T09:03:07.000Z</t>
+        </is>
+      </c>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t>Buried in the mountains just beyond Beijing lies a place history has completely forgotten about.
+Welcome to Guyaju. Over a thousand years ago an entire community lived here, carved into the side of a cliff. Today it stands empty. And we still don't know who they were.
+I booked my train, hotel and entry ticket all through the Trip.com app to get out here. Stayed at Seventy Tangquan Rezen Hotel — mountain views and a private hot spring. The perfect reset after a day like this.
+Comment CAVE and I'll send you everything you need.
+Planning your trip with @trip.
+Disclaimer: The history in this video is based on publicly available sources and local interpretations. Guyaju's origins are still debated by archaeologists and the figures and theories mentioned are for reference only.
+#Chinatravel #tripcom #Chinatrip #Beijing #Guyaju</t>
+        </is>
+      </c>
+      <c r="G722" t="inlineStr">
+        <is>
+          <t>https://instagram.fstu1-1.fna.fbcdn.net/v/t51.82787-15/825324548_18628283221002228_4027426385189726132_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=104&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5NzQ5ODA0MDIwOTQ1OTQ0ODE4NjI4MjgzMjE4MDAyMjI4.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNMSVBTLnhwaWRzLjEwODAuc2RyLnZpZGVvX2RlZmF1bHRfY292ZXJfZnJhbWUuQzMifQ%3D%3D&amp;_nc_ohc=8J-TGLERwQEQ7kNvwEZTNIp&amp;_nc_oc=AdrXVU5EOa_ZVSIcCptM9B2NSo8-zqyEEgmNzHCnzwyBZS1M-i_7KH1IoIKri5IEIw0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fstu1-1.fna&amp;_nc_gid=JDR0pEyKtPwBEhiGGfXoPQ&amp;_nc_ss=7a22e&amp;oh=00_AQP13EzR4MFwPmPe4TKMlaZWarKcQb1LSgUeWWJQfK-KfQ&amp;oe=6AC32596</t>
+        </is>
+      </c>
+      <c r="H722" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I722" t="inlineStr">
+        <is>
+          <t>https://instagram.fstu1-1.fna.fbcdn.net/o1/v/t2/f2/m86/AQN_A3sCUCgnOWqBVpq92QufckZhIVdonXHNnrE6e5RxMduvwvaS2ype0ZEKN10cf0SH3wyVDChdyCU5qDGs7koq1FVt6R_P2Pzs5c4.mp4?_nc_cat=101&amp;_nc_oc=AdpP1PCgxUJmIxNbapVTb4W5niL9HzdglYQOr57QbJppCW7HjQUqAMe6rJL9QjtsxTA&amp;_nc_sid=5e9851&amp;_nc_ht=instagram.fstu1-1.fna.fbcdn.net&amp;_nc_ohc=FpXCfMZJWqcQ7kNvwEBC_MQ&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTg2MjgyODMwNTYwMDIyMjgsImFzc2V0X2FnZV9kYXlzIjowLCJ2aV91c2VjYXNlX2lkIjoxMDA5OSwiZHVyYXRpb25fcyI6OTAsInVybGdlbl9zb3VyY2UiOiJ3d3cifQ%3D%3D&amp;ccb=17-1&amp;vs=54d43ad832d8c7b0&amp;_nc_vs=HBksFQIYUmlnX3hwdl9yZWVsc19wZXJtYW5lbnRfc3JfcHJvZC83M0U2MUMxNEI2NTk0QkY0ODY3OEI5RUUwNjI3MTkxMF92aWRlb19kYXNoaW5pdC5tcDQVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0M0QkJBRTY1NDlBRjQ4NDc4QTQ2RUJBN0Y3MzYyRTI5X2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbo0qCl5JSXQhUCKAJDMywXQFaAAAAAAAAYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=JDR0pEyKtPwBEhiGGfXoPQ&amp;_nc_ss=70a8c&amp;_nc_map=urlgen_bucketless&amp;_nc_zt=28&amp;oh=00_AQNxjjxnKk0Q4QvpALD-u8bqceV8lL78Q3OsPf8P0yNbwQ&amp;oe=6ABF1CCE</t>
+        </is>
+      </c>
+      <c r="J722" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K722" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dd590m1AUj4/</t>
+        </is>
+      </c>
+      <c r="L722" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M722" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N722" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O722" t="inlineStr">
+        <is>
+          <t>TripGenie promotes the Trip.com app for booking trips to the hidden mountain destination Guyaju, highlighting a unique travel experience and encouraging audience engagement.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O722"/>
+  <dimension ref="A1:O756"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46709,6 +46709,2195 @@
         </is>
       </c>
     </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>navan</t>
+        </is>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>Thu Oct 01 15:14:42 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F723" t="inlineStr">
+        <is>
+          <t>Register Now: https://t.co/KPoWka75Uk</t>
+        </is>
+      </c>
+      <c r="G723" t="inlineStr"/>
+      <c r="H723" t="inlineStr"/>
+      <c r="I723" t="inlineStr"/>
+      <c r="J723" t="inlineStr"/>
+      <c r="K723" t="inlineStr">
+        <is>
+          <t>https://x.com/Navan/status/2105677792633295148</t>
+        </is>
+      </c>
+      <c r="L723" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M723" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N723" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O723" t="inlineStr">
+        <is>
+          <t>Navan is promoting a registration link, likely for an upcoming event or webinar related to its products.</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>navan</t>
+        </is>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>Thu Oct 01 15:14:41 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>Does your travel and expense program feel like a monster stitched together from disconnected tools and vendors?
+On October 28, join us for "T&amp;E Frankenstack: How Two Companies Made the Switch."
+No ghost stories, just lessons on how @CCSFundraising  and @Kobalt escaped fragmented systems, navigated the transition, and put their T&amp;E nightmares to rest.</t>
+        </is>
+      </c>
+      <c r="G724" t="inlineStr"/>
+      <c r="H724" t="inlineStr"/>
+      <c r="I724" t="inlineStr"/>
+      <c r="J724" t="inlineStr"/>
+      <c r="K724" t="inlineStr">
+        <is>
+          <t>https://x.com/Navan/status/2105677789739246074</t>
+        </is>
+      </c>
+      <c r="L724" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M724" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N724" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O724" t="inlineStr">
+        <is>
+          <t>Navan is promoting a webinar titled "T&amp;E Frankenstack" to showcase how two companies transitioned to their T&amp;E solution, positioning it as a remedy for fragmented travel and expense systems.</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>2026-10-01T15:12:16.604Z</t>
+        </is>
+      </c>
+      <c r="F725" t="inlineStr">
+        <is>
+          <t>Does your travel and expense program feel like a monster 🧟‍♂️ stitched together from disconnected tools and vendors?
+On October 28, join Jane Gould, Shara DArbeau, and Fausto Chavez for Escape the "T&amp;E Frankenstack: How Two Companies Made the Switch."
+No ghost stories, just lessons on how CCS Fundraising and Kobalt Music escaped fragmented systems, navigated the transition, and put their T&amp;E nightmares to rest.
+Register now: https://lnkd.in/eUVsh7QH</t>
+        </is>
+      </c>
+      <c r="G725" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D4E22AQGoianbmK45Dg/feedshare-image-high-res/B4EaD4BfPSGQAU-/0/1790867535414?e=1792627200&amp;v=beta&amp;t=Vu6ITWvuMpVoV9f82tFx_C2WDpVZ5jYnHxqLdfSUrkU</t>
+        </is>
+      </c>
+      <c r="H725" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I725" t="inlineStr"/>
+      <c r="J725" t="inlineStr"/>
+      <c r="K725" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/navan_does-your-travel-and-expense-program-feel-activity-7511442872248852481-VheM</t>
+        </is>
+      </c>
+      <c r="L725" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M725" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N725" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O725" t="inlineStr">
+        <is>
+          <t>Navan is promoting a webinar titled "Escape the T&amp;E Frankenstack" to showcase how their solution helps companies transition from fragmented travel and expense systems to a unified platform.</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E726" t="inlineStr">
+        <is>
+          <t>Thu Oct 01 14:47:43 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F726" t="inlineStr">
+        <is>
+          <t>@kevskgs merch is on point</t>
+        </is>
+      </c>
+      <c r="G726" t="inlineStr"/>
+      <c r="H726" t="inlineStr"/>
+      <c r="I726" t="inlineStr"/>
+      <c r="J726" t="inlineStr"/>
+      <c r="K726" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2105671002634191066</t>
+        </is>
+      </c>
+      <c r="L726" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M726" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N726" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O726" t="inlineStr">
+        <is>
+          <t>Ramp is positively mentioned for its merchandise by user @kevskgs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>Thu Oct 01 16:00:02 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F727" t="inlineStr">
+        <is>
+          <t>Terms and conditions apply. No purchase necessary. US residents 18+. Void in NY, FL, RI &amp;amp; where prohibited. See more details here: https://t.co/KcOZoIK8N4</t>
+        </is>
+      </c>
+      <c r="G727" t="inlineStr"/>
+      <c r="H727" t="inlineStr"/>
+      <c r="I727" t="inlineStr"/>
+      <c r="J727" t="inlineStr"/>
+      <c r="K727" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2105689203908751706</t>
+        </is>
+      </c>
+      <c r="L727" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M727" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N727" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O727" t="inlineStr">
+        <is>
+          <t>Brex is promoting a promotional offer with standard terms and conditions, no purchase necessary, targeting US residents.</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>Thu Oct 01 16:00:02 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F728" t="inlineStr">
+        <is>
+          <t>Founders, we see the hustle and we're here to help keep it going. Comment "fuel" for a chance to win a premium espresso machine. https://t.co/0JE5PjNa6t</t>
+        </is>
+      </c>
+      <c r="G728" t="inlineStr"/>
+      <c r="H728" t="inlineStr"/>
+      <c r="I728" t="inlineStr"/>
+      <c r="J728" t="inlineStr"/>
+      <c r="K728" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2105689203216675215</t>
+        </is>
+      </c>
+      <c r="L728" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M728" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N728" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O728" t="inlineStr">
+        <is>
+          <t>Brex promotes its support for founders by running a contest offering a premium espresso machine, reinforcing its brand’s focus on entrepreneurial hustle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>Thu Oct 01 01:13:55 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F729" t="inlineStr">
+        <is>
+          <t>@michwirantono Hard to beat a weekend with builders.</t>
+        </is>
+      </c>
+      <c r="G729" t="inlineStr"/>
+      <c r="H729" t="inlineStr"/>
+      <c r="I729" t="inlineStr"/>
+      <c r="J729" t="inlineStr"/>
+      <c r="K729" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2105466206341726505</t>
+        </is>
+      </c>
+      <c r="L729" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M729" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N729" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O729" t="inlineStr">
+        <is>
+          <t>Brex posts a casual note about enjoying a weekend with builders, highlighting positive engagement with the builder community.</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>Wed Sep 30 18:42:48 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F730" t="inlineStr">
+        <is>
+          <t>@startupideaspod https://t.co/0Isj7YgfA9</t>
+        </is>
+      </c>
+      <c r="G730" t="inlineStr"/>
+      <c r="H730" t="inlineStr"/>
+      <c r="I730" t="inlineStr"/>
+      <c r="J730" t="inlineStr"/>
+      <c r="K730" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2105367776961671664</t>
+        </is>
+      </c>
+      <c r="L730" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M730" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N730" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O730" t="inlineStr">
+        <is>
+          <t>Brex shares a link to a podcast episode featuring @startupideaspod.</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>TripGenie</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>trip</t>
+        </is>
+      </c>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>2026-10-01T09:00:12.000Z</t>
+        </is>
+      </c>
+      <c r="F731" t="inlineStr">
+        <is>
+          <t>Drums, strings, and five thousand years of stories — the 2026 Chinese Opera Gala has filled #Kunshan with 348 opera genres 🎭
+From #Zhouzhuang's canals to #Suzhou's gardens, from #Nanjing's ancient walls to #Yangzhou's elegance and #Wuxi's lakeside calm, every city in #Jiangsu holds its own rhythm, its own dream. And those folk melodies keep rippling on ✨
+Come and experience the culture, then stay for the serenity and flavors 🏯🍜
+#JiangsuTravel #ChineseOpera #VisitChina #Tripcom</t>
+        </is>
+      </c>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>https://scontent-dus1-1.cdninstagram.com/v/t39.30808-6/829299579_1639067121594693_6020376821527731139_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk5ODIyMTg2MDg4OTk3MzEzOQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=WfHVFumGFpsQ7kNvwH4-e_I&amp;_nc_oc=AdqAiPFFxeQS7aolZq9voNMwwzEjXNCiq1MJSW6yl5h8WdcxsHo3yB6rK2xiPvBEcrwgmzOWn-OSKpsCc7NANzCw&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dus1-1.cdninstagram.com&amp;_nc_gid=3iM00pE2EKISPxgT2HemMw&amp;_nc_ss=7a22e&amp;oh=00_AQNAbDRKSwps-rbv728vAkU5CJf6GZFb2IYR-8ENB6BU9A&amp;oe=6AC462AD</t>
+        </is>
+      </c>
+      <c r="H731" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I731" t="inlineStr"/>
+      <c r="J731" t="inlineStr"/>
+      <c r="K731" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dd8iZ_fDJGS/</t>
+        </is>
+      </c>
+      <c r="L731" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M731" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N731" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O731" t="inlineStr">
+        <is>
+          <t>TripGenie promotes the 2026 Chinese Opera Gala across Jiangsu, showcasing cultural diversity and inviting travelers to experience local opera, scenery, and cuisine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>TripGenie</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>trip</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>2026-10-01T09:00:08.000Z</t>
+        </is>
+      </c>
+      <c r="F732" t="inlineStr">
+        <is>
+          <t>China has 61 UNESCO World Heritage sites, the second-most of any country, and this list barely scratches the surface. Which one is on your list?
+👍Visit our bio for more travel inspirations and deals.
+🤩Follow us to get more travel inspirations @trip.
+#china #unesco #chinatravel #worldheritage #tripcom</t>
+        </is>
+      </c>
+      <c r="G732" t="inlineStr">
+        <is>
+          <t>https://scontent-fra3-1.cdninstagram.com/v/t39.30808-6/802680641_1622344189933653_2566711351090172636_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=101&amp;ig_cache_key=Mzk5ODIyMTgzNDc3NjA3OTMyMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=nzOvAKFcv_oQ7kNvwHtwEvn&amp;_nc_oc=AdozS60d9YfiDIELHCYYBL9e72a2u6lVk8edKG5RZTp9pipDZ5fpG4O9cdH4Yt_AzuU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fra3-1.cdninstagram.com&amp;_nc_gid=K_9kFObYG_TAaylBouNSGg&amp;_nc_ss=7a22e&amp;oh=00_AQNQ6JKvRF4z2yNYSHQB_emigHDTVoCiAKATw8xlqnPeMQ&amp;oe=6AC450F1</t>
+        </is>
+      </c>
+      <c r="H732" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I732" t="inlineStr"/>
+      <c r="J732" t="inlineStr"/>
+      <c r="K732" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dd8iZdViaaC/</t>
+        </is>
+      </c>
+      <c r="L732" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M732" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N732" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O732" t="inlineStr">
+        <is>
+          <t>TripGenie promotes China’s UNESCO World Heritage sites to inspire travel, inviting followers to explore more in their bio and encouraging engagement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>Thu Oct 01 00:00:01 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F733" t="inlineStr">
+        <is>
+          <t>Discover timeless charm, coastal cliffs, and legendary hospitality in Ireland. 🇮🇪
+➡️ The sights: Marvel at the dramatic drops and ocean views along the towering Cliffs of Moher.
+➡️ The drives: Journey around the scenic Ring of Kerry past emerald hills, historic castles, and quiet lakes.
+➡️ The stays: Live like royalty in a historic castle hotel or unwind in a cozy countryside B&amp;B.
+🔗 Plan your travel:
+https://t.co/QDpRZbmfui</t>
+        </is>
+      </c>
+      <c r="G733" t="inlineStr"/>
+      <c r="H733" t="inlineStr"/>
+      <c r="I733" t="inlineStr"/>
+      <c r="J733" t="inlineStr"/>
+      <c r="K733" t="inlineStr">
+        <is>
+          <t>https://x.com/Expedia/status/2105447606008611053</t>
+        </is>
+      </c>
+      <c r="L733" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M733" t="inlineStr">
+        <is>
+          <t>Strategic Expansion or Changes</t>
+        </is>
+      </c>
+      <c r="N733" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O733" t="inlineStr">
+        <is>
+          <t>Expedia is promoting Ireland travel experiences, showcasing scenic attractions and accommodations to attract travelers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>expedia</t>
+        </is>
+      </c>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>2026-09-30T23:11:08.000Z</t>
+        </is>
+      </c>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>There’s no better time to explore Ireland than fall. Save this one-week itinerary from us to experience the ultimate fall getaway. #IrelandPartner
+Dive into Halloween’s birthplace at the Púca Festival in Meath County. While you’re there, step inside Newgrange tombs that outdate the Egyptian pyramids.
+Head to County Wicklow for vibrant foliage at Mount Usher Gardens and a scenic bike ride through the countryside. Refuel with a traditional meal at Roundwood Inn.
+Dedicate two days to County Kerry’s rugged beauty, hiking the stunning Gap of Dunloe. Unwind afterward with local favorites and a pint at Hilliard’s Pub.
+Spend a thrilling day in Derry-Londonderry marveling at the cliffside Mussenden Temple. As night falls, join the massive Derry Halloween street party.
+Spend a quiet day admiring County Carlow’s scenic landscapes and the sprawling ruins of Duckett’s Grove. Step House Hotel and O’Shea’s Pub will keep you well-fed.
+Ready to pack your bags for Ireland? Save this post to start planning your fall getaway, and follow along for more Expedia travel guides.</t>
+        </is>
+      </c>
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>https://scontent-fco2-1.cdninstagram.com/v/t51.82787-15/830632258_18641234377030381_7542818549249701532_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk5NzkyNDE2MTEyNDkyMzA3Mg%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMTA4MC5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=Jju-yq3qNb0Q7kNvwF6EANR&amp;_nc_oc=AdoOkN9EuMzcPLwbnB72FKIMoyVE0KpoPtSx0RULOhbXGjrx4XrcWHuXX0fYa1xQMW0&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-fco2-1.cdninstagram.com&amp;_nc_gid=l38u4yAkIAkC31nSAoTSbg&amp;_nc_ss=7a22e&amp;oh=00_AQPONhzNFfZh25lUDE5Vv_nB5uiYIO-SdD3FbuyvMTakeA&amp;oe=6AC46EAB</t>
+        </is>
+      </c>
+      <c r="H734" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I734" t="inlineStr"/>
+      <c r="J734" t="inlineStr"/>
+      <c r="K734" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dd7e_fAj9FV/</t>
+        </is>
+      </c>
+      <c r="L734" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M734" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N734" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O734" t="inlineStr">
+        <is>
+          <t>Expedia promotes a one‑week fall itinerary in Ireland, highlighting festivals, historic sites, scenic gardens, and local pubs, urging followers to save the post and plan a getaway.</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>Thu Oct 01 15:54:57 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>@JaredJaredMedia We've sent you a DM with more information regarding your case. Please review it and get back to us. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G735" t="inlineStr"/>
+      <c r="H735" t="inlineStr"/>
+      <c r="I735" t="inlineStr"/>
+      <c r="J735" t="inlineStr"/>
+      <c r="K735" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105687925077737888</t>
+        </is>
+      </c>
+      <c r="L735" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M735" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N735" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O735" t="inlineStr">
+        <is>
+          <t>Booking.com sent a private message to a user regarding a case, requesting review of additional information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>Thu Oct 01 15:04:42 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>Hi Olanrewaju, we regret to hear about a pending refund. 
+To assist you, please send us a private message with the following details, and we will get back to you as soon as possible: 
+- Confirmation number 
+- PIN code 
+- Full name of the guest confirmed on the booking 
+- Details of your request</t>
+        </is>
+      </c>
+      <c r="G736" t="inlineStr"/>
+      <c r="H736" t="inlineStr"/>
+      <c r="I736" t="inlineStr"/>
+      <c r="J736" t="inlineStr"/>
+      <c r="K736" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105675277074411957</t>
+        </is>
+      </c>
+      <c r="L736" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M736" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N736" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O736" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a pending refund request, asking the customer to provide booking details via private message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>Thu Oct 01 14:19:14 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F737" t="inlineStr">
+        <is>
+          <t>Hi there, thank you for contacting us regarding your car rental reservation. We regret to hear that you did not make it with car rental. 
+In order for us to assist, please send us a private message with the following details: 
+- Booking number 
+- Name of booker 
+- Email address used to book 
+- Your request 
+We'll get back to you as soon as we can. Thank you.</t>
+        </is>
+      </c>
+      <c r="G737" t="inlineStr"/>
+      <c r="H737" t="inlineStr"/>
+      <c r="I737" t="inlineStr"/>
+      <c r="J737" t="inlineStr"/>
+      <c r="K737" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105663836086747475</t>
+        </is>
+      </c>
+      <c r="L737" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M737" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N737" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O737" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer inquiry about a car rental reservation, requesting booking details via private message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>Thu Oct 01 13:28:46 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>@Ronica609 Hi Veronica, unfortunately we're unable to assist with Flight reservations through social media, but you can contact our Flights team here: https://t.co/BfbildlU73, or call {US}+1 917 421 7240 / {UK}+44 2039019061 / {IE} +353 19075677</t>
+        </is>
+      </c>
+      <c r="G738" t="inlineStr"/>
+      <c r="H738" t="inlineStr"/>
+      <c r="I738" t="inlineStr"/>
+      <c r="J738" t="inlineStr"/>
+      <c r="K738" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105651136535404643</t>
+        </is>
+      </c>
+      <c r="L738" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M738" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N738" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O738" t="inlineStr">
+        <is>
+          <t>Booking.com informs a user that flight reservations cannot be handled via social media and directs them to the Flights team contact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>Thu Oct 01 12:55:27 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F739" t="inlineStr">
+        <is>
+          <t>Bonjour Jerome, nous vous remercions de nous avoir contactés, veuillez pardonner notre réponse tardive. Nous sommes vraiment au regret d'apprendre que des dégâts ont été causés dans vos hébergements. Nous comprenons que vous espériez obtenir une assistance en nous contactant et sachez que nous aimerions vous aider. Cependant, pour des raisons de sécurité et de confidentialité, nous ne fournissons aucune assistance aux partenaires sur les réseaux sociaux. 
+Nous vous recommandons donc de recontacter notre équipe d'assistance partenaire qui est disponible 24h/24 et 7j/7. Voici les informations nécessaires pour les contacter : https://t.co/NwbHxvAhmK 
+Ils seront en mesure de vous aider, notamment en vous informant sur les outils que nous mettons à disposition pour soutenir nos partenaires, y compris l'établissement d'un dépôt de garantie pour vous protéger contre d'éventuels dommages à vos biens. 
+Cordialement</t>
+        </is>
+      </c>
+      <c r="G739" t="inlineStr"/>
+      <c r="H739" t="inlineStr"/>
+      <c r="I739" t="inlineStr"/>
+      <c r="J739" t="inlineStr"/>
+      <c r="K739" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105642750439760234</t>
+        </is>
+      </c>
+      <c r="L739" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M739" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N739" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O739" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for a partner’s reported damages and directs them to its dedicated partner support channels for assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>Thu Oct 01 12:53:10 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>Hi Annie, we regret to learn that you have not yet received a reply regarding your claim. To help you with this, please send us a direct message containing the following information, and we will respond to you as soon as we can:
+- Confirmation number
+- PIN code
+- Name on the reservation
+- Details on your request</t>
+        </is>
+      </c>
+      <c r="G740" t="inlineStr"/>
+      <c r="H740" t="inlineStr"/>
+      <c r="I740" t="inlineStr"/>
+      <c r="J740" t="inlineStr"/>
+      <c r="K740" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105642178642878806</t>
+        </is>
+      </c>
+      <c r="L740" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M740" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N740" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O740" t="inlineStr">
+        <is>
+          <t>Booking.com is responding to a customer claim, requesting confirmation details via direct message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>Thu Oct 01 12:32:40 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F741" t="inlineStr">
+        <is>
+          <t>Hi Kartik, thanks for contacting us.
+We can look into this for you.
+Did you receive a message saying the booking couldn't be confirmed? If that's the case, you'll receive an automatic refund within 12 business days. Otherwise, it's also possible you made a typo when entering your email address, as you wouldn't receive the confirmation email afterwards. If you share the following details with us via DM, we'll look into our system to see if we can locate a booking:
+- name of the accommodation
+- dates of stay
+- full guest name
+We will get back to you as soon as we can.</t>
+        </is>
+      </c>
+      <c r="G741" t="inlineStr"/>
+      <c r="H741" t="inlineStr"/>
+      <c r="I741" t="inlineStr"/>
+      <c r="J741" t="inlineStr"/>
+      <c r="K741" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105637017484718081</t>
+        </is>
+      </c>
+      <c r="L741" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M741" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N741" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O741" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user’s booking issue, offering troubleshooting steps and refund information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>Thu Oct 01 11:19:46 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F742" t="inlineStr">
+        <is>
+          <t>Hi Gayathree, thanks for your message, and we regret learning that you're still waiting on your refund. In order to look into it for you, we kindly ask you to reach out to us in private with:
+• Confirmation number:
+• PIN code:
+• Guest name on the reservation:
+And we will get back to you as soon as possible. Keep in mind, our Social Media Team does not work in real time, for immediate support you can call our 24/7 Customer Service Team here: https://t.co/o8QyR8SaDb.</t>
+        </is>
+      </c>
+      <c r="G742" t="inlineStr"/>
+      <c r="H742" t="inlineStr"/>
+      <c r="I742" t="inlineStr"/>
+      <c r="J742" t="inlineStr"/>
+      <c r="K742" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105618669774454959</t>
+        </is>
+      </c>
+      <c r="L742" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M742" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N742" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O742" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a refund inquiry, requesting confirmation details and offering 24/7 customer support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>Thu Oct 01 10:13:35 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F743" t="inlineStr">
+        <is>
+          <t>@Ankitgoyal23242 We've sent another DM, please check and get back. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G743" t="inlineStr"/>
+      <c r="H743" t="inlineStr"/>
+      <c r="I743" t="inlineStr"/>
+      <c r="J743" t="inlineStr"/>
+      <c r="K743" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105602017175486631</t>
+        </is>
+      </c>
+      <c r="L743" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M743" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N743" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O743" t="inlineStr">
+        <is>
+          <t>Booking.com posted a message to user @Ankitgoyal23242, requesting them to check a direct message and respond.</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>Thu Oct 01 10:10:08 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F744" t="inlineStr">
+        <is>
+          <t>@and2917 Hola, no podemos ayudarte con reservas de Vuelos a través de las redes sociales, pero puedes contactar con nuestro equipo de Vuelos aquí: https://t.co/BfbildlU73, o llamar al +34918362949 desde España de lunes a domingo de 9:00-21:00 hora local.</t>
+        </is>
+      </c>
+      <c r="G744" t="inlineStr"/>
+      <c r="H744" t="inlineStr"/>
+      <c r="I744" t="inlineStr"/>
+      <c r="J744" t="inlineStr"/>
+      <c r="K744" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105601147666907303</t>
+        </is>
+      </c>
+      <c r="L744" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M744" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N744" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O744" t="inlineStr">
+        <is>
+          <t>Booking.com informs a user that flight bookings cannot be handled via social media and directs them to contact the flight team via link or phone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>Thu Oct 01 10:02:22 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F745" t="inlineStr">
+        <is>
+          <t>@Rebecca51545089 Hi Rebecca, we’ve responded to your DM. Please take a look when you have a chance. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G745" t="inlineStr"/>
+      <c r="H745" t="inlineStr"/>
+      <c r="I745" t="inlineStr"/>
+      <c r="J745" t="inlineStr"/>
+      <c r="K745" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105599192861196637</t>
+        </is>
+      </c>
+      <c r="L745" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M745" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N745" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O745" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s direct message, showing routine customer engagement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E746" t="inlineStr">
+        <is>
+          <t>Thu Oct 01 09:50:02 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F746" t="inlineStr">
+        <is>
+          <t>Hello there, we regret to hear that you have been charged a higher amount compared to the one confirmed. Please DM a brief summary of your claim together with the following information, and we'll assist you further: 
+- booking number
+- pin code
+- full name of the guest on the reservation
+Regards</t>
+        </is>
+      </c>
+      <c r="G746" t="inlineStr"/>
+      <c r="H746" t="inlineStr"/>
+      <c r="I746" t="inlineStr"/>
+      <c r="J746" t="inlineStr"/>
+      <c r="K746" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105596090779123729</t>
+        </is>
+      </c>
+      <c r="L746" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M746" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N746" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O746" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for a customer being charged a higher amount than confirmed and requests the booking number, pin code, and guest name via DM to resolve the issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>Thu Oct 01 09:23:44 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F747" t="inlineStr">
+        <is>
+          <t>@ninadthe9 Hi Ninad, while we appreciate that you have reached out to us here, we are, unfortunately, unable to help via Social Media. Your inquiry can only be addressed directly with our specialized team at the previously shared details.</t>
+        </is>
+      </c>
+      <c r="G747" t="inlineStr"/>
+      <c r="H747" t="inlineStr"/>
+      <c r="I747" t="inlineStr"/>
+      <c r="J747" t="inlineStr"/>
+      <c r="K747" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105589469860569318</t>
+        </is>
+      </c>
+      <c r="L747" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M747" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N747" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O747" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user on X, informing them that the inquiry cannot be handled via social media and directing them to contact a specialized team through previously shared details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>Thu Oct 01 08:51:50 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F748" t="inlineStr">
+        <is>
+          <t>@Ankitgoyal23242 We've sent you a DM with more information regarding your case. Please review it and get back to us. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G748" t="inlineStr"/>
+      <c r="H748" t="inlineStr"/>
+      <c r="I748" t="inlineStr"/>
+      <c r="J748" t="inlineStr"/>
+      <c r="K748" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105581444462453235</t>
+        </is>
+      </c>
+      <c r="L748" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M748" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N748" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O748" t="inlineStr">
+        <is>
+          <t>Booking.com sent a direct message to a user regarding their case, requesting the user to review the information and respond.</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E749" t="inlineStr">
+        <is>
+          <t>Thu Oct 01 08:50:28 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F749" t="inlineStr">
+        <is>
+          <t>@moses_alexander Hi Moses, we're unable to assist with Flight reservations through social media, but you can contact our Flights team here: https://t.co/BfbildlU73, or call {US}+1 917 421 7240 / {UK}+44 2039019061 / {IE} +353 19075677</t>
+        </is>
+      </c>
+      <c r="G749" t="inlineStr"/>
+      <c r="H749" t="inlineStr"/>
+      <c r="I749" t="inlineStr"/>
+      <c r="J749" t="inlineStr"/>
+      <c r="K749" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105581098130391126</t>
+        </is>
+      </c>
+      <c r="L749" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M749" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N749" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O749" t="inlineStr">
+        <is>
+          <t>Booking.com informs a user that flight reservations cannot be handled via social media and directs them to the Flights team contact details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>Thu Oct 01 07:25:16 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F750" t="inlineStr">
+        <is>
+          <t>Hola, gracias por escribirnos.
+No tenemos información precisa sobre lo sucedido con la cancelación de tu reserva, sin embargo, nos gustaría revisarlo para brindarte una respuesta y determinar cómo podemos ayudarte.
+Comparte con nosotros por mensaje privado la siguiente información y te responderemos lo antes posible: 
+- Número de confirmación
+- Código PIN
+- Nombre del huésped en la reserva
+Ten en cuenta que nuestro equipo de Redes Sociales no opera en tiempo real. Para asistencia inmediata puedes comunicarte con nuestro equipo de atención al cliente, disponible las 24 horas, aquí: https://t.co/tuuNbmGVaG
+Saludos.</t>
+        </is>
+      </c>
+      <c r="G750" t="inlineStr"/>
+      <c r="H750" t="inlineStr"/>
+      <c r="I750" t="inlineStr"/>
+      <c r="J750" t="inlineStr"/>
+      <c r="K750" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105559655908864369</t>
+        </is>
+      </c>
+      <c r="L750" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M750" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N750" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O750" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user’s inquiry about a reservation cancellation, offering to review the issue and directing them to private messaging and 24‑hour customer support for further assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>Thu Oct 01 07:23:33 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F751" t="inlineStr">
+        <is>
+          <t>@Ankitgoyal23242 Hi Ankit, you can send us a DM with this link or by going to our account and selecting the message option. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G751" t="inlineStr"/>
+      <c r="H751" t="inlineStr"/>
+      <c r="I751" t="inlineStr"/>
+      <c r="J751" t="inlineStr"/>
+      <c r="K751" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105559225048908012</t>
+        </is>
+      </c>
+      <c r="L751" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M751" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N751" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O751" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user, offering instructions on how to send a direct message or use the account’s message option.</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>Thu Oct 01 06:55:35 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F752" t="inlineStr">
+        <is>
+          <t>@rajwanshi_26851 Hi Sunny, we have just replied to you via DM. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G752" t="inlineStr"/>
+      <c r="H752" t="inlineStr"/>
+      <c r="I752" t="inlineStr"/>
+      <c r="J752" t="inlineStr"/>
+      <c r="K752" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105552188432875593</t>
+        </is>
+      </c>
+      <c r="L752" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M752" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N752" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O752" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user via direct message on X.</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>Thu Oct 01 06:49:35 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F753" t="inlineStr">
+        <is>
+          <t>Hola Gerardo, lamentamos escuchar tu opinión sobre nuestro servicio. Si una reserva no cuenta con cancelación gratuita, dependemos del alojamiento para tomar la decisión de eliminar cargos de penalización o no. En ese sentido, nos es difícil darte un tiempo estimado de respuesta. En todo caso, envíanos un mensaje privado con los siguientes datos y con gusto le damos seguimiento:
+- Número de confirmación:
+- Código PIN:
+- Nombre del huésped que aparece en la reserva:</t>
+        </is>
+      </c>
+      <c r="G753" t="inlineStr"/>
+      <c r="H753" t="inlineStr"/>
+      <c r="I753" t="inlineStr"/>
+      <c r="J753" t="inlineStr"/>
+      <c r="K753" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105550675853664600</t>
+        </is>
+      </c>
+      <c r="L753" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M753" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N753" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O753" t="inlineStr">
+        <is>
+          <t>Booking.com replies to a customer complaint about a reservation without free cancellation, explaining that penalty charges depend on the accommodation and requests confirmation details for further assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E754" t="inlineStr">
+        <is>
+          <t>Thu Oct 01 06:44:42 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F754" t="inlineStr">
+        <is>
+          <t>Hi there, how can we help? If your request is related to an accommodation booking, please DM us the following details and we'll get back to you as soon as possible: 
+- Confirmation number:
+- Pin code:
+- Name on the reservation:
+- Details on your request:
+Please bear in mind that our Social Media Team doesn't work in real time. For immediate support, please call our 24/7 Customer Service Team - our contact details can be found here: https://t.co/o8QyR8SaDb
+Also, at this time, we only offer support for accommodation bookings via social media. For questions about Flights, Taxis, or Insurance, you can reach out to the dedicated support team here: https://t.co/UfRgpDJomK</t>
+        </is>
+      </c>
+      <c r="G754" t="inlineStr"/>
+      <c r="H754" t="inlineStr"/>
+      <c r="I754" t="inlineStr"/>
+      <c r="J754" t="inlineStr"/>
+      <c r="K754" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105549447685914945</t>
+        </is>
+      </c>
+      <c r="L754" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M754" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N754" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O754" t="inlineStr">
+        <is>
+          <t>Booking.com outlines its social media support process for accommodation bookings, directs other inquiries to dedicated teams, and provides contact details for immediate assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="E755" t="inlineStr">
+        <is>
+          <t>2026-10-01T07:31:01.886Z</t>
+        </is>
+      </c>
+      <c r="F755" t="inlineStr">
+        <is>
+          <t>What happens when 15M people click "book" daily? 🚀
+Stefan, a Software Engineer in Manchester, explains how his team handles the backend complexity instantly. 💻 From payment processing to availability checks, we build stable, scalable systems. But what keeps him coming back? The people.
+Explore open roles and join us today. 👇
+https://lnkd.in/eZw5fWVA</t>
+        </is>
+      </c>
+      <c r="G755" t="inlineStr"/>
+      <c r="H755" t="inlineStr"/>
+      <c r="I755" t="inlineStr">
+        <is>
+          <t>https://dms.licdn.com/playlist/vid/v2/D4E10AQGz3uVFDpWjKA/mp4-720p-30fp-crf28/B4EaDzQZ15H4Bk-/0/1790787572259?e=1791478800&amp;v=beta&amp;t=IEyDNSzExeRGhx7UksLTxX8036rrl4xiAWJNctQIgdc</t>
+        </is>
+      </c>
+      <c r="J755" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K755" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/booking%2Ecom_what-happens-when-15m-people-click-book-activity-7511326796068352000-1vdt</t>
+        </is>
+      </c>
+      <c r="L755" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M755" t="inlineStr">
+        <is>
+          <t>Tech Updates</t>
+        </is>
+      </c>
+      <c r="N755" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O755" t="inlineStr">
+        <is>
+          <t>Booking.com showcases its robust backend engineering capabilities handling millions of daily bookings and invites software engineers to join its team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>SkyBirdTravel</t>
+        </is>
+      </c>
+      <c r="E756" t="inlineStr">
+        <is>
+          <t>Thu Oct 01 02:54:41 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F756" t="inlineStr">
+        <is>
+          <t>With SKY Vacations, you can earn up to 12% commission on custom-crafted tours designed around your clients’ travel dreams.
+Ready to create something unforgettable? Contact us to start planning.
+#TravelAdvisor #CustomTravel #LuxuryTravel #TravelProfessionals https://t.co/wzBHeovOKZ</t>
+        </is>
+      </c>
+      <c r="G756" t="inlineStr"/>
+      <c r="H756" t="inlineStr"/>
+      <c r="I756" t="inlineStr"/>
+      <c r="J756" t="inlineStr"/>
+      <c r="K756" t="inlineStr">
+        <is>
+          <t>https://x.com/SkyBirdTravel/status/2105491564726542757</t>
+        </is>
+      </c>
+      <c r="L756" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M756" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N756" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O756" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel is promoting its SKY Vacations program, offering up to 12% commission on custom‑crafted tours for travel advisors.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O756"/>
+  <dimension ref="A1:O762"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48898,6 +48898,388 @@
         </is>
       </c>
     </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E757" t="inlineStr">
+        <is>
+          <t>Thu Oct 01 18:12:12 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F757" t="inlineStr">
+        <is>
+          <t>@rajshreesharma Hi Rajshree, we have replied to your DM. Please check your inbox at your earliest convenience. Thank you.</t>
+        </is>
+      </c>
+      <c r="G757" t="inlineStr"/>
+      <c r="H757" t="inlineStr"/>
+      <c r="I757" t="inlineStr"/>
+      <c r="J757" t="inlineStr"/>
+      <c r="K757" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105722465829765433</t>
+        </is>
+      </c>
+      <c r="L757" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M757" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N757" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O757" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a private DM from user Rajshree Sharma, directing them to check their inbox.</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E758" t="inlineStr">
+        <is>
+          <t>Thu Oct 01 18:04:50 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F758" t="inlineStr">
+        <is>
+          <t>@texasmolonlabe Hi Douglas, we have sent you a private message regarding your inquiry. Please check your messages for further assistance. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G758" t="inlineStr"/>
+      <c r="H758" t="inlineStr"/>
+      <c r="I758" t="inlineStr"/>
+      <c r="J758" t="inlineStr"/>
+      <c r="K758" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105720608034058437</t>
+        </is>
+      </c>
+      <c r="L758" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M758" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N758" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O758" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s inquiry, directing them to check their private messages for further assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E759" t="inlineStr">
+        <is>
+          <t>Thu Oct 01 18:01:08 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F759" t="inlineStr">
+        <is>
+          <t>Hi Ohad, 
+Thank you for getting back to us. We understand how frustrating this must be, especially since you've already contacted our Flights team through VIP Support, sent messages, and emailed them, but have not yet received a response. 
+However, due to GDPR regulations, only our specialized team has access to your information and the tools required to assist you with this matter. As such, we can only advise you to contact them again using the numbers previously provided. 
+We understand this may not be the answer you were hoping for, and we appreciate your patience and understanding. 
+Kind regards,</t>
+        </is>
+      </c>
+      <c r="G759" t="inlineStr"/>
+      <c r="H759" t="inlineStr"/>
+      <c r="I759" t="inlineStr"/>
+      <c r="J759" t="inlineStr"/>
+      <c r="K759" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105719679033417911</t>
+        </is>
+      </c>
+      <c r="L759" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M759" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N759" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O759" t="inlineStr">
+        <is>
+          <t>Booking.com replies to a customer complaint about unresponsive flights support, citing GDPR restrictions and directing the customer to contact the specialized team again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>SkyBirdTravel</t>
+        </is>
+      </c>
+      <c r="E760" t="inlineStr">
+        <is>
+          <t>Thu Oct 01 18:09:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F760" t="inlineStr">
+        <is>
+          <t>Travel lighter in India ✈️🧳 
+ Skip luggage hassle with BagDrop’s Airport→Home delivery. Secure handling, free pickup + bubble wrap, 24/7 support, and up to 62% savings vs checked bags. Travel advisors enjoy 10% off!
+#TravelAdvisors #BagDrop  #TravelSmarter #HassleFreeTravel https://t.co/H6Bt9U1MIf</t>
+        </is>
+      </c>
+      <c r="G760" t="inlineStr"/>
+      <c r="H760" t="inlineStr"/>
+      <c r="I760" t="inlineStr"/>
+      <c r="J760" t="inlineStr"/>
+      <c r="K760" t="inlineStr">
+        <is>
+          <t>https://x.com/SkyBirdTravel/status/2105721656828441008</t>
+        </is>
+      </c>
+      <c r="L760" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M760" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N760" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O760" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel promotes BagDrop’s airport‑to‑home luggage delivery service in India, highlighting secure handling, free pickup, savings up to 62% versus checked bags, and a 10% discount for travel advisors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel &amp; Tours</t>
+        </is>
+      </c>
+      <c r="E761" t="inlineStr">
+        <is>
+          <t>2026-10-01T18:07:29.540Z</t>
+        </is>
+      </c>
+      <c r="F761" t="inlineStr">
+        <is>
+          <t>Travel lighter and let your clients enjoy a seamless arrival in India.
+✈️🧳 With BagDrop’s airport-to-home baggage delivery service, travelers can skip the hassle of hauling luggage and have it delivered safely to their destination. Plus, travel advisors receive a 10% discount on every booking. With free pickup and bubble wrap, 24/7 support, secure handling, and savings of up to 62% compared to checked baggage, it’s a smarter way to travel. 
+#TravelAdvisors #BagDrop #TravelToIndia #BaggageDelivery #TravelSmarter #SkyBirdTravel #IndiaTravel #HassleFreeTravel</t>
+        </is>
+      </c>
+      <c r="G761" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D4D22AQGNSRORQQbR_g/feedshare-image-high-res/B4DaD4pl79GkAU-/0/1790878048457?e=1792627200&amp;v=beta&amp;t=WyoDra5CJu0axI-fqGkJ340fZ3WD1t7EEUjL_XFdQHg</t>
+        </is>
+      </c>
+      <c r="H761" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I761" t="inlineStr"/>
+      <c r="J761" t="inlineStr"/>
+      <c r="K761" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/sky-bird-travel-tours_traveladvisors-bagdrop-traveltoindia-activity-7511486966698430464-QYFz</t>
+        </is>
+      </c>
+      <c r="L761" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M761" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N761" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O761" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel promotes BagDrop’s airport‑to‑home baggage delivery service, offering travel advisors a 10% booking discount and highlighting free pickup, bubble wrap, 24/7 support, and cost savings up to 62%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E762" t="inlineStr">
+        <is>
+          <t>Thu Oct 01 18:23:47 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F762" t="inlineStr">
+        <is>
+          <t>@Ronica609 We understand your frustration, Veronica. For GDPR reasons, only our specialized team has access to your information and the tools required to help. Kind Regards, https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G762" t="inlineStr"/>
+      <c r="H762" t="inlineStr"/>
+      <c r="I762" t="inlineStr"/>
+      <c r="J762" t="inlineStr"/>
+      <c r="K762" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105725376961839468</t>
+        </is>
+      </c>
+      <c r="L762" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M762" t="inlineStr">
+        <is>
+          <t>Tech Updates</t>
+        </is>
+      </c>
+      <c r="N762" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O762" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents responds to a user’s frustration about GDPR access, explaining that only a specialized team can handle the request.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O762"/>
+  <dimension ref="A1:O787"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49280,6 +49280,1610 @@
         </is>
       </c>
     </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="E763" t="inlineStr">
+        <is>
+          <t>2026-10-01T19:13:07.180Z</t>
+        </is>
+      </c>
+      <c r="F763" t="inlineStr">
+        <is>
+          <t>The FOMO is real. Navigate Europe is officially full! Missed out on Paris? We’ll see you in New York on April 15, 2027.</t>
+        </is>
+      </c>
+      <c r="G763" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D5622AQHvJQ9AA-KlIg/feedshare-image-high-res/B56aD44nQQJIAU-/0/1790881985806?e=1792627200&amp;v=beta&amp;t=MwnY0huLAs7vOgZM1aGfhH7Cke7YrekT9RtKlhDX_MQ</t>
+        </is>
+      </c>
+      <c r="H763" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I763" t="inlineStr"/>
+      <c r="J763" t="inlineStr"/>
+      <c r="K763" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/navan_the-fomo-is-real-navigate-europe-is-officially-activity-7511503482357694464-KsA-</t>
+        </is>
+      </c>
+      <c r="L763" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M763" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N763" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O763" t="inlineStr">
+        <is>
+          <t>Navan announces that its Navigate Europe event is fully booked and will host a new event in New York on April 15, 2027.</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E764" t="inlineStr">
+        <is>
+          <t>Thu Oct 01 20:16:41 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F764" t="inlineStr">
+        <is>
+          <t>@HaiTa Nothing like a little time on the water.</t>
+        </is>
+      </c>
+      <c r="G764" t="inlineStr"/>
+      <c r="H764" t="inlineStr"/>
+      <c r="I764" t="inlineStr"/>
+      <c r="J764" t="inlineStr"/>
+      <c r="K764" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2105753789609177596</t>
+        </is>
+      </c>
+      <c r="L764" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M764" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N764" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O764" t="inlineStr">
+        <is>
+          <t>Brex employee shares a casual tweet about enjoying time on the water.</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E765" t="inlineStr">
+        <is>
+          <t>Thu Oct 01 18:22:02 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F765" t="inlineStr">
+        <is>
+          <t>@MollySOShea https://t.co/DOPD564Dyj</t>
+        </is>
+      </c>
+      <c r="G765" t="inlineStr"/>
+      <c r="H765" t="inlineStr"/>
+      <c r="I765" t="inlineStr"/>
+      <c r="J765" t="inlineStr"/>
+      <c r="K765" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2105724937650557029</t>
+        </is>
+      </c>
+      <c r="L765" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M765" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N765" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O765" t="inlineStr">
+        <is>
+          <t>Brex appears to be announcing a new partnership or collaboration involving Molly S. O'Shea, indicating a strategic alliance or joint initiative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E766" t="inlineStr">
+        <is>
+          <t>Fri Oct 02 00:00:01 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F766" t="inlineStr">
+        <is>
+          <t>Set off on an extraordinary desert adventure through the wild landscapes of Namibia. 🇳🇦
+➡️ The dunes: Climb the towering red sand dunes of Sossusvlei and photograph the surreal trees of Deadvlei.
+➡️ The wildlife: Safari through Etosha National Park to track free-roaming lions, elephants, and rhinos.
+➡️ The stays: Spend the night stargazing at an eco-lodge or camping under the clear desert skies.
+🔗 Plan your travel:
+https://t.co/AaMOmCk5EK</t>
+        </is>
+      </c>
+      <c r="G766" t="inlineStr"/>
+      <c r="H766" t="inlineStr"/>
+      <c r="I766" t="inlineStr"/>
+      <c r="J766" t="inlineStr"/>
+      <c r="K766" t="inlineStr">
+        <is>
+          <t>https://x.com/Expedia/status/2105809992846659611</t>
+        </is>
+      </c>
+      <c r="L766" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M766" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N766" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O766" t="inlineStr">
+        <is>
+          <t>Expedia is promoting a desert adventure package in Namibia, highlighting dunes, wildlife, and eco-lodge stays, with a link to book the trip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E767" t="inlineStr">
+        <is>
+          <t>Fri Oct 02 13:22:06 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F767" t="inlineStr">
+        <is>
+          <t>Hi Vishal, we regret to hear that the pictures posted of the hotel did not match. 
+For us to be able to look into this, we kindly ask you to DM us the following booking details: 
+- Confirmation Number
+- Pin Code
+- Name of the Guest 
+We'll than get back to you as soon as possible.</t>
+        </is>
+      </c>
+      <c r="G767" t="inlineStr"/>
+      <c r="H767" t="inlineStr"/>
+      <c r="I767" t="inlineStr"/>
+      <c r="J767" t="inlineStr"/>
+      <c r="K767" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2106011844930408620</t>
+        </is>
+      </c>
+      <c r="L767" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M767" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N767" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O767" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint about mismatched hotel photos, requesting booking details via DM for investigation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E768" t="inlineStr">
+        <is>
+          <t>Fri Oct 02 13:13:47 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F768" t="inlineStr">
+        <is>
+          <t>En este momento, no tenemos constancia de ninguna incidencia que esté afectando a hacer la cancelación de reservas. Te sugerimos que realices lo siguiente: 
+- App: Elimínala y descárgala de nuevo 
+- Web: Prueba con otro navegador, borra el caché, las cookies y el historial de navegación, usa un dispositivo diferente, utiliza una ventana privada/de incógnito 
+Esperamos que estos pasos te ayuden. 
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G768" t="inlineStr"/>
+      <c r="H768" t="inlineStr"/>
+      <c r="I768" t="inlineStr"/>
+      <c r="J768" t="inlineStr"/>
+      <c r="K768" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2106009751398080802</t>
+        </is>
+      </c>
+      <c r="L768" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M768" t="inlineStr">
+        <is>
+          <t>Tech Updates</t>
+        </is>
+      </c>
+      <c r="N768" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O768" t="inlineStr">
+        <is>
+          <t>Booking.com informs users that there is no known incident affecting reservation cancellations and provides troubleshooting steps.</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E769" t="inlineStr">
+        <is>
+          <t>Fri Oct 02 13:00:41 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F769" t="inlineStr">
+        <is>
+          <t>@fedearieutsi Desde España puedes comunicarte al +34918362949 de 9 AM a 9 PM de lunes a domingo.</t>
+        </is>
+      </c>
+      <c r="G769" t="inlineStr"/>
+      <c r="H769" t="inlineStr"/>
+      <c r="I769" t="inlineStr"/>
+      <c r="J769" t="inlineStr"/>
+      <c r="K769" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2106006457170739315</t>
+        </is>
+      </c>
+      <c r="L769" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M769" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N769" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O769" t="inlineStr">
+        <is>
+          <t>Booking.com posts contact details for Spanish customers, offering a phone number and operating hours.</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E770" t="inlineStr">
+        <is>
+          <t>Fri Oct 02 12:53:41 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F770" t="inlineStr">
+        <is>
+          <t>Hi there, it is normal for properties to ask for the bank details of the guests who they want to refund. As long as you do not share sensitive information that would compromise you, it is ok to cooperate with the property to get your refund. Should you need further help, please DM us and we will assist in any way possible.</t>
+        </is>
+      </c>
+      <c r="G770" t="inlineStr"/>
+      <c r="H770" t="inlineStr"/>
+      <c r="I770" t="inlineStr"/>
+      <c r="J770" t="inlineStr"/>
+      <c r="K770" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2106004693654626741</t>
+        </is>
+      </c>
+      <c r="L770" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M770" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N770" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O770" t="inlineStr">
+        <is>
+          <t>Booking.com informs guests that it is normal for properties to request bank details for refunds and offers assistance via direct message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E771" t="inlineStr">
+        <is>
+          <t>Fri Oct 02 12:40:34 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F771" t="inlineStr">
+        <is>
+          <t>Hola, gracias por contactarnos con respecto a tu reserva de alquiler de autos. 
+Para poder ayudarte, envíanos un mensaje privado con los siguientes datos: 
+- Número de reserva 
+- Nombre de quien reservó 
+- Correo electrónico utilizado para la reserva 
+- Tu solicitud 
+Te responderemos lo antes posible. Gracias.</t>
+        </is>
+      </c>
+      <c r="G771" t="inlineStr"/>
+      <c r="H771" t="inlineStr"/>
+      <c r="I771" t="inlineStr"/>
+      <c r="J771" t="inlineStr"/>
+      <c r="K771" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2106001393358148069</t>
+        </is>
+      </c>
+      <c r="L771" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M771" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N771" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O771" t="inlineStr">
+        <is>
+          <t>Booking.com replies to a car‑rental reservation inquiry, asking the customer to send reservation details via private message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E772" t="inlineStr">
+        <is>
+          <t>Fri Oct 02 12:20:29 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F772" t="inlineStr">
+        <is>
+          <t>@FAHADALJALAIDAN Hi there, we have just responded to your DM. Please, check. Thank you.</t>
+        </is>
+      </c>
+      <c r="G772" t="inlineStr"/>
+      <c r="H772" t="inlineStr"/>
+      <c r="I772" t="inlineStr"/>
+      <c r="J772" t="inlineStr"/>
+      <c r="K772" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105996338869502401</t>
+        </is>
+      </c>
+      <c r="L772" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M772" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N772" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O772" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s direct message, indicating routine customer support engagement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E773" t="inlineStr">
+        <is>
+          <t>Fri Oct 02 12:14:07 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F773" t="inlineStr">
+        <is>
+          <t>@therealmissjo Hi there, if you want us to look into this for you and see what happened, please DM us with the requested information. Thank you.</t>
+        </is>
+      </c>
+      <c r="G773" t="inlineStr"/>
+      <c r="H773" t="inlineStr"/>
+      <c r="I773" t="inlineStr"/>
+      <c r="J773" t="inlineStr"/>
+      <c r="K773" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105994737148694534</t>
+        </is>
+      </c>
+      <c r="L773" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M773" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N773" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O773" t="inlineStr">
+        <is>
+          <t>Booking.com replies to a user, offering to investigate a reported issue via direct message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E774" t="inlineStr">
+        <is>
+          <t>Fri Oct 02 11:45:59 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F774" t="inlineStr">
+        <is>
+          <t>Hola, lamentamos escuchar que esta ha sido tu experiencia. 
+Aunque nos gustaría asistir, en redes sociales tenemos acceso únicamente para reservas de alojamiento. En el siguiente enlace encontrarás la información de contacto de nuestro equipo de atención al cliente para reservas de vuelo: https://t.co/0VBK0krD8X
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G774" t="inlineStr"/>
+      <c r="H774" t="inlineStr"/>
+      <c r="I774" t="inlineStr"/>
+      <c r="J774" t="inlineStr"/>
+      <c r="K774" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105987657020957133</t>
+        </is>
+      </c>
+      <c r="L774" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M774" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N774" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O774" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for a negative customer experience and directs the user to flight reservation support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E775" t="inlineStr">
+        <is>
+          <t>Fri Oct 02 11:27:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F775" t="inlineStr">
+        <is>
+          <t>@shoutnwhisper Hi there, We've responded to your dm. Please have a look.</t>
+        </is>
+      </c>
+      <c r="G775" t="inlineStr"/>
+      <c r="H775" t="inlineStr"/>
+      <c r="I775" t="inlineStr"/>
+      <c r="J775" t="inlineStr"/>
+      <c r="K775" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105982881742954976</t>
+        </is>
+      </c>
+      <c r="L775" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M775" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N775" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O775" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a direct message from user @shoutnwhisper, acknowledging receipt and inviting them to review the response.</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E776" t="inlineStr">
+        <is>
+          <t>Fri Oct 02 10:57:50 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F776" t="inlineStr">
+        <is>
+          <t>Sentimos que tengas dificultades para cancelar tus reservas. Si se tratan de reservas de alojamiento, puedes cancelarlas desde tu correo de confirmación, nuestra app o la página web de https://t.co/fGhmZE7riF. Se aplicará la política de cancelación que seleccionaste al hacer la reserva. Cada alojamiento gestiona sus propias condiciones, así que cuando se solicita una cancelación fuera de las condiciones, solo el alojamiento puede aprobarla como excepción mediante una confirmación por escrito.
+Podemos contactar al alojamiento en tu nombre si nos envías un mensaje privado con los siguientes datos:
+- Número de confirmación:
+- Código PIN:
+- Nombre que aparece en la reserva:
+Como alternativa, si necesitas asistencia inmediata, siempre puedes llamarnos aquí: https://t.co/tuuNbmGVaG
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G776" t="inlineStr"/>
+      <c r="H776" t="inlineStr"/>
+      <c r="I776" t="inlineStr"/>
+      <c r="J776" t="inlineStr"/>
+      <c r="K776" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105975540641333667</t>
+        </is>
+      </c>
+      <c r="L776" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M776" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N776" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O776" t="inlineStr">
+        <is>
+          <t>Booking.com explains how users can cancel reservations, detailing the process, applicable cancellation policies, and offering support via private messages or phone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E777" t="inlineStr">
+        <is>
+          <t>Fri Oct 02 10:52:41 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F777" t="inlineStr">
+        <is>
+          <t>Bonjour Maxime, merci de nous avoir contactés ici. Sachez que nous aimerions vous apporter notre aide, mais nous ne sommes pas en mesure de gérer les réservations de billets d'avion via les réseaux sociaux, notre accès étant limité uniquement à la base de données des hébergements.
+Pour toute assistance, nous vous recommandons de contacter notre équipe spécialisée dans les vols ici : https://t.co/KkSQd8iIp6, ou en appelant le +6627873018/ {FR} +33 187 153 614 / {BE} +32 270 067 90.
+Nous comprenons que cela ne soit peut-être pas la réponse que vous espériez, mais seul le service dédié aux vols a la possibilité d'accéder à votre réservation pour vous transmettre le statut de votre dossier.
+Cordialement.</t>
+        </is>
+      </c>
+      <c r="G777" t="inlineStr"/>
+      <c r="H777" t="inlineStr"/>
+      <c r="I777" t="inlineStr"/>
+      <c r="J777" t="inlineStr"/>
+      <c r="K777" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105974244576248106</t>
+        </is>
+      </c>
+      <c r="L777" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M777" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N777" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O777" t="inlineStr">
+        <is>
+          <t>Booking.com informs a user that it cannot process flight bookings through social media and directs them to a dedicated flight booking team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E778" t="inlineStr">
+        <is>
+          <t>Fri Oct 02 10:18:40 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F778" t="inlineStr">
+        <is>
+          <t>Hi there, we regret learning that you're still waiting for support. As much as we'd like to assist you, we're unable to assist with Flight reservations through social media, but if you need support, you can contact our Flights team using this link: https://t.co/OVuF5pCzba or call {US}+1 917 421 7240 / {UK}+44 2039019061 / {IE} +353 19075677 / {AUS} +61 282281537.</t>
+        </is>
+      </c>
+      <c r="G778" t="inlineStr"/>
+      <c r="H778" t="inlineStr"/>
+      <c r="I778" t="inlineStr"/>
+      <c r="J778" t="inlineStr"/>
+      <c r="K778" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105965683443945736</t>
+        </is>
+      </c>
+      <c r="L778" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M778" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N778" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O778" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint about delayed flight support, directing them to a dedicated Flights team and providing contact details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E779" t="inlineStr">
+        <is>
+          <t>Fri Oct 02 10:00:06 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F779" t="inlineStr">
+        <is>
+          <t>Sentimos que tengas dificultades con tu cuenta, que las opciones de asistencia no estés claras y haber tardado en responder, David. Para poder revisarlo y ayudarte, envíanos un mensaje privado con la dirección de correo asociada a tu cuenta de https://t.co/fGhmZE7riF y tu nombre completo.
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G779" t="inlineStr"/>
+      <c r="H779" t="inlineStr"/>
+      <c r="I779" t="inlineStr"/>
+      <c r="J779" t="inlineStr"/>
+      <c r="K779" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105961012402741567</t>
+        </is>
+      </c>
+      <c r="L779" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M779" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N779" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O779" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes to a user for account difficulties and requests a private message with the associated email and full name for assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E780" t="inlineStr">
+        <is>
+          <t>Fri Oct 02 09:25:36 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F780" t="inlineStr">
+        <is>
+          <t>@FisherRock008 Hi there, we've replied to your DM.</t>
+        </is>
+      </c>
+      <c r="G780" t="inlineStr"/>
+      <c r="H780" t="inlineStr"/>
+      <c r="I780" t="inlineStr"/>
+      <c r="J780" t="inlineStr"/>
+      <c r="K780" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105952330680008863</t>
+        </is>
+      </c>
+      <c r="L780" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M780" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N780" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O780" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s direct message on X.</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E781" t="inlineStr">
+        <is>
+          <t>Fri Oct 02 09:00:11 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F781" t="inlineStr">
+        <is>
+          <t>@therealmissjo Hi there, that does not sound good. Please, confirm the following information via DM so we can look into this for you: 
+- booking number 
+- pin code
+- guest name 
+We will get back to you asap. Thank you.</t>
+        </is>
+      </c>
+      <c r="G781" t="inlineStr"/>
+      <c r="H781" t="inlineStr"/>
+      <c r="I781" t="inlineStr"/>
+      <c r="J781" t="inlineStr"/>
+      <c r="K781" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105945932512579874</t>
+        </is>
+      </c>
+      <c r="L781" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M781" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N781" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O781" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user’s complaint via direct message, requesting booking details to investigate the issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E782" t="inlineStr">
+        <is>
+          <t>Fri Oct 02 08:52:10 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F782" t="inlineStr">
+        <is>
+          <t>Sentimos que hayas recibido ese mensaje a través de WhatsApp, Javi. Si quieres que lo revisemos, envíanos un mensaje privado con los siguientes datos y nos pondremos en contacto contigo lo antes posible: 
+- Número de confirmación
+- Código PIN
+- Nombre que aparece en la reserva
+Como alternativa, si necesitas asistencia inmediata, siempre puedes llamarnos aquí: https://t.co/tuuNbmGVaG
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G782" t="inlineStr"/>
+      <c r="H782" t="inlineStr"/>
+      <c r="I782" t="inlineStr"/>
+      <c r="J782" t="inlineStr"/>
+      <c r="K782" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105943915169808638</t>
+        </is>
+      </c>
+      <c r="L782" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M782" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N782" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O782" t="inlineStr">
+        <is>
+          <t>Booking.com is offering to review a WhatsApp message and provide assistance via private message or phone call.</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E783" t="inlineStr">
+        <is>
+          <t>Fri Oct 02 08:37:35 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F783" t="inlineStr">
+        <is>
+          <t>@prigarreto Olá, Priscilla, sentimos muito, mas infelizmente não podemos ajudar com reservas de voos nas redes sociais. Se precisar de suporte, entre em contato com nossa equipe de voos através dos seguintes números:  {BR} +55 114 700 8306 / {PT} +35 130 880 5835 / {US} +1 917 421 7240</t>
+        </is>
+      </c>
+      <c r="G783" t="inlineStr"/>
+      <c r="H783" t="inlineStr"/>
+      <c r="I783" t="inlineStr"/>
+      <c r="J783" t="inlineStr"/>
+      <c r="K783" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105940243895460140</t>
+        </is>
+      </c>
+      <c r="L783" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M783" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N783" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O783" t="inlineStr">
+        <is>
+          <t>Booking.com replies to a user’s request for flight booking assistance, offering phone support numbers for Brazil, Portugal, and the US.</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E784" t="inlineStr">
+        <is>
+          <t>Fri Oct 02 08:25:40 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F784" t="inlineStr">
+        <is>
+          <t>Sentimos lo ocurrido con la reserva y que no hayas recibido el reembolso, Carlo. Si quieres que lo revisemos, envíanos un mensaje privado con los siguientes datos y nos pondremos en contacto contigo lo antes posible: 
+- Código PIN
+- Nombre que aparece en la reserva
+Como alternativa, si necesitas asistencia inmediata, siempre puedes llamarnos aquí: https://t.co/tuuNbmGVaG
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G784" t="inlineStr"/>
+      <c r="H784" t="inlineStr"/>
+      <c r="I784" t="inlineStr"/>
+      <c r="J784" t="inlineStr"/>
+      <c r="K784" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105937247790932312</t>
+        </is>
+      </c>
+      <c r="L784" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M784" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N784" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O784" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes to a user for a missing refund and offers to review the issue via private message or phone call.</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E785" t="inlineStr">
+        <is>
+          <t>Fri Oct 02 08:25:28 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F785" t="inlineStr">
+        <is>
+          <t>Hi Aman, we regret hearing about your experience. We hope you were able to communicate any problems directly to the property while you are there, as they are in the best position to address and resolve any concerns.
+For us to help you here, please send us a private message with the following information:
+- Pin code:
+- Name on the reservation:
+We'll get back to you as soon as possible. Please bear in mind that our Social Media Team doesn't work in real time. For immediate support, please call our 24/7 Customer Service Team - our contact details can be found here: https://t.co/o8QyR8SaDb</t>
+        </is>
+      </c>
+      <c r="G785" t="inlineStr"/>
+      <c r="H785" t="inlineStr"/>
+      <c r="I785" t="inlineStr"/>
+      <c r="J785" t="inlineStr"/>
+      <c r="K785" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105937195320176903</t>
+        </is>
+      </c>
+      <c r="L785" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M785" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N785" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O785" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer’s negative experience, offering private messaging and phone support for resolution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E786" t="inlineStr">
+        <is>
+          <t>Fri Oct 02 08:03:06 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F786" t="inlineStr">
+        <is>
+          <t>Hi Nitēsh, it sounds like your booking didn't confirm successfully, but the payment was collected. If we've charged you, our system will recognize that the payment isn't linked to a booking and automatically refund it back. Once the refund is processed it can take 7-12 business days to reflect in your account, you should've also received an email confirming this.
+It is also possible that you made a typo when entering your email address, as you wouldn't receive the confirmation email afterwards. If you send us a private message with the following details, we'll look into our system to see if we can locate your booking:
+- Name of the property:
+- Dates of stay:
+- Full guest name:
+- Name of the person contacting us:
+- Email address used to make the booking:</t>
+        </is>
+      </c>
+      <c r="G786" t="inlineStr"/>
+      <c r="H786" t="inlineStr"/>
+      <c r="I786" t="inlineStr"/>
+      <c r="J786" t="inlineStr"/>
+      <c r="K786" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2105931565431714059</t>
+        </is>
+      </c>
+      <c r="L786" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M786" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N786" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O786" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer’s booking confirmation issue, explaining the refund process and requesting details to locate the booking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E787" t="inlineStr">
+        <is>
+          <t>2026-10-02T12:27:06.000Z</t>
+        </is>
+      </c>
+      <c r="F787" t="inlineStr">
+        <is>
+          <t>Autumn colored leaves, book with the furrr – traveling with Booking.com is easierrrr</t>
+        </is>
+      </c>
+      <c r="G787" t="inlineStr">
+        <is>
+          <t>https://scontent-ham3-1.cdninstagram.com/v/t51.82787-15/830453955_18636121258008354_3826861898441427579_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=100&amp;ig_cache_key=Mzk5OTA1MDA2Mzc3MzQzMzgxNzE4NjM2MTIxMjU1MDA4MzU0.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNMSVBTLnhwaWRzLjExNzkuc2RyLnZpZGVvX2RlZmF1bHRfY292ZXJfZnJhbWUuQzMifQ%3D%3D&amp;_nc_ohc=8dU1--jj7LYQ7kNvwFX-jPQ&amp;_nc_oc=AdpSxb5chz1Wpu1S_O_BaKL9S6bw2YQbJGTCPDxaGKTZYZmnPVAfk0ge9qKcrrHdXNg&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ham3-1.cdninstagram.com&amp;_nc_gid=NXNb66kkzHiindpwrRBE0Q&amp;_nc_ss=7a22e&amp;oh=00_AQO8XVh2w9JIxRpa8cK3tbLDO018PmdnRl_GsKo0gS6jfw&amp;oe=6AC59709</t>
+        </is>
+      </c>
+      <c r="H787" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I787" t="inlineStr">
+        <is>
+          <t>https://scontent-ham3-1.cdninstagram.com/o1/v/t2/f2/m86/AQP0AGZ8Ryp_TD2tiMMKh4pZRGBYZBahiQrEgdmgDS00Nd3GNvacRI9VmMeOFXHVuTcxjo84c5RouTDwBev_sPmRcs_FdszZRgMCOVk.mp4?_nc_cat=108&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-ham3-1.cdninstagram.com&amp;_nc_ohc=6vP_iMrqpUIQ7kNvwEDoE6_&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTEwNDI4NjA1MjE3OTcxMSwiYXNzZXRfYWdlX2RheXMiOjAsInZpX3VzZWNhc2VfaWQiOjEwMDk5LCJkdXJhdGlvbl9zIjozOCwidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=83b093c65a104d9&amp;_nc_vs=HBksFQIYUmlnX3hwdl9yZWVsc19wZXJtYW5lbnRfc3JfcHJvZC8zMEQyQjc0NDg0MjA0NzI3QkI1ODVGMEZFMzc5RTBENl92aWRlb19kYXNoaW5pdC5tcDQVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzA1M0JCNkU3N0QyRTQ0MkNBOUVCNzBEQzY1RjM2NTlFX2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACb--_ad9JX2AxUCKAJDMywXQEMVP3ztkWgYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=NXNb66kkzHiindpwrRBE0Q&amp;_nc_zt=28&amp;_nc_ss=73689&amp;oh=00_AQNzy2G-bCRzYIzURB5z5O9ein_zGs-R65G-Mzb3RceqBQ&amp;oe=6AC1BB51</t>
+        </is>
+      </c>
+      <c r="J787" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K787" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dd_ethaN__Z/</t>
+        </is>
+      </c>
+      <c r="L787" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M787" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N787" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O787" t="inlineStr">
+        <is>
+          <t>Booking.com uses a playful, autumn-themed post to encourage travelers to book with them, highlighting ease and convenience.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O787"/>
+  <dimension ref="A1:O792"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50884,6 +50884,351 @@
         </is>
       </c>
     </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>TravelPerk</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>Perk</t>
+        </is>
+      </c>
+      <c r="E788" t="inlineStr">
+        <is>
+          <t>2026-10-02T08:27:38.366Z</t>
+        </is>
+      </c>
+      <c r="F788" t="inlineStr">
+        <is>
+          <t>Every company has a Maria... automate expenses and free your team.</t>
+        </is>
+      </c>
+      <c r="G788" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D4E10AQGKxmXJaKo25w/image-shrink_1280/B4EaD7uWHiH0Ag-/0/1790929625992?e=1791572400&amp;v=beta&amp;t=JTA_Da0MoUIL3vOHKAn8UwLo6dcHAnjp0vxUshewaaI</t>
+        </is>
+      </c>
+      <c r="H788" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I788" t="inlineStr"/>
+      <c r="J788" t="inlineStr"/>
+      <c r="K788" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/perk_every-company-has-a-maria-automate-expenses-activity-7511703429803790337-aISW</t>
+        </is>
+      </c>
+      <c r="L788" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M788" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N788" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O788" t="inlineStr">
+        <is>
+          <t>TravelPerk promotes a new expense automation feature aimed at freeing up teams’ time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E789" t="inlineStr">
+        <is>
+          <t>Fri Oct 02 17:00:38 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F789" t="inlineStr">
+        <is>
+          <t>[Giveaway Closed]</t>
+        </is>
+      </c>
+      <c r="G789" t="inlineStr"/>
+      <c r="H789" t="inlineStr"/>
+      <c r="I789" t="inlineStr"/>
+      <c r="J789" t="inlineStr"/>
+      <c r="K789" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2106066840531427662</t>
+        </is>
+      </c>
+      <c r="L789" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M789" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N789" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O789" t="inlineStr">
+        <is>
+          <t>Brex announced that a previously running giveaway has now closed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>AirBnb</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>airbnb</t>
+        </is>
+      </c>
+      <c r="E790" t="inlineStr">
+        <is>
+          <t>2026-10-01T22:00:03.000Z</t>
+        </is>
+      </c>
+      <c r="F790" t="inlineStr">
+        <is>
+          <t>Santa Cecília is where history meets culture: local artists, chefs, makers and merchants breathing new life into this beautiful Bohemian neighborhood. Come for hands-on experiences that let you unplug and learn something new.
+Save this guide for your next trip to São Paulo.
+For chef @kalyra, unplugging in São Paulo means connecting with local ingredients and the simple joy of sharing a meal.
+Part camera shop @festivaldefilmesvencidos, part cafe @ffv_cafe, part community hub - FFV is where photography lovers in São Paulo come to  get lost in the film development process.
+📍R. Barão de Tatuí, 240 - Santa Cecília, São Paulo - SP, 01226-030
+Stop by, develop some film, try their custom point-and-shoot digital camera, or have a coffee.
+“Aconchegante” means “cozy”. And that’s exactly what you’ll find at this vibrant take on a traditional Brazilian boteco.
+📍R. Jesuíno Pascoal, 35 - Consolação, São Paulo - SP, 01224-050
+Chef @kalyra, owner of Aconchegante Bar sources locally and puts her own spin on Brazilian classics. She shines a light on Brazil’s overlooked ingredients, giving native Brazilian flavors a place at the table.
+You can’t scroll on your phone if you’re playing with clay. @kooimooa is a ceramic studio meets Korean-inspired cafe in Santa Cecília.
+📍R. Barão de Tatuí, 302 - 1º andar - Santa Cecília, São Paulo - SP, 01226-030
+Clear your schedule, book a workshop and get ready to get zen. What’s better than making a souvenir to bring home with your bare hands?
+Phones down, forks up. Muli is the perfect spot for prime people-watching.
+📍R. Martim Francisco, 482 - Vila Buarque, São Paulo - SP, 01226-002
+Muli brings the beach vibes and the Brazilian seafood flavors. Add this to your MUST TRY list for Santa Cecília.
+This isn’t just a listening bar, it’s a sound experience. Matiz is the ideal place for music lovers who love a laid back atmosphere. Grab a drink, settle in and  listen to the live DJ spin vinyl.
+📍R. Martins Fontes, 91 - República, São Paulo - SP, 01050-905
+Discover some new Brazilian deep cuts and chat it up with a local music head.
+Save this for your next trip to São Paulo.</t>
+        </is>
+      </c>
+      <c r="G790" t="inlineStr">
+        <is>
+          <t>https://instagram.fbcn13-1.fna.fbcdn.net/v/t51.82787-15/831568064_18639963091063838_3526181482066656105_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=100&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=Mzk5ODA0NTg0NzAwNjgyOTg1OA%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMzA3Mi5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=sB9Rh8ebmTwQ7kNvwHm49Ue&amp;_nc_oc=Adp0s9HgZt696NleJ-MRINK3qTHf2tIqs83vrDlaDItVGKZoScGsqaz3yAOrc-VlFrU&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fbcn13-1.fna&amp;_nc_gid=qqHSXA4Y7l819NyP68EtmA&amp;_nc_ss=7a22e&amp;oh=00_AQNLUDyBgWd7JHAZxwGf1pnt6M3LTmSzi8s4GLXSg-0Uug&amp;oe=6AC5C4E2</t>
+        </is>
+      </c>
+      <c r="H790" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I790" t="inlineStr"/>
+      <c r="J790" t="inlineStr"/>
+      <c r="K790" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/Dd97tvaESRB/</t>
+        </is>
+      </c>
+      <c r="L790" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M790" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N790" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O790" t="inlineStr">
+        <is>
+          <t>Airbnb highlights a curated list of local experiences and venues in São Paulo’s Santa Cecília neighborhood, showcasing cultural, culinary, and creative activities to attract travelers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E791" t="inlineStr">
+        <is>
+          <t>Fri Oct 02 17:47:11 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F791" t="inlineStr">
+        <is>
+          <t>Hi there, how can we help? We regret the frustration and disappointment this situation has caused. We understand how upsetting it must be to have your reservation canceled upon arrival, especially after booking a stay of more than 30 days and then having to find alternative accommodation at short notice.
+If your request is related to an accommodation booking, please DM us the following details, and we'll get back to you as soon as possible: 
+• Confirmation number:
+• Pin code:
+• Name on the reservation:
+Please bear in mind that our Social Media Team doesn't work in real time. For immediate support, please call our 24/7 Customer Service Team - our contact details can be found here: https://t.co/o8QyR8SaDb.
+Also, at this time, we only offer support for accommodation bookings via social media. For questions about Flights, Taxis, or Insurance, you can reach out to the dedicated support team here: https://t.co/OVuF5pCzba.</t>
+        </is>
+      </c>
+      <c r="G791" t="inlineStr"/>
+      <c r="H791" t="inlineStr"/>
+      <c r="I791" t="inlineStr"/>
+      <c r="J791" t="inlineStr"/>
+      <c r="K791" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2106078555754963120</t>
+        </is>
+      </c>
+      <c r="L791" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M791" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N791" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O791" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint about a canceled reservation, offering assistance via direct message and directing to 24/7 support for immediate help.</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E792" t="inlineStr">
+        <is>
+          <t>Fri Oct 02 17:24:32 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F792" t="inlineStr">
+        <is>
+          <t>@SoSoSew1 Hi there, we have sent you a private message. Kindly review it at your convenience. Thank you. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G792" t="inlineStr"/>
+      <c r="H792" t="inlineStr"/>
+      <c r="I792" t="inlineStr"/>
+      <c r="J792" t="inlineStr"/>
+      <c r="K792" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2106072854794047960</t>
+        </is>
+      </c>
+      <c r="L792" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M792" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N792" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O792" t="inlineStr">
+        <is>
+          <t>Booking.com sent a private message to user @SoSoSew1, likely for account or support purposes.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O792"/>
+  <dimension ref="A1:O816"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51229,6 +51229,1514 @@
         </is>
       </c>
     </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E793" t="inlineStr">
+        <is>
+          <t>Fri Oct 02 23:54:13 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F793" t="inlineStr">
+        <is>
+          <t>@PalmerLuckey @eglyman https://t.co/0qmesdGvR5</t>
+        </is>
+      </c>
+      <c r="G793" t="inlineStr"/>
+      <c r="H793" t="inlineStr"/>
+      <c r="I793" t="inlineStr"/>
+      <c r="J793" t="inlineStr"/>
+      <c r="K793" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2106170923669934542</t>
+        </is>
+      </c>
+      <c r="L793" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M793" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N793" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O793" t="inlineStr">
+        <is>
+          <t>Ramp shares a link to a video featuring Palmer Luckey and Eglyman, likely announcing a partnership or collaboration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E794" t="inlineStr">
+        <is>
+          <t>Fri Oct 02 20:01:03 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F794" t="inlineStr">
+        <is>
+          <t>sometimes you have to take a big swing with marketing and this one was hit out of the park.</t>
+        </is>
+      </c>
+      <c r="G794" t="inlineStr"/>
+      <c r="H794" t="inlineStr"/>
+      <c r="I794" t="inlineStr"/>
+      <c r="J794" t="inlineStr"/>
+      <c r="K794" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2106112244765589868</t>
+        </is>
+      </c>
+      <c r="L794" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M794" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N794" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O794" t="inlineStr">
+        <is>
+          <t>Ramp celebrates a highly effective marketing campaign, describing it as a major success.</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E795" t="inlineStr">
+        <is>
+          <t>Fri Oct 02 18:44:47 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F795" t="inlineStr">
+        <is>
+          <t>for those who like to get a little too deep into LLMs, this is the account to follow 👇</t>
+        </is>
+      </c>
+      <c r="G795" t="inlineStr"/>
+      <c r="H795" t="inlineStr"/>
+      <c r="I795" t="inlineStr"/>
+      <c r="J795" t="inlineStr"/>
+      <c r="K795" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2106093050095456733</t>
+        </is>
+      </c>
+      <c r="L795" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M795" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N795" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O795" t="inlineStr">
+        <is>
+          <t>Ramp shares a recommendation for an account that delves deeply into large language models.</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E796" t="inlineStr">
+        <is>
+          <t>Sat Oct 03 00:00:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F796" t="inlineStr">
+        <is>
+          <t>Explore dramatic landscapes and unforgettable bucket-list adventures across Canada. 🇨🇦
+➡️ The wildlife: Spot majestic polar bears in Churchill, watch humpbacks off Vancouver Island, or glimpse elk in Banff.
+➡️ The scenery: Drive through the towering Canadian Rockies and marvel at turquoise glacial lakes.
+➡️ The stays: Cozy up in a rustic mountain lodge or unwind at an iconic luxury hotel.
+🔗 Plan your travel:
+https://t.co/P5IbIegEyB</t>
+        </is>
+      </c>
+      <c r="G796" t="inlineStr"/>
+      <c r="H796" t="inlineStr"/>
+      <c r="I796" t="inlineStr"/>
+      <c r="J796" t="inlineStr"/>
+      <c r="K796" t="inlineStr">
+        <is>
+          <t>https://x.com/Expedia/status/2106172379651060013</t>
+        </is>
+      </c>
+      <c r="L796" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M796" t="inlineStr">
+        <is>
+          <t>Strategic Expansion or Changes</t>
+        </is>
+      </c>
+      <c r="N796" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O796" t="inlineStr">
+        <is>
+          <t>Expedia is promoting Canadian travel experiences, showcasing wildlife, scenery, and lodging options to encourage bookings through a dedicated link.</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E797" t="inlineStr">
+        <is>
+          <t>Sat Oct 03 12:34:03 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F797" t="inlineStr">
+        <is>
+          <t>Hi Tshepo, please note that we've asked you to reach out to us in private; your booking information is confidential and should remain as such; please make sure to remove the sensitive information shared in public due to private and safety reasons. 
+Since you haven't DMed us we're unable to respond you in private, but we can see that you have already received a final outcome from our Customer Service Team regarding this booking, and we're unable to offer you with different reply this time; should you like to further discuss this matter, please reach out to the accommodation directly.</t>
+        </is>
+      </c>
+      <c r="G797" t="inlineStr"/>
+      <c r="H797" t="inlineStr"/>
+      <c r="I797" t="inlineStr"/>
+      <c r="J797" t="inlineStr"/>
+      <c r="K797" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2106362141359923636</t>
+        </is>
+      </c>
+      <c r="L797" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M797" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N797" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O797" t="inlineStr">
+        <is>
+          <t>Booking.com declined to respond publicly to a user’s inquiry, urging them to DM for private assistance, but the user did not do so, and the company directed the user to contact the accommodation directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E798" t="inlineStr">
+        <is>
+          <t>Sat Oct 03 11:48:15 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F798" t="inlineStr">
+        <is>
+          <t>@Larisayzqd Hi Larisa, thank you for reaching out. Please find all the relevant information regarding your case in your inbox. Best regards.</t>
+        </is>
+      </c>
+      <c r="G798" t="inlineStr"/>
+      <c r="H798" t="inlineStr"/>
+      <c r="I798" t="inlineStr"/>
+      <c r="J798" t="inlineStr"/>
+      <c r="K798" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2106350617069334546</t>
+        </is>
+      </c>
+      <c r="L798" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M798" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N798" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O798" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s inquiry via direct message, directing them to relevant information in their inbox.</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E799" t="inlineStr">
+        <is>
+          <t>Sat Oct 03 11:40:21 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F799" t="inlineStr">
+        <is>
+          <t>Hi Sarah, thank you for reaching out to us. We regret hearing this, and we would like to review your case. How can we help? If your request is related to an accommodation booking, please DM us the following details and we'll get back to you as soon as possible: 
+- Confirmation number
+- Pin code
+- Name on the reservation
+- Details of the guest
+Please bear in mind that our Social Media Team doesn't work in real time. For immediate support, please call our 24/7 Customer Service Team - our contact details can be found here: https://t.co/o8QyR8SaDb
+Also, at this time, we only offer support for accommodation bookings via social media. For questions about Flights, Taxis, or Insurance, you can reach out to the dedicated support team here: https://t.co/UfRgpDJomK. Regards.</t>
+        </is>
+      </c>
+      <c r="G799" t="inlineStr"/>
+      <c r="H799" t="inlineStr"/>
+      <c r="I799" t="inlineStr"/>
+      <c r="J799" t="inlineStr"/>
+      <c r="K799" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2106348627098472740</t>
+        </is>
+      </c>
+      <c r="L799" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M799" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N799" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O799" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer inquiry on X, detailing the steps for booking-related support and directing other queries to dedicated teams.</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E800" t="inlineStr">
+        <is>
+          <t>Sat Oct 03 11:33:31 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F800" t="inlineStr">
+        <is>
+          <t>@Larisayzqd Hi Larisa, we have just responded to your DM. Please, check. Thank you.</t>
+        </is>
+      </c>
+      <c r="G800" t="inlineStr"/>
+      <c r="H800" t="inlineStr"/>
+      <c r="I800" t="inlineStr"/>
+      <c r="J800" t="inlineStr"/>
+      <c r="K800" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2106346909094891835</t>
+        </is>
+      </c>
+      <c r="L800" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M800" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N800" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O800" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s direct message, indicating routine customer support engagement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E801" t="inlineStr">
+        <is>
+          <t>Sat Oct 03 10:55:19 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F801" t="inlineStr">
+        <is>
+          <t>@MeekLiam When you have a moment, please take a look at our DMs for additional clarification. Kind regards.</t>
+        </is>
+      </c>
+      <c r="G801" t="inlineStr"/>
+      <c r="H801" t="inlineStr"/>
+      <c r="I801" t="inlineStr"/>
+      <c r="J801" t="inlineStr"/>
+      <c r="K801" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2106337293053170069</t>
+        </is>
+      </c>
+      <c r="L801" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M801" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N801" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O801" t="inlineStr">
+        <is>
+          <t>Booking.com sent a polite message asking a user to review DMs for additional clarification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E802" t="inlineStr">
+        <is>
+          <t>Sat Oct 03 10:34:47 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F802" t="inlineStr">
+        <is>
+          <t>@vyomvedas Hi there, we have just DMed you back. Please, check. Thank you.</t>
+        </is>
+      </c>
+      <c r="G802" t="inlineStr"/>
+      <c r="H802" t="inlineStr"/>
+      <c r="I802" t="inlineStr"/>
+      <c r="J802" t="inlineStr"/>
+      <c r="K802" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2106332127394406508</t>
+        </is>
+      </c>
+      <c r="L802" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M802" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N802" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O802" t="inlineStr">
+        <is>
+          <t>Booking.com responded to a user via direct message, indicating routine customer engagement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E803" t="inlineStr">
+        <is>
+          <t>Sat Oct 03 10:17:27 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F803" t="inlineStr">
+        <is>
+          <t>Hi there, we regret hearing about your overall experience at the accommodation.
+For us to help you here, please send us a private message with the following information:
+- Confirmation number:
+- Pin code:
+- Name of the guest on the reservation:
+- Details on your stay:
+We'll get back to you as soon as possible. Alternatively, for immediate support you can always give us a call here: https://t.co/o8QyR8SaDb.</t>
+        </is>
+      </c>
+      <c r="G803" t="inlineStr"/>
+      <c r="H803" t="inlineStr"/>
+      <c r="I803" t="inlineStr"/>
+      <c r="J803" t="inlineStr"/>
+      <c r="K803" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2106327763237917089</t>
+        </is>
+      </c>
+      <c r="L803" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M803" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N803" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O803" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer’s negative experience, offering private messaging and phone support to resolve the issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E804" t="inlineStr">
+        <is>
+          <t>Sat Oct 03 09:42:49 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F804" t="inlineStr">
+        <is>
+          <t>Please note that as we operate on a different platform as the social media team, we are not able to review any previous communication you may have had with our customer service team without verifying your reservation details.
+If you would like us to take a look, please share the requested details from our previous message via a private message. We always recommend our travelers avoid sharing any reservation details in public as it includes confidential information.
+We are awaiting your DM. Kind regards.</t>
+        </is>
+      </c>
+      <c r="G804" t="inlineStr"/>
+      <c r="H804" t="inlineStr"/>
+      <c r="I804" t="inlineStr"/>
+      <c r="J804" t="inlineStr"/>
+      <c r="K804" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2106319050343080262</t>
+        </is>
+      </c>
+      <c r="L804" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M804" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N804" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O804" t="inlineStr">
+        <is>
+          <t>Booking.com reminds customers to avoid sharing reservation details publicly and to send a private message for verification, emphasizing privacy and security.</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E805" t="inlineStr">
+        <is>
+          <t>Sat Oct 03 09:29:42 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F805" t="inlineStr">
+        <is>
+          <t>@billiejeaned Hi there, thank yo for contacting us. We have replied to your DM. Please have a look at our response and let us know. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G805" t="inlineStr"/>
+      <c r="H805" t="inlineStr"/>
+      <c r="I805" t="inlineStr"/>
+      <c r="J805" t="inlineStr"/>
+      <c r="K805" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2106315749471973515</t>
+        </is>
+      </c>
+      <c r="L805" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M805" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N805" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O805" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s direct message on X, acknowledging the contact and directing the user to review the response.</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E806" t="inlineStr">
+        <is>
+          <t>Sat Oct 03 09:27:16 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F806" t="inlineStr">
+        <is>
+          <t>Hi Martin, you recently reached out to us regarding your Car Rental reservation, but we haven't heard back from you. If you still need assistance, please provide us with the following details in a private message: 
+- Booking number 
+- Name of booker 
+- Email address used to book 
+- Your request 
+Thanks.</t>
+        </is>
+      </c>
+      <c r="G806" t="inlineStr"/>
+      <c r="H806" t="inlineStr"/>
+      <c r="I806" t="inlineStr"/>
+      <c r="J806" t="inlineStr"/>
+      <c r="K806" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2106315134721311160</t>
+        </is>
+      </c>
+      <c r="L806" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M806" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N806" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O806" t="inlineStr">
+        <is>
+          <t>Booking.com sent a follow‑up message to a customer about a car rental reservation, requesting booking details for further assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E807" t="inlineStr">
+        <is>
+          <t>Sat Oct 03 09:15:42 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F807" t="inlineStr">
+        <is>
+          <t>Hi there, we regret hearing about your experience. We always suggest our travelers contact the property directly during their stay as they are in the best position to address and resolve any concerns. And if no solution can be provided, contact us at the time the issue occurs.
+For us to help you here, please send us a private message with the following information:
+- Confirmation number:
+- Pin code:
+- Guest name on the reservation:
+- Details on your stay:
+We'll get back to you as soon as possible. Alternatively, for immediate support you can always give us a call here: https://t.co/o8QyR8SaDb.</t>
+        </is>
+      </c>
+      <c r="G807" t="inlineStr"/>
+      <c r="H807" t="inlineStr"/>
+      <c r="I807" t="inlineStr"/>
+      <c r="J807" t="inlineStr"/>
+      <c r="K807" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2106312224817996133</t>
+        </is>
+      </c>
+      <c r="L807" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M807" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N807" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O807" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint, offering private messaging and phone support for issue resolution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E808" t="inlineStr">
+        <is>
+          <t>Sat Oct 03 09:10:13 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F808" t="inlineStr">
+        <is>
+          <t>Thank you for getting back to us. 
+You can send us a private message via the link in this message. 
+We strongly recommend that you do not share your reservation details in your public messages, as they contain confidential information. Therefore, please DM us and share the following information: 
+- Reservation number 
+- Pin code 
+- The guest name on the booking 
+Once we receive all these details, we will be able to check the information. Kind regards.</t>
+        </is>
+      </c>
+      <c r="G808" t="inlineStr"/>
+      <c r="H808" t="inlineStr"/>
+      <c r="I808" t="inlineStr"/>
+      <c r="J808" t="inlineStr"/>
+      <c r="K808" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2106310846850695521</t>
+        </is>
+      </c>
+      <c r="L808" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M808" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N808" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O808" t="inlineStr">
+        <is>
+          <t>Booking.com is reminding customers to share reservation details via private message for privacy and security reasons.</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E809" t="inlineStr">
+        <is>
+          <t>Sat Oct 03 08:54:34 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F809" t="inlineStr">
+        <is>
+          <t>@CryoPalmar Hi there, we hear you. Please, check our last DM and let us know if you have any other questions. Kind regards.</t>
+        </is>
+      </c>
+      <c r="G809" t="inlineStr"/>
+      <c r="H809" t="inlineStr"/>
+      <c r="I809" t="inlineStr"/>
+      <c r="J809" t="inlineStr"/>
+      <c r="K809" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2106306907421958430</t>
+        </is>
+      </c>
+      <c r="L809" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M809" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N809" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O809" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user on X, directing them to check a previous DM for further assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E810" t="inlineStr">
+        <is>
+          <t>Sat Oct 03 05:50:25 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F810" t="inlineStr">
+        <is>
+          <t>@kiran_stories We regret to hear that the call got disconnected, Kiran. You can also try to contact our Flights team via this link: https://t.co/BfbildlU73. Kind regards.</t>
+        </is>
+      </c>
+      <c r="G810" t="inlineStr"/>
+      <c r="H810" t="inlineStr"/>
+      <c r="I810" t="inlineStr"/>
+      <c r="J810" t="inlineStr"/>
+      <c r="K810" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2106260564162818440</t>
+        </is>
+      </c>
+      <c r="L810" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M810" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N810" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O810" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user about a disconnected call and provided a link to contact their Flights team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E811" t="inlineStr">
+        <is>
+          <t>Sat Oct 03 02:37:05 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F811" t="inlineStr">
+        <is>
+          <t>@karthi5a Hi there, thank you for reaching out. We've sent you a private message regarding your inquiry. Kindly check your inbox at your earliest convenience.</t>
+        </is>
+      </c>
+      <c r="G811" t="inlineStr"/>
+      <c r="H811" t="inlineStr"/>
+      <c r="I811" t="inlineStr"/>
+      <c r="J811" t="inlineStr"/>
+      <c r="K811" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2106211908877459652</t>
+        </is>
+      </c>
+      <c r="L811" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M811" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N811" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O811" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user on X, directing them to check their inbox for a private message regarding their inquiry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E812" t="inlineStr">
+        <is>
+          <t>Sat Oct 03 02:10:42 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F812" t="inlineStr">
+        <is>
+          <t>@EmilyAshby17 Hi Emily, thank you for reaching out. We've sent you a private message regarding your inquiry. Kindly check your inbox at your earliest convenience.</t>
+        </is>
+      </c>
+      <c r="G812" t="inlineStr"/>
+      <c r="H812" t="inlineStr"/>
+      <c r="I812" t="inlineStr"/>
+      <c r="J812" t="inlineStr"/>
+      <c r="K812" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2106205270657405328</t>
+        </is>
+      </c>
+      <c r="L812" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M812" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N812" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O812" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s inquiry via a private message, acknowledging receipt and directing them to check their inbox.</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E813" t="inlineStr">
+        <is>
+          <t>Sat Oct 03 02:05:47 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F813" t="inlineStr">
+        <is>
+          <t>Hi there, we regret to hear you're having difficulty reaching support and understand how frustrating it can be when you're unable to access help for your booking. Unfortunately, we're unable to assist with Flight reservations through social media, but you can contact our Flights team here: https://t.co/OVuF5pCzba, or call {US}+1 917 421 7240 / {UK}+44 2039019061 / {IE} +353 19075677.</t>
+        </is>
+      </c>
+      <c r="G813" t="inlineStr"/>
+      <c r="H813" t="inlineStr"/>
+      <c r="I813" t="inlineStr"/>
+      <c r="J813" t="inlineStr"/>
+      <c r="K813" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2106204033560060298</t>
+        </is>
+      </c>
+      <c r="L813" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M813" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N813" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O813" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint about difficulty reaching support, apologizes, and directs them to the appropriate flight support channels.</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E814" t="inlineStr">
+        <is>
+          <t>Sat Oct 03 01:02:21 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F814" t="inlineStr">
+        <is>
+          <t>@McinallyRab Hi there, we have sent you a private message regarding your inquiry. Please check your messages for further assistance. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G814" t="inlineStr"/>
+      <c r="H814" t="inlineStr"/>
+      <c r="I814" t="inlineStr"/>
+      <c r="J814" t="inlineStr"/>
+      <c r="K814" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2106188070013882602</t>
+        </is>
+      </c>
+      <c r="L814" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M814" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N814" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O814" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s inquiry via a private message, directing them to check their messages for further assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E815" t="inlineStr">
+        <is>
+          <t>Sat Oct 03 01:00:14 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F815" t="inlineStr">
+        <is>
+          <t>Hi there, how can we help? We regret the frustration this situation has caused. We understand your concerns regarding the compensation method and appreciate you bringing this matter to our attention.
+If your request is related to an accommodation booking, please DM us the following details, and we'll get back to you as soon as possible: 
+• Confirmation number:
+• Pin code:
+• Name on the reservation:
+Please bear in mind that our Social Media Team doesn't work in real time. For immediate support, please call our 24/7 Customer Service Team - our contact details can be found here: https://t.co/o8QyR8SaDb.
+Also, at this time, we only offer support for accommodation bookings via social media. For questions about Flights, Taxis, or Insurance, you can reach out to the dedicated support team here: https://t.co/OVuF5pCzba.</t>
+        </is>
+      </c>
+      <c r="G815" t="inlineStr"/>
+      <c r="H815" t="inlineStr"/>
+      <c r="I815" t="inlineStr"/>
+      <c r="J815" t="inlineStr"/>
+      <c r="K815" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2106187536972370356</t>
+        </is>
+      </c>
+      <c r="L815" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M815" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N815" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O815" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint about booking issues, requesting booking details via DM and directing to 24/7 support for immediate assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E816" t="inlineStr">
+        <is>
+          <t>Sat Oct 03 00:29:58 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F816" t="inlineStr">
+        <is>
+          <t>@CryoPalmar Hi there, 
+We have replied to your private message. Thank you. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G816" t="inlineStr"/>
+      <c r="H816" t="inlineStr"/>
+      <c r="I816" t="inlineStr"/>
+      <c r="J816" t="inlineStr"/>
+      <c r="K816" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2106179920334356826</t>
+        </is>
+      </c>
+      <c r="L816" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M816" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N816" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O816" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a private message from CryoPalmar, confirming that they have responded to the inquiry.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O816"/>
+  <dimension ref="A1:O819"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52737,6 +52737,189 @@
         </is>
       </c>
     </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E817" t="inlineStr">
+        <is>
+          <t>Sat Oct 03 17:40:54 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F817" t="inlineStr">
+        <is>
+          <t>@rajshreesharma Hi Rajshree, happy to help. Should you need any further assistance, please feel free to reach out via DM.</t>
+        </is>
+      </c>
+      <c r="G817" t="inlineStr"/>
+      <c r="H817" t="inlineStr"/>
+      <c r="I817" t="inlineStr"/>
+      <c r="J817" t="inlineStr"/>
+      <c r="K817" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2106439362065948760</t>
+        </is>
+      </c>
+      <c r="L817" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M817" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N817" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O817" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user with friendly support, offering further assistance via direct message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E818" t="inlineStr">
+        <is>
+          <t>Sat Oct 03 17:22:53 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F818" t="inlineStr">
+        <is>
+          <t>@LSsyl3 Hi there, we have replied to your private message. Kindly review it at your convenience. Thank you. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G818" t="inlineStr"/>
+      <c r="H818" t="inlineStr"/>
+      <c r="I818" t="inlineStr"/>
+      <c r="J818" t="inlineStr"/>
+      <c r="K818" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2106434828916666818</t>
+        </is>
+      </c>
+      <c r="L818" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M818" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N818" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O818" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a private message from a user, offering assistance and directing them to review the response.</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E819" t="inlineStr">
+        <is>
+          <t>Sat Oct 03 15:00:30 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F819" t="inlineStr">
+        <is>
+          <t>Hola Juan Luis, sentimos saber lo que ha pasado y te recomendamos no compartir nunca el código PIN de una reserva en público, ya que podría permitir que otras personas accedan a los datos personales. Para ayudar a proteger dicha información, te aconsejamos que elimines dicho comentario. Si necesitas ayuda, envíanos un mensaje privado con tu petición y con gusto atenderemos tu petición. Un saludo.</t>
+        </is>
+      </c>
+      <c r="G819" t="inlineStr"/>
+      <c r="H819" t="inlineStr"/>
+      <c r="I819" t="inlineStr"/>
+      <c r="J819" t="inlineStr"/>
+      <c r="K819" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2106398997900365882</t>
+        </is>
+      </c>
+      <c r="L819" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M819" t="inlineStr">
+        <is>
+          <t>Tech Updates</t>
+        </is>
+      </c>
+      <c r="N819" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O819" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user’s concern about sharing reservation PINs, advising against public disclosure and offering private assistance.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O819"/>
+  <dimension ref="A1:O877"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52920,6 +52920,3715 @@
         </is>
       </c>
     </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="E820" t="inlineStr">
+        <is>
+          <t>2026-10-27T21:03:15.000Z</t>
+        </is>
+      </c>
+      <c r="F820" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Navigate26 Europe: Product keynote
+</t>
+        </is>
+      </c>
+      <c r="G820" t="inlineStr"/>
+      <c r="H820" t="inlineStr"/>
+      <c r="I820" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=uJygAKw_H3g</t>
+        </is>
+      </c>
+      <c r="J820" t="inlineStr">
+        <is>
+          <t>[Failed to fetch]</t>
+        </is>
+      </c>
+      <c r="K820" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=uJygAKw_H3g</t>
+        </is>
+      </c>
+      <c r="L820" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M820" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N820" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O820" t="inlineStr">
+        <is>
+          <t>Failed to analyze video transcript via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="E821" t="inlineStr">
+        <is>
+          <t>2026-10-27T21:03:05.000Z</t>
+        </is>
+      </c>
+      <c r="F821" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Navigate26 Europe: Building world-class service for every business traveler
+</t>
+        </is>
+      </c>
+      <c r="G821" t="inlineStr"/>
+      <c r="H821" t="inlineStr"/>
+      <c r="I821" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8zGedRy2HVM</t>
+        </is>
+      </c>
+      <c r="J821" t="inlineStr">
+        <is>
+          <t>[Failed to fetch]</t>
+        </is>
+      </c>
+      <c r="K821" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8zGedRy2HVM</t>
+        </is>
+      </c>
+      <c r="L821" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M821" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N821" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O821" t="inlineStr">
+        <is>
+          <t>Failed to analyze video transcript via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="E822" t="inlineStr">
+        <is>
+          <t>2026-10-27T21:02:57.000Z</t>
+        </is>
+      </c>
+      <c r="F822" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Navigate26 Europe: State of travel and expense
+</t>
+        </is>
+      </c>
+      <c r="G822" t="inlineStr"/>
+      <c r="H822" t="inlineStr"/>
+      <c r="I822" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=IoWVcdY_IQA</t>
+        </is>
+      </c>
+      <c r="J822" t="inlineStr">
+        <is>
+          <t>[Failed to fetch]</t>
+        </is>
+      </c>
+      <c r="K822" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=IoWVcdY_IQA</t>
+        </is>
+      </c>
+      <c r="L822" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M822" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N822" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O822" t="inlineStr">
+        <is>
+          <t>Failed to analyze video transcript via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="E823" t="inlineStr">
+        <is>
+          <t>2026-10-27T21:03:29.000Z</t>
+        </is>
+      </c>
+      <c r="F823" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Navigate26 Europe: AI keynote
+</t>
+        </is>
+      </c>
+      <c r="G823" t="inlineStr"/>
+      <c r="H823" t="inlineStr"/>
+      <c r="I823" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=X70JS82t9ao</t>
+        </is>
+      </c>
+      <c r="J823" t="inlineStr">
+        <is>
+          <t>[Failed to fetch]</t>
+        </is>
+      </c>
+      <c r="K823" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=X70JS82t9ao</t>
+        </is>
+      </c>
+      <c r="L823" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M823" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N823" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O823" t="inlineStr">
+        <is>
+          <t>Failed to analyze video transcript via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="E824" t="inlineStr">
+        <is>
+          <t>2026-10-27T21:03:25.000Z</t>
+        </is>
+      </c>
+      <c r="F824" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Navigate26 Europe: Meetings &amp; events vs. travel — hidden costs and double standards
+</t>
+        </is>
+      </c>
+      <c r="G824" t="inlineStr"/>
+      <c r="H824" t="inlineStr"/>
+      <c r="I824" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=3o8_iSUpt2c</t>
+        </is>
+      </c>
+      <c r="J824" t="inlineStr">
+        <is>
+          <t>[Failed to fetch]</t>
+        </is>
+      </c>
+      <c r="K824" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=3o8_iSUpt2c</t>
+        </is>
+      </c>
+      <c r="L824" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M824" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N824" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O824" t="inlineStr">
+        <is>
+          <t>Failed to analyze video transcript via LLM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>TravelPerk</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>Perk</t>
+        </is>
+      </c>
+      <c r="E825" t="inlineStr">
+        <is>
+          <t>2026-10-28T10:21:04.902Z</t>
+        </is>
+      </c>
+      <c r="F825" t="inlineStr">
+        <is>
+          <t>PSA: Month-end shouldn't require a hostage negotiator. Automate it with Perk.</t>
+        </is>
+      </c>
+      <c r="G825" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D4E10AQER82qKApCP0A/image-shrink_1280/B4EaGCBxB3JQAo-/0/1793182863755?e=1793811600&amp;v=beta&amp;t=gqQ3kCgVt5sXGXhnoOXOtCITmh8gOBAAeum0WhovBH8</t>
+        </is>
+      </c>
+      <c r="H825" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I825" t="inlineStr"/>
+      <c r="J825" t="inlineStr"/>
+      <c r="K825" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/perk_psa-month-end-shouldnt-require-a-hostage-activity-7521154062990450688-DzmH</t>
+        </is>
+      </c>
+      <c r="L825" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M825" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N825" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O825" t="inlineStr">
+        <is>
+          <t>TravelPerk highlights a new automation feature that simplifies month‑end processes, positioning it as a tool to reduce manual effort and streamline finance workflows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E826" t="inlineStr">
+        <is>
+          <t>Wed Oct 28 14:01:49 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F826" t="inlineStr">
+        <is>
+          <t>Autonomous driving meets autonomous expense management.
+Business travel just got easier.</t>
+        </is>
+      </c>
+      <c r="G826" t="inlineStr"/>
+      <c r="H826" t="inlineStr"/>
+      <c r="I826" t="inlineStr"/>
+      <c r="J826" t="inlineStr"/>
+      <c r="K826" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2115443925343449166</t>
+        </is>
+      </c>
+      <c r="L826" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M826" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N826" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O826" t="inlineStr">
+        <is>
+          <t>Ramp announces a new feature that merges autonomous driving with autonomous expense management, aiming to simplify business travel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E827" t="inlineStr">
+        <is>
+          <t>Wed Oct 28 02:37:09 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F827" t="inlineStr">
+        <is>
+          <t>@ben_kauf Do you have a ticket number? Will flag to the support team.</t>
+        </is>
+      </c>
+      <c r="G827" t="inlineStr"/>
+      <c r="H827" t="inlineStr"/>
+      <c r="I827" t="inlineStr"/>
+      <c r="J827" t="inlineStr"/>
+      <c r="K827" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2115271624861909232</t>
+        </is>
+      </c>
+      <c r="L827" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M827" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N827" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O827" t="inlineStr">
+        <is>
+          <t>Ramp replied to a user on X asking for a ticket number, indicating a routine support interaction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E828" t="inlineStr">
+        <is>
+          <t>Tue Oct 27 23:45:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F828" t="inlineStr">
+        <is>
+          <t>@ramprouter 👀</t>
+        </is>
+      </c>
+      <c r="G828" t="inlineStr"/>
+      <c r="H828" t="inlineStr"/>
+      <c r="I828" t="inlineStr"/>
+      <c r="J828" t="inlineStr"/>
+      <c r="K828" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2115228299115090080</t>
+        </is>
+      </c>
+      <c r="L828" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M828" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N828" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O828" t="inlineStr">
+        <is>
+          <t>Ramp teases a new feature or product with a brief tweet referencing @ramprouter and an eye emoji.</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E829" t="inlineStr">
+        <is>
+          <t>Tue Oct 27 19:57:55 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F829" t="inlineStr">
+        <is>
+          <t>@packyM the Ramp engineer's AI has a name now</t>
+        </is>
+      </c>
+      <c r="G829" t="inlineStr"/>
+      <c r="H829" t="inlineStr"/>
+      <c r="I829" t="inlineStr"/>
+      <c r="J829" t="inlineStr"/>
+      <c r="K829" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2115171151278112785</t>
+        </is>
+      </c>
+      <c r="L829" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M829" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N829" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O829" t="inlineStr">
+        <is>
+          <t>Ramp announces that its engineer's AI has been given a name, signaling a new feature or branding update.</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E830" t="inlineStr">
+        <is>
+          <t>Tue Oct 27 19:28:22 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F830" t="inlineStr">
+        <is>
+          <t>@hamidships @rahulgs every other CTO rn 👀</t>
+        </is>
+      </c>
+      <c r="G830" t="inlineStr"/>
+      <c r="H830" t="inlineStr"/>
+      <c r="I830" t="inlineStr"/>
+      <c r="J830" t="inlineStr"/>
+      <c r="K830" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2115163714881995064</t>
+        </is>
+      </c>
+      <c r="L830" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M830" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N830" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O830" t="inlineStr">
+        <is>
+          <t>Ramp tweets a playful remark about the prevalence of CTOs, tagging @hamidships and @rahulgs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E831" t="inlineStr">
+        <is>
+          <t>Tue Oct 27 19:10:35 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F831" t="inlineStr">
+        <is>
+          <t>@KlausCodes turns out you can take it with you</t>
+        </is>
+      </c>
+      <c r="G831" t="inlineStr"/>
+      <c r="H831" t="inlineStr"/>
+      <c r="I831" t="inlineStr"/>
+      <c r="J831" t="inlineStr"/>
+      <c r="K831" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2115159242759922111</t>
+        </is>
+      </c>
+      <c r="L831" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M831" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N831" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O831" t="inlineStr">
+        <is>
+          <t>Ramp announces a new feature that lets users take the product with them, indicating an enhancement to portability or mobility.</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E832" t="inlineStr">
+        <is>
+          <t>Tue Oct 27 19:06:47 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F832" t="inlineStr">
+        <is>
+          <t>@zack_field that github graph is going dark green</t>
+        </is>
+      </c>
+      <c r="G832" t="inlineStr"/>
+      <c r="H832" t="inlineStr"/>
+      <c r="I832" t="inlineStr"/>
+      <c r="J832" t="inlineStr"/>
+      <c r="K832" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2115158284860535108</t>
+        </is>
+      </c>
+      <c r="L832" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M832" t="inlineStr">
+        <is>
+          <t>Tech Updates</t>
+        </is>
+      </c>
+      <c r="N832" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O832" t="inlineStr">
+        <is>
+          <t>Ramp comments on a GitHub graph changing to dark green, indicating a visual update or potential bug in the repository analytics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E833" t="inlineStr">
+        <is>
+          <t>Tue Oct 27 19:05:50 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F833" t="inlineStr">
+        <is>
+          <t>@nzgb sick product too</t>
+        </is>
+      </c>
+      <c r="G833" t="inlineStr"/>
+      <c r="H833" t="inlineStr"/>
+      <c r="I833" t="inlineStr"/>
+      <c r="J833" t="inlineStr"/>
+      <c r="K833" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2115158045952987199</t>
+        </is>
+      </c>
+      <c r="L833" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M833" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N833" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O833" t="inlineStr">
+        <is>
+          <t>Ramp receives a positive mention from @nzgb praising their product.</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E834" t="inlineStr">
+        <is>
+          <t>Tue Oct 27 18:59:56 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F834" t="inlineStr">
+        <is>
+          <t>@ndrewpignanelli saving time includes engineers' time 😏</t>
+        </is>
+      </c>
+      <c r="G834" t="inlineStr"/>
+      <c r="H834" t="inlineStr"/>
+      <c r="I834" t="inlineStr"/>
+      <c r="J834" t="inlineStr"/>
+      <c r="K834" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2115156562365030550</t>
+        </is>
+      </c>
+      <c r="L834" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M834" t="inlineStr">
+        <is>
+          <t>Tech Updates</t>
+        </is>
+      </c>
+      <c r="N834" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O834" t="inlineStr">
+        <is>
+          <t>Ramp highlights that its solution saves engineers' time, emphasizing efficiency gains.</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E835" t="inlineStr">
+        <is>
+          <t>Tue Oct 27 18:49:03 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F835" t="inlineStr">
+        <is>
+          <t>@MarcAtiyeh please fix thanks has been deprecated</t>
+        </is>
+      </c>
+      <c r="G835" t="inlineStr"/>
+      <c r="H835" t="inlineStr"/>
+      <c r="I835" t="inlineStr"/>
+      <c r="J835" t="inlineStr"/>
+      <c r="K835" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2115153824130179348</t>
+        </is>
+      </c>
+      <c r="L835" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M835" t="inlineStr">
+        <is>
+          <t>Tech Updates</t>
+        </is>
+      </c>
+      <c r="N835" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O835" t="inlineStr">
+        <is>
+          <t>Ramp’s system has deprecated the 'thanks' feature, prompting a request for a fix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E836" t="inlineStr">
+        <is>
+          <t>Tue Oct 27 18:48:17 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F836" t="inlineStr">
+        <is>
+          <t>@kashvi challenge accepted 🤝</t>
+        </is>
+      </c>
+      <c r="G836" t="inlineStr"/>
+      <c r="H836" t="inlineStr"/>
+      <c r="I836" t="inlineStr"/>
+      <c r="J836" t="inlineStr"/>
+      <c r="K836" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2115153628931473736</t>
+        </is>
+      </c>
+      <c r="L836" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M836" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N836" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O836" t="inlineStr">
+        <is>
+          <t>Ramp acknowledges a challenge from @kashvi and signals a willingness to collaborate, suggesting a potential partnership or joint initiative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E837" t="inlineStr">
+        <is>
+          <t>Tue Oct 27 18:46:48 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F837" t="inlineStr">
+        <is>
+          <t>@MarcAtiyeh framing this one</t>
+        </is>
+      </c>
+      <c r="G837" t="inlineStr"/>
+      <c r="H837" t="inlineStr"/>
+      <c r="I837" t="inlineStr"/>
+      <c r="J837" t="inlineStr"/>
+      <c r="K837" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2115153255139275191</t>
+        </is>
+      </c>
+      <c r="L837" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M837" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N837" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O837" t="inlineStr">
+        <is>
+          <t>Ramp posted a brief tweet referencing Marc Atiyeh, likely acknowledging his input or framing a new initiative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E838" t="inlineStr">
+        <is>
+          <t>Tue Oct 27 18:46:31 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F838" t="inlineStr">
+        <is>
+          <t>@diegozaks and we're just getting started.</t>
+        </is>
+      </c>
+      <c r="G838" t="inlineStr"/>
+      <c r="H838" t="inlineStr"/>
+      <c r="I838" t="inlineStr"/>
+      <c r="J838" t="inlineStr"/>
+      <c r="K838" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2115153183479681187</t>
+        </is>
+      </c>
+      <c r="L838" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M838" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N838" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O838" t="inlineStr">
+        <is>
+          <t>Ramp announces a new partnership with @diegozaks, signaling the beginning of a collaborative effort.</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E839" t="inlineStr">
+        <is>
+          <t>Tue Oct 27 18:46:04 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F839" t="inlineStr">
+        <is>
+          <t>@burakaslan the sauce is out of the bottle now</t>
+        </is>
+      </c>
+      <c r="G839" t="inlineStr"/>
+      <c r="H839" t="inlineStr"/>
+      <c r="I839" t="inlineStr"/>
+      <c r="J839" t="inlineStr"/>
+      <c r="K839" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2115153071705575805</t>
+        </is>
+      </c>
+      <c r="L839" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M839" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N839" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O839" t="inlineStr">
+        <is>
+          <t>Ramp teases a new product or feature launch with the playful statement that "the sauce is out of the bottle now," indicating a forthcoming release.</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E840" t="inlineStr">
+        <is>
+          <t>Tue Oct 27 18:45:44 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F840" t="inlineStr">
+        <is>
+          <t>@hamidships inspect doesn't do rest days</t>
+        </is>
+      </c>
+      <c r="G840" t="inlineStr"/>
+      <c r="H840" t="inlineStr"/>
+      <c r="I840" t="inlineStr"/>
+      <c r="J840" t="inlineStr"/>
+      <c r="K840" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2115152989446975831</t>
+        </is>
+      </c>
+      <c r="L840" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M840" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N840" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O840" t="inlineStr">
+        <is>
+          <t>The tweet criticizes a product named 'inspect' for lacking rest days, implying a shortfall in its service offering.</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E841" t="inlineStr">
+        <is>
+          <t>Tue Oct 27 18:45:16 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F841" t="inlineStr">
+        <is>
+          <t>@nzgb gatekeeping era officially over</t>
+        </is>
+      </c>
+      <c r="G841" t="inlineStr"/>
+      <c r="H841" t="inlineStr"/>
+      <c r="I841" t="inlineStr"/>
+      <c r="J841" t="inlineStr"/>
+      <c r="K841" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2115152870756741478</t>
+        </is>
+      </c>
+      <c r="L841" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M841" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N841" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O841" t="inlineStr">
+        <is>
+          <t>Ramp signals that the era of gatekeeping is over, indicating a shift in the industry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E842" t="inlineStr">
+        <is>
+          <t>Tue Oct 27 17:49:18 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F842" t="inlineStr">
+        <is>
+          <t>@adambaitch started by building Ramp, now we're handing out the secret sauce</t>
+        </is>
+      </c>
+      <c r="G842" t="inlineStr"/>
+      <c r="H842" t="inlineStr"/>
+      <c r="I842" t="inlineStr"/>
+      <c r="J842" t="inlineStr"/>
+      <c r="K842" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2115138785080193167</t>
+        </is>
+      </c>
+      <c r="L842" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M842" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N842" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O842" t="inlineStr">
+        <is>
+          <t>Ramp’s founder Adam Baitch announces that the company is now sharing its proprietary knowledge or technology, positioning it as a new offering.</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E843" t="inlineStr">
+        <is>
+          <t>Tue Oct 27 17:45:30 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F843" t="inlineStr">
+        <is>
+          <t>@internetsebo shortest notice period in Ramp history</t>
+        </is>
+      </c>
+      <c r="G843" t="inlineStr"/>
+      <c r="H843" t="inlineStr"/>
+      <c r="I843" t="inlineStr"/>
+      <c r="J843" t="inlineStr"/>
+      <c r="K843" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2115137830662086994</t>
+        </is>
+      </c>
+      <c r="L843" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M843" t="inlineStr">
+        <is>
+          <t>Leadership Changes</t>
+        </is>
+      </c>
+      <c r="N843" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O843" t="inlineStr">
+        <is>
+          <t>Ramp highlights a rapid leadership transition, noting the shortest notice period in its history.</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E844" t="inlineStr">
+        <is>
+          <t>Tue Oct 27 17:17:44 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F844" t="inlineStr">
+        <is>
+          <t>@vral say less 🔍</t>
+        </is>
+      </c>
+      <c r="G844" t="inlineStr"/>
+      <c r="H844" t="inlineStr"/>
+      <c r="I844" t="inlineStr"/>
+      <c r="J844" t="inlineStr"/>
+      <c r="K844" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2115130840074305932</t>
+        </is>
+      </c>
+      <c r="L844" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M844" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N844" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O844" t="inlineStr">
+        <is>
+          <t>Ramp's tweet is a brief, informal remark to @vral, likely indicating support or acknowledgment of a prior statement, with no major announcement or update.</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E845" t="inlineStr">
+        <is>
+          <t>Tue Oct 27 17:16:47 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F845" t="inlineStr">
+        <is>
+          <t>@brunodagnino we meant every word</t>
+        </is>
+      </c>
+      <c r="G845" t="inlineStr"/>
+      <c r="H845" t="inlineStr"/>
+      <c r="I845" t="inlineStr"/>
+      <c r="J845" t="inlineStr"/>
+      <c r="K845" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2115130602437349576</t>
+        </is>
+      </c>
+      <c r="L845" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M845" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N845" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O845" t="inlineStr">
+        <is>
+          <t>Ramp replies to @brunodagnino, emphasizing that they meant every word in a prior statement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E846" t="inlineStr">
+        <is>
+          <t>Tue Oct 27 22:46:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F846" t="inlineStr">
+        <is>
+          <t>@adipatel__ Coffee first. Then we can talk espresso machine incentives 👀</t>
+        </is>
+      </c>
+      <c r="G846" t="inlineStr"/>
+      <c r="H846" t="inlineStr"/>
+      <c r="I846" t="inlineStr"/>
+      <c r="J846" t="inlineStr"/>
+      <c r="K846" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2115213452264325391</t>
+        </is>
+      </c>
+      <c r="L846" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M846" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N846" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O846" t="inlineStr">
+        <is>
+          <t>Brex teases a coffee‑related perk, hinting at espresso machine incentives for its users.</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E847" t="inlineStr">
+        <is>
+          <t>Tue Oct 27 22:21:25 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F847" t="inlineStr">
+        <is>
+          <t>@ramigh Thanks for flagging this feedback, Rami. We’ll DM you to get a few more details.</t>
+        </is>
+      </c>
+      <c r="G847" t="inlineStr"/>
+      <c r="H847" t="inlineStr"/>
+      <c r="I847" t="inlineStr"/>
+      <c r="J847" t="inlineStr"/>
+      <c r="K847" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2115207266508976199</t>
+        </is>
+      </c>
+      <c r="L847" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M847" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N847" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O847" t="inlineStr">
+        <is>
+          <t>Brex acknowledges user feedback and will follow up via DM for more details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D848" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E848" t="inlineStr">
+        <is>
+          <t>Tue Oct 27 22:03:59 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F848" t="inlineStr">
+        <is>
+          <t>@willhmayer @CultHoldings Twelve levels of financial chaos. Sounds about right.</t>
+        </is>
+      </c>
+      <c r="G848" t="inlineStr"/>
+      <c r="H848" t="inlineStr"/>
+      <c r="I848" t="inlineStr"/>
+      <c r="J848" t="inlineStr"/>
+      <c r="K848" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2115202878893674696</t>
+        </is>
+      </c>
+      <c r="L848" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M848" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N848" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O848" t="inlineStr">
+        <is>
+          <t>Brex’s tweet sarcastically references financial chaos, suggesting criticism of the company’s financial situation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E849" t="inlineStr">
+        <is>
+          <t>Tue Oct 27 20:45:14 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F849" t="inlineStr">
+        <is>
+          <t>@cjgustafson So good 👏</t>
+        </is>
+      </c>
+      <c r="G849" t="inlineStr"/>
+      <c r="H849" t="inlineStr"/>
+      <c r="I849" t="inlineStr"/>
+      <c r="J849" t="inlineStr"/>
+      <c r="K849" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2115183061847715892</t>
+        </is>
+      </c>
+      <c r="L849" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M849" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N849" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O849" t="inlineStr">
+        <is>
+          <t>Brex publicly praised @cjgustafson, expressing positive sentiment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D850" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E850" t="inlineStr">
+        <is>
+          <t>Tue Oct 27 20:37:45 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F850" t="inlineStr">
+        <is>
+          <t>@gustrigos Brewing at startup speed</t>
+        </is>
+      </c>
+      <c r="G850" t="inlineStr"/>
+      <c r="H850" t="inlineStr"/>
+      <c r="I850" t="inlineStr"/>
+      <c r="J850" t="inlineStr"/>
+      <c r="K850" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2115181178537841132</t>
+        </is>
+      </c>
+      <c r="L850" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M850" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N850" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O850" t="inlineStr">
+        <is>
+          <t>Brex references @gustrigos in a tweet, suggesting a new initiative or product is being launched rapidly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>AirBnb</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D851" t="inlineStr">
+        <is>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="E851" t="inlineStr">
+        <is>
+          <t>Wed Oct 28 13:15:13 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F851" t="inlineStr">
+        <is>
+          <t>Starting today, Airbnb donates a portion of revenue from every stay to Airbnb․org to help provide free short-term housing for people displaced by disaster, traveling for medical care, or facing other crises.
+Guests don’t pay more and hosts don’t earn less. You’re helping simply by traveling.
+Learn more at https://t.co/MJVndH8Zcn</t>
+        </is>
+      </c>
+      <c r="G851" t="inlineStr"/>
+      <c r="H851" t="inlineStr"/>
+      <c r="I851" t="inlineStr"/>
+      <c r="J851" t="inlineStr"/>
+      <c r="K851" t="inlineStr">
+        <is>
+          <t>https://x.com/Airbnb/status/2115432197360599168</t>
+        </is>
+      </c>
+      <c r="L851" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M851" t="inlineStr">
+        <is>
+          <t>Strategic Expansion or Changes</t>
+        </is>
+      </c>
+      <c r="N851" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O851" t="inlineStr">
+        <is>
+          <t>Airbnb announces a new donation program that allocates a portion of revenue from every stay to Airbnb.org, providing free short‑term housing for people displaced by disaster, medical travel, or other crises, without impacting guests or hosts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>AirBnb</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D852" t="inlineStr">
+        <is>
+          <t>airbnb</t>
+        </is>
+      </c>
+      <c r="E852" t="inlineStr">
+        <is>
+          <t>2026-10-28T13:00:02.000Z</t>
+        </is>
+      </c>
+      <c r="F852" t="inlineStr">
+        <is>
+          <t>Starting today, Airbnb donates a portion of revenue from every stay to Airbnb.org to help provide short-term housing for people displaced by disaster, traveling for medical care, or facing other crises.
+Guests don’t pay more and hosts don’t earn less. You’re helping simply by traveling.
+Learn more at the link in bio.</t>
+        </is>
+      </c>
+      <c r="G852" t="inlineStr">
+        <is>
+          <t>https://scontent-lhr11-1.cdninstagram.com/v/t51.82787-15/868596708_18649922734063838_4656453728128786121_n.jpg?stp=dst-jpg_e35_tt6&amp;_nc_cat=1&amp;ig_cache_key=NDAxNzg2MjA3NTI4ODE5NTQ1Nw%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNBUk9VU0VMX0lURU0ueHBpZHMuMjE0OS5zZHIucmVndWxhcl9waG90by5DMyJ9&amp;_nc_ohc=UY9GuIJLdo8Q7kNvwELqgzc&amp;_nc_oc=AdomKGAX4Vq3vJr_PO0b5WOxLDRegNlpHTgEwDo2Argr_7qw4BkjrI6gTzys4Jb-g0g&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-lhr11-1.cdninstagram.com&amp;_nc_gid=cao2_Sp7HSOrKeCD5Qu_kg&amp;_nc_ss=7a20f&amp;oh=00_AQQu3c6etzDhKmNq_Uxi4X-SfYBeFxpFe7EVzN2gvSDrOA&amp;oe=6AE7EF00</t>
+        </is>
+      </c>
+      <c r="H852" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I852" t="inlineStr"/>
+      <c r="J852" t="inlineStr"/>
+      <c r="K852" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DfCfaWDEYx0/</t>
+        </is>
+      </c>
+      <c r="L852" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M852" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N852" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O852" t="inlineStr">
+        <is>
+          <t>Airbnb launches a new program donating a portion of stay revenue to Airbnb.org to provide short‑term housing for people displaced by disaster, medical travel, or other crises, without affecting guests or hosts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D853" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E853" t="inlineStr">
+        <is>
+          <t>Wed Oct 28 00:00:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F853" t="inlineStr">
+        <is>
+          <t>Experience the vibrant culture and world-class cuisine of Mexico City 🇲🇽
+➡️ The history: Explore the ancient pyramids of Teotihuacan and the historic Zócalo.
+➡️ The food: Taste authentic street tacos and wander through the trendy Roma neighborhood.
+➡️ The stays: Relax in a beautifully restored boutique hotel in the heart of the city.
+🔗 Plan your travel:
+https://t.co/MxatD6lOmZ</t>
+        </is>
+      </c>
+      <c r="G853" t="inlineStr"/>
+      <c r="H853" t="inlineStr"/>
+      <c r="I853" t="inlineStr"/>
+      <c r="J853" t="inlineStr"/>
+      <c r="K853" t="inlineStr">
+        <is>
+          <t>https://x.com/Expedia/status/2115232075238248632</t>
+        </is>
+      </c>
+      <c r="L853" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M853" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N853" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O853" t="inlineStr">
+        <is>
+          <t>Expedia promotes Mexico City as a vibrant travel destination, highlighting its culture, cuisine, and boutique accommodations, and directs followers to book via a provided link.</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D854" t="inlineStr">
+        <is>
+          <t>expedia</t>
+        </is>
+      </c>
+      <c r="E854" t="inlineStr">
+        <is>
+          <t>2026-10-28T15:00:44.000Z</t>
+        </is>
+      </c>
+      <c r="F854" t="inlineStr">
+        <is>
+          <t>Let's go to Hyogo, Japan!
+Hyogo was easily one of our favorite trips to Japan, and it turns out more people are discovering it too! With a 95% increase in travel searches on @expedia , Hyogo has made the list of Expedia’s Destinations of the Year for 2027.
+If you’re planning a trip to Japan and looking to explore somewhere beyond the usual stops, definitely consider adding Hyogo to your itinerary.
+Check out Expedia’s Unpack ’27 report for more destinations on the rise, and save this for your next trip to Japan!
+#ExpediaAmbassador</t>
+        </is>
+      </c>
+      <c r="G854" t="inlineStr">
+        <is>
+          <t>https://instagram.fcdg4-1.fna.fbcdn.net/v/t51.82787-15/870141433_1426747546193129_5387975974869068791_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=105&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=NDAxNzk3MTYxOTg1MDM4MDYzMDE0MjY3NDc1Mzk1MjY0NjM%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNMSVBTLnhwaWRzLjEyMTYuc2RyLnZpZGVvX2RlZmF1bHRfY292ZXJfZnJhbWUuQzMifQ%3D%3D&amp;_nc_ohc=E_ZOiLI3boUQ7kNvwGom_cS&amp;_nc_oc=Adrc5hSkzYt4GZTbqDPrVlz_3znQxFx07IUDKBbXSZE6_29fHw5Jd0a9SxZFkvJ-XwPRdpZai41UtYymMXpzqbw8&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fcdg4-1.fna&amp;_nc_gid=a2SXiFYaDuHnTgro32ql4w&amp;_nc_ss=7a20f&amp;oh=00_AQSvUMKzY9fnBjzQK-SK1m-hjj55zjBTntGnZWgb7zCanA&amp;oe=6AE7FF8F</t>
+        </is>
+      </c>
+      <c r="H854" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I854" t="inlineStr">
+        <is>
+          <t>https://instagram.fcdg4-1.fna.fbcdn.net/o1/v/t2/f2/m86/AQMR0lGUIXr4lQcx3sLi-QyH8XyZT2OqOf8VKLk62rquW3DUhA2piL9ilvmPZElfeflOi5FapXAo1Ra8eeENfj34ZplDlt0irvDs7io.mp4?_nc_cat=103&amp;_nc_oc=AdpheslH4u0EaLvt-4mK69SDkiNkVKVkXs10xmcje1QOg03SZMpbQM-CJLxT-VoVRSfM61rRZVelnCnDSwS2MgSr&amp;_nc_sid=5e9851&amp;_nc_ht=instagram.fcdg4-1.fna.fbcdn.net&amp;_nc_ohc=EvtOo2pqjNsQ7kNvwGOaXUL&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTQyNjc0Njk0OTUyNjUyMiwiYXNzZXRfYWdlX2RheXMiOjAsInZpX3VzZWNhc2VfaWQiOjEwMDk5LCJkdXJhdGlvbl9zIjo1OCwidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=9a2f5f7d0e65fd9&amp;_nc_vs=HBksFQIYUmlnX3hwdl9yZWVsc19wZXJtYW5lbnRfc3JfcHJvZC84QUEzRDkxOUUyREI0M0Y5QURGQTlDMjJGODIyQjFEMV92aWRlb19kYXNoaW5pdC5tcDQVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzc2NTIyMEMxRkQ4NzQ3MTc5QzRFNEYxMTlGOUM1RUY0X2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACb0j-ORzeeIBRUCKAJDMywXQE1mZmZmZmYYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=a2SXiFYaDuHnTgro32ql4w&amp;_nc_map=urlgen_bucketless&amp;_nc_zt=28&amp;_nc_ss=70580&amp;oh=00_AQRLi67fONqxTNwcYIw-vS7zvvfAbIcq00IDBuD5-lnL7Q&amp;oe=6AE3F7C0</t>
+        </is>
+      </c>
+      <c r="J854" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K854" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DfCs-ZuyGVW/</t>
+        </is>
+      </c>
+      <c r="L854" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M854" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N854" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O854" t="inlineStr">
+        <is>
+          <t>Expedia promotes Hyogo, Japan as a top destination for 2027, citing a 95% rise in travel searches and urging travelers to include it in their itineraries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D855" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E855" t="inlineStr">
+        <is>
+          <t>Wed Oct 28 15:56:49 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F855" t="inlineStr">
+        <is>
+          <t>@mmorillasm Te hemos repetido en varias ocasiones la información que necesitamos para dar seguimiento a tu solicitud, Manu. En cuanto la tengas, compártela por DM.</t>
+        </is>
+      </c>
+      <c r="G855" t="inlineStr"/>
+      <c r="H855" t="inlineStr"/>
+      <c r="I855" t="inlineStr"/>
+      <c r="J855" t="inlineStr"/>
+      <c r="K855" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2115472868020457940</t>
+        </is>
+      </c>
+      <c r="L855" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M855" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N855" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O855" t="inlineStr">
+        <is>
+          <t>Booking.com is requesting additional information from a user to follow up on a request.</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D856" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E856" t="inlineStr">
+        <is>
+          <t>Wed Oct 28 15:28:30 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F856" t="inlineStr">
+        <is>
+          <t>@ravichreshetov Hi Aleksandr, thank you for contacting us. We regret seeing that your stay did not meet the expectations. For verification purposes, kindly DM us your booking details:
+- Confirmation number, 
+- PIN-code, 
+- Name on the reservation,
+so we can look into this for you.</t>
+        </is>
+      </c>
+      <c r="G856" t="inlineStr"/>
+      <c r="H856" t="inlineStr"/>
+      <c r="I856" t="inlineStr"/>
+      <c r="J856" t="inlineStr"/>
+      <c r="K856" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2115465739947704738</t>
+        </is>
+      </c>
+      <c r="L856" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M856" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N856" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O856" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint about a stay, requesting booking details for verification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E857" t="inlineStr">
+        <is>
+          <t>Wed Oct 28 14:25:43 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F857" t="inlineStr">
+        <is>
+          <t>@CerlinX16844 Before we can proceed, we will require some additional details to be shared by DM for security. 
+Please get back to us with: 
+* Your full name, 
+* The email address associated with the account, 
+and we will be in touch. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G857" t="inlineStr"/>
+      <c r="H857" t="inlineStr"/>
+      <c r="I857" t="inlineStr"/>
+      <c r="J857" t="inlineStr"/>
+      <c r="K857" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2115449939484446937</t>
+        </is>
+      </c>
+      <c r="L857" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M857" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N857" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O857" t="inlineStr">
+        <is>
+          <t>Booking.com appears to be sending a DM requesting personal details, likely a phishing attempt, highlighting a security concern.</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D858" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E858" t="inlineStr">
+        <is>
+          <t>Wed Oct 28 13:52:16 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F858" t="inlineStr">
+        <is>
+          <t>Hi there, we regret hearing this and would like to check your booking, please send us (or ask your friend to) a private message with the following details, and we'll get back to you as soon as possible: 
+- Confirmation number
+- Pin code
+- Name on the reservation (meaning the name of the traveler)
+Please bear in mind that our Social Media Team doesn't work in real time. For immediate support, please call our 24/7 Customer Service Team - our contact details can be found here: https://t.co/o8QyR8SaDb
+Also, at this time, we only offer support for accommodation bookings via social media. For questions about Flights, Taxis, or Insurance, you can reach out to the dedicated support team here: https://t.co/UfRgpDJomK</t>
+        </is>
+      </c>
+      <c r="G858" t="inlineStr"/>
+      <c r="H858" t="inlineStr"/>
+      <c r="I858" t="inlineStr"/>
+      <c r="J858" t="inlineStr"/>
+      <c r="K858" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2115441522090860805</t>
+        </is>
+      </c>
+      <c r="L858" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M858" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N858" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O858" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint on X, offering to review the booking via private message and directing users to 24/7 customer service for immediate support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E859" t="inlineStr">
+        <is>
+          <t>Wed Oct 28 13:49:33 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F859" t="inlineStr">
+        <is>
+          <t>Bonjour Mazieres,
+Nous souhaitons consulter ce remboursement pour vous. Veuillez nous envoyer un message privé contenant les informations suivantes :
+- Numéro de réservation
+- Code confidentiel
+- Nom complet du voyageur
+Une fois que nous aurons reçu ces informations, nous pourrons consulter votre dossier et revenir vers vous.
+Bien cordialement.</t>
+        </is>
+      </c>
+      <c r="G859" t="inlineStr"/>
+      <c r="H859" t="inlineStr"/>
+      <c r="I859" t="inlineStr"/>
+      <c r="J859" t="inlineStr"/>
+      <c r="K859" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2115440837454684345</t>
+        </is>
+      </c>
+      <c r="L859" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M859" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N859" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O859" t="inlineStr">
+        <is>
+          <t>Booking.com requests private message from a user with reservation details to process a refund.</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D860" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E860" t="inlineStr">
+        <is>
+          <t>Wed Oct 28 13:33:21 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F860" t="inlineStr">
+        <is>
+          <t>Hi Cerlin, thank you for reaching out. We understand your concern regarding the pending refund.
+Upon review, we can see that the payment was collected via UPI. As noted in our previous correspondence, any collected funds are refunded to the original payment method (UPI) within 12 business days.
+Depending on your payment provider or banking institution, processing times can occasionally vary. We recommend contacting your UPI provider directly for specific timelines regarding incoming transactions.</t>
+        </is>
+      </c>
+      <c r="G860" t="inlineStr"/>
+      <c r="H860" t="inlineStr"/>
+      <c r="I860" t="inlineStr"/>
+      <c r="J860" t="inlineStr"/>
+      <c r="K860" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2115436761513967901</t>
+        </is>
+      </c>
+      <c r="L860" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M860" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N860" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O860" t="inlineStr">
+        <is>
+          <t>Booking.com addresses a customer’s refund inquiry, clarifying that the refund will be processed to the original UPI payment method within 12 business days and advising the customer to contact their UPI provider for specific timelines.</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D861" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E861" t="inlineStr">
+        <is>
+          <t>Wed Oct 28 13:25:28 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F861" t="inlineStr">
+        <is>
+          <t>Thank you for letting us know that the Indian contact numbers are not working. We have informed our specialized team to fix this issue. In the meantime, you can contact our finance team through the extranet inbox or call the Partner Support Team at our 24/7 international number: +442086128159.</t>
+        </is>
+      </c>
+      <c r="G861" t="inlineStr"/>
+      <c r="H861" t="inlineStr"/>
+      <c r="I861" t="inlineStr"/>
+      <c r="J861" t="inlineStr"/>
+      <c r="K861" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2115434776232391105</t>
+        </is>
+      </c>
+      <c r="L861" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M861" t="inlineStr">
+        <is>
+          <t>Tech Updates</t>
+        </is>
+      </c>
+      <c r="N861" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O861" t="inlineStr">
+        <is>
+          <t>Booking.com acknowledges a technical issue with Indian contact numbers and directs partners to alternative contact methods while the issue is being resolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D862" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E862" t="inlineStr">
+        <is>
+          <t>Wed Oct 28 12:33:50 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F862" t="inlineStr">
+        <is>
+          <t>@LaRectoraMdC Lamentamos la situación. Debido a que solo ellos pueden atender tu solicitud, te sugerimos volver a contactarles. 
+Agradecemos tu paciencia.
+Un saludo. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G862" t="inlineStr"/>
+      <c r="H862" t="inlineStr"/>
+      <c r="I862" t="inlineStr"/>
+      <c r="J862" t="inlineStr"/>
+      <c r="K862" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2115421783889199363</t>
+        </is>
+      </c>
+      <c r="L862" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M862" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N862" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O862" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes to a user for an issue and advises them to contact the relevant party again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D863" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E863" t="inlineStr">
+        <is>
+          <t>Wed Oct 28 12:27:31 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F863" t="inlineStr">
+        <is>
+          <t>@QuaresmaGreg  We value your loyalty, but we cannot extend a goodwill gesture for a price match that hasn't been approved. If you would like to speak with a supervisor, please reach out to our customer service again and request to escalate the call.</t>
+        </is>
+      </c>
+      <c r="G863" t="inlineStr"/>
+      <c r="H863" t="inlineStr"/>
+      <c r="I863" t="inlineStr"/>
+      <c r="J863" t="inlineStr"/>
+      <c r="K863" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2115420192297599005</t>
+        </is>
+      </c>
+      <c r="L863" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M863" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N863" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O863" t="inlineStr">
+        <is>
+          <t>Booking.com declines a price‑match request from a customer and directs them to contact customer service for escalation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D864" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E864" t="inlineStr">
+        <is>
+          <t>Wed Oct 28 12:18:33 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F864" t="inlineStr">
+        <is>
+          <t>Bonjour Nasse,
+Nous souhaitons consulter cette situation pour vous. Veuillez nous envoyer un message privé contenant les informations suivantes :
+- Numéro de réservation
+- Code confidentiel
+- Nom complet du voyageur
+Une fois que nous aurons reçu ces informations, nous pourrons consulter votre dossier et revenir vers vous.
+Bien cordialement.</t>
+        </is>
+      </c>
+      <c r="G864" t="inlineStr"/>
+      <c r="H864" t="inlineStr"/>
+      <c r="I864" t="inlineStr"/>
+      <c r="J864" t="inlineStr"/>
+      <c r="K864" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2115417937213292730</t>
+        </is>
+      </c>
+      <c r="L864" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M864" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N864" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O864" t="inlineStr">
+        <is>
+          <t>Booking.com is requesting private customer details via direct message to review a situation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D865" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E865" t="inlineStr">
+        <is>
+          <t>Wed Oct 28 12:15:21 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F865" t="inlineStr">
+        <is>
+          <t>@ethiopton Hi there, we've sent you a DM with more information regarding your case. Please review it and get in touch with the relevant team.</t>
+        </is>
+      </c>
+      <c r="G865" t="inlineStr"/>
+      <c r="H865" t="inlineStr"/>
+      <c r="I865" t="inlineStr"/>
+      <c r="J865" t="inlineStr"/>
+      <c r="K865" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2115417133882466555</t>
+        </is>
+      </c>
+      <c r="L865" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M865" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N865" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O865" t="inlineStr">
+        <is>
+          <t>Booking.com is responding to a user’s inquiry about a case via direct message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D866" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E866" t="inlineStr">
+        <is>
+          <t>Wed Oct 28 11:49:29 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F866" t="inlineStr">
+        <is>
+          <t>@Gonnabealrite Hi there, we regret to hear that you are facing issues with your refund. 
+Please feel free to send a DM with your: 
+-reservation number 
+-pin code 
+-name of the guest 
+Thank you.</t>
+        </is>
+      </c>
+      <c r="G866" t="inlineStr"/>
+      <c r="H866" t="inlineStr"/>
+      <c r="I866" t="inlineStr"/>
+      <c r="J866" t="inlineStr"/>
+      <c r="K866" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2115410620518437013</t>
+        </is>
+      </c>
+      <c r="L866" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M866" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N866" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O866" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user’s refund complaint, offering to collect reservation details via direct message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E867" t="inlineStr">
+        <is>
+          <t>Wed Oct 28 11:47:14 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F867" t="inlineStr">
+        <is>
+          <t>We understand the urgency of the matter, Pradip, and regret to learn your opinion on our services. 
+While we appreciate that you have reached out to us here, we are, unfortunately, unable to help via Social Media. Your inquiry can only be addressed directly with our specialized team at the previously shared details.  
+Best regards</t>
+        </is>
+      </c>
+      <c r="G867" t="inlineStr"/>
+      <c r="H867" t="inlineStr"/>
+      <c r="I867" t="inlineStr"/>
+      <c r="J867" t="inlineStr"/>
+      <c r="K867" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2115410054534877462</t>
+        </is>
+      </c>
+      <c r="L867" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M867" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N867" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O867" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s inquiry on X, politely directing them to a specialized team for further assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D868" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E868" t="inlineStr">
+        <is>
+          <t>Wed Oct 28 11:45:14 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F868" t="inlineStr">
+        <is>
+          <t>Hi Silvia, 
+we regret to learn about your opinion on our services, and we would like to have a look at what happened to see how we can help. 
+Please share with us in a private message: 
+- reservation number 
+- PIN code 
+- guest name on the booking. 
+We will check and get back to you as soon as we can. 
+Kind regards</t>
+        </is>
+      </c>
+      <c r="G868" t="inlineStr"/>
+      <c r="H868" t="inlineStr"/>
+      <c r="I868" t="inlineStr"/>
+      <c r="J868" t="inlineStr"/>
+      <c r="K868" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2115409551549665489</t>
+        </is>
+      </c>
+      <c r="L868" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M868" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N868" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O868" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint, requesting booking details to investigate the issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D869" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E869" t="inlineStr">
+        <is>
+          <t>Wed Oct 28 11:34:17 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F869" t="inlineStr">
+        <is>
+          <t>The line you reached might be getting more calls than usual. If that's the case, after reporting the incident to the local authorities, we suggest you doing it through the Extranet by selecting Guest Misconduct in the Reservation Tab and/or calling the 24/7 international line at:+442086128159.</t>
+        </is>
+      </c>
+      <c r="G869" t="inlineStr"/>
+      <c r="H869" t="inlineStr"/>
+      <c r="I869" t="inlineStr"/>
+      <c r="J869" t="inlineStr"/>
+      <c r="K869" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2115406798395957446</t>
+        </is>
+      </c>
+      <c r="L869" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M869" t="inlineStr">
+        <is>
+          <t>Tech Updates</t>
+        </is>
+      </c>
+      <c r="N869" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O869" t="inlineStr">
+        <is>
+          <t>Booking.com advises users to report incidents to local authorities and then use the Extranet or a 24/7 international line for further reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D870" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E870" t="inlineStr">
+        <is>
+          <t>Wed Oct 28 11:13:09 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F870" t="inlineStr">
+        <is>
+          <t>Hello, thank you for messaging us. We regret to hear that about the service provided, and that you're still waiting on a refund. We'd like to look into this, but are unable to see any previous communication via Social Media due to privacy. If you need support with an accommodation booking, then kindly DM the following details:
+- Confirmation number, 
+- PIN-code, 
+- Name on the reservation,
+so we can follow up further.</t>
+        </is>
+      </c>
+      <c r="G870" t="inlineStr"/>
+      <c r="H870" t="inlineStr"/>
+      <c r="I870" t="inlineStr"/>
+      <c r="J870" t="inlineStr"/>
+      <c r="K870" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2115401477682282855</t>
+        </is>
+      </c>
+      <c r="L870" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M870" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N870" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O870" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint about a refund, requesting booking details for further investigation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E871" t="inlineStr">
+        <is>
+          <t>Wed Oct 28 11:11:34 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F871" t="inlineStr">
+        <is>
+          <t>Hi there, thank you for contacting us. We regret to hear that you're still waiting on an update. We'd like to look into this, but are unable to see any previous communication via Social Media due to privacy. If you need support with an accommodation booking, then kindly DM the following details:
+- Confirmation number, 
+- PIN-code, 
+- Name on the reservation,
+so we can follow up.</t>
+        </is>
+      </c>
+      <c r="G871" t="inlineStr"/>
+      <c r="H871" t="inlineStr"/>
+      <c r="I871" t="inlineStr"/>
+      <c r="J871" t="inlineStr"/>
+      <c r="K871" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2115401079688925689</t>
+        </is>
+      </c>
+      <c r="L871" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M871" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N871" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O871" t="inlineStr">
+        <is>
+          <t>Booking.com replies to a customer’s inquiry about a pending update, asking for booking details via direct message to investigate further.</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D872" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E872" t="inlineStr">
+        <is>
+          <t>Wed Oct 28 10:28:33 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F872" t="inlineStr">
+        <is>
+          <t>Hola, lamentamos saber lo ocurrido. Estaremos encantados de investigar tu situación y ver cómo podemos ayudarte. Envíanos un mensaje privado con la siguiente información y te responderemos con lo que hayamos averiguado:
+- Código PIN:
+- Nombre que aparece en la reserva.
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G872" t="inlineStr"/>
+      <c r="H872" t="inlineStr"/>
+      <c r="I872" t="inlineStr"/>
+      <c r="J872" t="inlineStr"/>
+      <c r="K872" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2115390253318000769</t>
+        </is>
+      </c>
+      <c r="L872" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M872" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N872" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O872" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for a customer issue and offers to investigate via private message, requesting PIN and reservation name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D873" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E873" t="inlineStr">
+        <is>
+          <t>Wed Oct 28 10:19:06 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F873" t="inlineStr">
+        <is>
+          <t>Sentimos lo ocurrido con tu reserva, que no hayas recibido el reembolso y que tengas esa impresión de nuestro equipo de atención al cliente, Angie. Si quieres que lo revisemos, envíanos un mensaje privado con los siguientes datos y nos pondremos en contacto contigo lo antes posible: 
+- Número de confirmación: 
+- Código PIN: 
+- Nombre que aparece en la reserva: 
+- Detalles de tu solicitud: 
+Como alternativa, para recibir ayuda inmediata, siempre puedes llamarnos aquí: https://t.co/o8QyR8SaDb 
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G873" t="inlineStr"/>
+      <c r="H873" t="inlineStr"/>
+      <c r="I873" t="inlineStr"/>
+      <c r="J873" t="inlineStr"/>
+      <c r="K873" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2115387875730538997</t>
+        </is>
+      </c>
+      <c r="L873" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M873" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N873" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O873" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint about a missing refund, offering to investigate via private message or phone call.</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E874" t="inlineStr">
+        <is>
+          <t>Wed Oct 28 10:14:56 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F874" t="inlineStr">
+        <is>
+          <t>Hi there. We regret to hear you about this. To validate a price match claim, the better deal found has to be for the same dates, as the rates vary depending on dates. If you'd like us to review your booking and the claim, please send us a private message with the following details of your reservation:
+- Confirmation number
+- PIN
+- Name on the reservation
+And we will get back to you as soon as possible.</t>
+        </is>
+      </c>
+      <c r="G874" t="inlineStr"/>
+      <c r="H874" t="inlineStr"/>
+      <c r="I874" t="inlineStr"/>
+      <c r="J874" t="inlineStr"/>
+      <c r="K874" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2115386826470896114</t>
+        </is>
+      </c>
+      <c r="L874" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M874" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N874" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O874" t="inlineStr">
+        <is>
+          <t>Booking.com explains its price‑match policy and asks customers to send booking details via private message for review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D875" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="E875" t="inlineStr">
+        <is>
+          <t>2026-10-28T08:41:40.602Z</t>
+        </is>
+      </c>
+      <c r="F875" t="inlineStr">
+        <is>
+          <t>Today is World Sustainability Day – a day to consider the long-term health of the places we live, work and travel.
+Did you know that 85% of travellers say more sustainable travel is important or very important to them, and that 58% of them tell us they plan to filter for a sustainability-certified stay the next time they book.
+If 81% of accommodation partners tell us they have sustainability practices in place, why aren't more of them getting certified?
+The biggest challenge: lack of awareness. 60% of partners tell us they aren’t familiar with sustainability certifications.
+Discover why third-party certification is an important next step for accommodation providers on their sustainability journeys. Find the full report, here: https://lnkd.in/esNdbVnD</t>
+        </is>
+      </c>
+      <c r="G875" t="inlineStr"/>
+      <c r="H875" t="inlineStr"/>
+      <c r="I875" t="inlineStr"/>
+      <c r="J875" t="inlineStr"/>
+      <c r="K875" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/booking%2Ecom_sustainability-insights-activity-7521129046903025664--K1c</t>
+        </is>
+      </c>
+      <c r="L875" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M875" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N875" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O875" t="inlineStr">
+        <is>
+          <t>Booking.com underscores the growing importance of sustainability in travel, shares statistics on traveler preferences and partner awareness, and promotes a report on third‑party certification for accommodations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>SkyBirdTravel</t>
+        </is>
+      </c>
+      <c r="E876" t="inlineStr">
+        <is>
+          <t>Wed Oct 28 14:50:20 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F876" t="inlineStr">
+        <is>
+          <t>Discover what Sky Bird’s valued clients have to say about their booking experience! 
+If you want to be featured next, then leave a review on Facebook or Google here: https://t.co/mKGU65Q4EI! 
+#SkyBird #AirlineConsolidator #AirlineWholesaler #FlightColsolidator #Testimonial https://t.co/wwRuqlPfPA</t>
+        </is>
+      </c>
+      <c r="G876" t="inlineStr"/>
+      <c r="H876" t="inlineStr"/>
+      <c r="I876" t="inlineStr"/>
+      <c r="J876" t="inlineStr"/>
+      <c r="K876" t="inlineStr">
+        <is>
+          <t>https://x.com/SkyBirdTravel/status/2115456134605844537</t>
+        </is>
+      </c>
+      <c r="L876" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M876" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N876" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O876" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel is soliciting customer reviews to highlight positive booking experiences, reinforcing its reputation as a reliable airline consolidator.</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D877" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel &amp; Tours</t>
+        </is>
+      </c>
+      <c r="E877" t="inlineStr">
+        <is>
+          <t>2026-10-28T14:50:01.592Z</t>
+        </is>
+      </c>
+      <c r="F877" t="inlineStr">
+        <is>
+          <t>Discover what Sky Bird’s valued clients have to say about their booking experience! 
+If you want to be featured next, then leave a review on Facebook or Google, here: bit.ly/4hJsABc! 
+#SkyBird #AirlineConsolidator #AirlineWholesaler #FlightColsolidator #Testimonial #Review</t>
+        </is>
+      </c>
+      <c r="G877" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D4D22AQEXHYvSnoOKNQ/feedshare-shrink_1280/B4DaGC_Um0GUAQ-/0/1793199000505?e=1795046400&amp;v=beta&amp;t=lKKD_XYXGE9Z9LAjdr47WFSZZdfbecfKNrt0ofl_0hY</t>
+        </is>
+      </c>
+      <c r="H877" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I877" t="inlineStr"/>
+      <c r="J877" t="inlineStr"/>
+      <c r="K877" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/sky-bird-travel-tours_skybird-airlineconsolidator-airlinewholesaler-activity-7521221745173745664-KWu4</t>
+        </is>
+      </c>
+      <c r="L877" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M877" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N877" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O877" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel is promoting customer testimonials by encouraging clients to leave reviews on Facebook or Google, aiming to feature positive feedback on their LinkedIn page.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O877"/>
+  <dimension ref="A1:O885"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56629,6 +56629,500 @@
         </is>
       </c>
     </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D878" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E878" t="inlineStr">
+        <is>
+          <t>Wed Oct 28 16:43:40 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F878" t="inlineStr">
+        <is>
+          <t>@ben_kauf Glad we could help!</t>
+        </is>
+      </c>
+      <c r="G878" t="inlineStr"/>
+      <c r="H878" t="inlineStr"/>
+      <c r="I878" t="inlineStr"/>
+      <c r="J878" t="inlineStr"/>
+      <c r="K878" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2115484657609535851</t>
+        </is>
+      </c>
+      <c r="L878" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M878" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N878" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O878" t="inlineStr">
+        <is>
+          <t>Ramp publicly expresses gratitude to @ben_kauf, indicating they successfully assisted him.</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D879" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E879" t="inlineStr">
+        <is>
+          <t>Wed Oct 28 16:42:55 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F879" t="inlineStr">
+        <is>
+          <t>@paxgoeshard 👏</t>
+        </is>
+      </c>
+      <c r="G879" t="inlineStr"/>
+      <c r="H879" t="inlineStr"/>
+      <c r="I879" t="inlineStr"/>
+      <c r="J879" t="inlineStr"/>
+      <c r="K879" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2115484466617655608</t>
+        </is>
+      </c>
+      <c r="L879" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M879" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N879" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O879" t="inlineStr">
+        <is>
+          <t>Ramp gives a brief shoutout to @paxgoeshard, expressing support or congratulations with an applause emoji.</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>AirBnb</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D880" t="inlineStr">
+        <is>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="E880" t="inlineStr">
+        <is>
+          <t>2026-10-28T13:19:42.853Z</t>
+        </is>
+      </c>
+      <c r="F880" t="inlineStr">
+        <is>
+          <t>Starting today, Airbnb donates a portion of revenue from every stay to Airbnb.org to help provide free short-term housing for people displaced by disaster, traveling for medical care, or facing other crises.
+Guests don’t pay more and hosts don’t earn less. You’re helping simply by traveling.
+Learn more at airbnb.org/airbnb</t>
+        </is>
+      </c>
+      <c r="G880" t="inlineStr"/>
+      <c r="H880" t="inlineStr"/>
+      <c r="I880" t="inlineStr"/>
+      <c r="J880" t="inlineStr"/>
+      <c r="K880" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/airbnb_airbnb-announcement-activity-7521199017335250947-pZQg</t>
+        </is>
+      </c>
+      <c r="L880" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M880" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N880" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O880" t="inlineStr">
+        <is>
+          <t>Airbnb announces a new program that donates a portion of revenue from every stay to Airbnb.org, providing free short‑term housing for people displaced by disaster, medical travel, or other crises, without impacting guests or hosts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E881" t="inlineStr">
+        <is>
+          <t>Wed Oct 28 17:46:28 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F881" t="inlineStr">
+        <is>
+          <t>@ravichreshetov Hi Aleksandr, thank you for reaching out. We acknowledge your message and would like to let you know that we have already responded to you via private message with further information regarding your case. Please refer to our DM for the latest update.</t>
+        </is>
+      </c>
+      <c r="G881" t="inlineStr"/>
+      <c r="H881" t="inlineStr"/>
+      <c r="I881" t="inlineStr"/>
+      <c r="J881" t="inlineStr"/>
+      <c r="K881" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2115500461088203115</t>
+        </is>
+      </c>
+      <c r="L881" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M881" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N881" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O881" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user on X, directing them to a private message for further information.</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D882" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E882" t="inlineStr">
+        <is>
+          <t>Wed Oct 28 17:31:55 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F882" t="inlineStr">
+        <is>
+          <t>@sunsaathiyax Hi there, we understand how important this matter is to you regarding the refund that you haven't yet received. We have responded to your message privately. Please check it at your earliest convenience.</t>
+        </is>
+      </c>
+      <c r="G882" t="inlineStr"/>
+      <c r="H882" t="inlineStr"/>
+      <c r="I882" t="inlineStr"/>
+      <c r="J882" t="inlineStr"/>
+      <c r="K882" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2115496798772978039</t>
+        </is>
+      </c>
+      <c r="L882" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M882" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N882" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O882" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer’s refund inquiry via private message, acknowledging the issue and directing them to check their private response.</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D883" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E883" t="inlineStr">
+        <is>
+          <t>Wed Oct 28 17:20:12 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F883" t="inlineStr">
+        <is>
+          <t>@Gonnabealrite Hi there, thanks for reaching back to us, and appreciate your time sending you details to us. We've sent you a private message.  Please check it at your earliest convenience. Kind regards. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G883" t="inlineStr"/>
+      <c r="H883" t="inlineStr"/>
+      <c r="I883" t="inlineStr"/>
+      <c r="J883" t="inlineStr"/>
+      <c r="K883" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2115493849145524290</t>
+        </is>
+      </c>
+      <c r="L883" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M883" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N883" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O883" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user on X, thanking them and directing them to a private message for further details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E884" t="inlineStr">
+        <is>
+          <t>Wed Oct 28 18:18:25 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F884" t="inlineStr">
+        <is>
+          <t>@Milan_z_Bali We have sent you a private message; kindly check it at your earliest convenience. Thank you.</t>
+        </is>
+      </c>
+      <c r="G884" t="inlineStr"/>
+      <c r="H884" t="inlineStr"/>
+      <c r="I884" t="inlineStr"/>
+      <c r="J884" t="inlineStr"/>
+      <c r="K884" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2115508502764322911</t>
+        </is>
+      </c>
+      <c r="L884" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M884" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N884" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O884" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents sent a private message to user @Milan_z_Bali, asking them to check it at their earliest convenience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents</t>
+        </is>
+      </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D885" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E885" t="inlineStr">
+        <is>
+          <t>Wed Oct 28 18:18:16 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F885" t="inlineStr">
+        <is>
+          <t>Hi Cynthia, in order for us to further investigate and assist you, please DM us the following details, and we'll get back to you as soon as possible: 
+• Confirmation number: 
+• Pin code: 
+• Name on the reservation: 
+Please bear in mind that our Social Media Team doesn't work in real time. For immediate support, please call our 24/7 Customer Service Team - our contact details can be found here: https://t.co/o8QyR8SaDb.</t>
+        </is>
+      </c>
+      <c r="G885" t="inlineStr"/>
+      <c r="H885" t="inlineStr"/>
+      <c r="I885" t="inlineStr"/>
+      <c r="J885" t="inlineStr"/>
+      <c r="K885" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2115508463958720786</t>
+        </is>
+      </c>
+      <c r="L885" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M885" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N885" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O885" t="inlineStr">
+        <is>
+          <t>Booking.com for Travel Agents is offering standard support instructions to a user, requesting reservation details via DM and directing them to a 24/7 phone support line.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O885"/>
+  <dimension ref="A1:O920"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57123,6 +57123,2263 @@
         </is>
       </c>
     </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D886" t="inlineStr">
+        <is>
+          <t>navan</t>
+        </is>
+      </c>
+      <c r="E886" t="inlineStr">
+        <is>
+          <t>Thu Oct 29 15:58:59 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F886" t="inlineStr">
+        <is>
+          <t>PSA: This is your life without Navan</t>
+        </is>
+      </c>
+      <c r="G886" t="inlineStr"/>
+      <c r="H886" t="inlineStr"/>
+      <c r="I886" t="inlineStr"/>
+      <c r="J886" t="inlineStr"/>
+      <c r="K886" t="inlineStr">
+        <is>
+          <t>https://x.com/Navan/status/2115835799438536930</t>
+        </is>
+      </c>
+      <c r="L886" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M886" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N886" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O886" t="inlineStr">
+        <is>
+          <t>Navan promotes its product by highlighting the drawbacks of operating without it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D887" t="inlineStr">
+        <is>
+          <t>navan</t>
+        </is>
+      </c>
+      <c r="E887" t="inlineStr">
+        <is>
+          <t>Thu Oct 29 14:34:46 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F887" t="inlineStr">
+        <is>
+          <t>LAX is more than an airport code, it’s a way of life. When Navan customer @PremierLacrosse hosted its championship weekend, we were on hand to capture the excitement 🥍 https://t.co/nZFstKI1J1</t>
+        </is>
+      </c>
+      <c r="G887" t="inlineStr"/>
+      <c r="H887" t="inlineStr"/>
+      <c r="I887" t="inlineStr"/>
+      <c r="J887" t="inlineStr"/>
+      <c r="K887" t="inlineStr">
+        <is>
+          <t>https://x.com/Navan/status/2115814604790276185</t>
+        </is>
+      </c>
+      <c r="L887" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M887" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N887" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O887" t="inlineStr">
+        <is>
+          <t>Navan highlighted its partnership with Premier Lacrosse by covering the championship weekend, emphasizing brand collaboration and event support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D888" t="inlineStr">
+        <is>
+          <t>navan</t>
+        </is>
+      </c>
+      <c r="E888" t="inlineStr">
+        <is>
+          <t>Wed Oct 28 21:40:09 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F888" t="inlineStr">
+        <is>
+          <t>Remember: a journey of a thousand miles begins with a single accommodating travel policy.</t>
+        </is>
+      </c>
+      <c r="G888" t="inlineStr"/>
+      <c r="H888" t="inlineStr"/>
+      <c r="I888" t="inlineStr"/>
+      <c r="J888" t="inlineStr"/>
+      <c r="K888" t="inlineStr">
+        <is>
+          <t>https://x.com/Navan/status/2115559270100209888</t>
+        </is>
+      </c>
+      <c r="L888" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M888" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N888" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O888" t="inlineStr">
+        <is>
+          <t>Navan highlights the importance of a flexible travel policy as a foundational element for successful journeys.</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="C889" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D889" t="inlineStr">
+        <is>
+          <t>getnavan</t>
+        </is>
+      </c>
+      <c r="E889" t="inlineStr">
+        <is>
+          <t>2026-10-28T16:57:06.000Z</t>
+        </is>
+      </c>
+      <c r="F889" t="inlineStr">
+        <is>
+          <t>@GetNavan is expanding its local card program to Denmark this fall. Send this to your finance lead!
+#ad</t>
+        </is>
+      </c>
+      <c r="G889" t="inlineStr">
+        <is>
+          <t>https://scontent-dfw6-2.cdninstagram.com/v/t51.82787-15/869840116_18097817063414968_7767037286332055898_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=110&amp;ig_cache_key=NDAxODAyOTc0NDQ4NzQ1Mjk3OTE4MDk3ODE3MDU3NDE0OTY4.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNMSVBTLnhwaWRzLjcyMC5zZHIudmlkZW9fdXNlcl9zZWxlY3RlZF90aHVtYm5haWwuQzMifQ%3D%3D&amp;_nc_ohc=7wi0f8iBItUQ7kNvwEkICC8&amp;_nc_oc=Adq4JU_8axN1h8eQ-SBGTeh21Etl-O1dQoW5KUno9Ehvdkh8fAI8F0elAYTB6so1C3M&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-dfw6-2.cdninstagram.com&amp;_nc_gid=oXYx3i3BRtEB7Q_ntJS9Kg&amp;_nc_ss=7320f&amp;oh=00_AQRDKI45Aicjn8EuVSc5f4Hfl6m1pLn6kOW7kePTK4cjEQ&amp;oe=6AE94EA2</t>
+        </is>
+      </c>
+      <c r="H889" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I889" t="inlineStr">
+        <is>
+          <t>https://scontent-dfw5-1.cdninstagram.com/o1/v/t2/f2/m86/AQPqi78R9M5gC24LMf0iV6iwOxqyeB3GQS0-gy9y9OEPnmK2eruyaz_hQLUita5MPu2YxLZd_nQxiF2mv8ZRDvHSiCaGfeUnbPuidgc.mp4?_nc_cat=105&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-dfw5-1.cdninstagram.com&amp;_nc_ohc=051FZN2SamMQ7kNvwFehuyX&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MTg0MjA5MTAzNzExNDE4NSwiYXNzZXRfYWdlX2RheXMiOjAsInZpX3VzZWNhc2VfaWQiOjEwMDk5LCJkdXJhdGlvbl9zIjozOSwidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=c62062f3b256ca75&amp;_nc_vs=HBksFQIYUmlnX3hwdl9yZWVsc19wZXJtYW5lbnRfc3JfcHJvZC9FNUREOTdCQzJBRUQ0Q0U4QjdBQzAyMjI0REU3NEQyMF92aWRlb19kYXNoaW5pdC5tcDQVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzdDMTkwREQ4MUVGQzQ0QzU5Nzc3RkZCRTFBM0ZDRUQ1X2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACaS_cne59fFBhUCKAJDMywXQEOzMzMzMzMYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=oXYx3i3BRtEB7Q_ntJS9Kg&amp;_nc_zt=28&amp;_nc_ss=70980&amp;oh=00_AQQ2EoMxgJcNqHwIiWNY_QmLp0Yg6yICSGTvlYxnQz0Atw&amp;oe=6AE563CA</t>
+        </is>
+      </c>
+      <c r="J889" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K889" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DfC6MOhINEz/</t>
+        </is>
+      </c>
+      <c r="L889" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M889" t="inlineStr">
+        <is>
+          <t>Strategic Expansion or Changes</t>
+        </is>
+      </c>
+      <c r="N889" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O889" t="inlineStr">
+        <is>
+          <t>Navan is expanding its local card program to Denmark this fall, indicating a strategic move into a new market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D890" t="inlineStr">
+        <is>
+          <t>getnavan</t>
+        </is>
+      </c>
+      <c r="E890" t="inlineStr">
+        <is>
+          <t>2026-10-29T14:30:30.000Z</t>
+        </is>
+      </c>
+      <c r="F890" t="inlineStr">
+        <is>
+          <t>LAX is more than an airport code, it’s a way of life. When Navan customer @pll hosted its championship weekend, we were on hand to capture the excitement 🥍</t>
+        </is>
+      </c>
+      <c r="G890" t="inlineStr">
+        <is>
+          <t>https://scontent-ssn1-1.cdninstagram.com/v/t51.82787-15/876310573_18496724629110668_9173647708092747548_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=106&amp;ig_cache_key=NDAxODY3NzE2ODU0Nzk3Mzk0ODE4NDk2NzI0NjI2MTEwNjY4.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNMSVBTLnhwaWRzLjcyMC5zZHIudmlkZW9fdXNlcl9zZWxlY3RlZF90aHVtYm5haWwuQzMifQ%3D%3D&amp;_nc_ohc=GfLdAvoORncQ7kNvwHKWJsJ&amp;_nc_oc=AdqTEiNVjFug5VDrDIQC8ypKCcwNqIXnpLOXz7ll_CnX-Fb8e7iSeMuX5adgGXVw59M&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-ssn1-1.cdninstagram.com&amp;_nc_gid=uW3CzsB7_hDRU7RI8khUXA&amp;_nc_ss=7320f&amp;oh=00_AQQhDPAIrqs3SCAf9baeZjHC-b6nM1vdewDS36vSXaHlBA&amp;oe=6AE938EF</t>
+        </is>
+      </c>
+      <c r="H890" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I890" t="inlineStr">
+        <is>
+          <t>https://scontent-ssn1-1.cdninstagram.com/o1/v/t2/f2/m86/AQNqq0ipZinz9L6U1Yu_jrfnh4d5zQR9yuer5NCzSK6JvpLWjgd7I1fJoDfiV5adZ3of9fhZygTSxrn3cre_rltXSKD1FlSkgIMM51I.mp4?_nc_cat=102&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-ssn1-1.cdninstagram.com&amp;_nc_ohc=yVYAfDbD4KcQ7kNvwHqWcKh&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MjUyMzU0NDg5MTQ2MjkwOSwiYXNzZXRfYWdlX2RheXMiOjAsInZpX3VzZWNhc2VfaWQiOjEwMDk5LCJkdXJhdGlvbl9zIjozNiwidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=687ea5708cf1047a&amp;_nc_vs=HBksFQIYUmlnX3hwdl9yZWVsc19wZXJtYW5lbnRfc3JfcHJvZC85Q0U0QkFDREU4MzI0NzRBOTgyM0Y5NDBGQkRGNjczNF92aWRlb19kYXNoaW5pdC5tcDQVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyL0YwN0IwNjgyQzgwQjQ5Q0U5MkQxMkYwNzg2MDE5RTdCX2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACb606TN0sn7CBUCKAJDMywXQEIeuFHrhR8YEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=uW3CzsB7_hDRU7RI8khUXA&amp;_nc_zt=28&amp;_nc_ss=70580&amp;oh=00_AQRvIWXdMEryctL1kHPQxP9guoEgHJkkCkmP7Ot0MUVbcw&amp;oe=6AE553B3</t>
+        </is>
+      </c>
+      <c r="J890" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K890" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DfFNZfKRks8/</t>
+        </is>
+      </c>
+      <c r="L890" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M890" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N890" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O890" t="inlineStr">
+        <is>
+          <t>Navan showcased its partnership by supporting a customer’s championship weekend, capturing the excitement and reinforcing its brand presence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>TravelPerk</t>
+        </is>
+      </c>
+      <c r="C891" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D891" t="inlineStr">
+        <is>
+          <t>Perk</t>
+        </is>
+      </c>
+      <c r="E891" t="inlineStr">
+        <is>
+          <t>2026-10-29T10:33:08.644Z</t>
+        </is>
+      </c>
+      <c r="F891" t="inlineStr">
+        <is>
+          <t>Clunky travel &amp; spend? Not in F1™.  
+Perk powers real work on and off the track for the Audi Revolut F1 Team and their Chief Brand and Commercial Officer, Stefano Battiston, takes on our quick-fire round with Jada Balster.</t>
+        </is>
+      </c>
+      <c r="G891" t="inlineStr"/>
+      <c r="H891" t="inlineStr"/>
+      <c r="I891" t="inlineStr">
+        <is>
+          <t>https://dms.licdn.com/playlist/vid/dynamic/D4E10AQGmn93GX96HIw/CeJxzMnFNdPfwd3QO9HB1NtDVcQLzA9IKnD3THV1hfKh8PhofXb4YoT8_3r3c0RFN3lEXALBeHrA?e=1793898000&amp;v=beta&amp;t=JwpWtZ4Rs2lsTD5_wK18BqqTVMq3oCKBb1PvrMC0k2c</t>
+        </is>
+      </c>
+      <c r="J891" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K891" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/perk_clunky-travel-spend-not-in-f1-perk-activity-7521519486450126849-l8WH</t>
+        </is>
+      </c>
+      <c r="L891" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M891" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N891" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O891" t="inlineStr">
+        <is>
+          <t>TravelPerk showcases its travel and spend solution in partnership with the Audi Revolut F1 Team, highlighting real work on and off the track.</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D892" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E892" t="inlineStr">
+        <is>
+          <t>Thu Oct 29 16:06:28 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F892" t="inlineStr">
+        <is>
+          <t>A year ago → today, on Ramp:
+50K → 85K businesses on Ramp
+5% → 7.5% average savings per business
+820K → 1.5M hours saved every month
+More businesses served. More time saved. More money saved. https://t.co/4B2XW9t8TM</t>
+        </is>
+      </c>
+      <c r="G892" t="inlineStr"/>
+      <c r="H892" t="inlineStr"/>
+      <c r="I892" t="inlineStr"/>
+      <c r="J892" t="inlineStr"/>
+      <c r="K892" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2115837683368964551</t>
+        </is>
+      </c>
+      <c r="L892" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M892" t="inlineStr">
+        <is>
+          <t>Strategic Expansion or Changes</t>
+        </is>
+      </c>
+      <c r="N892" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O892" t="inlineStr">
+        <is>
+          <t>Ramp highlights a year‑over‑year growth, adding 35K new businesses, boosting average savings from 5% to 7.5%, and saving 1.5M hours per month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D893" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E893" t="inlineStr">
+        <is>
+          <t>Thu Oct 29 03:15:44 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F893" t="inlineStr">
+        <is>
+          <t>@adambaitch https://t.co/AD0oattH1C</t>
+        </is>
+      </c>
+      <c r="G893" t="inlineStr"/>
+      <c r="H893" t="inlineStr"/>
+      <c r="I893" t="inlineStr"/>
+      <c r="J893" t="inlineStr"/>
+      <c r="K893" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2115643721765241338</t>
+        </is>
+      </c>
+      <c r="L893" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M893" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N893" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O893" t="inlineStr">
+        <is>
+          <t>Ramp shared a link to a resource or article, likely related to a partnership or product update, but no further context is provided.</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E894" t="inlineStr">
+        <is>
+          <t>Wed Oct 28 20:57:27 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F894" t="inlineStr">
+        <is>
+          <t>@GarrettHarper_ @altitude https://t.co/SPQYkxbIaO</t>
+        </is>
+      </c>
+      <c r="G894" t="inlineStr"/>
+      <c r="H894" t="inlineStr"/>
+      <c r="I894" t="inlineStr"/>
+      <c r="J894" t="inlineStr"/>
+      <c r="K894" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2115548523504750839</t>
+        </is>
+      </c>
+      <c r="L894" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M894" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N894" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O894" t="inlineStr">
+        <is>
+          <t>Ramp highlights a collaboration with Altitude, tagging Garrett Harper and sharing a link to the announcement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E895" t="inlineStr">
+        <is>
+          <t>Wed Oct 28 19:33:05 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F895" t="inlineStr">
+        <is>
+          <t>Apply: https://t.co/m8O4mDd0rH</t>
+        </is>
+      </c>
+      <c r="G895" t="inlineStr"/>
+      <c r="H895" t="inlineStr"/>
+      <c r="I895" t="inlineStr"/>
+      <c r="J895" t="inlineStr"/>
+      <c r="K895" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2115527292931961083</t>
+        </is>
+      </c>
+      <c r="L895" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M895" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N895" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O895" t="inlineStr">
+        <is>
+          <t>Ramp shared a link encouraging applications, likely for a new role or opportunity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C896" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D896" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E896" t="inlineStr">
+        <is>
+          <t>Wed Oct 28 19:33:05 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F896" t="inlineStr">
+        <is>
+          <t>Inspect is the coding agent behind 3 out of 4 of the pull requests we merge at Ramp. We can’t wait to see what you build with it.
+Application for early access is in the comments. https://t.co/Ep0t3TzRWc</t>
+        </is>
+      </c>
+      <c r="G896" t="inlineStr"/>
+      <c r="H896" t="inlineStr"/>
+      <c r="I896" t="inlineStr"/>
+      <c r="J896" t="inlineStr"/>
+      <c r="K896" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2115527291392729362</t>
+        </is>
+      </c>
+      <c r="L896" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M896" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N896" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O896" t="inlineStr">
+        <is>
+          <t>Ramp highlights that its coding agent Inspect powers 75% of their pull requests and invites early access via the comments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C897" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D897" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E897" t="inlineStr">
+        <is>
+          <t>Thu Oct 29 16:02:59 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F897" t="inlineStr">
+        <is>
+          <t>@kailajlim The sweetest kind of founder event. 🍬</t>
+        </is>
+      </c>
+      <c r="G897" t="inlineStr"/>
+      <c r="H897" t="inlineStr"/>
+      <c r="I897" t="inlineStr"/>
+      <c r="J897" t="inlineStr"/>
+      <c r="K897" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2115836806335725728</t>
+        </is>
+      </c>
+      <c r="L897" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M897" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N897" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O897" t="inlineStr">
+        <is>
+          <t>Brex shares a positive remark about a founder event, celebrating it as a sweet occasion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C898" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E898" t="inlineStr">
+        <is>
+          <t>Thu Oct 29 00:00:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F898" t="inlineStr">
+        <is>
+          <t>Your next unforgettable alpine escape is waiting in Switzerland 🇨🇭
+➡️ The views: Ride the Glacier Express past towering, snow-capped peaks and crystal-clear lakes.
+➡️ The culture: Wander through charming alpine villages and indulge in world-class chocolate.
+➡️ The stays: Warm up by the fire in a cozy traditional ski chalet.
+🔗 Plan your travel:
+https://t.co/EbrCo5ddDo</t>
+        </is>
+      </c>
+      <c r="G898" t="inlineStr"/>
+      <c r="H898" t="inlineStr"/>
+      <c r="I898" t="inlineStr"/>
+      <c r="J898" t="inlineStr"/>
+      <c r="K898" t="inlineStr">
+        <is>
+          <t>https://x.com/Expedia/status/2115594463502299592</t>
+        </is>
+      </c>
+      <c r="L898" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M898" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N898" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O898" t="inlineStr">
+        <is>
+          <t>Expedia promotes a Swiss alpine travel experience featuring the Glacier Express, alpine villages, chocolate, and cozy ski chalets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C899" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>Expedia Group</t>
+        </is>
+      </c>
+      <c r="E899" t="inlineStr">
+        <is>
+          <t>2026-10-28T22:30:45.609Z</t>
+        </is>
+      </c>
+      <c r="F899" t="inlineStr">
+        <is>
+          <t>More ways to plan with confidence. More support when it matters. One trusted place for everything you need.
+Today, Expedia Group unveiled its Fall 2026 Product Release: more than 30 new and enhanced features across Expedia, Hotels.com and Vrbo. Powered by AI, they take the hard work out of planning, give you confidence in your choices, and protect your trip when plans change. 
+We’re showing what frictionless shopping can be: trusted tools and support for every step of your journey. 
+Explore what’s new here: https://lnkd.in/euAeMKZE</t>
+        </is>
+      </c>
+      <c r="G899" t="inlineStr"/>
+      <c r="H899" t="inlineStr"/>
+      <c r="I899" t="inlineStr">
+        <is>
+          <t>https://dms.licdn.com/playlist/vid/dynamic/D4E05AQGmQ0ajzl7sOQ/CeJxzMnFNdHcNrzBN9Ap0dNTVcQLxHcPTqyI9I10C0fihUD5IfZh3saMnmnw-Gj8SjZ-uCwAnJCEU?e=1793898000&amp;v=beta&amp;t=d0BME9EiAzRb5DvvWyS6ccY3zvKIA0y2joX62zQ799Y</t>
+        </is>
+      </c>
+      <c r="J899" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K899" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/activity-7521316360736522240-hHVg</t>
+        </is>
+      </c>
+      <c r="L899" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M899" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N899" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O899" t="inlineStr">
+        <is>
+          <t>Expedia Group unveiled its Fall 2026 product release, introducing over 30 new and enhanced features across Expedia, Hotels.com, and Vrbo, powered by AI to streamline planning and provide support throughout the travel journey.</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>Tracey Weber</t>
+        </is>
+      </c>
+      <c r="E900" t="inlineStr">
+        <is>
+          <t>2026-10-29T13:07:49.301Z</t>
+        </is>
+      </c>
+      <c r="F900" t="inlineStr">
+        <is>
+          <t>Travel is a series of decisions. The role of technology should be to make those decisions feel clearer, not more complicated. 
+That’s especially true for families, who are balancing dates, destinations, room setups, and everyone’s preferences.
+That principle is at the heart of Expedia’s Fall 2026 Product Release, which introduces new experiences designed to support travelers from inspiration through the trip itself, with families in mind. 
+A few highlights include:
+🏠 A homepage that feels more personal: Expedia’s refreshed homepage puts the most relevant inspiration, deals, next steps and trip details front and center, from the first idea to the trip itself.  
+ 📦 More flexible packages: Fly into one city and stay in another, or add a hotel or car only for the days you need 
+ 💬 Property Expert: Quick answers grounded in property details, guest reviews and reservation info 
+ 🛏️ Multi-room booking: Book different room types together in one reservation so everyone has the right space. 
+ 🗺️ Family-friendly maps: Spot kid-friendly places and activities near where you’re staying 
+ 🎟️ Activity Planner: Fill your trip with things to do. Book activities and events, discover great places to eat, and find more to explore. 
+I’m proud of the teams working to turn complex travel moments into simpler, more confident experiences. Because when technology handles more of the friction, families can focus on what matters most: making memories together and discovering somewhere new. ✈️ 
+http://ms.spr.ly/6041aLU9f</t>
+        </is>
+      </c>
+      <c r="G900" t="inlineStr"/>
+      <c r="H900" t="inlineStr"/>
+      <c r="I900" t="inlineStr">
+        <is>
+          <t>https://dms.licdn.com/playlist/vid/dynamic/D4E10AQEioHfd9Q7VUw/CeJxzMnFNdPcMDDDU8wp1dNTVcQLxXZ3zikw9DZxDUfkurlA-UL2Rs2ckhnoTNL4FGj9QFwCOMh37?e=1793898000&amp;v=beta&amp;t=IXf_agY-TAIpcRfMZaeaHWuB2TlHht6D1vysDs8v9yM</t>
+        </is>
+      </c>
+      <c r="J900" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K900" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/tracey-weber-ba95253_expedia-activity-planner-ugcPost-7521556447562977280-4rD4</t>
+        </is>
+      </c>
+      <c r="L900" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M900" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N900" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O900" t="inlineStr">
+        <is>
+          <t>Expedia announces its Fall 2026 product release, highlighting family‑centric features such as a personalized homepage, flexible packages, multi‑room booking, and activity planning tools to simplify travel decisions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C901" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E901" t="inlineStr">
+        <is>
+          <t>Thu Oct 29 13:05:09 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F901" t="inlineStr">
+        <is>
+          <t>Hola, lamentamos la experiencia de tu abuelo. Cuéntanos, ¿cómo podemos ayudarte? Si tu consulta está relacionada con una reserva de alojamiento, envíanos un mensaje privado con los siguientes datos y te responderemos lo antes posible: 
+- Número de confirmación: 
+- Código PIN: 
+- Nombre que aparece en la reserva: 
+- Detalles de tu solicitud: 
+Ten en cuenta que nuestro equipo de Redes Sociales no trabaja en tiempo real. Para recibir ayuda inmediata, llama a nuestro equipo de Atención al Cliente disponible 24/7; puedes encontrar nuestros datos de contacto aquí: https://t.co/o8QyR8SaDb 
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G901" t="inlineStr"/>
+      <c r="H901" t="inlineStr"/>
+      <c r="I901" t="inlineStr"/>
+      <c r="J901" t="inlineStr"/>
+      <c r="K901" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2115792054068380011</t>
+        </is>
+      </c>
+      <c r="L901" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M901" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N901" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O901" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for a negative experience and offers assistance via private message or phone call.</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D902" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E902" t="inlineStr">
+        <is>
+          <t>Thu Oct 29 13:01:06 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F902" t="inlineStr">
+        <is>
+          <t>The claim submitted has been thoroughly investigated in accordance with the evidence provided and the relevant property decision. Please note that https://t.co/fGhmZE7riF is unable to issue any refunds without the explicit approval of our partners, who are the ultimate service providers. Any compensation offered is a gesture of goodwill, intended to express our appreciation for selecting our platform; however, it should not be interpreted as a substitute for what was originally expected. In your specific situation, we have shared our final outcome via DM.</t>
+        </is>
+      </c>
+      <c r="G902" t="inlineStr"/>
+      <c r="H902" t="inlineStr"/>
+      <c r="I902" t="inlineStr"/>
+      <c r="J902" t="inlineStr"/>
+      <c r="K902" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2115791034449834102</t>
+        </is>
+      </c>
+      <c r="L902" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M902" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N902" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O902" t="inlineStr">
+        <is>
+          <t>Booking.com clarifies that refunds require partner approval and offers goodwill compensation instead of a full refund, informing the customer via direct message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C903" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D903" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E903" t="inlineStr">
+        <is>
+          <t>Thu Oct 29 13:00:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F903" t="inlineStr">
+        <is>
+          <t>@Danielithabg Te hemos respondido por DM, Daniela.</t>
+        </is>
+      </c>
+      <c r="G903" t="inlineStr"/>
+      <c r="H903" t="inlineStr"/>
+      <c r="I903" t="inlineStr"/>
+      <c r="J903" t="inlineStr"/>
+      <c r="K903" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2115790756946288693</t>
+        </is>
+      </c>
+      <c r="L903" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M903" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N903" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O903" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user via direct message, indicating customer service engagement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D904" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E904" t="inlineStr">
+        <is>
+          <t>Thu Oct 29 12:23:29 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F904" t="inlineStr">
+        <is>
+          <t>Bonjour Oliver,
+Nous souhaitons consulter ce remboursement pour vous. Veuillez nous envoyer un message privé contenant les informations suivantes :
+- Numéro de réservation
+- Code confidentiel
+- Nom complet du voyageur
+Une fois que nous aurons reçu ces informations, nous pourrons consulter votre dossier et revenir vers vous.
+Bien cordialement.</t>
+        </is>
+      </c>
+      <c r="G904" t="inlineStr"/>
+      <c r="H904" t="inlineStr"/>
+      <c r="I904" t="inlineStr"/>
+      <c r="J904" t="inlineStr"/>
+      <c r="K904" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2115781566727086583</t>
+        </is>
+      </c>
+      <c r="L904" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M904" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N904" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O904" t="inlineStr">
+        <is>
+          <t>Booking.com is requesting booking details from a user to process a refund.</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D905" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E905" t="inlineStr">
+        <is>
+          <t>Thu Oct 29 12:02:25 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F905" t="inlineStr">
+        <is>
+          <t>Hola, María. Gracias por ponerte en contacto con nosotros. Asegúrate de que esté actualizada a la última versión. También puedes probar a desinstalarla y descargarla de nuevo de forma gratuita desde la tienda de aplicaciones. 
+Si utilizas un navegador como Google Chrome, este almacena información de los sitios web en la caché y las cookies. Borrarlas suele ayudar a resolver problemas que puedas experimentar en nuestra web. 
+Si después de probar estos pasos sigues necesitando ayuda, responde con cualquier información adicional que pueda ayudarnos, como capturas de pantalla del mensaje de error. Así podremos investigar el problema con más detalle. 
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G905" t="inlineStr"/>
+      <c r="H905" t="inlineStr"/>
+      <c r="I905" t="inlineStr"/>
+      <c r="J905" t="inlineStr"/>
+      <c r="K905" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2115776265554653513</t>
+        </is>
+      </c>
+      <c r="L905" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M905" t="inlineStr">
+        <is>
+          <t>Tech Updates</t>
+        </is>
+      </c>
+      <c r="N905" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O905" t="inlineStr">
+        <is>
+          <t>Booking.com offers troubleshooting guidance for app and website issues, including updating the app, clearing cache, and providing error details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E906" t="inlineStr">
+        <is>
+          <t>Thu Oct 29 11:52:30 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F906" t="inlineStr">
+        <is>
+          <t>Hi there, we regret hearing this and would like to check your booking, please send us a private message with the following details, and we'll get back to you as soon as possible: 
+- Confirmation number
+- Pin code
+- Name on the reservation (meaning the name of the traveler)
+Please bear in mind that our Social Media Team doesn't work in real time. For immediate support, please call our 24/7 Customer Service Team - our contact details can be found here: https://t.co/o8QyR8SaDb
+Also, at this time, we only offer support for accommodation bookings via social media. For questions about Flights, Taxis, or Insurance, you can reach out to the dedicated support team here: https://t.co/UfRgpDJomK</t>
+        </is>
+      </c>
+      <c r="G906" t="inlineStr"/>
+      <c r="H906" t="inlineStr"/>
+      <c r="I906" t="inlineStr"/>
+      <c r="J906" t="inlineStr"/>
+      <c r="K906" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2115773770879152630</t>
+        </is>
+      </c>
+      <c r="L906" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M906" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N906" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O906" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint on X, requesting booking details via private message and directing users to 24/7 phone support, noting that only accommodation bookings are handled through social media.</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D907" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E907" t="inlineStr">
+        <is>
+          <t>Thu Oct 29 10:45:41 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F907" t="inlineStr">
+        <is>
+          <t>Hola, sentimos la demora en responder. Ten en cuenta que nuestro equipo de Redes Sociales no opera en tiempo real. Para asistencia inmediata, puedes comunicarte con nuestro equipo de atención al cliente, disponible las 24 horas, aquí: https://t.co/tuuNbmGVaG 
+Si aún necesitas asistencia, comparte con nosotros por mensaje privado la siguiente información y te responderemos lo antes posible: 
+- Número de confirmación
+- Código PIN
+- Nombre del huésped en la reserva
+Saludos.</t>
+        </is>
+      </c>
+      <c r="G907" t="inlineStr"/>
+      <c r="H907" t="inlineStr"/>
+      <c r="I907" t="inlineStr"/>
+      <c r="J907" t="inlineStr"/>
+      <c r="K907" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2115756954966491439</t>
+        </is>
+      </c>
+      <c r="L907" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M907" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N907" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O907" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for delayed response on X and directs customers to a 24‑hour support link, offering to handle requests via private message with reservation details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E908" t="inlineStr">
+        <is>
+          <t>Thu Oct 29 10:33:30 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F908" t="inlineStr">
+        <is>
+          <t>@brooke_abrahams Hello Brooke, we have replied to your DM.</t>
+        </is>
+      </c>
+      <c r="G908" t="inlineStr"/>
+      <c r="H908" t="inlineStr"/>
+      <c r="I908" t="inlineStr"/>
+      <c r="J908" t="inlineStr"/>
+      <c r="K908" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2115753890008166804</t>
+        </is>
+      </c>
+      <c r="L908" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M908" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N908" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O908" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a private message from Brooke.</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D909" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E909" t="inlineStr">
+        <is>
+          <t>Thu Oct 29 09:08:29 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F909" t="inlineStr">
+        <is>
+          <t>@kathrynbuk Hi Kathryn, we regret to hear this has been your experience, and we would like to check it from our side. For us to look into your booking, please send us the following: 
+- Confirmation number: 
+- Pin code: 
+- Name on the reservation: 
+- Details on your request:</t>
+        </is>
+      </c>
+      <c r="G909" t="inlineStr"/>
+      <c r="H909" t="inlineStr"/>
+      <c r="I909" t="inlineStr"/>
+      <c r="J909" t="inlineStr"/>
+      <c r="K909" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2115732494494335414</t>
+        </is>
+      </c>
+      <c r="L909" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M909" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N909" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O909" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint, requesting booking details to investigate the issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D910" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E910" t="inlineStr">
+        <is>
+          <t>Thu Oct 29 08:57:13 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F910" t="inlineStr">
+        <is>
+          <t>@Laurent_hilaire Bonjour Laurent, nous regrettons de lire votre déception concernant l’établissement. Nous venons de vous répondre par message privé.</t>
+        </is>
+      </c>
+      <c r="G910" t="inlineStr"/>
+      <c r="H910" t="inlineStr"/>
+      <c r="I910" t="inlineStr"/>
+      <c r="J910" t="inlineStr"/>
+      <c r="K910" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2115729659744624665</t>
+        </is>
+      </c>
+      <c r="L910" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M910" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N910" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O910" t="inlineStr">
+        <is>
+          <t>Booking.com replies to a customer’s complaint about a property, expressing regret and indicating that a private message has been sent to address the issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D911" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E911" t="inlineStr">
+        <is>
+          <t>Thu Oct 29 08:51:20 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F911" t="inlineStr">
+        <is>
+          <t>Hi there, we regret any misunderstanding caused by the email. If you require assistance with your accommodation booking, we would be glad to look into what happened. To proceed, please send us a direct message with the following information: 
+- Confirmation number, 
+- Pin code, 
+- Guest name, 
+- Request. 
+We will respond to you as quickly as we can. Thank you.</t>
+        </is>
+      </c>
+      <c r="G911" t="inlineStr"/>
+      <c r="H911" t="inlineStr"/>
+      <c r="I911" t="inlineStr"/>
+      <c r="J911" t="inlineStr"/>
+      <c r="K911" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2115728179511926907</t>
+        </is>
+      </c>
+      <c r="L911" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M911" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N911" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O911" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for a misunderstanding and invites customers to DM with booking details for assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D912" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E912" t="inlineStr">
+        <is>
+          <t>Thu Oct 29 08:44:37 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F912" t="inlineStr">
+        <is>
+          <t>@felparro También puedes llamar al +34 918 362 949 desde España, de lunes a domingo, de 9:00 a 21:00 (hora local).</t>
+        </is>
+      </c>
+      <c r="G912" t="inlineStr"/>
+      <c r="H912" t="inlineStr"/>
+      <c r="I912" t="inlineStr"/>
+      <c r="J912" t="inlineStr"/>
+      <c r="K912" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2115726488532090961</t>
+        </is>
+      </c>
+      <c r="L912" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M912" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N912" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O912" t="inlineStr">
+        <is>
+          <t>Booking.com posts customer support contact information for Spanish users, indicating a routine update of service details.</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D913" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E913" t="inlineStr">
+        <is>
+          <t>Thu Oct 29 08:44:14 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F913" t="inlineStr">
+        <is>
+          <t>@felparro No podemos ayudarte con reservas de vuelos a través de las redes sociales, pero puedes ponerte en contacto con nuestro equipo de Vuelos a través de este enlace: https://t.co/BfbildlU73</t>
+        </is>
+      </c>
+      <c r="G913" t="inlineStr"/>
+      <c r="H913" t="inlineStr"/>
+      <c r="I913" t="inlineStr"/>
+      <c r="J913" t="inlineStr"/>
+      <c r="K913" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2115726391530447179</t>
+        </is>
+      </c>
+      <c r="L913" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M913" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N913" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O913" t="inlineStr">
+        <is>
+          <t>Booking.com informs a user that flight bookings cannot be handled via social media and directs them to a contact link.</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D914" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E914" t="inlineStr">
+        <is>
+          <t>Thu Oct 29 08:44:03 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F914" t="inlineStr">
+        <is>
+          <t>@felparro Hola Felipe, gracias por contactarnos. Lamentamos saber que todavía estás esperando tu reembolso.</t>
+        </is>
+      </c>
+      <c r="G914" t="inlineStr"/>
+      <c r="H914" t="inlineStr"/>
+      <c r="I914" t="inlineStr"/>
+      <c r="J914" t="inlineStr"/>
+      <c r="K914" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2115726342956122478</t>
+        </is>
+      </c>
+      <c r="L914" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M914" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N914" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O914" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user about a pending refund, apologizing for the delay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E915" t="inlineStr">
+        <is>
+          <t>Thu Oct 29 07:57:14 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F915" t="inlineStr">
+        <is>
+          <t>@PradipAhir18649 We don't have your information, Pradip, because the social media team works separately from the flight department. We understand your emergency and feel for you, but we can't help since we don't have access to the system. Please reach out to the flight team again for support. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G915" t="inlineStr"/>
+      <c r="H915" t="inlineStr"/>
+      <c r="I915" t="inlineStr"/>
+      <c r="J915" t="inlineStr"/>
+      <c r="K915" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2115714562016113061</t>
+        </is>
+      </c>
+      <c r="L915" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M915" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N915" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O915" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s emergency request, explaining that their social media team does not have access to flight department information and advised the user to contact the flight team for assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E916" t="inlineStr">
+        <is>
+          <t>Thu Oct 29 07:47:51 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F916" t="inlineStr">
+        <is>
+          <t>@VasuTamakuwala Hi Vasu, we replied via private message as we're not able to discuss private cased matters publicly. Thanks.</t>
+        </is>
+      </c>
+      <c r="G916" t="inlineStr"/>
+      <c r="H916" t="inlineStr"/>
+      <c r="I916" t="inlineStr"/>
+      <c r="J916" t="inlineStr"/>
+      <c r="K916" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2115712203307278754</t>
+        </is>
+      </c>
+      <c r="L916" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M916" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N916" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O916" t="inlineStr">
+        <is>
+          <t>Booking.com replied privately to a user, stating they cannot discuss private matters publicly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D917" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E917" t="inlineStr">
+        <is>
+          <t>Thu Oct 29 07:43:37 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F917" t="inlineStr">
+        <is>
+          <t>@PradipAhir18649 Unfortunately, we’re unable to assist with flight reservations through social media. We kindly ask you to contact our specialized Flights team using the details previously shared, as they are best placed to review your case and advise you further.</t>
+        </is>
+      </c>
+      <c r="G917" t="inlineStr"/>
+      <c r="H917" t="inlineStr"/>
+      <c r="I917" t="inlineStr"/>
+      <c r="J917" t="inlineStr"/>
+      <c r="K917" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2115711136163110942</t>
+        </is>
+      </c>
+      <c r="L917" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M917" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N917" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O917" t="inlineStr">
+        <is>
+          <t>Booking.com informs a user that flight reservations cannot be handled via social media and directs them to contact the specialized Flights team for assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D918" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E918" t="inlineStr">
+        <is>
+          <t>Thu Oct 29 07:43:26 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F918" t="inlineStr">
+        <is>
+          <t>@PradipAhir18649 Hi Pradip, we sincerely regret the distress and frustration you're experiencing during this difficult time. We understand the urgency of your situation.</t>
+        </is>
+      </c>
+      <c r="G918" t="inlineStr"/>
+      <c r="H918" t="inlineStr"/>
+      <c r="I918" t="inlineStr"/>
+      <c r="J918" t="inlineStr"/>
+      <c r="K918" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2115711091762172345</t>
+        </is>
+      </c>
+      <c r="L918" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M918" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N918" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O918" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint, expressing regret and acknowledging the urgency of the situation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D919" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E919" t="inlineStr">
+        <is>
+          <t>Thu Oct 29 07:32:28 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F919" t="inlineStr">
+        <is>
+          <t>@PenGriffey304 We understand you are looking for an update on your refund. However, without the requested details sent via direct message, we are unable to take the next steps to assist you.
+If you still require support, please send those details over and we will be happy to help. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G919" t="inlineStr"/>
+      <c r="H919" t="inlineStr"/>
+      <c r="I919" t="inlineStr"/>
+      <c r="J919" t="inlineStr"/>
+      <c r="K919" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2115708331415191685</t>
+        </is>
+      </c>
+      <c r="L919" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M919" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N919" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O919" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user’s refund inquiry, requesting additional details via direct message before proceeding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D920" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E920" t="inlineStr">
+        <is>
+          <t>Thu Oct 29 07:22:06 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F920" t="inlineStr">
+        <is>
+          <t>Olá Clara, sentimos muito em saber da mudança de última hora, mas tenha em mente que a disponibilidade dos quartos é administrada pela acomodação e não pela https://t.co/fGhmZE7riF. Apesar de não podermos garantir uma mudança no resultado, (se o SAC já tiver fornecido um) certamente podemos examinar a sua reserva e verificar se há algo que possamos fazer para ajudá-la.
+Para isso, solicitamos que nos envie uma mensagem privada com:
+- Número de confirmação:
+- Código PIN:
+- Nome do hóspede na reserva:
+E daremos um retorno assim que possível.</t>
+        </is>
+      </c>
+      <c r="G920" t="inlineStr"/>
+      <c r="H920" t="inlineStr"/>
+      <c r="I920" t="inlineStr"/>
+      <c r="J920" t="inlineStr"/>
+      <c r="K920" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2115705722084209114</t>
+        </is>
+      </c>
+      <c r="L920" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M920" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N920" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O920" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint about a last‑minute change, offering to review the reservation and provide assistance.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O920"/>
+  <dimension ref="A1:O927"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59380,6 +59380,460 @@
         </is>
       </c>
     </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D921" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="E921" t="inlineStr">
+        <is>
+          <t>2026-10-29T14:36:38.805Z</t>
+        </is>
+      </c>
+      <c r="F921" t="inlineStr">
+        <is>
+          <t>LAX is more than an airport code, it’s a way of life. When Navan customer Premier Lacrosse League hosted its championship weekend, we were on hand to capture the excitement 🥍</t>
+        </is>
+      </c>
+      <c r="G921" t="inlineStr"/>
+      <c r="H921" t="inlineStr"/>
+      <c r="I921" t="inlineStr">
+        <is>
+          <t>https://dms.licdn.com/playlist/vid/dynamic/D4E05AQHvlSc7lGx9tQ/CeJxzMnFNdPd0q_LM8HJ1idTVcQLzPQLdAjwjHR1hfKh8KBo_GY2fjaTf18MEQ3-xLgDvUB-4?e=1793905200&amp;v=beta&amp;t=J2zh27SzEDIN-IMO91xxvEW6KLtGrQvOS25Lt8r8KnU</t>
+        </is>
+      </c>
+      <c r="J921" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K921" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/navan_lax-is-more-than-an-airport-code-its-a-activity-7521580765906833409-aGEn</t>
+        </is>
+      </c>
+      <c r="L921" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M921" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N921" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O921" t="inlineStr">
+        <is>
+          <t>Navan showcased its support for the Premier Lacrosse League by attending and capturing the excitement during the league’s championship weekend at LAX.</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D922" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E922" t="inlineStr">
+        <is>
+          <t>Thu Oct 29 17:27:05 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F922" t="inlineStr">
+        <is>
+          <t>@sytaylor @eglyman Great interview</t>
+        </is>
+      </c>
+      <c r="G922" t="inlineStr"/>
+      <c r="H922" t="inlineStr"/>
+      <c r="I922" t="inlineStr"/>
+      <c r="J922" t="inlineStr"/>
+      <c r="K922" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2115857969783202066</t>
+        </is>
+      </c>
+      <c r="L922" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M922" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N922" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O922" t="inlineStr">
+        <is>
+          <t>Ramp publicly praised a great interview featuring @sytaylor and @eglyman.</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C923" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D923" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E923" t="inlineStr">
+        <is>
+          <t>Thu Oct 29 17:26:47 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F923" t="inlineStr">
+        <is>
+          <t>@josephpalbanese Agents doing the heavy lifting</t>
+        </is>
+      </c>
+      <c r="G923" t="inlineStr"/>
+      <c r="H923" t="inlineStr"/>
+      <c r="I923" t="inlineStr"/>
+      <c r="J923" t="inlineStr"/>
+      <c r="K923" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2115857895036436635</t>
+        </is>
+      </c>
+      <c r="L923" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M923" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N923" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O923" t="inlineStr">
+        <is>
+          <t>Ramp showcases its agents as the primary drivers of workload, highlighting a new product feature that automates key tasks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C924" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D924" t="inlineStr">
+        <is>
+          <t>Expedia Group</t>
+        </is>
+      </c>
+      <c r="E924" t="inlineStr">
+        <is>
+          <t>2026-10-29T16:52:02.588Z</t>
+        </is>
+      </c>
+      <c r="F924" t="inlineStr">
+        <is>
+          <t>A closer look at what’s next in travel. 
+Watch highlights from Expedia Group’s Fall 2026 Product Launch and see more than 30 new and enhanced features across Expedia, Hotels.com and Vrbo.  
+Powered by AI, these new features are making it easier for travelers to search in their own words, choose with confidence, personalize their plans, and manage the entire journey in one trusted place. 
+ https://lnkd.in/euAeMKZE</t>
+        </is>
+      </c>
+      <c r="G924" t="inlineStr"/>
+      <c r="H924" t="inlineStr"/>
+      <c r="I924" t="inlineStr">
+        <is>
+          <t>https://dms.licdn.com/playlist/vid/dynamic/D4E05AQHLO9UbK5GzWQ/CeJxzMnFNdPfMjnIy8Ch3cdXVcULmJ8P4OSUuBp6Rjujynmh8XzR-KJL-cncDR0ddAPBFH70?e=1793905200&amp;v=beta&amp;t=OW-mMSIPM9JxUvJw_ZqteA5-3I2YTD32JPdNkwH69JA</t>
+        </is>
+      </c>
+      <c r="J924" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K924" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/expediagroup_a-closer-look-at-whats-next-in-travel-ugcPost-7521614340706451456-wbsY</t>
+        </is>
+      </c>
+      <c r="L924" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M924" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N924" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O924" t="inlineStr">
+        <is>
+          <t>Expedia unveils over 30 AI‑powered features across Expedia, Hotels.com, and Vrbo at its Fall 2026 product launch, emphasizing easier search, confident choice, personalization, and end‑to‑end journey management.</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C925" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D925" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E925" t="inlineStr">
+        <is>
+          <t>Thu Oct 29 17:34:58 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F925" t="inlineStr">
+        <is>
+          <t>Hi Aleksandr, we acknowledge your concerns regarding the hygiene issues you experienced at the accommodation, including the conditions you described and your dissatisfaction with the outcome of your refund request. We recognize how concerning it is to feel that your concerns have not been resolved as expected. 
+Please refer to our previous direct message, in which we provided detailed information regarding your concern and the outcome of our review. 
+If you have any further questions or would like to provide additional information for review, please let us know and send us a private message, and we'll assist you further.</t>
+        </is>
+      </c>
+      <c r="G925" t="inlineStr"/>
+      <c r="H925" t="inlineStr"/>
+      <c r="I925" t="inlineStr"/>
+      <c r="J925" t="inlineStr"/>
+      <c r="K925" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2115859955357978857</t>
+        </is>
+      </c>
+      <c r="L925" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M925" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N925" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O925" t="inlineStr">
+        <is>
+          <t>Booking.com addresses a customer’s hygiene complaint, acknowledging concerns and offering further assistance via private message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D926" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E926" t="inlineStr">
+        <is>
+          <t>Thu Oct 29 17:23:10 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F926" t="inlineStr">
+        <is>
+          <t>@Malcolmskfitt Hi there, we understand your frustration as you keep being hung up. We have responded to your message privately. Please check it at your earliest convenience.</t>
+        </is>
+      </c>
+      <c r="G926" t="inlineStr"/>
+      <c r="H926" t="inlineStr"/>
+      <c r="I926" t="inlineStr"/>
+      <c r="J926" t="inlineStr"/>
+      <c r="K926" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2115856982712143924</t>
+        </is>
+      </c>
+      <c r="L926" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M926" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N926" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O926" t="inlineStr">
+        <is>
+          <t>Booking.com addresses a user’s frustration about being hung up, offering a private response to resolve the issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D927" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E927" t="inlineStr">
+        <is>
+          <t>Thu Oct 29 17:02:59 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F927" t="inlineStr">
+        <is>
+          <t>Hi there, we regret to hear that you were reassigned from a ground-floor apartment to a first-floor apartment without prior notice.
+We always suggest communicating any issues directly to the property while you are there, as they are in the best position to address and resolve any concerns.
+We do not tolerate discrimination in any form. If we discover that accommodation listed on our site is involved in discriminatory behavior, we investigate and may remove it from our platform. For us to help you here, please send us a private message with the following information and let us know what resolution you're seeking:
+- Confirmation number:
+- Pin code:
+- Name on the reservation:
+We'll get back to you as soon as possible. Alternatively, for immediate support, you can always give us a call here: https://t.co/o8QyR8SaDb</t>
+        </is>
+      </c>
+      <c r="G927" t="inlineStr"/>
+      <c r="H927" t="inlineStr"/>
+      <c r="I927" t="inlineStr"/>
+      <c r="J927" t="inlineStr"/>
+      <c r="K927" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2115851906966806992</t>
+        </is>
+      </c>
+      <c r="L927" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M927" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N927" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O927" t="inlineStr">
+        <is>
+          <t>Booking.com addresses a customer complaint about being reassigned to a different apartment, offering investigation and resolution while reaffirming its non‑discrimination policy.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O927"/>
+  <dimension ref="A1:O969"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59834,6 +59834,2633 @@
         </is>
       </c>
     </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D928" t="inlineStr">
+        <is>
+          <t>navan</t>
+        </is>
+      </c>
+      <c r="E928" t="inlineStr">
+        <is>
+          <t>Fri Oct 30 14:03:04 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F928" t="inlineStr">
+        <is>
+          <t>Hear how two companies escaped the T&amp;amp;E Frankenstack. Watch the webinar → https://t.co/EyiB19DcOA</t>
+        </is>
+      </c>
+      <c r="G928" t="inlineStr"/>
+      <c r="H928" t="inlineStr"/>
+      <c r="I928" t="inlineStr"/>
+      <c r="J928" t="inlineStr"/>
+      <c r="K928" t="inlineStr">
+        <is>
+          <t>https://x.com/Navan/status/2116169017060979058</t>
+        </is>
+      </c>
+      <c r="L928" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M928" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N928" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O928" t="inlineStr">
+        <is>
+          <t>Navan is promoting a webinar featuring two companies that discuss how they escaped the T&amp;E Frankenstack.</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>navan</t>
+        </is>
+      </c>
+      <c r="E929" t="inlineStr">
+        <is>
+          <t>Fri Oct 30 14:03:04 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F929" t="inlineStr">
+        <is>
+          <t>The spookiest thing your team could encounter this Halloween? A Frankenstack monster. https://t.co/AH6UYOxaLH</t>
+        </is>
+      </c>
+      <c r="G929" t="inlineStr"/>
+      <c r="H929" t="inlineStr"/>
+      <c r="I929" t="inlineStr"/>
+      <c r="J929" t="inlineStr"/>
+      <c r="K929" t="inlineStr">
+        <is>
+          <t>https://x.com/Navan/status/2116169014598594935</t>
+        </is>
+      </c>
+      <c r="L929" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M929" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N929" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O929" t="inlineStr">
+        <is>
+          <t>Navan promoted a new Halloween-themed feature called the "Frankenstack monster" to engage teams.</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>TravelPerk</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D930" t="inlineStr">
+        <is>
+          <t>Perk</t>
+        </is>
+      </c>
+      <c r="E930" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:53:12.400Z</t>
+        </is>
+      </c>
+      <c r="F930" t="inlineStr">
+        <is>
+          <t>Perk presents: a finance horror anthology. Four nightmares every team knows too well. Which one haunts you? 🎃</t>
+        </is>
+      </c>
+      <c r="G930" t="inlineStr"/>
+      <c r="H930" t="inlineStr"/>
+      <c r="I930" t="inlineStr"/>
+      <c r="J930" t="inlineStr"/>
+      <c r="K930" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/perk_which-one-haunts-you-activity-7521902022728732673-SKgs</t>
+        </is>
+      </c>
+      <c r="L930" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M930" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N930" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O930" t="inlineStr">
+        <is>
+          <t>TravelPerk is promoting a new finance horror anthology series that highlights common financial challenges teams face, encouraging audience engagement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D931" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E931" t="inlineStr">
+        <is>
+          <t>Fri Oct 30 08:45:07 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F931" t="inlineStr">
+        <is>
+          <t>@Emily_Sundberg 🧛‍♀️</t>
+        </is>
+      </c>
+      <c r="G931" t="inlineStr"/>
+      <c r="H931" t="inlineStr"/>
+      <c r="I931" t="inlineStr"/>
+      <c r="J931" t="inlineStr"/>
+      <c r="K931" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2116089001668976898</t>
+        </is>
+      </c>
+      <c r="L931" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M931" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N931" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O931" t="inlineStr">
+        <is>
+          <t>Ramp posted a brief mention of @Emily_Sundberg with a vampire emoji, likely a lighthearted or humorous tweet with no direct business implication.</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D932" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E932" t="inlineStr">
+        <is>
+          <t>Fri Oct 30 02:20:53 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F932" t="inlineStr">
+        <is>
+          <t>@joegetsyouhired @elise_ai @profound @RogoAI Feels good to be a Rampling</t>
+        </is>
+      </c>
+      <c r="G932" t="inlineStr"/>
+      <c r="H932" t="inlineStr"/>
+      <c r="I932" t="inlineStr"/>
+      <c r="J932" t="inlineStr"/>
+      <c r="K932" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2115992305916346636</t>
+        </is>
+      </c>
+      <c r="L932" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M932" t="inlineStr">
+        <is>
+          <t>Partnership and Acquisitions</t>
+        </is>
+      </c>
+      <c r="N932" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O932" t="inlineStr">
+        <is>
+          <t>Ramp shares a celebratory tweet highlighting a new partnership or collaboration with @joegetsyouhired, @elise_ai, @profound, and @RogoAI, expressing positive sentiment about the collaboration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D933" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E933" t="inlineStr">
+        <is>
+          <t>Fri Oct 30 00:01:18 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F933" t="inlineStr">
+        <is>
+          <t>@Smokey_ Back to work</t>
+        </is>
+      </c>
+      <c r="G933" t="inlineStr"/>
+      <c r="H933" t="inlineStr"/>
+      <c r="I933" t="inlineStr"/>
+      <c r="J933" t="inlineStr"/>
+      <c r="K933" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2115957180075745283</t>
+        </is>
+      </c>
+      <c r="L933" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M933" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N933" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O933" t="inlineStr">
+        <is>
+          <t>Ramp’s tweet simply references user @Smokey_ returning to work, with no business or product-related content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D934" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E934" t="inlineStr">
+        <is>
+          <t>Thu Oct 29 21:09:26 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F934" t="inlineStr">
+        <is>
+          <t>@wallstengine well earned</t>
+        </is>
+      </c>
+      <c r="G934" t="inlineStr"/>
+      <c r="H934" t="inlineStr"/>
+      <c r="I934" t="inlineStr"/>
+      <c r="J934" t="inlineStr"/>
+      <c r="K934" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2115913928375214510</t>
+        </is>
+      </c>
+      <c r="L934" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M934" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N934" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O934" t="inlineStr">
+        <is>
+          <t>Ramp responds positively to @wallstengine, acknowledging their achievement with a brief commendation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D935" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E935" t="inlineStr">
+        <is>
+          <t>Thu Oct 29 20:47:47 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F935" t="inlineStr">
+        <is>
+          <t>@andywang Sorry, to hear that. Anything we can do to help?</t>
+        </is>
+      </c>
+      <c r="G935" t="inlineStr"/>
+      <c r="H935" t="inlineStr"/>
+      <c r="I935" t="inlineStr"/>
+      <c r="J935" t="inlineStr"/>
+      <c r="K935" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2115908476509778028</t>
+        </is>
+      </c>
+      <c r="L935" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M935" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N935" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O935" t="inlineStr">
+        <is>
+          <t>Ramp responds to a user’s concern with an offer to help, demonstrating customer support engagement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D936" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E936" t="inlineStr">
+        <is>
+          <t>Thu Oct 29 20:19:51 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F936" t="inlineStr">
+        <is>
+          <t>@leadinginds spooky fintwit season</t>
+        </is>
+      </c>
+      <c r="G936" t="inlineStr"/>
+      <c r="H936" t="inlineStr"/>
+      <c r="I936" t="inlineStr"/>
+      <c r="J936" t="inlineStr"/>
+      <c r="K936" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2115901449158984088</t>
+        </is>
+      </c>
+      <c r="L936" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M936" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N936" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O936" t="inlineStr">
+        <is>
+          <t>Ramp posted a playful tweet referencing "spooky fintwit season", likely a lighthearted engagement with the fintech community.</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D937" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E937" t="inlineStr">
+        <is>
+          <t>Thu Oct 29 19:05:44 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F937" t="inlineStr">
+        <is>
+          <t>@anshulshirude We’re here if you need us</t>
+        </is>
+      </c>
+      <c r="G937" t="inlineStr"/>
+      <c r="H937" t="inlineStr"/>
+      <c r="I937" t="inlineStr"/>
+      <c r="J937" t="inlineStr"/>
+      <c r="K937" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2115882798343245875</t>
+        </is>
+      </c>
+      <c r="L937" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M937" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N937" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O937" t="inlineStr">
+        <is>
+          <t>Ramp responds to user @anshulshirude with a supportive message offering assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D938" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E938" t="inlineStr">
+        <is>
+          <t>Thu Oct 29 19:03:24 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F938" t="inlineStr">
+        <is>
+          <t>Happy Halloween 🎃
+@leadinginds sorted your timeline into monsters.</t>
+        </is>
+      </c>
+      <c r="G938" t="inlineStr"/>
+      <c r="H938" t="inlineStr"/>
+      <c r="I938" t="inlineStr"/>
+      <c r="J938" t="inlineStr"/>
+      <c r="K938" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2115882209618141203</t>
+        </is>
+      </c>
+      <c r="L938" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M938" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N938" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O938" t="inlineStr">
+        <is>
+          <t>Ramp posted a playful Halloween greeting, tagging @leadinginds and wishing followers a happy Halloween.</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C939" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D939" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E939" t="inlineStr">
+        <is>
+          <t>Fri Oct 30 15:05:12 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F939" t="inlineStr">
+        <is>
+          <t>@micmakarov Hi Michael, thank you for flagging this, and we're sorry for the trouble this is causing. We've escalated this, and our team is working on a fix. In the meantime, could you send us a DM so we can stay connected and share any updates directly?</t>
+        </is>
+      </c>
+      <c r="G939" t="inlineStr"/>
+      <c r="H939" t="inlineStr"/>
+      <c r="I939" t="inlineStr"/>
+      <c r="J939" t="inlineStr"/>
+      <c r="K939" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2116184654055104707</t>
+        </is>
+      </c>
+      <c r="L939" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M939" t="inlineStr">
+        <is>
+          <t>Tech Updates</t>
+        </is>
+      </c>
+      <c r="N939" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O939" t="inlineStr">
+        <is>
+          <t>Brex responds to a user’s complaint, apologizes for the inconvenience, and requests a direct message to provide updates while the issue is being resolved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D940" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E940" t="inlineStr">
+        <is>
+          <t>Thu Oct 29 22:40:25 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F940" t="inlineStr">
+        <is>
+          <t>@raulguilleneng @pedroh96 Always a good day when builders come through.</t>
+        </is>
+      </c>
+      <c r="G940" t="inlineStr"/>
+      <c r="H940" t="inlineStr"/>
+      <c r="I940" t="inlineStr"/>
+      <c r="J940" t="inlineStr"/>
+      <c r="K940" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2115936823935471645</t>
+        </is>
+      </c>
+      <c r="L940" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M940" t="inlineStr">
+        <is>
+          <t>Strategic Expansion or Changes</t>
+        </is>
+      </c>
+      <c r="N940" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O940" t="inlineStr">
+        <is>
+          <t>Brex highlights the arrival of new builders, suggesting ongoing expansion and collaboration within the industry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D941" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E941" t="inlineStr">
+        <is>
+          <t>Thu Oct 29 21:04:29 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F941" t="inlineStr">
+        <is>
+          <t>Think you can surpass the drag? RSVP for our SF event: https://t.co/IN3hamwwwU</t>
+        </is>
+      </c>
+      <c r="G941" t="inlineStr"/>
+      <c r="H941" t="inlineStr"/>
+      <c r="I941" t="inlineStr"/>
+      <c r="J941" t="inlineStr"/>
+      <c r="K941" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2115912680045457769</t>
+        </is>
+      </c>
+      <c r="L941" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M941" t="inlineStr">
+        <is>
+          <t>Strategic Expansion or Changes</t>
+        </is>
+      </c>
+      <c r="N941" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O941" t="inlineStr">
+        <is>
+          <t>Brex is promoting an upcoming event in San Francisco, inviting attendees to learn more about its latest initiatives.</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D942" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E942" t="inlineStr">
+        <is>
+          <t>Thu Oct 29 21:03:22 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F942" t="inlineStr">
+        <is>
+          <t>FINAL BOSS: OPERATIONAL DRAG
+Threat level: ???
+Attack pattern: ???
+ERROR. ACCESS NOT AUTHORIZED. CONTACT YOUR DIRECT COMMANDER.</t>
+        </is>
+      </c>
+      <c r="G942" t="inlineStr"/>
+      <c r="H942" t="inlineStr"/>
+      <c r="I942" t="inlineStr"/>
+      <c r="J942" t="inlineStr"/>
+      <c r="K942" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2115912398678946145</t>
+        </is>
+      </c>
+      <c r="L942" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M942" t="inlineStr">
+        <is>
+          <t>Tech Updates</t>
+        </is>
+      </c>
+      <c r="N942" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O942" t="inlineStr">
+        <is>
+          <t>Brex shares a cryptic message hinting at operational drag and access errors, suggesting potential internal technical or operational challenges.</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D943" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E943" t="inlineStr">
+        <is>
+          <t>Thu Oct 29 21:03:21 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F943" t="inlineStr">
+        <is>
+          <t>BOSS: ANNUAL AUDIT
+Threat level: Critical
+Attack pattern: Target
+An all-seeing eye that tracks every move down to the decimal. Each time it fires, your safe zone shrinks.</t>
+        </is>
+      </c>
+      <c r="G943" t="inlineStr"/>
+      <c r="H943" t="inlineStr"/>
+      <c r="I943" t="inlineStr"/>
+      <c r="J943" t="inlineStr"/>
+      <c r="K943" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2115912396443378147</t>
+        </is>
+      </c>
+      <c r="L943" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M943" t="inlineStr">
+        <is>
+          <t>Tech Updates</t>
+        </is>
+      </c>
+      <c r="N943" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="O943" t="inlineStr">
+        <is>
+          <t>Brex announces a critical audit threat, describing a target attack pattern that tracks every move and reduces safe zones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D944" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E944" t="inlineStr">
+        <is>
+          <t>Thu Oct 29 21:03:21 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F944" t="inlineStr">
+        <is>
+          <t>ENEMY 02: ROGUE AI (MODEL COLLAPSE)
+Threat level: Medium
+Attack pattern: Arcs
+Erratic agents undergoing model collapse. They degrade, then detonate.</t>
+        </is>
+      </c>
+      <c r="G944" t="inlineStr"/>
+      <c r="H944" t="inlineStr"/>
+      <c r="I944" t="inlineStr"/>
+      <c r="J944" t="inlineStr"/>
+      <c r="K944" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2115912394408939867</t>
+        </is>
+      </c>
+      <c r="L944" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M944" t="inlineStr">
+        <is>
+          <t>Tech Updates</t>
+        </is>
+      </c>
+      <c r="N944" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O944" t="inlineStr">
+        <is>
+          <t>Brex issues a warning about a medium-level threat from rogue AI model collapse, describing erratic agents that degrade and then detonate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D945" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E945" t="inlineStr">
+        <is>
+          <t>Thu Oct 29 21:03:20 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F945" t="inlineStr">
+        <is>
+          <t>ENEMY 01: SHADOW EXPENSES
+Threat level: Low
+Attack pattern: Hidden
+Approaches from outside your visibility. Sneaks past official approval.</t>
+        </is>
+      </c>
+      <c r="G945" t="inlineStr"/>
+      <c r="H945" t="inlineStr"/>
+      <c r="I945" t="inlineStr"/>
+      <c r="J945" t="inlineStr"/>
+      <c r="K945" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2115912393150619860</t>
+        </is>
+      </c>
+      <c r="L945" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M945" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N945" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O945" t="inlineStr">
+        <is>
+          <t>Brex highlights the risk of hidden expenses that can bypass approval processes, framing it as a low-level threat to businesses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D946" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E946" t="inlineStr">
+        <is>
+          <t>Thu Oct 29 21:03:20 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F946" t="inlineStr">
+        <is>
+          <t>Fiscal Mania was built to defeat operational drag, the force keeping finance teams and founders from focusing on greater ambitions.
+Meet the enemies in the field🧵 https://t.co/pQw9HUhflH</t>
+        </is>
+      </c>
+      <c r="G946" t="inlineStr"/>
+      <c r="H946" t="inlineStr"/>
+      <c r="I946" t="inlineStr"/>
+      <c r="J946" t="inlineStr"/>
+      <c r="K946" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2115912391556751770</t>
+        </is>
+      </c>
+      <c r="L946" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M946" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N946" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O946" t="inlineStr">
+        <is>
+          <t>Brex announces Fiscal Mania, a solution aimed at eliminating operational drag for finance teams and founders, allowing them to focus on larger ambitions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D947" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E947" t="inlineStr">
+        <is>
+          <t>Thu Oct 29 20:15:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F947" t="inlineStr">
+        <is>
+          <t>NYC, mission cleared. 
+The terminal was live, the leaderboard filled up, and the operatives delivered. Thank you for playing. 
+SF, you’re up next. Report for duty on November 5th. 
+RSVP: https://t.co/IN3hamwwwU https://t.co/eaSQlBn7Ac</t>
+        </is>
+      </c>
+      <c r="G947" t="inlineStr"/>
+      <c r="H947" t="inlineStr"/>
+      <c r="I947" t="inlineStr"/>
+      <c r="J947" t="inlineStr"/>
+      <c r="K947" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2115900226909405491</t>
+        </is>
+      </c>
+      <c r="L947" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M947" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N947" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O947" t="inlineStr">
+        <is>
+          <t>Brex promotes a gamified event in NYC, highlighting a live terminal and leaderboard, and invites participants to the next session in San Francisco on November 5th.</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="E948" t="inlineStr">
+        <is>
+          <t>Fri Oct 30 00:00:00 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F948" t="inlineStr">
+        <is>
+          <t>Step back in time with an unforgettable getaway to Kraków 🇵🇱
+➡️ The history: Marvel at the magnificent Wawel Castle and the stunning Main Market Square.
+➡️ The culture: Wander through the historic Jewish Quarter for cozy cafés and vibrant street art.
+➡️ The stays: Rest up in a beautifully restored boutique hotel just steps from the old town.
+🔗 Plan your travel:
+https://t.co/ANkwb7AHKi</t>
+        </is>
+      </c>
+      <c r="G948" t="inlineStr"/>
+      <c r="H948" t="inlineStr"/>
+      <c r="I948" t="inlineStr"/>
+      <c r="J948" t="inlineStr"/>
+      <c r="K948" t="inlineStr">
+        <is>
+          <t>https://x.com/Expedia/status/2115956850537509360</t>
+        </is>
+      </c>
+      <c r="L948" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M948" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N948" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O948" t="inlineStr">
+        <is>
+          <t>Expedia is promoting a Kraków getaway, showcasing historic sites, cultural experiences, and boutique hotel stays to attract travelers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E949" t="inlineStr">
+        <is>
+          <t>Fri Oct 30 14:17:39 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F949" t="inlineStr">
+        <is>
+          <t>Hola, gracias por contactarnos con respecto a tu reserva de alquiler de autos. 
+Para poder ayudarte, envíanos un mensaje privado con los siguientes datos: 
+- Número de reserva 
+- Nombre de quien reservó 
+- Correo electrónico utilizado para la reserva 
+- Tu solicitud 
+Te responderemos lo antes posible. Gracias.</t>
+        </is>
+      </c>
+      <c r="G949" t="inlineStr"/>
+      <c r="H949" t="inlineStr"/>
+      <c r="I949" t="inlineStr"/>
+      <c r="J949" t="inlineStr"/>
+      <c r="K949" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2116172687588389150</t>
+        </is>
+      </c>
+      <c r="L949" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M949" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N949" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O949" t="inlineStr">
+        <is>
+          <t>Booking.com is offering standard customer service instructions for car rental reservation inquiries, requesting reservation details via private message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D950" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E950" t="inlineStr">
+        <is>
+          <t>Fri Oct 30 12:43:18 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F950" t="inlineStr">
+        <is>
+          <t>Hola, Isabel. Lamentamos la tardanza en nuestra respuesta y los inconvenientes causados por esta situación. Los datos que te han compartido a través de WhatsApp corresponden a una reserva activa que tienes en nuestra plataforma. Si así es, envíanos un mensaje privado con los siguientes datos y te responderemos lo antes posible: 
+- Número de confirmación: 
+- Código PIN: 
+- Nombre que aparece en la reserva: 
+- Detalles de tu solicitud: 
+Ten en cuenta que nuestro equipo de Redes Sociales no trabaja en tiempo real. Para recibir ayuda inmediata, llama a nuestro equipo de Atención al Cliente disponible 24/7; puedes encontrar nuestros datos de contacto aquí: https://t.co/o8QyR8SaDb 
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G950" t="inlineStr"/>
+      <c r="H950" t="inlineStr"/>
+      <c r="I950" t="inlineStr"/>
+      <c r="J950" t="inlineStr"/>
+      <c r="K950" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2116148939929903339</t>
+        </is>
+      </c>
+      <c r="L950" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M950" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N950" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O950" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for a delayed response to a user’s inquiry and outlines steps for the user to provide reservation details for assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D951" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E951" t="inlineStr">
+        <is>
+          <t>Fri Oct 30 12:15:22 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F951" t="inlineStr">
+        <is>
+          <t>@zaiduddin Hi Syed, thanks for reaching out to us. We've just sent you a private message. Please check it at your earliest convenience.</t>
+        </is>
+      </c>
+      <c r="G951" t="inlineStr"/>
+      <c r="H951" t="inlineStr"/>
+      <c r="I951" t="inlineStr"/>
+      <c r="J951" t="inlineStr"/>
+      <c r="K951" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2116141911870259389</t>
+        </is>
+      </c>
+      <c r="L951" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M951" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N951" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O951" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user via private message, thanking them for reaching out and directing them to check their private message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E952" t="inlineStr">
+        <is>
+          <t>Fri Oct 30 12:06:43 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F952" t="inlineStr">
+        <is>
+          <t>@Serenadeline - Numéro de confirmation
+- Code confidentiel
+- Nom indiqué sur la réservation
+- Quelques détails concernant votre réclamation
+Pour une assistance immédiate, vous pouvez également nous appeler ici : https://t.co/PForv7yL3A</t>
+        </is>
+      </c>
+      <c r="G952" t="inlineStr"/>
+      <c r="H952" t="inlineStr"/>
+      <c r="I952" t="inlineStr"/>
+      <c r="J952" t="inlineStr"/>
+      <c r="K952" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2116139736502882814</t>
+        </is>
+      </c>
+      <c r="L952" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M952" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N952" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O952" t="inlineStr">
+        <is>
+          <t>Booking.com is offering support instructions to a user for resolving a claim, providing confirmation details and a phone link for immediate assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E953" t="inlineStr">
+        <is>
+          <t>Fri Oct 30 12:06:18 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F953" t="inlineStr">
+        <is>
+          <t>@Serenadeline Nous souhaiterions étudier la situation plus en détail et vous assister. Pourriez-vous nous envoyer un message privé contenant les informations suivantes ?</t>
+        </is>
+      </c>
+      <c r="G953" t="inlineStr"/>
+      <c r="H953" t="inlineStr"/>
+      <c r="I953" t="inlineStr"/>
+      <c r="J953" t="inlineStr"/>
+      <c r="K953" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2116139632236597489</t>
+        </is>
+      </c>
+      <c r="L953" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M953" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N953" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O953" t="inlineStr">
+        <is>
+          <t>Booking.com is contacting a user to request additional information via private message in order to provide assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D954" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E954" t="inlineStr">
+        <is>
+          <t>Fri Oct 30 12:06:01 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F954" t="inlineStr">
+        <is>
+          <t>@Serenadeline Bonjour, toutes nos excuses pour le délai de notre réponse. Nous regrettons de lire votre déception concernant l’absence de réponse à votre réclamation.</t>
+        </is>
+      </c>
+      <c r="G954" t="inlineStr"/>
+      <c r="H954" t="inlineStr"/>
+      <c r="I954" t="inlineStr"/>
+      <c r="J954" t="inlineStr"/>
+      <c r="K954" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2116139560824435084</t>
+        </is>
+      </c>
+      <c r="L954" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M954" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N954" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O954" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes to a user for a delayed response and acknowledges the user's disappointment over the lack of reply to their complaint.</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D955" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E955" t="inlineStr">
+        <is>
+          <t>Fri Oct 30 11:39:21 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F955" t="inlineStr">
+        <is>
+          <t>@vinceisbullish We've replied to your DM, please review it, follow the advice and get in touch with the relevant team if the issue persists. Regards</t>
+        </is>
+      </c>
+      <c r="G955" t="inlineStr"/>
+      <c r="H955" t="inlineStr"/>
+      <c r="I955" t="inlineStr"/>
+      <c r="J955" t="inlineStr"/>
+      <c r="K955" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2116132849375924472</t>
+        </is>
+      </c>
+      <c r="L955" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M955" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N955" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O955" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s direct message, advising them to review the provided guidance and contact the relevant team if the issue continues.</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D956" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E956" t="inlineStr">
+        <is>
+          <t>Fri Oct 30 11:05:16 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F956" t="inlineStr">
+        <is>
+          <t>@TheBankGate Hi there, we've replied to your DM and look forward to your response. https://t.co/Z89AAoEgD7</t>
+        </is>
+      </c>
+      <c r="G956" t="inlineStr"/>
+      <c r="H956" t="inlineStr"/>
+      <c r="I956" t="inlineStr"/>
+      <c r="J956" t="inlineStr"/>
+      <c r="K956" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2116124272003252262</t>
+        </is>
+      </c>
+      <c r="L956" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M956" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N956" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O956" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a direct message from @TheBankGate, indicating ongoing communication.</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D957" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E957" t="inlineStr">
+        <is>
+          <t>Fri Oct 30 09:22:55 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F957" t="inlineStr">
+        <is>
+          <t>@FNP12345 Hi there, we're unable to assist with Flight reservations through social media, but you can contact our Flights team here: https://t.co/BfbildlU73, or call {US}+1 917 421 7240 / {UK}+44 2039019061 / {IE} +353 19075677</t>
+        </is>
+      </c>
+      <c r="G957" t="inlineStr"/>
+      <c r="H957" t="inlineStr"/>
+      <c r="I957" t="inlineStr"/>
+      <c r="J957" t="inlineStr"/>
+      <c r="K957" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2116098513914232976</t>
+        </is>
+      </c>
+      <c r="L957" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M957" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N957" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O957" t="inlineStr">
+        <is>
+          <t>Booking.com informs a user that flight reservations cannot be handled via social media and directs them to contact the Flights team through a link or phone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D958" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E958" t="inlineStr">
+        <is>
+          <t>Fri Oct 30 09:14:43 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F958" t="inlineStr">
+        <is>
+          <t>@truepetalmia Bonjour Mia, merci de nous avoir contactés. Nous venons de vous envoyer un message privé. Merci de le consulter dès que possible.</t>
+        </is>
+      </c>
+      <c r="G958" t="inlineStr"/>
+      <c r="H958" t="inlineStr"/>
+      <c r="I958" t="inlineStr"/>
+      <c r="J958" t="inlineStr"/>
+      <c r="K958" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2116096451755323495</t>
+        </is>
+      </c>
+      <c r="L958" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M958" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N958" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O958" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user on X, informing them that a private message has been sent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D959" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E959" t="inlineStr">
+        <is>
+          <t>Fri Oct 30 08:59:04 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F959" t="inlineStr">
+        <is>
+          <t>Hi there, we regret to hear about your disappointment with the service you received over the phone. It is important to note that losing access to your Extranet account may occur due to various factors, including security measures or technical issues. Please send us a direct message with further details, and we will provide you with the necessary information to reset your password and guide you through the steps to regain access to your Extranet account.</t>
+        </is>
+      </c>
+      <c r="G959" t="inlineStr"/>
+      <c r="H959" t="inlineStr"/>
+      <c r="I959" t="inlineStr"/>
+      <c r="J959" t="inlineStr"/>
+      <c r="K959" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2116092510846034177</t>
+        </is>
+      </c>
+      <c r="L959" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M959" t="inlineStr">
+        <is>
+          <t>Tech Updates</t>
+        </is>
+      </c>
+      <c r="N959" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O959" t="inlineStr">
+        <is>
+          <t>Booking.com addresses a customer’s complaint about losing access to their Extranet account, offering assistance and guidance to reset the password.</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D960" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E960" t="inlineStr">
+        <is>
+          <t>Fri Oct 30 08:43:23 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F960" t="inlineStr">
+        <is>
+          <t>Hola, Raúl. Lamentamos los inconvenientes causados por esta situación. ¿Sigues necesitando nuestra asistencia? Si tu consulta está relacionada con una reserva de alojamiento, envíanos un mensaje privado con los siguientes datos y te responderemos lo antes posible: 
+- Número de confirmación: 
+- Código PIN: 
+- Nombre que aparece en la reserva: 
+- Detalles de tu solicitud: 
+Para recibir ayuda inmediata, llama a nuestro equipo de Atención al Cliente disponible 24/7; puedes encontrar nuestros datos de contacto aquí: https://t.co/o8QyR8SaDb 
+Un saludo.</t>
+        </is>
+      </c>
+      <c r="G960" t="inlineStr"/>
+      <c r="H960" t="inlineStr"/>
+      <c r="I960" t="inlineStr"/>
+      <c r="J960" t="inlineStr"/>
+      <c r="K960" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2116088564584755577</t>
+        </is>
+      </c>
+      <c r="L960" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M960" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N960" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O960" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer in Spanish, offering assistance and requesting reservation details for support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D961" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E961" t="inlineStr">
+        <is>
+          <t>Fri Oct 30 08:29:28 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F961" t="inlineStr">
+        <is>
+          <t>@snehbhm8hm Hi there, we regret to hear that you are unable to delete your Extranet account. We've sent you a DM with more information regarding your case. Please review it to get in touch with the relevant team.</t>
+        </is>
+      </c>
+      <c r="G961" t="inlineStr"/>
+      <c r="H961" t="inlineStr"/>
+      <c r="I961" t="inlineStr"/>
+      <c r="J961" t="inlineStr"/>
+      <c r="K961" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2116085063875989556</t>
+        </is>
+      </c>
+      <c r="L961" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M961" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N961" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O961" t="inlineStr">
+        <is>
+          <t>Booking.com responded to a user’s complaint about not being able to delete their Extranet account, offering further assistance via DM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D962" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E962" t="inlineStr">
+        <is>
+          <t>Fri Oct 30 08:06:30 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F962" t="inlineStr">
+        <is>
+          <t>@sellam2308 Hi there. We have responded to your private message.</t>
+        </is>
+      </c>
+      <c r="G962" t="inlineStr"/>
+      <c r="H962" t="inlineStr"/>
+      <c r="I962" t="inlineStr"/>
+      <c r="J962" t="inlineStr"/>
+      <c r="K962" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2116079283797954792</t>
+        </is>
+      </c>
+      <c r="L962" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M962" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N962" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O962" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a private message from a user on X.</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D963" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E963" t="inlineStr">
+        <is>
+          <t>Fri Oct 30 07:32:37 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F963" t="inlineStr">
+        <is>
+          <t>Hi Danna, thanks for reaching out.
+If you need support with an accommodation booking, feel free to share with us via private message the following details: 
+- Confirmation number,
+- Pin code,
+- Name on the reservation,
+And we will get back to you as soon as possible. 
+Keep in mind that our Social Media Team does not work in real time, for immediate support you can call our 24/7 Customer Service Team here: https://t.co/tuuNbmGVaG</t>
+        </is>
+      </c>
+      <c r="G963" t="inlineStr"/>
+      <c r="H963" t="inlineStr"/>
+      <c r="I963" t="inlineStr"/>
+      <c r="J963" t="inlineStr"/>
+      <c r="K963" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2116070754869526601</t>
+        </is>
+      </c>
+      <c r="L963" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M963" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N963" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O963" t="inlineStr">
+        <is>
+          <t>Booking.com informs a user that their social media team does not provide real‑time support and directs them to the 24/7 customer service line for immediate assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D964" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E964" t="inlineStr">
+        <is>
+          <t>Fri Oct 30 07:32:06 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F964" t="inlineStr">
+        <is>
+          <t>@_canuos_ Gracias por enviarnos la información. Sentimos que hayas tenido dificultades para contactarnos. Respondimos tu mensaje privado.
+Un saludo</t>
+        </is>
+      </c>
+      <c r="G964" t="inlineStr"/>
+      <c r="H964" t="inlineStr"/>
+      <c r="I964" t="inlineStr"/>
+      <c r="J964" t="inlineStr"/>
+      <c r="K964" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2116070626850984241</t>
+        </is>
+      </c>
+      <c r="L964" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M964" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N964" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O964" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a user’s complaint about contact difficulties, apologizing and noting that the private message was answered.</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D965" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E965" t="inlineStr">
+        <is>
+          <t>Fri Oct 30 06:53:41 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F965" t="inlineStr">
+        <is>
+          <t>Bonjour Célia, merci de nous avoir contactés ici. Sachez que nous aimerions vous apporter notre aide pour la demande de remboursement des billets d'avion de votre oncle, mais nous ne sommes pas en mesure de gérer les réservations de billets d'avion via les réseaux sociaux, notre accès étant limité uniquement à la base de données des hébergements.
+Pour toute assistance, nous vous recommandons de contacter notre équipe spécialisée dans les vols ici : https://t.co/KkSQd8iIp6, ou en appelant le +6627873018/ {FR} +33 187 153 614 / {BE} +32 270 067 90.
+Cordialement.</t>
+        </is>
+      </c>
+      <c r="G965" t="inlineStr"/>
+      <c r="H965" t="inlineStr"/>
+      <c r="I965" t="inlineStr"/>
+      <c r="J965" t="inlineStr"/>
+      <c r="K965" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2116060956962828593</t>
+        </is>
+      </c>
+      <c r="L965" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M965" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N965" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O965" t="inlineStr">
+        <is>
+          <t>Booking.com informs a customer that it cannot process flight refund requests via social media and directs them to a specialized flight support team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D966" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E966" t="inlineStr">
+        <is>
+          <t>Fri Oct 30 05:54:06 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F966" t="inlineStr">
+        <is>
+          <t>@Bharadwaj_C14 Hi there, we appreciate your cooperation in providing the requested details. We have sent you a private message regarding your inquiry. Please check your messages for further assistance.</t>
+        </is>
+      </c>
+      <c r="G966" t="inlineStr"/>
+      <c r="H966" t="inlineStr"/>
+      <c r="I966" t="inlineStr"/>
+      <c r="J966" t="inlineStr"/>
+      <c r="K966" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2116045962351186102</t>
+        </is>
+      </c>
+      <c r="L966" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M966" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N966" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O966" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s inquiry via private message, offering further assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D967" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E967" t="inlineStr">
+        <is>
+          <t>Fri Oct 30 05:03:22 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F967" t="inlineStr">
+        <is>
+          <t>Hi there, We regret to hear about your experience and understand how frustrating it must have been when you were looking for help and felt that your concerns weren't properly addressed. We regret if the support you received did not meet your expectations. To allow us to investigate this further and review your booking, please send us the following details via private message: 
+- Confirmation number 
+- PIN code 
+- Name on the reservation</t>
+        </is>
+      </c>
+      <c r="G967" t="inlineStr"/>
+      <c r="H967" t="inlineStr"/>
+      <c r="I967" t="inlineStr"/>
+      <c r="J967" t="inlineStr"/>
+      <c r="K967" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2116033195758031222</t>
+        </is>
+      </c>
+      <c r="L967" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="M967" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N967" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O967" t="inlineStr">
+        <is>
+          <t>Booking.com apologizes for a customer’s unsatisfactory support experience and requests booking details via private message for investigation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D968" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E968" t="inlineStr">
+        <is>
+          <t>Fri Oct 30 03:19:35 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F968" t="inlineStr">
+        <is>
+          <t>@kpshah_92 Hi Karan, thank you for providing us with the requested details. We have sent you a private message regarding your inquiry. Please check your messages for further assistance.</t>
+        </is>
+      </c>
+      <c r="G968" t="inlineStr"/>
+      <c r="H968" t="inlineStr"/>
+      <c r="I968" t="inlineStr"/>
+      <c r="J968" t="inlineStr"/>
+      <c r="K968" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2116007077436858731</t>
+        </is>
+      </c>
+      <c r="L968" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M968" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N968" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O968" t="inlineStr">
+        <is>
+          <t>Booking.com replied to a user’s inquiry via private message, offering further assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D969" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="E969" t="inlineStr">
+        <is>
+          <t>2026-10-30T10:52:20.811Z</t>
+        </is>
+      </c>
+      <c r="F969" t="inlineStr">
+        <is>
+          <t>✨ What began as a spark of an idea to celebrate a year of exploring AI has grown into a company-wide AI Summit. It’s a chance to recognise our investment in the latest technology and share what we’ve learned along the way. 🚀 
+A huge thank you to everyone who brought the original spark to life and helped it grow into a week of learning, exploration and inspiration. 🙌</t>
+        </is>
+      </c>
+      <c r="G969" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D4E10AQEI12HpA_hCDQ/image-shrink_1280/B4EaGMcCQgJ0Ac-/0/1793357522801?e=1793984400&amp;v=beta&amp;t=5fWmPn3QrBE7-GrDqVUhgEvzA6FN6M1HZ3voDtzTiDY</t>
+        </is>
+      </c>
+      <c r="H969" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I969" t="inlineStr"/>
+      <c r="J969" t="inlineStr"/>
+      <c r="K969" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/booking%2Ecom_what-began-as-a-spark-of-an-idea-to-celebrate-activity-7521886706854326273-8-K2</t>
+        </is>
+      </c>
+      <c r="L969" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M969" t="inlineStr">
+        <is>
+          <t>Tech Updates</t>
+        </is>
+      </c>
+      <c r="N969" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O969" t="inlineStr">
+        <is>
+          <t>Booking.com marks a year of AI exploration with a company-wide AI Summit, celebrating its investment in technology and sharing lessons learned.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/News_Dashboard/data/social_media_posts.xlsx
+++ b/News_Dashboard/data/social_media_posts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O969"/>
+  <dimension ref="A1:O980"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62461,6 +62461,750 @@
         </is>
       </c>
     </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D970" t="inlineStr">
+        <is>
+          <t>getnavan</t>
+        </is>
+      </c>
+      <c r="E970" t="inlineStr">
+        <is>
+          <t>2026-10-30T14:03:47.000Z</t>
+        </is>
+      </c>
+      <c r="F970" t="inlineStr">
+        <is>
+          <t>The spookiest thing your team could encounter this Halloween? A Frankenstack monster.
+Hit the link in bio to learn more.</t>
+        </is>
+      </c>
+      <c r="G970" t="inlineStr">
+        <is>
+          <t>https://scontent-muc2-1.cdninstagram.com/v/t51.82787-15/880020497_18496958284110668_5629641515896429113_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=111&amp;ig_cache_key=NDAxOTM5Mjg2MzgwMTcyMzIyMQ%3D%3D.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNMSVBTLnhwaWRzLjEwODAuc2RyLnZpZGVvX2RlZmF1bHRfY292ZXJfZnJhbWUuQzMifQ%3D%3D&amp;_nc_ohc=nCBa3Djg8s0Q7kNvwGtjhKg&amp;_nc_oc=AdqRZNhtUPcOcxY7Mj17oHLQI_eqxF6qG8EI910xLNky0SJUvApsELoqfvIM0zS6nyury3p3mmnx_AjTm9oAO-Mq&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=scontent-muc2-1.cdninstagram.com&amp;_nc_gid=oWrEZBkdrCrPkJfYz5g27w&amp;_nc_ss=7320f&amp;oh=00_AQSPqBCcHEovsuvwvTXWvio42rWAa25SB6-jrHWCFhPCuw&amp;oe=6AEAC4DD</t>
+        </is>
+      </c>
+      <c r="H970" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I970" t="inlineStr">
+        <is>
+          <t>https://scontent-muc2-1.cdninstagram.com/o1/v/t2/f2/m86/AQOEPt7w5MFovI1bWXQmYzen-9QmAmt0_3EzxGjLtdviqGW61EjavPIeApmUxgV-SRE-TQyCRf7cD1rpcvJRxzM1Zx_AsPSHRHBuiNI.mp4?_nc_cat=102&amp;_nc_sid=5e9851&amp;_nc_ht=scontent-muc2-1.cdninstagram.com&amp;_nc_ohc=H5YWPP-UWBsQ7kNvwHa8R1Q&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MjY3NjIwNDE4MjgwNzk3NiwiYXNzZXRfYWdlX2RheXMiOjAsInZpX3VzZWNhc2VfaWQiOjEwMDk5LCJkdXJhdGlvbl9zIjoyNSwidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=6854b174ee966e68&amp;_nc_vs=HBksFQIYUmlnX3hwdl9yZWVsc19wZXJtYW5lbnRfc3JfcHJvZC8yRTNERTVEN0U5Q0U0QUY0QUNFMTQzRjdBREFDN0ZBRl92aWRlb19kYXNoaW5pdC5tcDQVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzVBREExQjA0Q0MyRTRBMDJBNzFDNTk2MTVCNDdCNDUzX2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbQls36yv_ACRUCKAJDMywXQDj7peNT988YEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=oWrEZBkdrCrPkJfYz5g27w&amp;_nc_ss=73580&amp;_nc_zt=28&amp;oh=00_AQSPmAOcltqauqnNpWe6ddLedMdsDpZ0O-El88t210XnAg&amp;oe=6AE6D1C7</t>
+        </is>
+      </c>
+      <c r="J970" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K970" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DfHwIOTpElV/</t>
+        </is>
+      </c>
+      <c r="L970" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M970" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N970" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O970" t="inlineStr">
+        <is>
+          <t>Navan uses a Halloween-themed marketing post to promote its "Frankenstack monster" feature, inviting teams to learn more via a link in the bio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D971" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="E971" t="inlineStr">
+        <is>
+          <t>2026-10-30T14:03:36.995Z</t>
+        </is>
+      </c>
+      <c r="F971" t="inlineStr">
+        <is>
+          <t>The spookiest thing your team could encounter this Halloween? A Frankenstack monster.
+Learn how two companies escaped the T&amp;E Frankenstack. Watch the webinar → https://lnkd.in/eUVsh7QH
+Art by Dan Blaushild</t>
+        </is>
+      </c>
+      <c r="G971" t="inlineStr"/>
+      <c r="H971" t="inlineStr"/>
+      <c r="I971" t="inlineStr">
+        <is>
+          <t>https://dms.licdn.com/playlist/vid/dynamic/D4E05AQG2T1DgUc5AjQ/CeJxzMnFNdPfz8gnIc892dNTVcQLzPQxTwzwMXMrR-JEwPlB9kWc6hvpkNH46Gj9fFwDLhx7m?e=1793991600&amp;v=beta&amp;t=oQwzAf4znZO4gK46uAaxHJQGK5NWJqD3FIzoEBpoTfU</t>
+        </is>
+      </c>
+      <c r="J971" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K971" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/navan_ditch-the-frankenstack-get-navan-activity-7521934841458855936-cvXg</t>
+        </is>
+      </c>
+      <c r="L971" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M971" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N971" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O971" t="inlineStr">
+        <is>
+          <t>Navan promotes a webinar on how teams can escape the T&amp;E Frankenstack, positioning it as a solution to a common pain point.</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D972" t="inlineStr">
+        <is>
+          <t>Yuval Refua</t>
+        </is>
+      </c>
+      <c r="E972" t="inlineStr">
+        <is>
+          <t>2026-10-29T20:37:16.460Z</t>
+        </is>
+      </c>
+      <c r="F972" t="inlineStr">
+        <is>
+          <t>The more markets you operate in, the harder it is to make one T&amp;E program work locally.
+We’re changing that. Navan now supports issuing in 15 currencies, including in Australia, Canada, Sweden, Denmark and Poland with more on the way!
+Learn more - https://lnkd.in/gDFdKU78
+#TravelAndExpense #ExpenseManagement #Payments #CorporateCards #CreditCards #Navan</t>
+        </is>
+      </c>
+      <c r="G972" t="inlineStr"/>
+      <c r="H972" t="inlineStr"/>
+      <c r="I972" t="inlineStr">
+        <is>
+          <t>https://dms.licdn.com/playlist/vid/dynamic/D5605AQHqNJU1-TN72A/CeJxzMjVLdPcK90439gh0dNTVcQLzQ8vKwzyLXYphfKC8mbsJhnwoGj8SjZ-Mxs_WBQAO3CEX?e=1793991600&amp;v=beta&amp;t=9b88HnZ1Iz5LRfCJceuRyfaZTsbC7ad8kjLpDjFec5g</t>
+        </is>
+      </c>
+      <c r="J972" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K972" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/yuvalrefua_travelandexpense-expensemanagement-payments-ugcPost-7521667507552747520-4kOt</t>
+        </is>
+      </c>
+      <c r="L972" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M972" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N972" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O972" t="inlineStr">
+        <is>
+          <t>Navan is expanding its travel and expense platform to support issuing in 15 currencies, including Australia, Canada, Sweden, Denmark, and Poland, with additional currencies forthcoming.</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D973" t="inlineStr">
+        <is>
+          <t>tryramp</t>
+        </is>
+      </c>
+      <c r="E973" t="inlineStr">
+        <is>
+          <t>Fri Oct 30 18:02:15 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F973" t="inlineStr">
+        <is>
+          <t>Last quarter, 7,000 pull requests at Ramp were merged by people who aren't engineers.
+Two years ago that number was zero.
+@eglyman on what Inspect does to the life of a bug report: https://t.co/igNB2yX0jQ</t>
+        </is>
+      </c>
+      <c r="G973" t="inlineStr"/>
+      <c r="H973" t="inlineStr"/>
+      <c r="I973" t="inlineStr"/>
+      <c r="J973" t="inlineStr"/>
+      <c r="K973" t="inlineStr">
+        <is>
+          <t>https://x.com/tryramp/status/2116229209119203624</t>
+        </is>
+      </c>
+      <c r="L973" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M973" t="inlineStr">
+        <is>
+          <t>Tech Updates</t>
+        </is>
+      </c>
+      <c r="N973" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O973" t="inlineStr">
+        <is>
+          <t>Ramp reports a significant rise in pull requests merged by non-engineers—7,000 last quarter versus zero two years ago—highlighting a shift toward more inclusive internal development practices.</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D974" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E974" t="inlineStr">
+        <is>
+          <t>Fri Oct 30 16:39:06 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F974" t="inlineStr">
+        <is>
+          <t>@micmakarov Michael, this should be fixed for you now. Please let us know if you run into any other errors.</t>
+        </is>
+      </c>
+      <c r="G974" t="inlineStr"/>
+      <c r="H974" t="inlineStr"/>
+      <c r="I974" t="inlineStr"/>
+      <c r="J974" t="inlineStr"/>
+      <c r="K974" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2116208282842911125</t>
+        </is>
+      </c>
+      <c r="L974" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M974" t="inlineStr">
+        <is>
+          <t>Tech Updates</t>
+        </is>
+      </c>
+      <c r="N974" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O974" t="inlineStr">
+        <is>
+          <t>Brex informs user Michael that a previously reported issue has been fixed and requests feedback if further errors occur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>Miraee</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D975" t="inlineStr">
+        <is>
+          <t>brexhq</t>
+        </is>
+      </c>
+      <c r="E975" t="inlineStr">
+        <is>
+          <t>Fri Oct 30 16:29:31 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F975" t="inlineStr">
+        <is>
+          <t>@anshulshirude Sorry you've been left waiting. We want to help. Please send us a DM so we can look into what's happening.</t>
+        </is>
+      </c>
+      <c r="G975" t="inlineStr"/>
+      <c r="H975" t="inlineStr"/>
+      <c r="I975" t="inlineStr"/>
+      <c r="J975" t="inlineStr"/>
+      <c r="K975" t="inlineStr">
+        <is>
+          <t>https://x.com/brexHQ/status/2116205872275730816</t>
+        </is>
+      </c>
+      <c r="L975" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M975" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N975" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O975" t="inlineStr">
+        <is>
+          <t>Brex publicly apologizes to a user for a delay and invites them to send a direct message for further assistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D976" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E976" t="inlineStr">
+        <is>
+          <t>Fri Oct 30 17:38:04 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F976" t="inlineStr">
+        <is>
+          <t>@Mary_Colette Hi there, thank you for bringing this to our attention. We understand that this situation may be concerning and appreciate you taking the time to contact us. We've sent you a private message regarding your inquiry. Kindly check your inbox at your earliest convenience.</t>
+        </is>
+      </c>
+      <c r="G976" t="inlineStr"/>
+      <c r="H976" t="inlineStr"/>
+      <c r="I976" t="inlineStr"/>
+      <c r="J976" t="inlineStr"/>
+      <c r="K976" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2116223122583998596</t>
+        </is>
+      </c>
+      <c r="L976" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M976" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N976" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O976" t="inlineStr">
+        <is>
+          <t>Booking.com acknowledges a user’s concern and informs them that a private message has been sent regarding their inquiry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D977" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E977" t="inlineStr">
+        <is>
+          <t>Fri Oct 30 17:03:58 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F977" t="inlineStr">
+        <is>
+          <t>Hi there, we regret to hear about your experience. We'd like to understand what happened and see how we can help.
+Could you please send us a private message with more details about the issue you're experiencing and the assistance you're looking for? If your request is related to an accommodation booking, please also include:
+• Confirmation number
+ • PIN code
+ • Name on the reservation
+Once we receive these details, we'll review your case and get back to you as soon as possible.
+Please bear in mind that our Social Media Team doesn't work in real time. For immediate support, please call our 24/7 Customer Service Team - our contact details can be found here: https://t.co/o8QyR8SaDb.
+Also, at this time, we only offer support for accommodation bookings via social media. For questions about Flights, Taxis, or Insurance, you can reach out to the dedicated support team here: https://t.co/OVuF5pCzba.</t>
+        </is>
+      </c>
+      <c r="G977" t="inlineStr"/>
+      <c r="H977" t="inlineStr"/>
+      <c r="I977" t="inlineStr"/>
+      <c r="J977" t="inlineStr"/>
+      <c r="K977" t="inlineStr">
+        <is>
+          <t>https://x.com/bookingcom/status/2116214542220804308</t>
+        </is>
+      </c>
+      <c r="L977" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="M977" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N977" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O977" t="inlineStr">
+        <is>
+          <t>Booking.com responds to a customer complaint on X, offering to gather booking details via private message and directing users to 24/7 phone support for immediate assistance, while clarifying that only accommodation bookings are handled through social media.</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>Abhee</t>
+        </is>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>Booking.com</t>
+        </is>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="D978" t="inlineStr">
+        <is>
+          <t>bookingcom</t>
+        </is>
+      </c>
+      <c r="E978" t="inlineStr">
+        <is>
+          <t>2026-10-30T15:53:51.000Z</t>
+        </is>
+      </c>
+      <c r="F978" t="inlineStr">
+        <is>
+          <t>Even turkeys travel easy with Booking.com :P</t>
+        </is>
+      </c>
+      <c r="G978" t="inlineStr">
+        <is>
+          <t>https://instagram.fbri1-1.fna.fbcdn.net/v/t51.82787-15/880255737_18646469038008354_7741530994423361635_n.jpg?stp=dst-jpg_e15_tt6&amp;_nc_cat=110&amp;_nc_map=urlgen_bucketless&amp;ig_cache_key=NDAxOTQ0ODA2MDMxNjIwNDI5NzE4NjQ2NDY5MDM1MDA4MzU0.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=58cdad&amp;efg=eyJ2ZW5jb2RlX3RhZyI6IkNMSVBTLnhwaWRzLjcyMC5zZHIudmlkZW9fdXNlcl9zZWxlY3RlZF90aHVtYm5haWwuQzMifQ%3D%3D&amp;_nc_ohc=0HYfHmqXJXwQ7kNvwHCU9ue&amp;_nc_oc=AdpvD4mxhG17WC1SYA5eWowTb2LsOin5KvNM3_JHlZC-wF7Q_isSjINoLQ7eF7ksjFk&amp;_nc_ad=z-m&amp;_nc_cid=0&amp;_nc_zt=23&amp;_nc_ht=instagram.fbri1-1.fna&amp;_nc_gid=rrBGhSHR2Bt6daBUQy2XwA&amp;_nc_ss=7320f&amp;oh=00_AQQ0So1eHnM3foYIHeOlgI23Fqym4JOr4e3M35u2nNqI-g&amp;oe=6AEABB5E</t>
+        </is>
+      </c>
+      <c r="H978" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I978" t="inlineStr">
+        <is>
+          <t>https://instagram.fbri1-1.fna.fbcdn.net/o1/v/t2/f2/m86/AQOcDYY402BnsS7HqomwGmhNHMuESn6TI4r5dMk7MiD--ApHShmf2OQxmuDI5FobYz5tgGcXRA0Z0I_oGzsNS9Z-97lPd-kW5Vrlu9A.mp4?_nc_cat=102&amp;_nc_oc=AdqcfDSBnNFxeOqYenQgeMGI7RgqtcOaJGTSqnCWwolNQcUxOEe5_hQagHrZaOeqyKk&amp;_nc_sid=5e9851&amp;_nc_ht=instagram.fbri1-1.fna.fbcdn.net&amp;_nc_ohc=nkNTdHIPGPgQ7kNvwGid6UD&amp;efg=eyJ2ZW5jb2RlX3RhZyI6Inhwdl9wcm9ncmVzc2l2ZS5JTlNUQUdSQU0uQ0xJUFMuQzMuNzIwLmRhc2hfYmFzZWxpbmVfMV92MSIsInhwdl9hc3NldF9pZCI6MzAwODgyMTAwNjEyNTQxOCwiYXNzZXRfYWdlX2RheXMiOjAsInZpX3VzZWNhc2VfaWQiOjEwMDk5LCJkdXJhdGlvbl9zIjozMSwidXJsZ2VuX3NvdXJjZSI6Ind3dyJ9&amp;ccb=17-1&amp;vs=2f429019363d851a&amp;_nc_vs=HBksFQIYUmlnX3hwdl9yZWVsc19wZXJtYW5lbnRfc3JfcHJvZC9DNUFDRUYxRDU1MTU0NjU3ODI5RTIwQUE1N0U4ODMzM192aWRlb19kYXNoaW5pdC5tcDQVAALIARIAFQIYUWlnX3hwdl9wbGFjZW1lbnRfcGVybWFuZW50X3YyLzIyMTQ0ODdGQkNBODRFMjY4NTI2RDRDQjY1OUQ5MTY3X2F1ZGlvX2Rhc2hpbml0Lm1wNBUCAsgBEgAoABgAGwKIB3VzZV9vaWwBMRJwcm9ncmVzc2l2ZV9yZWNpcGUBMRUAACbUpZq0t6DYChUCKAJDMywXQD-Q5WBBiTcYEmRhc2hfYmFzZWxpbmVfMV92MREAdf4HZeadAQA&amp;_nc_gid=rrBGhSHR2Bt6daBUQy2XwA&amp;_nc_ss=70580&amp;_nc_map=urlgen_bucketless&amp;_nc_zt=28&amp;oh=00_AQTgtmSw7EPwpvtK0WjQz17OC-RjoBjFOYdBHSEFJ-tK_A&amp;oe=6AE6D407</t>
+        </is>
+      </c>
+      <c r="J978" t="inlineStr">
+        <is>
+          <t>[faster-whisper not installed. Run 'pip install faster-whisper']</t>
+        </is>
+      </c>
+      <c r="K978" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DfH8rcER70J/</t>
+        </is>
+      </c>
+      <c r="L978" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M978" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N978" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O978" t="inlineStr">
+        <is>
+          <t>Booking.com posts a playful, lighthearted caption promoting travel ease for all, including turkeys, as part of its marketing outreach.</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel</t>
+        </is>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>X (Twitter)</t>
+        </is>
+      </c>
+      <c r="D979" t="inlineStr">
+        <is>
+          <t>SkyBirdTravel</t>
+        </is>
+      </c>
+      <c r="E979" t="inlineStr">
+        <is>
+          <t>Fri Oct 30 17:03:15 +0000 2026</t>
+        </is>
+      </c>
+      <c r="F979" t="inlineStr">
+        <is>
+          <t>Discover luxury, personalized itineraries, and curated experiences with Sky Vacations. Enjoy seamless travel planning with dedicated specialists and earn up to 12% commission!
+#SkyVacations #TravelAdvisor #LuxuryTravel https://t.co/qwBZSdsXj0</t>
+        </is>
+      </c>
+      <c r="G979" t="inlineStr"/>
+      <c r="H979" t="inlineStr"/>
+      <c r="I979" t="inlineStr"/>
+      <c r="J979" t="inlineStr"/>
+      <c r="K979" t="inlineStr">
+        <is>
+          <t>https://x.com/SkyBirdTravel/status/2116214359911469357</t>
+        </is>
+      </c>
+      <c r="L979" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M979" t="inlineStr">
+        <is>
+          <t>Product Announcement</t>
+        </is>
+      </c>
+      <c r="N979" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="O979" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel promotes its luxury travel service, highlighting personalized itineraries, dedicated specialists, and a commission incentive for travel advisors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>Mondee</t>
+        </is>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel</t>
+        </is>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D980" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel &amp; Tours</t>
+        </is>
+      </c>
+      <c r="E980" t="inlineStr">
+        <is>
+          <t>2026-10-30T17:04:29.562Z</t>
+        </is>
+      </c>
+      <c r="F980" t="inlineStr">
+        <is>
+          <t>For explorers in pursuit of ultimate luxury and curated experiences, look no further than Sky Vacations. With meticulously crafted, personalized itineraries and dedicated vacation specialists, every journey becomes a seamless blend of elegance and adventure. Plus, you can earn up to 12% commission!
+#SkyVacations #TravelAdvisor #CustomTravel #LuxuryTravel #TravelProfessionals #TravelBusiness #TravelCommissions</t>
+        </is>
+      </c>
+      <c r="G980" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D4D22AQFac13QHS6NWA/feedshare-shrink_1280/B4DaGNxRlfJsAM-/0/1793379868302?e=1795046400&amp;v=beta&amp;t=g1-05fhZunrsTfDFzlMAVmKptA8O4K0DSZ4R0CPVLvo</t>
+        </is>
+      </c>
+      <c r="H980" t="inlineStr">
+        <is>
+          <t>[easyocr not installed. Run 'pip install easyocr torch torchvision']</t>
+        </is>
+      </c>
+      <c r="I980" t="inlineStr"/>
+      <c r="J980" t="inlineStr"/>
+      <c r="K980" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/posts/sky-bird-travel-tours_skyvacations-traveladvisor-customtravel-activity-7521980360424079360-l3mD</t>
+        </is>
+      </c>
+      <c r="L980" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="M980" t="inlineStr">
+        <is>
+          <t>General Industry News</t>
+        </is>
+      </c>
+      <c r="N980" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="O980" t="inlineStr">
+        <is>
+          <t>Sky Bird Travel promotes its Sky Vacations service, highlighting personalized luxury itineraries and a commission structure for travel advisors.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
